--- a/data/annotations/TE_discrete_percentages.xlsx
+++ b/data/annotations/TE_discrete_percentages.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dobregeo\Documents\GitHub\vilearn_ml\data\annotations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{D21AAE26-FCBE-4EBD-9703-A77F78489E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{C9FCEF07-616C-433A-A7E2-D45A8732D095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="38580" windowHeight="21060" activeTab="1" xr2:uid="{8450E3AB-A0C1-455F-AE9B-DBE7A60F6C99}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{8450E3AB-A0C1-455F-AE9B-DBE7A60F6C99}"/>
   </bookViews>
   <sheets>
     <sheet name="TE_discrete_percentages" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="TE_discrete_.1" sheetId="2" r:id="rId2"/>
+    <sheet name="TE_discrete_twobins" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="74">
   <si>
     <t>task_eng</t>
   </si>
@@ -241,6 +242,9 @@
   <si>
     <t>Laura</t>
   </si>
+  <si>
+    <t>lo</t>
+  </si>
 </sst>
 </file>
 
@@ -382,7 +386,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -562,8 +566,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -678,6 +688,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -723,9 +770,14 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1721,7 +1773,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$2</c:f>
+              <c:f>TE_discrete_.1!$A$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1747,11 +1799,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$B$1,Sheet1!$D$1,Sheet1!$F$1,Sheet1!$H$1,Sheet1!$J$1,Sheet1!$L$1,Sheet1!$N$1,Sheet1!$P$1,Sheet1!$R$1,Sheet1!$T$1,Sheet1!$V$1)</c:f>
+              <c:f>(TE_discrete_.1!$B$1,TE_discrete_.1!$D$1,TE_discrete_.1!$F$1,TE_discrete_.1!$H$1,TE_discrete_.1!$J$1,TE_discrete_.1!$L$1,TE_discrete_.1!$N$1,TE_discrete_.1!$P$1,TE_discrete_.1!$R$1,TE_discrete_.1!$T$1,TE_discrete_.1!$V$1)</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
@@ -1795,11 +1847,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$2:$AY$2</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$2:$AY$2</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$B$2,Sheet1!$D$2,Sheet1!$F$2,Sheet1!$H$2,Sheet1!$J$2,Sheet1!$L$2,Sheet1!$N$2,Sheet1!$P$2,Sheet1!$R$2,Sheet1!$T$2,Sheet1!$V$2)</c:f>
+              <c:f>(TE_discrete_.1!$B$2,TE_discrete_.1!$D$2,TE_discrete_.1!$F$2,TE_discrete_.1!$H$2,TE_discrete_.1!$J$2,TE_discrete_.1!$L$2,TE_discrete_.1!$N$2,TE_discrete_.1!$P$2,TE_discrete_.1!$R$2,TE_discrete_.1!$T$2,TE_discrete_.1!$V$2)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -1850,7 +1902,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$3</c:f>
+              <c:f>TE_discrete_.1!$A$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1876,11 +1928,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$B$1,Sheet1!$D$1,Sheet1!$F$1,Sheet1!$H$1,Sheet1!$J$1,Sheet1!$L$1,Sheet1!$N$1,Sheet1!$P$1,Sheet1!$R$1,Sheet1!$T$1,Sheet1!$V$1)</c:f>
+              <c:f>(TE_discrete_.1!$B$1,TE_discrete_.1!$D$1,TE_discrete_.1!$F$1,TE_discrete_.1!$H$1,TE_discrete_.1!$J$1,TE_discrete_.1!$L$1,TE_discrete_.1!$N$1,TE_discrete_.1!$P$1,TE_discrete_.1!$R$1,TE_discrete_.1!$T$1,TE_discrete_.1!$V$1)</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
@@ -1924,11 +1976,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$3:$AY$3</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$3:$AY$3</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$B$3,Sheet1!$D$3,Sheet1!$F$3,Sheet1!$H$3,Sheet1!$J$3,Sheet1!$L$3,Sheet1!$N$3,Sheet1!$P$3,Sheet1!$R$3,Sheet1!$T$3,Sheet1!$V$3)</c:f>
+              <c:f>(TE_discrete_.1!$B$3,TE_discrete_.1!$D$3,TE_discrete_.1!$F$3,TE_discrete_.1!$H$3,TE_discrete_.1!$J$3,TE_discrete_.1!$L$3,TE_discrete_.1!$N$3,TE_discrete_.1!$P$3,TE_discrete_.1!$R$3,TE_discrete_.1!$T$3,TE_discrete_.1!$V$3)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -1979,7 +2031,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$4</c:f>
+              <c:f>TE_discrete_.1!$A$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2005,11 +2057,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$B$1,Sheet1!$D$1,Sheet1!$F$1,Sheet1!$H$1,Sheet1!$J$1,Sheet1!$L$1,Sheet1!$N$1,Sheet1!$P$1,Sheet1!$R$1,Sheet1!$T$1,Sheet1!$V$1)</c:f>
+              <c:f>(TE_discrete_.1!$B$1,TE_discrete_.1!$D$1,TE_discrete_.1!$F$1,TE_discrete_.1!$H$1,TE_discrete_.1!$J$1,TE_discrete_.1!$L$1,TE_discrete_.1!$N$1,TE_discrete_.1!$P$1,TE_discrete_.1!$R$1,TE_discrete_.1!$T$1,TE_discrete_.1!$V$1)</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
@@ -2053,11 +2105,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$4:$AY$4</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$4:$AY$4</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$B$4,Sheet1!$D$4,Sheet1!$F$4,Sheet1!$H$4,Sheet1!$J$4,Sheet1!$L$4,Sheet1!$N$4,Sheet1!$P$4,Sheet1!$R$4,Sheet1!$T$4,Sheet1!$V$4)</c:f>
+              <c:f>(TE_discrete_.1!$B$4,TE_discrete_.1!$D$4,TE_discrete_.1!$F$4,TE_discrete_.1!$H$4,TE_discrete_.1!$J$4,TE_discrete_.1!$L$4,TE_discrete_.1!$N$4,TE_discrete_.1!$P$4,TE_discrete_.1!$R$4,TE_discrete_.1!$T$4,TE_discrete_.1!$V$4)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -2108,7 +2160,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$5</c:f>
+              <c:f>TE_discrete_.1!$A$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2134,11 +2186,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$B$1,Sheet1!$D$1,Sheet1!$F$1,Sheet1!$H$1,Sheet1!$J$1,Sheet1!$L$1,Sheet1!$N$1,Sheet1!$P$1,Sheet1!$R$1,Sheet1!$T$1,Sheet1!$V$1)</c:f>
+              <c:f>(TE_discrete_.1!$B$1,TE_discrete_.1!$D$1,TE_discrete_.1!$F$1,TE_discrete_.1!$H$1,TE_discrete_.1!$J$1,TE_discrete_.1!$L$1,TE_discrete_.1!$N$1,TE_discrete_.1!$P$1,TE_discrete_.1!$R$1,TE_discrete_.1!$T$1,TE_discrete_.1!$V$1)</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
@@ -2182,11 +2234,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$5:$AY$5</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$5:$AY$5</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$B$5,Sheet1!$D$5,Sheet1!$F$5,Sheet1!$H$5,Sheet1!$J$5,Sheet1!$L$5,Sheet1!$N$5,Sheet1!$P$5,Sheet1!$R$5,Sheet1!$T$5,Sheet1!$V$5)</c:f>
+              <c:f>(TE_discrete_.1!$B$5,TE_discrete_.1!$D$5,TE_discrete_.1!$F$5,TE_discrete_.1!$H$5,TE_discrete_.1!$J$5,TE_discrete_.1!$L$5,TE_discrete_.1!$N$5,TE_discrete_.1!$P$5,TE_discrete_.1!$R$5,TE_discrete_.1!$T$5,TE_discrete_.1!$V$5)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -2237,7 +2289,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$6</c:f>
+              <c:f>TE_discrete_.1!$A$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2263,11 +2315,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$B$1,Sheet1!$D$1,Sheet1!$F$1,Sheet1!$H$1,Sheet1!$J$1,Sheet1!$L$1,Sheet1!$N$1,Sheet1!$P$1,Sheet1!$R$1,Sheet1!$T$1,Sheet1!$V$1)</c:f>
+              <c:f>(TE_discrete_.1!$B$1,TE_discrete_.1!$D$1,TE_discrete_.1!$F$1,TE_discrete_.1!$H$1,TE_discrete_.1!$J$1,TE_discrete_.1!$L$1,TE_discrete_.1!$N$1,TE_discrete_.1!$P$1,TE_discrete_.1!$R$1,TE_discrete_.1!$T$1,TE_discrete_.1!$V$1)</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
@@ -2311,11 +2363,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$6:$AY$6</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$6:$AY$6</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$B$6,Sheet1!$D$6,Sheet1!$F$6,Sheet1!$H$6,Sheet1!$J$6,Sheet1!$L$6,Sheet1!$N$6,Sheet1!$P$6,Sheet1!$R$6,Sheet1!$T$6,Sheet1!$V$6)</c:f>
+              <c:f>(TE_discrete_.1!$B$6,TE_discrete_.1!$D$6,TE_discrete_.1!$F$6,TE_discrete_.1!$H$6,TE_discrete_.1!$J$6,TE_discrete_.1!$L$6,TE_discrete_.1!$N$6,TE_discrete_.1!$P$6,TE_discrete_.1!$R$6,TE_discrete_.1!$T$6,TE_discrete_.1!$V$6)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -2366,7 +2418,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$7</c:f>
+              <c:f>TE_discrete_.1!$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2392,11 +2444,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$B$1,Sheet1!$D$1,Sheet1!$F$1,Sheet1!$H$1,Sheet1!$J$1,Sheet1!$L$1,Sheet1!$N$1,Sheet1!$P$1,Sheet1!$R$1,Sheet1!$T$1,Sheet1!$V$1)</c:f>
+              <c:f>(TE_discrete_.1!$B$1,TE_discrete_.1!$D$1,TE_discrete_.1!$F$1,TE_discrete_.1!$H$1,TE_discrete_.1!$J$1,TE_discrete_.1!$L$1,TE_discrete_.1!$N$1,TE_discrete_.1!$P$1,TE_discrete_.1!$R$1,TE_discrete_.1!$T$1,TE_discrete_.1!$V$1)</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
@@ -2440,11 +2492,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$7:$AY$7</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$7:$AY$7</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$B$7,Sheet1!$D$7,Sheet1!$F$7,Sheet1!$H$7,Sheet1!$J$7,Sheet1!$L$7,Sheet1!$N$7,Sheet1!$P$7,Sheet1!$R$7,Sheet1!$T$7,Sheet1!$V$7)</c:f>
+              <c:f>(TE_discrete_.1!$B$7,TE_discrete_.1!$D$7,TE_discrete_.1!$F$7,TE_discrete_.1!$H$7,TE_discrete_.1!$J$7,TE_discrete_.1!$L$7,TE_discrete_.1!$N$7,TE_discrete_.1!$P$7,TE_discrete_.1!$R$7,TE_discrete_.1!$T$7,TE_discrete_.1!$V$7)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -2495,7 +2547,7 @@
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$8</c:f>
+              <c:f>TE_discrete_.1!$A$8</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2521,11 +2573,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$B$1,Sheet1!$D$1,Sheet1!$F$1,Sheet1!$H$1,Sheet1!$J$1,Sheet1!$L$1,Sheet1!$N$1,Sheet1!$P$1,Sheet1!$R$1,Sheet1!$T$1,Sheet1!$V$1)</c:f>
+              <c:f>(TE_discrete_.1!$B$1,TE_discrete_.1!$D$1,TE_discrete_.1!$F$1,TE_discrete_.1!$H$1,TE_discrete_.1!$J$1,TE_discrete_.1!$L$1,TE_discrete_.1!$N$1,TE_discrete_.1!$P$1,TE_discrete_.1!$R$1,TE_discrete_.1!$T$1,TE_discrete_.1!$V$1)</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
@@ -2569,11 +2621,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$8:$AY$8</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$8:$AY$8</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$B$8,Sheet1!$D$8,Sheet1!$F$8,Sheet1!$H$8,Sheet1!$J$8,Sheet1!$L$8,Sheet1!$N$8,Sheet1!$P$8,Sheet1!$R$8,Sheet1!$T$8,Sheet1!$V$8)</c:f>
+              <c:f>(TE_discrete_.1!$B$8,TE_discrete_.1!$D$8,TE_discrete_.1!$F$8,TE_discrete_.1!$H$8,TE_discrete_.1!$J$8,TE_discrete_.1!$L$8,TE_discrete_.1!$N$8,TE_discrete_.1!$P$8,TE_discrete_.1!$R$8,TE_discrete_.1!$T$8,TE_discrete_.1!$V$8)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -2624,7 +2676,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$9</c:f>
+              <c:f>TE_discrete_.1!$A$9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2650,11 +2702,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$B$1,Sheet1!$D$1,Sheet1!$F$1,Sheet1!$H$1,Sheet1!$J$1,Sheet1!$L$1,Sheet1!$N$1,Sheet1!$P$1,Sheet1!$R$1,Sheet1!$T$1,Sheet1!$V$1)</c:f>
+              <c:f>(TE_discrete_.1!$B$1,TE_discrete_.1!$D$1,TE_discrete_.1!$F$1,TE_discrete_.1!$H$1,TE_discrete_.1!$J$1,TE_discrete_.1!$L$1,TE_discrete_.1!$N$1,TE_discrete_.1!$P$1,TE_discrete_.1!$R$1,TE_discrete_.1!$T$1,TE_discrete_.1!$V$1)</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
@@ -2698,11 +2750,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$9:$AY$9</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$9:$AY$9</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$B$9,Sheet1!$D$9,Sheet1!$F$9,Sheet1!$H$9,Sheet1!$J$9,Sheet1!$L$9,Sheet1!$N$9,Sheet1!$P$9,Sheet1!$R$9,Sheet1!$T$9,Sheet1!$V$9)</c:f>
+              <c:f>(TE_discrete_.1!$B$9,TE_discrete_.1!$D$9,TE_discrete_.1!$F$9,TE_discrete_.1!$H$9,TE_discrete_.1!$J$9,TE_discrete_.1!$L$9,TE_discrete_.1!$N$9,TE_discrete_.1!$P$9,TE_discrete_.1!$R$9,TE_discrete_.1!$T$9,TE_discrete_.1!$V$9)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -2753,7 +2805,7 @@
           <c:order val="8"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$10</c:f>
+              <c:f>TE_discrete_.1!$A$10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2779,11 +2831,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$B$1,Sheet1!$D$1,Sheet1!$F$1,Sheet1!$H$1,Sheet1!$J$1,Sheet1!$L$1,Sheet1!$N$1,Sheet1!$P$1,Sheet1!$R$1,Sheet1!$T$1,Sheet1!$V$1)</c:f>
+              <c:f>(TE_discrete_.1!$B$1,TE_discrete_.1!$D$1,TE_discrete_.1!$F$1,TE_discrete_.1!$H$1,TE_discrete_.1!$J$1,TE_discrete_.1!$L$1,TE_discrete_.1!$N$1,TE_discrete_.1!$P$1,TE_discrete_.1!$R$1,TE_discrete_.1!$T$1,TE_discrete_.1!$V$1)</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
@@ -2827,11 +2879,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$10:$AY$10</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$10:$AY$10</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$B$10,Sheet1!$D$10,Sheet1!$F$10,Sheet1!$H$10,Sheet1!$J$10,Sheet1!$L$10,Sheet1!$N$10,Sheet1!$P$10,Sheet1!$R$10,Sheet1!$T$10,Sheet1!$V$10)</c:f>
+              <c:f>(TE_discrete_.1!$B$10,TE_discrete_.1!$D$10,TE_discrete_.1!$F$10,TE_discrete_.1!$H$10,TE_discrete_.1!$J$10,TE_discrete_.1!$L$10,TE_discrete_.1!$N$10,TE_discrete_.1!$P$10,TE_discrete_.1!$R$10,TE_discrete_.1!$T$10,TE_discrete_.1!$V$10)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -2882,7 +2934,7 @@
           <c:order val="9"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$11</c:f>
+              <c:f>TE_discrete_.1!$A$11</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2908,11 +2960,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$B$1,Sheet1!$D$1,Sheet1!$F$1,Sheet1!$H$1,Sheet1!$J$1,Sheet1!$L$1,Sheet1!$N$1,Sheet1!$P$1,Sheet1!$R$1,Sheet1!$T$1,Sheet1!$V$1)</c:f>
+              <c:f>(TE_discrete_.1!$B$1,TE_discrete_.1!$D$1,TE_discrete_.1!$F$1,TE_discrete_.1!$H$1,TE_discrete_.1!$J$1,TE_discrete_.1!$L$1,TE_discrete_.1!$N$1,TE_discrete_.1!$P$1,TE_discrete_.1!$R$1,TE_discrete_.1!$T$1,TE_discrete_.1!$V$1)</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
@@ -2956,11 +3008,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$11:$AY$11</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$11:$AY$11</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$B$11,Sheet1!$D$11,Sheet1!$F$11,Sheet1!$H$11,Sheet1!$J$11,Sheet1!$L$11,Sheet1!$N$11,Sheet1!$P$11,Sheet1!$R$11,Sheet1!$T$11,Sheet1!$V$11)</c:f>
+              <c:f>(TE_discrete_.1!$B$11,TE_discrete_.1!$D$11,TE_discrete_.1!$F$11,TE_discrete_.1!$H$11,TE_discrete_.1!$J$11,TE_discrete_.1!$L$11,TE_discrete_.1!$N$11,TE_discrete_.1!$P$11,TE_discrete_.1!$R$11,TE_discrete_.1!$T$11,TE_discrete_.1!$V$11)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -3283,7 +3335,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$2</c:f>
+              <c:f>TE_discrete_.1!$A$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3309,11 +3361,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$C$1,Sheet1!$E$1,Sheet1!$G$1,Sheet1!$I$1,Sheet1!$K$1,Sheet1!$M$1,Sheet1!$O$1,Sheet1!$Q$1,Sheet1!$S$1,Sheet1!$U$1,Sheet1!$W$1)</c:f>
+              <c:f>(TE_discrete_.1!$C$1,TE_discrete_.1!$E$1,TE_discrete_.1!$G$1,TE_discrete_.1!$I$1,TE_discrete_.1!$K$1,TE_discrete_.1!$M$1,TE_discrete_.1!$O$1,TE_discrete_.1!$Q$1,TE_discrete_.1!$S$1,TE_discrete_.1!$U$1,TE_discrete_.1!$W$1)</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
@@ -3357,11 +3409,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$2:$AY$2</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$2:$AY$2</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$C$2,Sheet1!$E$2,Sheet1!$G$2,Sheet1!$I$2,Sheet1!$K$2,Sheet1!$M$2,Sheet1!$O$2,Sheet1!$Q$2,Sheet1!$S$2,Sheet1!$U$2,Sheet1!$W$2)</c:f>
+              <c:f>(TE_discrete_.1!$C$2,TE_discrete_.1!$E$2,TE_discrete_.1!$G$2,TE_discrete_.1!$I$2,TE_discrete_.1!$K$2,TE_discrete_.1!$M$2,TE_discrete_.1!$O$2,TE_discrete_.1!$Q$2,TE_discrete_.1!$S$2,TE_discrete_.1!$U$2,TE_discrete_.1!$W$2)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -3412,7 +3464,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$3</c:f>
+              <c:f>TE_discrete_.1!$A$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3438,11 +3490,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$C$1,Sheet1!$E$1,Sheet1!$G$1,Sheet1!$I$1,Sheet1!$K$1,Sheet1!$M$1,Sheet1!$O$1,Sheet1!$Q$1,Sheet1!$S$1,Sheet1!$U$1,Sheet1!$W$1)</c:f>
+              <c:f>(TE_discrete_.1!$C$1,TE_discrete_.1!$E$1,TE_discrete_.1!$G$1,TE_discrete_.1!$I$1,TE_discrete_.1!$K$1,TE_discrete_.1!$M$1,TE_discrete_.1!$O$1,TE_discrete_.1!$Q$1,TE_discrete_.1!$S$1,TE_discrete_.1!$U$1,TE_discrete_.1!$W$1)</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
@@ -3486,11 +3538,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$3:$AY$3</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$3:$AY$3</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$C$3,Sheet1!$E$3,Sheet1!$G$3,Sheet1!$I$3,Sheet1!$K$3,Sheet1!$M$3,Sheet1!$O$3,Sheet1!$Q$3,Sheet1!$S$3,Sheet1!$U$3,Sheet1!$W$3)</c:f>
+              <c:f>(TE_discrete_.1!$C$3,TE_discrete_.1!$E$3,TE_discrete_.1!$G$3,TE_discrete_.1!$I$3,TE_discrete_.1!$K$3,TE_discrete_.1!$M$3,TE_discrete_.1!$O$3,TE_discrete_.1!$Q$3,TE_discrete_.1!$S$3,TE_discrete_.1!$U$3,TE_discrete_.1!$W$3)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -3541,7 +3593,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$4</c:f>
+              <c:f>TE_discrete_.1!$A$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3567,11 +3619,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$C$1,Sheet1!$E$1,Sheet1!$G$1,Sheet1!$I$1,Sheet1!$K$1,Sheet1!$M$1,Sheet1!$O$1,Sheet1!$Q$1,Sheet1!$S$1,Sheet1!$U$1,Sheet1!$W$1)</c:f>
+              <c:f>(TE_discrete_.1!$C$1,TE_discrete_.1!$E$1,TE_discrete_.1!$G$1,TE_discrete_.1!$I$1,TE_discrete_.1!$K$1,TE_discrete_.1!$M$1,TE_discrete_.1!$O$1,TE_discrete_.1!$Q$1,TE_discrete_.1!$S$1,TE_discrete_.1!$U$1,TE_discrete_.1!$W$1)</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
@@ -3615,11 +3667,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$4:$AY$4</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$4:$AY$4</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$C$4,Sheet1!$E$4,Sheet1!$G$4,Sheet1!$I$4,Sheet1!$K$4,Sheet1!$M$4,Sheet1!$O$4,Sheet1!$Q$4,Sheet1!$S$4,Sheet1!$U$4,Sheet1!$W$4)</c:f>
+              <c:f>(TE_discrete_.1!$C$4,TE_discrete_.1!$E$4,TE_discrete_.1!$G$4,TE_discrete_.1!$I$4,TE_discrete_.1!$K$4,TE_discrete_.1!$M$4,TE_discrete_.1!$O$4,TE_discrete_.1!$Q$4,TE_discrete_.1!$S$4,TE_discrete_.1!$U$4,TE_discrete_.1!$W$4)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -3670,7 +3722,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$5</c:f>
+              <c:f>TE_discrete_.1!$A$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3696,11 +3748,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$C$1,Sheet1!$E$1,Sheet1!$G$1,Sheet1!$I$1,Sheet1!$K$1,Sheet1!$M$1,Sheet1!$O$1,Sheet1!$Q$1,Sheet1!$S$1,Sheet1!$U$1,Sheet1!$W$1)</c:f>
+              <c:f>(TE_discrete_.1!$C$1,TE_discrete_.1!$E$1,TE_discrete_.1!$G$1,TE_discrete_.1!$I$1,TE_discrete_.1!$K$1,TE_discrete_.1!$M$1,TE_discrete_.1!$O$1,TE_discrete_.1!$Q$1,TE_discrete_.1!$S$1,TE_discrete_.1!$U$1,TE_discrete_.1!$W$1)</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
@@ -3744,11 +3796,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$5:$AY$5</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$5:$AY$5</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$C$5,Sheet1!$E$5,Sheet1!$G$5,Sheet1!$I$5,Sheet1!$K$5,Sheet1!$M$5,Sheet1!$O$5,Sheet1!$Q$5,Sheet1!$S$5,Sheet1!$U$5,Sheet1!$W$5)</c:f>
+              <c:f>(TE_discrete_.1!$C$5,TE_discrete_.1!$E$5,TE_discrete_.1!$G$5,TE_discrete_.1!$I$5,TE_discrete_.1!$K$5,TE_discrete_.1!$M$5,TE_discrete_.1!$O$5,TE_discrete_.1!$Q$5,TE_discrete_.1!$S$5,TE_discrete_.1!$U$5,TE_discrete_.1!$W$5)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -3799,7 +3851,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$6</c:f>
+              <c:f>TE_discrete_.1!$A$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3825,11 +3877,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$C$1,Sheet1!$E$1,Sheet1!$G$1,Sheet1!$I$1,Sheet1!$K$1,Sheet1!$M$1,Sheet1!$O$1,Sheet1!$Q$1,Sheet1!$S$1,Sheet1!$U$1,Sheet1!$W$1)</c:f>
+              <c:f>(TE_discrete_.1!$C$1,TE_discrete_.1!$E$1,TE_discrete_.1!$G$1,TE_discrete_.1!$I$1,TE_discrete_.1!$K$1,TE_discrete_.1!$M$1,TE_discrete_.1!$O$1,TE_discrete_.1!$Q$1,TE_discrete_.1!$S$1,TE_discrete_.1!$U$1,TE_discrete_.1!$W$1)</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
@@ -3873,11 +3925,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$6:$AY$6</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$6:$AY$6</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$C$6,Sheet1!$E$6,Sheet1!$G$6,Sheet1!$I$6,Sheet1!$K$6,Sheet1!$M$6,Sheet1!$O$6,Sheet1!$Q$6,Sheet1!$S$6,Sheet1!$U$6,Sheet1!$W$6)</c:f>
+              <c:f>(TE_discrete_.1!$C$6,TE_discrete_.1!$E$6,TE_discrete_.1!$G$6,TE_discrete_.1!$I$6,TE_discrete_.1!$K$6,TE_discrete_.1!$M$6,TE_discrete_.1!$O$6,TE_discrete_.1!$Q$6,TE_discrete_.1!$S$6,TE_discrete_.1!$U$6,TE_discrete_.1!$W$6)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -3928,7 +3980,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$7</c:f>
+              <c:f>TE_discrete_.1!$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3954,11 +4006,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$C$1,Sheet1!$E$1,Sheet1!$G$1,Sheet1!$I$1,Sheet1!$K$1,Sheet1!$M$1,Sheet1!$O$1,Sheet1!$Q$1,Sheet1!$S$1,Sheet1!$U$1,Sheet1!$W$1)</c:f>
+              <c:f>(TE_discrete_.1!$C$1,TE_discrete_.1!$E$1,TE_discrete_.1!$G$1,TE_discrete_.1!$I$1,TE_discrete_.1!$K$1,TE_discrete_.1!$M$1,TE_discrete_.1!$O$1,TE_discrete_.1!$Q$1,TE_discrete_.1!$S$1,TE_discrete_.1!$U$1,TE_discrete_.1!$W$1)</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
@@ -4002,11 +4054,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$7:$AY$7</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$7:$AY$7</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$C$7,Sheet1!$E$7,Sheet1!$G$7,Sheet1!$I$7,Sheet1!$K$7,Sheet1!$M$7,Sheet1!$O$7,Sheet1!$Q$7,Sheet1!$S$7,Sheet1!$U$7,Sheet1!$W$7)</c:f>
+              <c:f>(TE_discrete_.1!$C$7,TE_discrete_.1!$E$7,TE_discrete_.1!$G$7,TE_discrete_.1!$I$7,TE_discrete_.1!$K$7,TE_discrete_.1!$M$7,TE_discrete_.1!$O$7,TE_discrete_.1!$Q$7,TE_discrete_.1!$S$7,TE_discrete_.1!$U$7,TE_discrete_.1!$W$7)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -4057,7 +4109,7 @@
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$8</c:f>
+              <c:f>TE_discrete_.1!$A$8</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4083,11 +4135,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$C$1,Sheet1!$E$1,Sheet1!$G$1,Sheet1!$I$1,Sheet1!$K$1,Sheet1!$M$1,Sheet1!$O$1,Sheet1!$Q$1,Sheet1!$S$1,Sheet1!$U$1,Sheet1!$W$1)</c:f>
+              <c:f>(TE_discrete_.1!$C$1,TE_discrete_.1!$E$1,TE_discrete_.1!$G$1,TE_discrete_.1!$I$1,TE_discrete_.1!$K$1,TE_discrete_.1!$M$1,TE_discrete_.1!$O$1,TE_discrete_.1!$Q$1,TE_discrete_.1!$S$1,TE_discrete_.1!$U$1,TE_discrete_.1!$W$1)</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
@@ -4131,11 +4183,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$8:$AY$8</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$8:$AY$8</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$C$8,Sheet1!$E$8,Sheet1!$G$8,Sheet1!$I$8,Sheet1!$K$8,Sheet1!$M$8,Sheet1!$O$8,Sheet1!$Q$8,Sheet1!$S$8,Sheet1!$U$8,Sheet1!$W$8)</c:f>
+              <c:f>(TE_discrete_.1!$C$8,TE_discrete_.1!$E$8,TE_discrete_.1!$G$8,TE_discrete_.1!$I$8,TE_discrete_.1!$K$8,TE_discrete_.1!$M$8,TE_discrete_.1!$O$8,TE_discrete_.1!$Q$8,TE_discrete_.1!$S$8,TE_discrete_.1!$U$8,TE_discrete_.1!$W$8)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -4186,7 +4238,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$9</c:f>
+              <c:f>TE_discrete_.1!$A$9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4212,11 +4264,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$C$1,Sheet1!$E$1,Sheet1!$G$1,Sheet1!$I$1,Sheet1!$K$1,Sheet1!$M$1,Sheet1!$O$1,Sheet1!$Q$1,Sheet1!$S$1,Sheet1!$U$1,Sheet1!$W$1)</c:f>
+              <c:f>(TE_discrete_.1!$C$1,TE_discrete_.1!$E$1,TE_discrete_.1!$G$1,TE_discrete_.1!$I$1,TE_discrete_.1!$K$1,TE_discrete_.1!$M$1,TE_discrete_.1!$O$1,TE_discrete_.1!$Q$1,TE_discrete_.1!$S$1,TE_discrete_.1!$U$1,TE_discrete_.1!$W$1)</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
@@ -4260,11 +4312,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$9:$AY$9</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$9:$AY$9</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$C$9,Sheet1!$E$9,Sheet1!$G$9,Sheet1!$I$9,Sheet1!$K$9,Sheet1!$M$9,Sheet1!$O$9,Sheet1!$Q$9,Sheet1!$S$9,Sheet1!$U$9,Sheet1!$W$9)</c:f>
+              <c:f>(TE_discrete_.1!$C$9,TE_discrete_.1!$E$9,TE_discrete_.1!$G$9,TE_discrete_.1!$I$9,TE_discrete_.1!$K$9,TE_discrete_.1!$M$9,TE_discrete_.1!$O$9,TE_discrete_.1!$Q$9,TE_discrete_.1!$S$9,TE_discrete_.1!$U$9,TE_discrete_.1!$W$9)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -4315,7 +4367,7 @@
           <c:order val="8"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$10</c:f>
+              <c:f>TE_discrete_.1!$A$10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4341,11 +4393,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$C$1,Sheet1!$E$1,Sheet1!$G$1,Sheet1!$I$1,Sheet1!$K$1,Sheet1!$M$1,Sheet1!$O$1,Sheet1!$Q$1,Sheet1!$S$1,Sheet1!$U$1,Sheet1!$W$1)</c:f>
+              <c:f>(TE_discrete_.1!$C$1,TE_discrete_.1!$E$1,TE_discrete_.1!$G$1,TE_discrete_.1!$I$1,TE_discrete_.1!$K$1,TE_discrete_.1!$M$1,TE_discrete_.1!$O$1,TE_discrete_.1!$Q$1,TE_discrete_.1!$S$1,TE_discrete_.1!$U$1,TE_discrete_.1!$W$1)</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
@@ -4389,11 +4441,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$10:$AY$10</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$10:$AY$10</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$C$10,Sheet1!$E$10,Sheet1!$G$10,Sheet1!$I$10,Sheet1!$K$10,Sheet1!$M$10,Sheet1!$O$10,Sheet1!$Q$10,Sheet1!$S$10,Sheet1!$U$10,Sheet1!$W$10)</c:f>
+              <c:f>(TE_discrete_.1!$C$10,TE_discrete_.1!$E$10,TE_discrete_.1!$G$10,TE_discrete_.1!$I$10,TE_discrete_.1!$K$10,TE_discrete_.1!$M$10,TE_discrete_.1!$O$10,TE_discrete_.1!$Q$10,TE_discrete_.1!$S$10,TE_discrete_.1!$U$10,TE_discrete_.1!$W$10)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -4444,7 +4496,7 @@
           <c:order val="9"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$11</c:f>
+              <c:f>TE_discrete_.1!$A$11</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4470,11 +4522,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$C$1,Sheet1!$E$1,Sheet1!$G$1,Sheet1!$I$1,Sheet1!$K$1,Sheet1!$M$1,Sheet1!$O$1,Sheet1!$Q$1,Sheet1!$S$1,Sheet1!$U$1,Sheet1!$W$1)</c:f>
+              <c:f>(TE_discrete_.1!$C$1,TE_discrete_.1!$E$1,TE_discrete_.1!$G$1,TE_discrete_.1!$I$1,TE_discrete_.1!$K$1,TE_discrete_.1!$M$1,TE_discrete_.1!$O$1,TE_discrete_.1!$Q$1,TE_discrete_.1!$S$1,TE_discrete_.1!$U$1,TE_discrete_.1!$W$1)</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
@@ -4518,11 +4570,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$11:$AY$11</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$11:$AY$11</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$C$11,Sheet1!$E$11,Sheet1!$G$11,Sheet1!$I$11,Sheet1!$K$11,Sheet1!$M$11,Sheet1!$O$11,Sheet1!$Q$11,Sheet1!$S$11,Sheet1!$U$11,Sheet1!$W$11)</c:f>
+              <c:f>(TE_discrete_.1!$C$11,TE_discrete_.1!$E$11,TE_discrete_.1!$G$11,TE_discrete_.1!$I$11,TE_discrete_.1!$K$11,TE_discrete_.1!$M$11,TE_discrete_.1!$O$11,TE_discrete_.1!$Q$11,TE_discrete_.1!$S$11,TE_discrete_.1!$U$11,TE_discrete_.1!$W$11)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -4686,6 +4738,1641 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="1856454368"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Helen Ann</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="percentStacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>TE_discrete_twobins!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>high</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="C00000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobins!$B$1:$AY$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobins!$D$1,TE_discrete_twobins!$F$1,TE_discrete_twobins!$H$1,TE_discrete_twobins!$J$1,TE_discrete_twobins!$L$1,TE_discrete_twobins!$N$1,TE_discrete_twobins!$T$1,TE_discrete_twobins!$V$1,TE_discrete_twobins!$X$1,TE_discrete_twobins!$Z$1,TE_discrete_twobins!$AF$1,TE_discrete_twobins!$AH$1,TE_discrete_twobins!$AJ$1,TE_discrete_twobins!$AL$1,TE_discrete_twobins!$AN$1,TE_discrete_twobins!$AP$1,TE_discrete_twobins!$AR$1,TE_discrete_twobins!$AT$1,TE_discrete_twobins!$AV$1,TE_discrete_twobins!$AX$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>dyad_02_anno01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>dyad_03_anno01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>dyad_04_anno01</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>dyad_05_anno01</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>dyad_06_anno01</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>dyad_07_anno01</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>dyad_10_anno01</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>dyad_11_anno01</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>triad_01_anno01</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>triad_02_anno01</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>triad_05_anno01</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>triad_06_anno01</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>triad_07_anno01</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>triad_08_anno01</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>triad_09_anno01</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>triad_10_anno01</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>triad_11_anno01</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>triad_12_anno01</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>triad_13_anno01</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>triad_14_anno01</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobins!$B$2:$AY$2</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobins!$D$2,TE_discrete_twobins!$F$2,TE_discrete_twobins!$H$2,TE_discrete_twobins!$J$2,TE_discrete_twobins!$L$2,TE_discrete_twobins!$N$2,TE_discrete_twobins!$T$2,TE_discrete_twobins!$V$2,TE_discrete_twobins!$X$2,TE_discrete_twobins!$Z$2,TE_discrete_twobins!$AF$2,TE_discrete_twobins!$AH$2,TE_discrete_twobins!$AJ$2,TE_discrete_twobins!$AL$2,TE_discrete_twobins!$AN$2,TE_discrete_twobins!$AP$2,TE_discrete_twobins!$AR$2,TE_discrete_twobins!$AT$2,TE_discrete_twobins!$AV$2,TE_discrete_twobins!$AX$2)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.47961134477407102</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.74818318506452797</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.66684062557869395</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.43899452362325198</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.92854612515368096</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.695354742861091</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.116140428350629</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.60213659380017204</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.43328185212397402</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.79845533254624101</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.63778406624884898</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.71398762283533301</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.35741104952619301</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.3156048068769899E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.69235877004801305</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.32977909011373502</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.21420744199342501</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.72785443888142598</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.69873102402570397</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.55135905721345702</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-77AB-4F5E-BAC3-912E0FB8E4E3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>TE_discrete_twobins!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>mid</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobins!$B$1:$AY$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobins!$D$1,TE_discrete_twobins!$F$1,TE_discrete_twobins!$H$1,TE_discrete_twobins!$J$1,TE_discrete_twobins!$L$1,TE_discrete_twobins!$N$1,TE_discrete_twobins!$T$1,TE_discrete_twobins!$V$1,TE_discrete_twobins!$X$1,TE_discrete_twobins!$Z$1,TE_discrete_twobins!$AF$1,TE_discrete_twobins!$AH$1,TE_discrete_twobins!$AJ$1,TE_discrete_twobins!$AL$1,TE_discrete_twobins!$AN$1,TE_discrete_twobins!$AP$1,TE_discrete_twobins!$AR$1,TE_discrete_twobins!$AT$1,TE_discrete_twobins!$AV$1,TE_discrete_twobins!$AX$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>dyad_02_anno01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>dyad_03_anno01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>dyad_04_anno01</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>dyad_05_anno01</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>dyad_06_anno01</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>dyad_07_anno01</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>dyad_10_anno01</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>dyad_11_anno01</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>triad_01_anno01</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>triad_02_anno01</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>triad_05_anno01</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>triad_06_anno01</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>triad_07_anno01</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>triad_08_anno01</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>triad_09_anno01</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>triad_10_anno01</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>triad_11_anno01</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>triad_12_anno01</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>triad_13_anno01</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>triad_14_anno01</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobins!$B$3:$AY$3</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobins!$D$3,TE_discrete_twobins!$F$3,TE_discrete_twobins!$H$3,TE_discrete_twobins!$J$3,TE_discrete_twobins!$L$3,TE_discrete_twobins!$N$3,TE_discrete_twobins!$T$3,TE_discrete_twobins!$V$3,TE_discrete_twobins!$X$3,TE_discrete_twobins!$Z$3,TE_discrete_twobins!$AF$3,TE_discrete_twobins!$AH$3,TE_discrete_twobins!$AJ$3,TE_discrete_twobins!$AL$3,TE_discrete_twobins!$AN$3,TE_discrete_twobins!$AP$3,TE_discrete_twobins!$AR$3,TE_discrete_twobins!$AT$3,TE_discrete_twobins!$AV$3,TE_discrete_twobins!$AX$3)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.14992915139110599</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.143731988472622</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.13700106058820499</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.30067349229565599</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1044197628623201E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.110888455093544</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.22885846765290299</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.34173150549586201</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.132581607713184</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.01908697363242E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.28904012083123498</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.20964491448342201</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.218027636586549</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.15169147100961899</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.22900704872816399</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.33970363079615001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.71232550383534199</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.20410306508731199</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.26164732215382902</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.36618513590572099</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-77AB-4F5E-BAC3-912E0FB8E4E3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>TE_discrete_twobins!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>low</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobins!$B$1:$AY$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobins!$D$1,TE_discrete_twobins!$F$1,TE_discrete_twobins!$H$1,TE_discrete_twobins!$J$1,TE_discrete_twobins!$L$1,TE_discrete_twobins!$N$1,TE_discrete_twobins!$T$1,TE_discrete_twobins!$V$1,TE_discrete_twobins!$X$1,TE_discrete_twobins!$Z$1,TE_discrete_twobins!$AF$1,TE_discrete_twobins!$AH$1,TE_discrete_twobins!$AJ$1,TE_discrete_twobins!$AL$1,TE_discrete_twobins!$AN$1,TE_discrete_twobins!$AP$1,TE_discrete_twobins!$AR$1,TE_discrete_twobins!$AT$1,TE_discrete_twobins!$AV$1,TE_discrete_twobins!$AX$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>dyad_02_anno01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>dyad_03_anno01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>dyad_04_anno01</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>dyad_05_anno01</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>dyad_06_anno01</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>dyad_07_anno01</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>dyad_10_anno01</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>dyad_11_anno01</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>triad_01_anno01</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>triad_02_anno01</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>triad_05_anno01</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>triad_06_anno01</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>triad_07_anno01</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>triad_08_anno01</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>triad_09_anno01</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>triad_10_anno01</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>triad_11_anno01</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>triad_12_anno01</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>triad_13_anno01</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>triad_14_anno01</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobins!$B$4:$AY$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobins!$D$4,TE_discrete_twobins!$F$4,TE_discrete_twobins!$H$4,TE_discrete_twobins!$J$4,TE_discrete_twobins!$L$4,TE_discrete_twobins!$N$4,TE_discrete_twobins!$T$4,TE_discrete_twobins!$V$4,TE_discrete_twobins!$X$4,TE_discrete_twobins!$Z$4,TE_discrete_twobins!$AF$4,TE_discrete_twobins!$AH$4,TE_discrete_twobins!$AJ$4,TE_discrete_twobins!$AL$4,TE_discrete_twobins!$AN$4,TE_discrete_twobins!$AP$4,TE_discrete_twobins!$AR$4,TE_discrete_twobins!$AT$4,TE_discrete_twobins!$AV$4,TE_discrete_twobins!$AX$4)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.37045950383482101</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.108069164265129</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.19615831383310001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.25801898023742298</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.0388839108962401E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.19373952700951799</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.65381430779421501</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.6131900703964399E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.42654930950203102</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.16135379771743399</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7.3175812919914499E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7.6367462681243406E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.42456131388725699</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.78515248092161005</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7.8608642353662203E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.33051727909011303</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7.3467054171232504E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>6.8042496031261404E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.9621653820466E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.2455806880821103E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-77AB-4F5E-BAC3-912E0FB8E4E3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="1983489136"/>
+        <c:axId val="1983488656"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1983489136"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1983488656"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1983488656"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1983489136"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Laura</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-GB" baseline="0"/>
+              <a:t> Ann</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-GB"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="percentStacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>TE_discrete_twobins!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>high</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="C00000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobins!$B$1:$AY$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobins!$E$1,TE_discrete_twobins!$G$1,TE_discrete_twobins!$I$1,TE_discrete_twobins!$K$1,TE_discrete_twobins!$M$1,TE_discrete_twobins!$O$1,TE_discrete_twobins!$U$1,TE_discrete_twobins!$W$1,TE_discrete_twobins!$Y$1,TE_discrete_twobins!$AA$1,TE_discrete_twobins!$AG$1,TE_discrete_twobins!$AI$1,TE_discrete_twobins!$AK$1,TE_discrete_twobins!$AM$1,TE_discrete_twobins!$AO$1,TE_discrete_twobins!$AQ$1,TE_discrete_twobins!$AS$1,TE_discrete_twobins!$AU$1,TE_discrete_twobins!$AW$1,TE_discrete_twobins!$AY$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>dyad_02_anno02</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>dyad_03_anno02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>dyad_04_anno02</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>dyad_05_anno02</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>dyad_06_anno02</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>dyad_07_anno02</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>dyad_10_anno02</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>dyad_11_anno02</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>triad_01_anno02</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>triad_02_anno02</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>triad_05_anno02</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>triad_06_anno02</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>triad_07_anno02</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>triad_08_anno02</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>triad_09_anno02</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>triad_10_anno02</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>triad_11_anno02</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>triad_12_anno02</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>triad_13_anno02</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>triad_14_anno02</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobins!$B$2:$AY$2</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobins!$E$2,TE_discrete_twobins!$G$2,TE_discrete_twobins!$I$2,TE_discrete_twobins!$K$2,TE_discrete_twobins!$M$2,TE_discrete_twobins!$O$2,TE_discrete_twobins!$U$2,TE_discrete_twobins!$W$2,TE_discrete_twobins!$Y$2,TE_discrete_twobins!$AA$2,TE_discrete_twobins!$AG$2,TE_discrete_twobins!$AI$2,TE_discrete_twobins!$AK$2,TE_discrete_twobins!$AM$2,TE_discrete_twobins!$AO$2,TE_discrete_twobins!$AQ$2,TE_discrete_twobins!$AS$2,TE_discrete_twobins!$AU$2,TE_discrete_twobins!$AW$2,TE_discrete_twobins!$AY$2)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.241717460246058</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.48646786117027901</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.52275214221982702</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.35996122317085599</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.826293525599616</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.56917788104410305</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.9939280194303301E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.1466798402700593E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.212697365461606</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.60706906729634003</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.68918942379472E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.28492447076028599</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7.0496283619830902E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.50807028297068102</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.6438101487314E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.12382464281353001</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.14697016191628001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.21199391750617699</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C46B-4A5C-B8EA-04111DA8B0FC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>TE_discrete_twobins!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>mid</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobins!$B$1:$AY$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobins!$E$1,TE_discrete_twobins!$G$1,TE_discrete_twobins!$I$1,TE_discrete_twobins!$K$1,TE_discrete_twobins!$M$1,TE_discrete_twobins!$O$1,TE_discrete_twobins!$U$1,TE_discrete_twobins!$W$1,TE_discrete_twobins!$Y$1,TE_discrete_twobins!$AA$1,TE_discrete_twobins!$AG$1,TE_discrete_twobins!$AI$1,TE_discrete_twobins!$AK$1,TE_discrete_twobins!$AM$1,TE_discrete_twobins!$AO$1,TE_discrete_twobins!$AQ$1,TE_discrete_twobins!$AS$1,TE_discrete_twobins!$AU$1,TE_discrete_twobins!$AW$1,TE_discrete_twobins!$AY$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>dyad_02_anno02</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>dyad_03_anno02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>dyad_04_anno02</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>dyad_05_anno02</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>dyad_06_anno02</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>dyad_07_anno02</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>dyad_10_anno02</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>dyad_11_anno02</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>triad_01_anno02</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>triad_02_anno02</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>triad_05_anno02</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>triad_06_anno02</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>triad_07_anno02</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>triad_08_anno02</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>triad_09_anno02</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>triad_10_anno02</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>triad_11_anno02</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>triad_12_anno02</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>triad_13_anno02</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>triad_14_anno02</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobins!$B$3:$AY$3</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobins!$E$3,TE_discrete_twobins!$G$3,TE_discrete_twobins!$I$3,TE_discrete_twobins!$K$3,TE_discrete_twobins!$M$3,TE_discrete_twobins!$O$3,TE_discrete_twobins!$U$3,TE_discrete_twobins!$W$3,TE_discrete_twobins!$Y$3,TE_discrete_twobins!$AA$3,TE_discrete_twobins!$AG$3,TE_discrete_twobins!$AI$3,TE_discrete_twobins!$AK$3,TE_discrete_twobins!$AM$3,TE_discrete_twobins!$AO$3,TE_discrete_twobins!$AQ$3,TE_discrete_twobins!$AS$3,TE_discrete_twobins!$AU$3,TE_discrete_twobins!$AW$3,TE_discrete_twobins!$AY$3)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.24365173972695101</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.39512592406966501</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.21691554014242101</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.28138712201095201</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.123424118027047</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.255929656054036</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.22656767498343999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.68852661479560295</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.326925672129672</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.25819067296339998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.27978680925678301</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.52822314565461603</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.13473474496181401</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.33621823923277E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.35110838696496</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.473507217847769</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.51803325551479296</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.53185981194285004</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.28960811566995698</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.50058924158905105</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C46B-4A5C-B8EA-04111DA8B0FC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>TE_discrete_twobins!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>low</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobins!$B$1:$AY$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobins!$E$1,TE_discrete_twobins!$G$1,TE_discrete_twobins!$I$1,TE_discrete_twobins!$K$1,TE_discrete_twobins!$M$1,TE_discrete_twobins!$O$1,TE_discrete_twobins!$U$1,TE_discrete_twobins!$W$1,TE_discrete_twobins!$Y$1,TE_discrete_twobins!$AA$1,TE_discrete_twobins!$AG$1,TE_discrete_twobins!$AI$1,TE_discrete_twobins!$AK$1,TE_discrete_twobins!$AM$1,TE_discrete_twobins!$AO$1,TE_discrete_twobins!$AQ$1,TE_discrete_twobins!$AS$1,TE_discrete_twobins!$AU$1,TE_discrete_twobins!$AW$1,TE_discrete_twobins!$AY$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>dyad_02_anno02</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>dyad_03_anno02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>dyad_04_anno02</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>dyad_05_anno02</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>dyad_06_anno02</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>dyad_07_anno02</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>dyad_10_anno02</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>dyad_11_anno02</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>triad_01_anno02</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>triad_02_anno02</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>triad_05_anno02</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>triad_06_anno02</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>triad_07_anno02</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>triad_08_anno02</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>triad_09_anno02</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>triad_10_anno02</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>triad_11_anno02</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>triad_12_anno02</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>triad_13_anno02</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>triad_14_anno02</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobins!$B$4:$AY$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobins!$E$4,TE_discrete_twobins!$G$4,TE_discrete_twobins!$I$4,TE_discrete_twobins!$K$4,TE_discrete_twobins!$M$4,TE_discrete_twobins!$O$4,TE_discrete_twobins!$U$4,TE_discrete_twobins!$W$4,TE_discrete_twobins!$Y$4,TE_discrete_twobins!$AA$4,TE_discrete_twobins!$AG$4,TE_discrete_twobins!$AI$4,TE_discrete_twobins!$AK$4,TE_discrete_twobins!$AM$4,TE_discrete_twobins!$AO$4,TE_discrete_twobins!$AQ$4,TE_discrete_twobins!$AS$4,TE_discrete_twobins!$AU$4,TE_discrete_twobins!$AW$4,TE_discrete_twobins!$AY$4)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.41566766379523601</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.118374890364615</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.26033231763775</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.35149154733154098</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.9990622851069998E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.16620311987147299</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.38024398321925301</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.22852085134411901</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.44551738615405301</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.13474025974025899</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.35603548549504299</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.17344081610814799</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.64189931291665603</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.96657992456360897</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.140770252324037</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.46855861767279</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.48196674448520599</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.33659787519843598</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.55623747721077998</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.27099410758410902</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C46B-4A5C-B8EA-04111DA8B0FC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="1983489136"/>
+        <c:axId val="1983488656"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1983489136"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1983488656"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1983488656"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1983489136"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8526,7 +10213,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$2</c:f>
+              <c:f>TE_discrete_.1!$A$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8549,7 +10236,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$B$1:$AY$1</c:f>
+              <c:f>TE_discrete_.1!$B$1:$AY$1</c:f>
               <c:strCache>
                 <c:ptCount val="50"/>
                 <c:pt idx="0">
@@ -8707,7 +10394,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$AY$2</c:f>
+              <c:f>TE_discrete_.1!$B$2:$AY$2</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -8875,7 +10562,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$3</c:f>
+              <c:f>TE_discrete_.1!$A$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8898,7 +10585,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$B$1:$AY$1</c:f>
+              <c:f>TE_discrete_.1!$B$1:$AY$1</c:f>
               <c:strCache>
                 <c:ptCount val="50"/>
                 <c:pt idx="0">
@@ -9056,7 +10743,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$3:$AY$3</c:f>
+              <c:f>TE_discrete_.1!$B$3:$AY$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -9224,7 +10911,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$4</c:f>
+              <c:f>TE_discrete_.1!$A$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9247,7 +10934,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$B$1:$AY$1</c:f>
+              <c:f>TE_discrete_.1!$B$1:$AY$1</c:f>
               <c:strCache>
                 <c:ptCount val="50"/>
                 <c:pt idx="0">
@@ -9405,7 +11092,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$4:$AY$4</c:f>
+              <c:f>TE_discrete_.1!$B$4:$AY$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -9573,7 +11260,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$5</c:f>
+              <c:f>TE_discrete_.1!$A$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9596,7 +11283,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$B$1:$AY$1</c:f>
+              <c:f>TE_discrete_.1!$B$1:$AY$1</c:f>
               <c:strCache>
                 <c:ptCount val="50"/>
                 <c:pt idx="0">
@@ -9754,7 +11441,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$5:$AY$5</c:f>
+              <c:f>TE_discrete_.1!$B$5:$AY$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -9922,7 +11609,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$6</c:f>
+              <c:f>TE_discrete_.1!$A$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9945,7 +11632,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$B$1:$AY$1</c:f>
+              <c:f>TE_discrete_.1!$B$1:$AY$1</c:f>
               <c:strCache>
                 <c:ptCount val="50"/>
                 <c:pt idx="0">
@@ -10103,7 +11790,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$6:$AY$6</c:f>
+              <c:f>TE_discrete_.1!$B$6:$AY$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -10271,7 +11958,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$7</c:f>
+              <c:f>TE_discrete_.1!$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10294,7 +11981,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$B$1:$AY$1</c:f>
+              <c:f>TE_discrete_.1!$B$1:$AY$1</c:f>
               <c:strCache>
                 <c:ptCount val="50"/>
                 <c:pt idx="0">
@@ -10452,7 +12139,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$7:$AY$7</c:f>
+              <c:f>TE_discrete_.1!$B$7:$AY$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -10620,7 +12307,7 @@
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$8</c:f>
+              <c:f>TE_discrete_.1!$A$8</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10643,7 +12330,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$B$1:$AY$1</c:f>
+              <c:f>TE_discrete_.1!$B$1:$AY$1</c:f>
               <c:strCache>
                 <c:ptCount val="50"/>
                 <c:pt idx="0">
@@ -10801,7 +12488,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$8:$AY$8</c:f>
+              <c:f>TE_discrete_.1!$B$8:$AY$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -10969,7 +12656,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$9</c:f>
+              <c:f>TE_discrete_.1!$A$9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10992,7 +12679,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$B$1:$AY$1</c:f>
+              <c:f>TE_discrete_.1!$B$1:$AY$1</c:f>
               <c:strCache>
                 <c:ptCount val="50"/>
                 <c:pt idx="0">
@@ -11150,7 +12837,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$9:$AY$9</c:f>
+              <c:f>TE_discrete_.1!$B$9:$AY$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -11318,7 +13005,7 @@
           <c:order val="8"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$10</c:f>
+              <c:f>TE_discrete_.1!$A$10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -11341,7 +13028,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$B$1:$AY$1</c:f>
+              <c:f>TE_discrete_.1!$B$1:$AY$1</c:f>
               <c:strCache>
                 <c:ptCount val="50"/>
                 <c:pt idx="0">
@@ -11499,7 +13186,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$10:$AY$10</c:f>
+              <c:f>TE_discrete_.1!$B$10:$AY$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -11667,7 +13354,7 @@
           <c:order val="9"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$11</c:f>
+              <c:f>TE_discrete_.1!$A$11</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -11690,7 +13377,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$B$1:$AY$1</c:f>
+              <c:f>TE_discrete_.1!$B$1:$AY$1</c:f>
               <c:strCache>
                 <c:ptCount val="50"/>
                 <c:pt idx="0">
@@ -11848,7 +13535,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$11:$AY$11</c:f>
+              <c:f>TE_discrete_.1!$B$11:$AY$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -12288,7 +13975,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$2</c:f>
+              <c:f>TE_discrete_.1!$A$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12314,11 +14001,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$X$1,Sheet1!$Z$1,Sheet1!$AB$1,Sheet1!$AD$1,Sheet1!$AF$1,Sheet1!$AH$1,Sheet1!$AJ$1,Sheet1!$AL$1,Sheet1!$AN$1,Sheet1!$AP$1,Sheet1!$AR$1,Sheet1!$AT$1,Sheet1!$AV$1,Sheet1!$AX$1)</c:f>
+              <c:f>(TE_discrete_.1!$X$1,TE_discrete_.1!$Z$1,TE_discrete_.1!$AB$1,TE_discrete_.1!$AD$1,TE_discrete_.1!$AF$1,TE_discrete_.1!$AH$1,TE_discrete_.1!$AJ$1,TE_discrete_.1!$AL$1,TE_discrete_.1!$AN$1,TE_discrete_.1!$AP$1,TE_discrete_.1!$AR$1,TE_discrete_.1!$AT$1,TE_discrete_.1!$AV$1,TE_discrete_.1!$AX$1)</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
@@ -12371,11 +14058,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$2:$AY$2</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$2:$AY$2</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$X$2,Sheet1!$Z$2,Sheet1!$AB$2,Sheet1!$AD$2,Sheet1!$AF$2,Sheet1!$AH$2,Sheet1!$AJ$2,Sheet1!$AL$2,Sheet1!$AN$2,Sheet1!$AP$2,Sheet1!$AR$2,Sheet1!$AT$2,Sheet1!$AV$2,Sheet1!$AX$2)</c:f>
+              <c:f>(TE_discrete_.1!$X$2,TE_discrete_.1!$Z$2,TE_discrete_.1!$AB$2,TE_discrete_.1!$AD$2,TE_discrete_.1!$AF$2,TE_discrete_.1!$AH$2,TE_discrete_.1!$AJ$2,TE_discrete_.1!$AL$2,TE_discrete_.1!$AN$2,TE_discrete_.1!$AP$2,TE_discrete_.1!$AR$2,TE_discrete_.1!$AT$2,TE_discrete_.1!$AV$2,TE_discrete_.1!$AX$2)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
@@ -12435,7 +14122,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$3</c:f>
+              <c:f>TE_discrete_.1!$A$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12461,11 +14148,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$X$1,Sheet1!$Z$1,Sheet1!$AB$1,Sheet1!$AD$1,Sheet1!$AF$1,Sheet1!$AH$1,Sheet1!$AJ$1,Sheet1!$AL$1,Sheet1!$AN$1,Sheet1!$AP$1,Sheet1!$AR$1,Sheet1!$AT$1,Sheet1!$AV$1,Sheet1!$AX$1)</c:f>
+              <c:f>(TE_discrete_.1!$X$1,TE_discrete_.1!$Z$1,TE_discrete_.1!$AB$1,TE_discrete_.1!$AD$1,TE_discrete_.1!$AF$1,TE_discrete_.1!$AH$1,TE_discrete_.1!$AJ$1,TE_discrete_.1!$AL$1,TE_discrete_.1!$AN$1,TE_discrete_.1!$AP$1,TE_discrete_.1!$AR$1,TE_discrete_.1!$AT$1,TE_discrete_.1!$AV$1,TE_discrete_.1!$AX$1)</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
@@ -12518,11 +14205,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$3:$AY$3</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$3:$AY$3</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$X$3,Sheet1!$Z$3,Sheet1!$AB$3,Sheet1!$AD$3,Sheet1!$AF$3,Sheet1!$AH$3,Sheet1!$AJ$3,Sheet1!$AL$3,Sheet1!$AN$3,Sheet1!$AP$3,Sheet1!$AR$3,Sheet1!$AT$3,Sheet1!$AV$3,Sheet1!$AX$3)</c:f>
+              <c:f>(TE_discrete_.1!$X$3,TE_discrete_.1!$Z$3,TE_discrete_.1!$AB$3,TE_discrete_.1!$AD$3,TE_discrete_.1!$AF$3,TE_discrete_.1!$AH$3,TE_discrete_.1!$AJ$3,TE_discrete_.1!$AL$3,TE_discrete_.1!$AN$3,TE_discrete_.1!$AP$3,TE_discrete_.1!$AR$3,TE_discrete_.1!$AT$3,TE_discrete_.1!$AV$3,TE_discrete_.1!$AX$3)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
@@ -12582,7 +14269,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$4</c:f>
+              <c:f>TE_discrete_.1!$A$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12608,11 +14295,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$X$1,Sheet1!$Z$1,Sheet1!$AB$1,Sheet1!$AD$1,Sheet1!$AF$1,Sheet1!$AH$1,Sheet1!$AJ$1,Sheet1!$AL$1,Sheet1!$AN$1,Sheet1!$AP$1,Sheet1!$AR$1,Sheet1!$AT$1,Sheet1!$AV$1,Sheet1!$AX$1)</c:f>
+              <c:f>(TE_discrete_.1!$X$1,TE_discrete_.1!$Z$1,TE_discrete_.1!$AB$1,TE_discrete_.1!$AD$1,TE_discrete_.1!$AF$1,TE_discrete_.1!$AH$1,TE_discrete_.1!$AJ$1,TE_discrete_.1!$AL$1,TE_discrete_.1!$AN$1,TE_discrete_.1!$AP$1,TE_discrete_.1!$AR$1,TE_discrete_.1!$AT$1,TE_discrete_.1!$AV$1,TE_discrete_.1!$AX$1)</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
@@ -12665,11 +14352,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$4:$AY$4</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$4:$AY$4</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$X$4,Sheet1!$Z$4,Sheet1!$AB$4,Sheet1!$AD$4,Sheet1!$AF$4,Sheet1!$AH$4,Sheet1!$AJ$4,Sheet1!$AL$4,Sheet1!$AN$4,Sheet1!$AP$4,Sheet1!$AR$4,Sheet1!$AT$4,Sheet1!$AV$4,Sheet1!$AX$4)</c:f>
+              <c:f>(TE_discrete_.1!$X$4,TE_discrete_.1!$Z$4,TE_discrete_.1!$AB$4,TE_discrete_.1!$AD$4,TE_discrete_.1!$AF$4,TE_discrete_.1!$AH$4,TE_discrete_.1!$AJ$4,TE_discrete_.1!$AL$4,TE_discrete_.1!$AN$4,TE_discrete_.1!$AP$4,TE_discrete_.1!$AR$4,TE_discrete_.1!$AT$4,TE_discrete_.1!$AV$4,TE_discrete_.1!$AX$4)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
@@ -12729,7 +14416,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$5</c:f>
+              <c:f>TE_discrete_.1!$A$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12755,11 +14442,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$X$1,Sheet1!$Z$1,Sheet1!$AB$1,Sheet1!$AD$1,Sheet1!$AF$1,Sheet1!$AH$1,Sheet1!$AJ$1,Sheet1!$AL$1,Sheet1!$AN$1,Sheet1!$AP$1,Sheet1!$AR$1,Sheet1!$AT$1,Sheet1!$AV$1,Sheet1!$AX$1)</c:f>
+              <c:f>(TE_discrete_.1!$X$1,TE_discrete_.1!$Z$1,TE_discrete_.1!$AB$1,TE_discrete_.1!$AD$1,TE_discrete_.1!$AF$1,TE_discrete_.1!$AH$1,TE_discrete_.1!$AJ$1,TE_discrete_.1!$AL$1,TE_discrete_.1!$AN$1,TE_discrete_.1!$AP$1,TE_discrete_.1!$AR$1,TE_discrete_.1!$AT$1,TE_discrete_.1!$AV$1,TE_discrete_.1!$AX$1)</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
@@ -12812,11 +14499,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$5:$AY$5</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$5:$AY$5</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$X$5,Sheet1!$Z$5,Sheet1!$AB$5,Sheet1!$AD$5,Sheet1!$AF$5,Sheet1!$AH$5,Sheet1!$AJ$5,Sheet1!$AL$5,Sheet1!$AN$5,Sheet1!$AP$5,Sheet1!$AR$5,Sheet1!$AT$5,Sheet1!$AV$5,Sheet1!$AX$5)</c:f>
+              <c:f>(TE_discrete_.1!$X$5,TE_discrete_.1!$Z$5,TE_discrete_.1!$AB$5,TE_discrete_.1!$AD$5,TE_discrete_.1!$AF$5,TE_discrete_.1!$AH$5,TE_discrete_.1!$AJ$5,TE_discrete_.1!$AL$5,TE_discrete_.1!$AN$5,TE_discrete_.1!$AP$5,TE_discrete_.1!$AR$5,TE_discrete_.1!$AT$5,TE_discrete_.1!$AV$5,TE_discrete_.1!$AX$5)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
@@ -12876,7 +14563,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$6</c:f>
+              <c:f>TE_discrete_.1!$A$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12902,11 +14589,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$X$1,Sheet1!$Z$1,Sheet1!$AB$1,Sheet1!$AD$1,Sheet1!$AF$1,Sheet1!$AH$1,Sheet1!$AJ$1,Sheet1!$AL$1,Sheet1!$AN$1,Sheet1!$AP$1,Sheet1!$AR$1,Sheet1!$AT$1,Sheet1!$AV$1,Sheet1!$AX$1)</c:f>
+              <c:f>(TE_discrete_.1!$X$1,TE_discrete_.1!$Z$1,TE_discrete_.1!$AB$1,TE_discrete_.1!$AD$1,TE_discrete_.1!$AF$1,TE_discrete_.1!$AH$1,TE_discrete_.1!$AJ$1,TE_discrete_.1!$AL$1,TE_discrete_.1!$AN$1,TE_discrete_.1!$AP$1,TE_discrete_.1!$AR$1,TE_discrete_.1!$AT$1,TE_discrete_.1!$AV$1,TE_discrete_.1!$AX$1)</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
@@ -12959,11 +14646,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$6:$AY$6</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$6:$AY$6</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$X$6,Sheet1!$Z$6,Sheet1!$AB$6,Sheet1!$AD$6,Sheet1!$AF$6,Sheet1!$AH$6,Sheet1!$AJ$6,Sheet1!$AL$6,Sheet1!$AN$6,Sheet1!$AP$6,Sheet1!$AR$6,Sheet1!$AT$6,Sheet1!$AV$6,Sheet1!$AX$6)</c:f>
+              <c:f>(TE_discrete_.1!$X$6,TE_discrete_.1!$Z$6,TE_discrete_.1!$AB$6,TE_discrete_.1!$AD$6,TE_discrete_.1!$AF$6,TE_discrete_.1!$AH$6,TE_discrete_.1!$AJ$6,TE_discrete_.1!$AL$6,TE_discrete_.1!$AN$6,TE_discrete_.1!$AP$6,TE_discrete_.1!$AR$6,TE_discrete_.1!$AT$6,TE_discrete_.1!$AV$6,TE_discrete_.1!$AX$6)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
@@ -13023,7 +14710,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$7</c:f>
+              <c:f>TE_discrete_.1!$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13049,11 +14736,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$X$1,Sheet1!$Z$1,Sheet1!$AB$1,Sheet1!$AD$1,Sheet1!$AF$1,Sheet1!$AH$1,Sheet1!$AJ$1,Sheet1!$AL$1,Sheet1!$AN$1,Sheet1!$AP$1,Sheet1!$AR$1,Sheet1!$AT$1,Sheet1!$AV$1,Sheet1!$AX$1)</c:f>
+              <c:f>(TE_discrete_.1!$X$1,TE_discrete_.1!$Z$1,TE_discrete_.1!$AB$1,TE_discrete_.1!$AD$1,TE_discrete_.1!$AF$1,TE_discrete_.1!$AH$1,TE_discrete_.1!$AJ$1,TE_discrete_.1!$AL$1,TE_discrete_.1!$AN$1,TE_discrete_.1!$AP$1,TE_discrete_.1!$AR$1,TE_discrete_.1!$AT$1,TE_discrete_.1!$AV$1,TE_discrete_.1!$AX$1)</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
@@ -13106,11 +14793,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$7:$AY$7</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$7:$AY$7</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$X$7,Sheet1!$Z$7,Sheet1!$AB$7,Sheet1!$AD$7,Sheet1!$AF$7,Sheet1!$AH$7,Sheet1!$AJ$7,Sheet1!$AL$7,Sheet1!$AN$7,Sheet1!$AP$7,Sheet1!$AR$7,Sheet1!$AT$7,Sheet1!$AV$7,Sheet1!$AX$7)</c:f>
+              <c:f>(TE_discrete_.1!$X$7,TE_discrete_.1!$Z$7,TE_discrete_.1!$AB$7,TE_discrete_.1!$AD$7,TE_discrete_.1!$AF$7,TE_discrete_.1!$AH$7,TE_discrete_.1!$AJ$7,TE_discrete_.1!$AL$7,TE_discrete_.1!$AN$7,TE_discrete_.1!$AP$7,TE_discrete_.1!$AR$7,TE_discrete_.1!$AT$7,TE_discrete_.1!$AV$7,TE_discrete_.1!$AX$7)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
@@ -13170,7 +14857,7 @@
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$8</c:f>
+              <c:f>TE_discrete_.1!$A$8</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13196,11 +14883,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$X$1,Sheet1!$Z$1,Sheet1!$AB$1,Sheet1!$AD$1,Sheet1!$AF$1,Sheet1!$AH$1,Sheet1!$AJ$1,Sheet1!$AL$1,Sheet1!$AN$1,Sheet1!$AP$1,Sheet1!$AR$1,Sheet1!$AT$1,Sheet1!$AV$1,Sheet1!$AX$1)</c:f>
+              <c:f>(TE_discrete_.1!$X$1,TE_discrete_.1!$Z$1,TE_discrete_.1!$AB$1,TE_discrete_.1!$AD$1,TE_discrete_.1!$AF$1,TE_discrete_.1!$AH$1,TE_discrete_.1!$AJ$1,TE_discrete_.1!$AL$1,TE_discrete_.1!$AN$1,TE_discrete_.1!$AP$1,TE_discrete_.1!$AR$1,TE_discrete_.1!$AT$1,TE_discrete_.1!$AV$1,TE_discrete_.1!$AX$1)</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
@@ -13253,11 +14940,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$8:$AY$8</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$8:$AY$8</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$X$8,Sheet1!$Z$8,Sheet1!$AB$8,Sheet1!$AD$8,Sheet1!$AF$8,Sheet1!$AH$8,Sheet1!$AJ$8,Sheet1!$AL$8,Sheet1!$AN$8,Sheet1!$AP$8,Sheet1!$AR$8,Sheet1!$AT$8,Sheet1!$AV$8,Sheet1!$AX$8)</c:f>
+              <c:f>(TE_discrete_.1!$X$8,TE_discrete_.1!$Z$8,TE_discrete_.1!$AB$8,TE_discrete_.1!$AD$8,TE_discrete_.1!$AF$8,TE_discrete_.1!$AH$8,TE_discrete_.1!$AJ$8,TE_discrete_.1!$AL$8,TE_discrete_.1!$AN$8,TE_discrete_.1!$AP$8,TE_discrete_.1!$AR$8,TE_discrete_.1!$AT$8,TE_discrete_.1!$AV$8,TE_discrete_.1!$AX$8)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
@@ -13317,7 +15004,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$9</c:f>
+              <c:f>TE_discrete_.1!$A$9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13343,11 +15030,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$X$1,Sheet1!$Z$1,Sheet1!$AB$1,Sheet1!$AD$1,Sheet1!$AF$1,Sheet1!$AH$1,Sheet1!$AJ$1,Sheet1!$AL$1,Sheet1!$AN$1,Sheet1!$AP$1,Sheet1!$AR$1,Sheet1!$AT$1,Sheet1!$AV$1,Sheet1!$AX$1)</c:f>
+              <c:f>(TE_discrete_.1!$X$1,TE_discrete_.1!$Z$1,TE_discrete_.1!$AB$1,TE_discrete_.1!$AD$1,TE_discrete_.1!$AF$1,TE_discrete_.1!$AH$1,TE_discrete_.1!$AJ$1,TE_discrete_.1!$AL$1,TE_discrete_.1!$AN$1,TE_discrete_.1!$AP$1,TE_discrete_.1!$AR$1,TE_discrete_.1!$AT$1,TE_discrete_.1!$AV$1,TE_discrete_.1!$AX$1)</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
@@ -13400,11 +15087,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$9:$AY$9</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$9:$AY$9</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$X$9,Sheet1!$Z$9,Sheet1!$AB$9,Sheet1!$AD$9,Sheet1!$AF$9,Sheet1!$AH$9,Sheet1!$AJ$9,Sheet1!$AL$9,Sheet1!$AN$9,Sheet1!$AP$9,Sheet1!$AR$9,Sheet1!$AT$9,Sheet1!$AV$9,Sheet1!$AX$9)</c:f>
+              <c:f>(TE_discrete_.1!$X$9,TE_discrete_.1!$Z$9,TE_discrete_.1!$AB$9,TE_discrete_.1!$AD$9,TE_discrete_.1!$AF$9,TE_discrete_.1!$AH$9,TE_discrete_.1!$AJ$9,TE_discrete_.1!$AL$9,TE_discrete_.1!$AN$9,TE_discrete_.1!$AP$9,TE_discrete_.1!$AR$9,TE_discrete_.1!$AT$9,TE_discrete_.1!$AV$9,TE_discrete_.1!$AX$9)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
@@ -13464,7 +15151,7 @@
           <c:order val="8"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$10</c:f>
+              <c:f>TE_discrete_.1!$A$10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13490,11 +15177,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$X$1,Sheet1!$Z$1,Sheet1!$AB$1,Sheet1!$AD$1,Sheet1!$AF$1,Sheet1!$AH$1,Sheet1!$AJ$1,Sheet1!$AL$1,Sheet1!$AN$1,Sheet1!$AP$1,Sheet1!$AR$1,Sheet1!$AT$1,Sheet1!$AV$1,Sheet1!$AX$1)</c:f>
+              <c:f>(TE_discrete_.1!$X$1,TE_discrete_.1!$Z$1,TE_discrete_.1!$AB$1,TE_discrete_.1!$AD$1,TE_discrete_.1!$AF$1,TE_discrete_.1!$AH$1,TE_discrete_.1!$AJ$1,TE_discrete_.1!$AL$1,TE_discrete_.1!$AN$1,TE_discrete_.1!$AP$1,TE_discrete_.1!$AR$1,TE_discrete_.1!$AT$1,TE_discrete_.1!$AV$1,TE_discrete_.1!$AX$1)</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
@@ -13547,11 +15234,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$10:$AY$10</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$10:$AY$10</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$X$10,Sheet1!$Z$10,Sheet1!$AB$10,Sheet1!$AD$10,Sheet1!$AF$10,Sheet1!$AH$10,Sheet1!$AJ$10,Sheet1!$AL$10,Sheet1!$AN$10,Sheet1!$AP$10,Sheet1!$AR$10,Sheet1!$AT$10,Sheet1!$AV$10,Sheet1!$AX$10)</c:f>
+              <c:f>(TE_discrete_.1!$X$10,TE_discrete_.1!$Z$10,TE_discrete_.1!$AB$10,TE_discrete_.1!$AD$10,TE_discrete_.1!$AF$10,TE_discrete_.1!$AH$10,TE_discrete_.1!$AJ$10,TE_discrete_.1!$AL$10,TE_discrete_.1!$AN$10,TE_discrete_.1!$AP$10,TE_discrete_.1!$AR$10,TE_discrete_.1!$AT$10,TE_discrete_.1!$AV$10,TE_discrete_.1!$AX$10)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
@@ -13611,7 +15298,7 @@
           <c:order val="9"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$11</c:f>
+              <c:f>TE_discrete_.1!$A$11</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13637,11 +15324,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$X$1,Sheet1!$Z$1,Sheet1!$AB$1,Sheet1!$AD$1,Sheet1!$AF$1,Sheet1!$AH$1,Sheet1!$AJ$1,Sheet1!$AL$1,Sheet1!$AN$1,Sheet1!$AP$1,Sheet1!$AR$1,Sheet1!$AT$1,Sheet1!$AV$1,Sheet1!$AX$1)</c:f>
+              <c:f>(TE_discrete_.1!$X$1,TE_discrete_.1!$Z$1,TE_discrete_.1!$AB$1,TE_discrete_.1!$AD$1,TE_discrete_.1!$AF$1,TE_discrete_.1!$AH$1,TE_discrete_.1!$AJ$1,TE_discrete_.1!$AL$1,TE_discrete_.1!$AN$1,TE_discrete_.1!$AP$1,TE_discrete_.1!$AR$1,TE_discrete_.1!$AT$1,TE_discrete_.1!$AV$1,TE_discrete_.1!$AX$1)</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
@@ -13694,11 +15381,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$11:$AY$11</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$11:$AY$11</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$X$11,Sheet1!$Z$11,Sheet1!$AB$11,Sheet1!$AD$11,Sheet1!$AF$11,Sheet1!$AH$11,Sheet1!$AJ$11,Sheet1!$AL$11,Sheet1!$AN$11,Sheet1!$AP$11,Sheet1!$AR$11,Sheet1!$AT$11,Sheet1!$AV$11,Sheet1!$AX$11)</c:f>
+              <c:f>(TE_discrete_.1!$X$11,TE_discrete_.1!$Z$11,TE_discrete_.1!$AB$11,TE_discrete_.1!$AD$11,TE_discrete_.1!$AF$11,TE_discrete_.1!$AH$11,TE_discrete_.1!$AJ$11,TE_discrete_.1!$AL$11,TE_discrete_.1!$AN$11,TE_discrete_.1!$AP$11,TE_discrete_.1!$AR$11,TE_discrete_.1!$AT$11,TE_discrete_.1!$AV$11,TE_discrete_.1!$AX$11)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
@@ -14037,7 +15724,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$2</c:f>
+              <c:f>TE_discrete_.1!$A$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14063,11 +15750,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$Y$1,Sheet1!$AA$1,Sheet1!$AC$1,Sheet1!$AE$1,Sheet1!$AG$1,Sheet1!$AI$1,Sheet1!$AK$1,Sheet1!$AM$1,Sheet1!$AO$1,Sheet1!$AQ$1,Sheet1!$AS$1,Sheet1!$AU$1,Sheet1!$AW$1,Sheet1!$AY$1)</c:f>
+              <c:f>(TE_discrete_.1!$Y$1,TE_discrete_.1!$AA$1,TE_discrete_.1!$AC$1,TE_discrete_.1!$AE$1,TE_discrete_.1!$AG$1,TE_discrete_.1!$AI$1,TE_discrete_.1!$AK$1,TE_discrete_.1!$AM$1,TE_discrete_.1!$AO$1,TE_discrete_.1!$AQ$1,TE_discrete_.1!$AS$1,TE_discrete_.1!$AU$1,TE_discrete_.1!$AW$1,TE_discrete_.1!$AY$1)</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
@@ -14120,11 +15807,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$2:$AY$2</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$2:$AY$2</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$Y$2,Sheet1!$AA$2,Sheet1!$AC$2,Sheet1!$AE$2,Sheet1!$AG$2,Sheet1!$AI$2,Sheet1!$AK$2,Sheet1!$AM$2,Sheet1!$AO$2,Sheet1!$AQ$2,Sheet1!$AS$2,Sheet1!$AU$2,Sheet1!$AW$2,Sheet1!$AY$2)</c:f>
+              <c:f>(TE_discrete_.1!$Y$2,TE_discrete_.1!$AA$2,TE_discrete_.1!$AC$2,TE_discrete_.1!$AE$2,TE_discrete_.1!$AG$2,TE_discrete_.1!$AI$2,TE_discrete_.1!$AK$2,TE_discrete_.1!$AM$2,TE_discrete_.1!$AO$2,TE_discrete_.1!$AQ$2,TE_discrete_.1!$AS$2,TE_discrete_.1!$AU$2,TE_discrete_.1!$AW$2,TE_discrete_.1!$AY$2)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
@@ -14184,7 +15871,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$3</c:f>
+              <c:f>TE_discrete_.1!$A$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14210,11 +15897,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$Y$1,Sheet1!$AA$1,Sheet1!$AC$1,Sheet1!$AE$1,Sheet1!$AG$1,Sheet1!$AI$1,Sheet1!$AK$1,Sheet1!$AM$1,Sheet1!$AO$1,Sheet1!$AQ$1,Sheet1!$AS$1,Sheet1!$AU$1,Sheet1!$AW$1,Sheet1!$AY$1)</c:f>
+              <c:f>(TE_discrete_.1!$Y$1,TE_discrete_.1!$AA$1,TE_discrete_.1!$AC$1,TE_discrete_.1!$AE$1,TE_discrete_.1!$AG$1,TE_discrete_.1!$AI$1,TE_discrete_.1!$AK$1,TE_discrete_.1!$AM$1,TE_discrete_.1!$AO$1,TE_discrete_.1!$AQ$1,TE_discrete_.1!$AS$1,TE_discrete_.1!$AU$1,TE_discrete_.1!$AW$1,TE_discrete_.1!$AY$1)</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
@@ -14267,11 +15954,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$3:$AY$3</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$3:$AY$3</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$Y$3,Sheet1!$AA$3,Sheet1!$AC$3,Sheet1!$AE$3,Sheet1!$AG$3,Sheet1!$AI$3,Sheet1!$AK$3,Sheet1!$AM$3,Sheet1!$AO$3,Sheet1!$AQ$3,Sheet1!$AS$3,Sheet1!$AU$3,Sheet1!$AW$3,Sheet1!$AY$3)</c:f>
+              <c:f>(TE_discrete_.1!$Y$3,TE_discrete_.1!$AA$3,TE_discrete_.1!$AC$3,TE_discrete_.1!$AE$3,TE_discrete_.1!$AG$3,TE_discrete_.1!$AI$3,TE_discrete_.1!$AK$3,TE_discrete_.1!$AM$3,TE_discrete_.1!$AO$3,TE_discrete_.1!$AQ$3,TE_discrete_.1!$AS$3,TE_discrete_.1!$AU$3,TE_discrete_.1!$AW$3,TE_discrete_.1!$AY$3)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
@@ -14331,7 +16018,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$4</c:f>
+              <c:f>TE_discrete_.1!$A$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14357,11 +16044,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$Y$1,Sheet1!$AA$1,Sheet1!$AC$1,Sheet1!$AE$1,Sheet1!$AG$1,Sheet1!$AI$1,Sheet1!$AK$1,Sheet1!$AM$1,Sheet1!$AO$1,Sheet1!$AQ$1,Sheet1!$AS$1,Sheet1!$AU$1,Sheet1!$AW$1,Sheet1!$AY$1)</c:f>
+              <c:f>(TE_discrete_.1!$Y$1,TE_discrete_.1!$AA$1,TE_discrete_.1!$AC$1,TE_discrete_.1!$AE$1,TE_discrete_.1!$AG$1,TE_discrete_.1!$AI$1,TE_discrete_.1!$AK$1,TE_discrete_.1!$AM$1,TE_discrete_.1!$AO$1,TE_discrete_.1!$AQ$1,TE_discrete_.1!$AS$1,TE_discrete_.1!$AU$1,TE_discrete_.1!$AW$1,TE_discrete_.1!$AY$1)</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
@@ -14414,11 +16101,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$4:$AY$4</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$4:$AY$4</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$Y$4,Sheet1!$AA$4,Sheet1!$AC$4,Sheet1!$AE$4,Sheet1!$AG$4,Sheet1!$AI$4,Sheet1!$AK$4,Sheet1!$AM$4,Sheet1!$AO$4,Sheet1!$AQ$4,Sheet1!$AS$4,Sheet1!$AU$4,Sheet1!$AW$4,Sheet1!$AY$4)</c:f>
+              <c:f>(TE_discrete_.1!$Y$4,TE_discrete_.1!$AA$4,TE_discrete_.1!$AC$4,TE_discrete_.1!$AE$4,TE_discrete_.1!$AG$4,TE_discrete_.1!$AI$4,TE_discrete_.1!$AK$4,TE_discrete_.1!$AM$4,TE_discrete_.1!$AO$4,TE_discrete_.1!$AQ$4,TE_discrete_.1!$AS$4,TE_discrete_.1!$AU$4,TE_discrete_.1!$AW$4,TE_discrete_.1!$AY$4)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
@@ -14478,7 +16165,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$5</c:f>
+              <c:f>TE_discrete_.1!$A$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14504,11 +16191,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$Y$1,Sheet1!$AA$1,Sheet1!$AC$1,Sheet1!$AE$1,Sheet1!$AG$1,Sheet1!$AI$1,Sheet1!$AK$1,Sheet1!$AM$1,Sheet1!$AO$1,Sheet1!$AQ$1,Sheet1!$AS$1,Sheet1!$AU$1,Sheet1!$AW$1,Sheet1!$AY$1)</c:f>
+              <c:f>(TE_discrete_.1!$Y$1,TE_discrete_.1!$AA$1,TE_discrete_.1!$AC$1,TE_discrete_.1!$AE$1,TE_discrete_.1!$AG$1,TE_discrete_.1!$AI$1,TE_discrete_.1!$AK$1,TE_discrete_.1!$AM$1,TE_discrete_.1!$AO$1,TE_discrete_.1!$AQ$1,TE_discrete_.1!$AS$1,TE_discrete_.1!$AU$1,TE_discrete_.1!$AW$1,TE_discrete_.1!$AY$1)</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
@@ -14561,11 +16248,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$5:$AY$5</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$5:$AY$5</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$Y$5,Sheet1!$AA$5,Sheet1!$AC$5,Sheet1!$AE$5,Sheet1!$AG$5,Sheet1!$AI$5,Sheet1!$AK$5,Sheet1!$AM$5,Sheet1!$AO$5,Sheet1!$AQ$5,Sheet1!$AS$5,Sheet1!$AU$5,Sheet1!$AW$5,Sheet1!$AY$5)</c:f>
+              <c:f>(TE_discrete_.1!$Y$5,TE_discrete_.1!$AA$5,TE_discrete_.1!$AC$5,TE_discrete_.1!$AE$5,TE_discrete_.1!$AG$5,TE_discrete_.1!$AI$5,TE_discrete_.1!$AK$5,TE_discrete_.1!$AM$5,TE_discrete_.1!$AO$5,TE_discrete_.1!$AQ$5,TE_discrete_.1!$AS$5,TE_discrete_.1!$AU$5,TE_discrete_.1!$AW$5,TE_discrete_.1!$AY$5)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
@@ -14625,7 +16312,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$6</c:f>
+              <c:f>TE_discrete_.1!$A$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14651,11 +16338,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$Y$1,Sheet1!$AA$1,Sheet1!$AC$1,Sheet1!$AE$1,Sheet1!$AG$1,Sheet1!$AI$1,Sheet1!$AK$1,Sheet1!$AM$1,Sheet1!$AO$1,Sheet1!$AQ$1,Sheet1!$AS$1,Sheet1!$AU$1,Sheet1!$AW$1,Sheet1!$AY$1)</c:f>
+              <c:f>(TE_discrete_.1!$Y$1,TE_discrete_.1!$AA$1,TE_discrete_.1!$AC$1,TE_discrete_.1!$AE$1,TE_discrete_.1!$AG$1,TE_discrete_.1!$AI$1,TE_discrete_.1!$AK$1,TE_discrete_.1!$AM$1,TE_discrete_.1!$AO$1,TE_discrete_.1!$AQ$1,TE_discrete_.1!$AS$1,TE_discrete_.1!$AU$1,TE_discrete_.1!$AW$1,TE_discrete_.1!$AY$1)</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
@@ -14708,11 +16395,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$6:$AY$6</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$6:$AY$6</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$Y$6,Sheet1!$AA$6,Sheet1!$AC$6,Sheet1!$AE$6,Sheet1!$AG$6,Sheet1!$AI$6,Sheet1!$AK$6,Sheet1!$AM$6,Sheet1!$AO$6,Sheet1!$AQ$6,Sheet1!$AS$6,Sheet1!$AU$6,Sheet1!$AW$6,Sheet1!$AY$6)</c:f>
+              <c:f>(TE_discrete_.1!$Y$6,TE_discrete_.1!$AA$6,TE_discrete_.1!$AC$6,TE_discrete_.1!$AE$6,TE_discrete_.1!$AG$6,TE_discrete_.1!$AI$6,TE_discrete_.1!$AK$6,TE_discrete_.1!$AM$6,TE_discrete_.1!$AO$6,TE_discrete_.1!$AQ$6,TE_discrete_.1!$AS$6,TE_discrete_.1!$AU$6,TE_discrete_.1!$AW$6,TE_discrete_.1!$AY$6)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
@@ -14772,7 +16459,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$7</c:f>
+              <c:f>TE_discrete_.1!$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14798,11 +16485,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$Y$1,Sheet1!$AA$1,Sheet1!$AC$1,Sheet1!$AE$1,Sheet1!$AG$1,Sheet1!$AI$1,Sheet1!$AK$1,Sheet1!$AM$1,Sheet1!$AO$1,Sheet1!$AQ$1,Sheet1!$AS$1,Sheet1!$AU$1,Sheet1!$AW$1,Sheet1!$AY$1)</c:f>
+              <c:f>(TE_discrete_.1!$Y$1,TE_discrete_.1!$AA$1,TE_discrete_.1!$AC$1,TE_discrete_.1!$AE$1,TE_discrete_.1!$AG$1,TE_discrete_.1!$AI$1,TE_discrete_.1!$AK$1,TE_discrete_.1!$AM$1,TE_discrete_.1!$AO$1,TE_discrete_.1!$AQ$1,TE_discrete_.1!$AS$1,TE_discrete_.1!$AU$1,TE_discrete_.1!$AW$1,TE_discrete_.1!$AY$1)</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
@@ -14855,11 +16542,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$7:$AY$7</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$7:$AY$7</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$Y$7,Sheet1!$AA$7,Sheet1!$AC$7,Sheet1!$AE$7,Sheet1!$AG$7,Sheet1!$AI$7,Sheet1!$AK$7,Sheet1!$AM$7,Sheet1!$AO$7,Sheet1!$AQ$7,Sheet1!$AS$7,Sheet1!$AU$7,Sheet1!$AW$7,Sheet1!$AY$7)</c:f>
+              <c:f>(TE_discrete_.1!$Y$7,TE_discrete_.1!$AA$7,TE_discrete_.1!$AC$7,TE_discrete_.1!$AE$7,TE_discrete_.1!$AG$7,TE_discrete_.1!$AI$7,TE_discrete_.1!$AK$7,TE_discrete_.1!$AM$7,TE_discrete_.1!$AO$7,TE_discrete_.1!$AQ$7,TE_discrete_.1!$AS$7,TE_discrete_.1!$AU$7,TE_discrete_.1!$AW$7,TE_discrete_.1!$AY$7)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
@@ -14919,7 +16606,7 @@
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$8</c:f>
+              <c:f>TE_discrete_.1!$A$8</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14945,11 +16632,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$Y$1,Sheet1!$AA$1,Sheet1!$AC$1,Sheet1!$AE$1,Sheet1!$AG$1,Sheet1!$AI$1,Sheet1!$AK$1,Sheet1!$AM$1,Sheet1!$AO$1,Sheet1!$AQ$1,Sheet1!$AS$1,Sheet1!$AU$1,Sheet1!$AW$1,Sheet1!$AY$1)</c:f>
+              <c:f>(TE_discrete_.1!$Y$1,TE_discrete_.1!$AA$1,TE_discrete_.1!$AC$1,TE_discrete_.1!$AE$1,TE_discrete_.1!$AG$1,TE_discrete_.1!$AI$1,TE_discrete_.1!$AK$1,TE_discrete_.1!$AM$1,TE_discrete_.1!$AO$1,TE_discrete_.1!$AQ$1,TE_discrete_.1!$AS$1,TE_discrete_.1!$AU$1,TE_discrete_.1!$AW$1,TE_discrete_.1!$AY$1)</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
@@ -15002,11 +16689,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$8:$AY$8</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$8:$AY$8</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$Y$8,Sheet1!$AA$8,Sheet1!$AC$8,Sheet1!$AE$8,Sheet1!$AG$8,Sheet1!$AI$8,Sheet1!$AK$8,Sheet1!$AM$8,Sheet1!$AO$8,Sheet1!$AQ$8,Sheet1!$AS$8,Sheet1!$AU$8,Sheet1!$AW$8,Sheet1!$AY$8)</c:f>
+              <c:f>(TE_discrete_.1!$Y$8,TE_discrete_.1!$AA$8,TE_discrete_.1!$AC$8,TE_discrete_.1!$AE$8,TE_discrete_.1!$AG$8,TE_discrete_.1!$AI$8,TE_discrete_.1!$AK$8,TE_discrete_.1!$AM$8,TE_discrete_.1!$AO$8,TE_discrete_.1!$AQ$8,TE_discrete_.1!$AS$8,TE_discrete_.1!$AU$8,TE_discrete_.1!$AW$8,TE_discrete_.1!$AY$8)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
@@ -15066,7 +16753,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$9</c:f>
+              <c:f>TE_discrete_.1!$A$9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -15092,11 +16779,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$Y$1,Sheet1!$AA$1,Sheet1!$AC$1,Sheet1!$AE$1,Sheet1!$AG$1,Sheet1!$AI$1,Sheet1!$AK$1,Sheet1!$AM$1,Sheet1!$AO$1,Sheet1!$AQ$1,Sheet1!$AS$1,Sheet1!$AU$1,Sheet1!$AW$1,Sheet1!$AY$1)</c:f>
+              <c:f>(TE_discrete_.1!$Y$1,TE_discrete_.1!$AA$1,TE_discrete_.1!$AC$1,TE_discrete_.1!$AE$1,TE_discrete_.1!$AG$1,TE_discrete_.1!$AI$1,TE_discrete_.1!$AK$1,TE_discrete_.1!$AM$1,TE_discrete_.1!$AO$1,TE_discrete_.1!$AQ$1,TE_discrete_.1!$AS$1,TE_discrete_.1!$AU$1,TE_discrete_.1!$AW$1,TE_discrete_.1!$AY$1)</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
@@ -15149,11 +16836,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$9:$AY$9</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$9:$AY$9</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$Y$9,Sheet1!$AA$9,Sheet1!$AC$9,Sheet1!$AE$9,Sheet1!$AG$9,Sheet1!$AI$9,Sheet1!$AK$9,Sheet1!$AM$9,Sheet1!$AO$9,Sheet1!$AQ$9,Sheet1!$AS$9,Sheet1!$AU$9,Sheet1!$AW$9,Sheet1!$AY$9)</c:f>
+              <c:f>(TE_discrete_.1!$Y$9,TE_discrete_.1!$AA$9,TE_discrete_.1!$AC$9,TE_discrete_.1!$AE$9,TE_discrete_.1!$AG$9,TE_discrete_.1!$AI$9,TE_discrete_.1!$AK$9,TE_discrete_.1!$AM$9,TE_discrete_.1!$AO$9,TE_discrete_.1!$AQ$9,TE_discrete_.1!$AS$9,TE_discrete_.1!$AU$9,TE_discrete_.1!$AW$9,TE_discrete_.1!$AY$9)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
@@ -15213,7 +16900,7 @@
           <c:order val="8"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$10</c:f>
+              <c:f>TE_discrete_.1!$A$10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -15239,11 +16926,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$Y$1,Sheet1!$AA$1,Sheet1!$AC$1,Sheet1!$AE$1,Sheet1!$AG$1,Sheet1!$AI$1,Sheet1!$AK$1,Sheet1!$AM$1,Sheet1!$AO$1,Sheet1!$AQ$1,Sheet1!$AS$1,Sheet1!$AU$1,Sheet1!$AW$1,Sheet1!$AY$1)</c:f>
+              <c:f>(TE_discrete_.1!$Y$1,TE_discrete_.1!$AA$1,TE_discrete_.1!$AC$1,TE_discrete_.1!$AE$1,TE_discrete_.1!$AG$1,TE_discrete_.1!$AI$1,TE_discrete_.1!$AK$1,TE_discrete_.1!$AM$1,TE_discrete_.1!$AO$1,TE_discrete_.1!$AQ$1,TE_discrete_.1!$AS$1,TE_discrete_.1!$AU$1,TE_discrete_.1!$AW$1,TE_discrete_.1!$AY$1)</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
@@ -15296,11 +16983,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$10:$AY$10</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$10:$AY$10</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$Y$10,Sheet1!$AA$10,Sheet1!$AC$10,Sheet1!$AE$10,Sheet1!$AG$10,Sheet1!$AI$10,Sheet1!$AK$10,Sheet1!$AM$10,Sheet1!$AO$10,Sheet1!$AQ$10,Sheet1!$AS$10,Sheet1!$AU$10,Sheet1!$AW$10,Sheet1!$AY$10)</c:f>
+              <c:f>(TE_discrete_.1!$Y$10,TE_discrete_.1!$AA$10,TE_discrete_.1!$AC$10,TE_discrete_.1!$AE$10,TE_discrete_.1!$AG$10,TE_discrete_.1!$AI$10,TE_discrete_.1!$AK$10,TE_discrete_.1!$AM$10,TE_discrete_.1!$AO$10,TE_discrete_.1!$AQ$10,TE_discrete_.1!$AS$10,TE_discrete_.1!$AU$10,TE_discrete_.1!$AW$10,TE_discrete_.1!$AY$10)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
@@ -15360,7 +17047,7 @@
           <c:order val="9"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$11</c:f>
+              <c:f>TE_discrete_.1!$A$11</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -15386,11 +17073,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$Y$1,Sheet1!$AA$1,Sheet1!$AC$1,Sheet1!$AE$1,Sheet1!$AG$1,Sheet1!$AI$1,Sheet1!$AK$1,Sheet1!$AM$1,Sheet1!$AO$1,Sheet1!$AQ$1,Sheet1!$AS$1,Sheet1!$AU$1,Sheet1!$AW$1,Sheet1!$AY$1)</c:f>
+              <c:f>(TE_discrete_.1!$Y$1,TE_discrete_.1!$AA$1,TE_discrete_.1!$AC$1,TE_discrete_.1!$AE$1,TE_discrete_.1!$AG$1,TE_discrete_.1!$AI$1,TE_discrete_.1!$AK$1,TE_discrete_.1!$AM$1,TE_discrete_.1!$AO$1,TE_discrete_.1!$AQ$1,TE_discrete_.1!$AS$1,TE_discrete_.1!$AU$1,TE_discrete_.1!$AW$1,TE_discrete_.1!$AY$1)</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
@@ -15443,11 +17130,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$11:$AY$11</c15:sqref>
+                    <c15:sqref>TE_discrete_.1!$B$11:$AY$11</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Sheet1!$Y$11,Sheet1!$AA$11,Sheet1!$AC$11,Sheet1!$AE$11,Sheet1!$AG$11,Sheet1!$AI$11,Sheet1!$AK$11,Sheet1!$AM$11,Sheet1!$AO$11,Sheet1!$AQ$11,Sheet1!$AS$11,Sheet1!$AU$11,Sheet1!$AW$11,Sheet1!$AY$11)</c:f>
+              <c:f>(TE_discrete_.1!$Y$11,TE_discrete_.1!$AA$11,TE_discrete_.1!$AC$11,TE_discrete_.1!$AE$11,TE_discrete_.1!$AG$11,TE_discrete_.1!$AI$11,TE_discrete_.1!$AK$11,TE_discrete_.1!$AM$11,TE_discrete_.1!$AO$11,TE_discrete_.1!$AQ$11,TE_discrete_.1!$AS$11,TE_discrete_.1!$AU$11,TE_discrete_.1!$AW$11,TE_discrete_.1!$AY$11)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
@@ -15750,6 +17437,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -16979,6 +18746,1016 @@
 </file>
 
 <file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style13.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -21947,6 +24724,85 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>66674</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>685800</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>5900</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAE96C8A-ADE6-410F-7A72-6C3F68D8E5A1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>673100</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>145600</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A54DB18-A492-44DF-9E02-F3A178E3E851}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F55E9D27-6B14-49E4-88EA-1619B28E4CAD}" name="Table1" displayName="Table1" ref="A1:AY4" totalsRowShown="0">
   <autoFilter ref="A1:AY4" xr:uid="{F55E9D27-6B14-49E4-88EA-1619B28E4CAD}"/>
@@ -22168,6 +25024,66 @@
     <tableColumn id="51" xr3:uid="{B40C0A05-F900-4746-9B23-3C6B0F8C432E}" name="triad_14_anno02"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2F1AF335-BE9C-41E6-927D-8C1CDBF06C25}" name="Table5" displayName="Table5" ref="A1:AY4" totalsRowShown="0">
+  <autoFilter ref="A1:AY4" xr:uid="{2F1AF335-BE9C-41E6-927D-8C1CDBF06C25}"/>
+  <tableColumns count="51">
+    <tableColumn id="1" xr3:uid="{FA44A002-4487-403B-B67B-4BA01D584059}" name="task_eng"/>
+    <tableColumn id="2" xr3:uid="{80795396-0428-4E51-968E-B0E70845A037}" name="dyad_01_anno01"/>
+    <tableColumn id="3" xr3:uid="{92D6A142-8A55-410A-AF7F-4A8785060F53}" name="dyad_01_anno02"/>
+    <tableColumn id="4" xr3:uid="{C07BAEB0-4522-4602-951D-DB776F502DA9}" name="dyad_02_anno01"/>
+    <tableColumn id="5" xr3:uid="{573B75E0-EE46-4788-A967-08C4439F6B74}" name="dyad_02_anno02"/>
+    <tableColumn id="6" xr3:uid="{5E18B03D-DE40-4659-8231-0A86F5BED277}" name="dyad_03_anno01"/>
+    <tableColumn id="7" xr3:uid="{96061D73-7D97-4FDC-819F-D2444199B9D3}" name="dyad_03_anno02"/>
+    <tableColumn id="8" xr3:uid="{A47D0A62-8D84-4D70-BFCC-C239F5764578}" name="dyad_04_anno01"/>
+    <tableColumn id="9" xr3:uid="{99D21C13-117D-473F-96FF-EE6E0ABFB9AE}" name="dyad_04_anno02"/>
+    <tableColumn id="10" xr3:uid="{175BEC0E-48CB-47A6-825E-5B804B72AC33}" name="dyad_05_anno01"/>
+    <tableColumn id="11" xr3:uid="{5DB3F8D6-BC13-4467-AC98-4D1DFB2B0F24}" name="dyad_05_anno02"/>
+    <tableColumn id="12" xr3:uid="{B14B9BB9-683E-4869-BC43-1A5EA9AB1CAA}" name="dyad_06_anno01"/>
+    <tableColumn id="13" xr3:uid="{488ECBD8-EDBB-4259-939D-E6943568983C}" name="dyad_06_anno02"/>
+    <tableColumn id="14" xr3:uid="{70CA275E-6C35-4286-BC14-94CC4F809634}" name="dyad_07_anno01"/>
+    <tableColumn id="15" xr3:uid="{358F8847-CD33-4E09-A148-5FB4913127B8}" name="dyad_07_anno02"/>
+    <tableColumn id="16" xr3:uid="{CFB2F49C-3BF3-43AC-9DAF-4332FEE96E40}" name="dyad_08_anno01"/>
+    <tableColumn id="17" xr3:uid="{C3193FB6-89EF-4836-89DD-46A1BB24DF60}" name="dyad_08_anno02"/>
+    <tableColumn id="18" xr3:uid="{40AB845E-A237-4595-85D5-215ACAA4F7D4}" name="dyad_09_anno01"/>
+    <tableColumn id="19" xr3:uid="{A28DA239-2C16-46A8-969A-113D91D1C2CE}" name="dyad_09_anno02"/>
+    <tableColumn id="20" xr3:uid="{31E278B9-FB6E-4291-ABB0-E0A36F65E4F3}" name="dyad_10_anno01"/>
+    <tableColumn id="21" xr3:uid="{215B7B48-02DF-4343-82FA-FCB86514C35E}" name="dyad_10_anno02"/>
+    <tableColumn id="22" xr3:uid="{F32BE191-02D0-49F4-95F2-9A882B61F55A}" name="dyad_11_anno01"/>
+    <tableColumn id="23" xr3:uid="{38DF2395-92A6-443A-8353-17C1AA1779A6}" name="dyad_11_anno02"/>
+    <tableColumn id="24" xr3:uid="{C53E071F-A59A-4212-94E7-132830FE6A57}" name="triad_01_anno01"/>
+    <tableColumn id="25" xr3:uid="{EC88B560-B041-4C23-BA9A-860654C922F5}" name="triad_01_anno02"/>
+    <tableColumn id="26" xr3:uid="{26668FA4-80BD-4ED9-AB5A-1E7F50AFFF95}" name="triad_02_anno01"/>
+    <tableColumn id="27" xr3:uid="{10AD3845-CC0D-4255-A916-B8C29DD011D2}" name="triad_02_anno02"/>
+    <tableColumn id="28" xr3:uid="{B772DEC3-5A89-4E2C-918E-F5EF07151A38}" name="triad_03_anno01"/>
+    <tableColumn id="29" xr3:uid="{387D18C9-FF8B-4DD4-BF1A-176DF6C09F53}" name="triad_03_anno02"/>
+    <tableColumn id="30" xr3:uid="{77C87B00-A776-4A54-B4FD-53E082A09D26}" name="triad_04_anno01"/>
+    <tableColumn id="31" xr3:uid="{035B8759-3D5B-480B-A040-652BA73FB171}" name="triad_04_anno02"/>
+    <tableColumn id="32" xr3:uid="{B0FFD696-6FDD-41D9-9B75-BB963D6424A1}" name="triad_05_anno01"/>
+    <tableColumn id="33" xr3:uid="{58B04F41-D18E-4DAE-83BE-9D6DD4264A2B}" name="triad_05_anno02"/>
+    <tableColumn id="34" xr3:uid="{DD4CD57F-F36E-4070-A05D-211C18880816}" name="triad_06_anno01"/>
+    <tableColumn id="35" xr3:uid="{192BB3C9-1A46-4D08-ADCE-A8182C931E76}" name="triad_06_anno02"/>
+    <tableColumn id="36" xr3:uid="{522CC6B0-2E51-4106-8760-403EFF6F0610}" name="triad_07_anno01"/>
+    <tableColumn id="37" xr3:uid="{EA20B2EB-C17E-4C24-BB91-29FE78B92383}" name="triad_07_anno02"/>
+    <tableColumn id="38" xr3:uid="{586DEDB7-BFE6-44DF-A725-7FD2C840F2EF}" name="triad_08_anno01"/>
+    <tableColumn id="39" xr3:uid="{9D1ECA2D-3CA3-4A83-B2EF-A32F376EBEA5}" name="triad_08_anno02"/>
+    <tableColumn id="40" xr3:uid="{4E7696BD-F336-4FDD-8D82-C05D710DAD21}" name="triad_09_anno01"/>
+    <tableColumn id="41" xr3:uid="{E6DB0D79-982C-4EB3-9536-0943585318B2}" name="triad_09_anno02"/>
+    <tableColumn id="42" xr3:uid="{F2EF31AF-02D0-4DD3-B4B2-578C7E47172C}" name="triad_10_anno01"/>
+    <tableColumn id="43" xr3:uid="{19E50B5A-4A31-47E4-BF87-BD488B2946B6}" name="triad_10_anno02"/>
+    <tableColumn id="44" xr3:uid="{4B8A1D33-A9BA-466B-B23B-8A59D1CDA63E}" name="triad_11_anno01"/>
+    <tableColumn id="45" xr3:uid="{E3640C3A-D438-42F3-B78B-3E1151BB94CB}" name="triad_11_anno02"/>
+    <tableColumn id="46" xr3:uid="{668FCCA1-A61B-4812-BD68-476F89794E83}" name="triad_12_anno01"/>
+    <tableColumn id="47" xr3:uid="{80320D00-CB68-4A1B-B5BB-5C0FAD54A411}" name="triad_12_anno02"/>
+    <tableColumn id="48" xr3:uid="{397FDBDB-2145-4F0B-A981-C9F54DFA78BC}" name="triad_13_anno01"/>
+    <tableColumn id="49" xr3:uid="{BBE75FCD-EE61-406C-B693-24BD8C05CE9A}" name="triad_13_anno02"/>
+    <tableColumn id="50" xr3:uid="{A72876DC-B454-4519-9E91-F26D1B0BE059}" name="triad_14_anno01"/>
+    <tableColumn id="51" xr3:uid="{76C054D2-C636-43FC-B237-541AE5CF3F1D}" name="triad_14_anno02"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -27482,4 +30398,904 @@
     <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4135E192-98BF-45B4-BA3D-15FECDE552EF}">
+  <dimension ref="A1:AY9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="23" width="16.26953125" customWidth="1"/>
+    <col min="24" max="51" width="16.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:51" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:51" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2">
+        <v>0.69790045944610202</v>
+      </c>
+      <c r="C2">
+        <v>0.42697369625304299</v>
+      </c>
+      <c r="D2">
+        <v>0.47961134477407102</v>
+      </c>
+      <c r="E2">
+        <v>0.241717460246058</v>
+      </c>
+      <c r="F2">
+        <v>0.74818318506452797</v>
+      </c>
+      <c r="G2">
+        <v>0.48646786117027901</v>
+      </c>
+      <c r="H2">
+        <v>0.66684062557869395</v>
+      </c>
+      <c r="I2">
+        <v>0.52275214221982702</v>
+      </c>
+      <c r="J2">
+        <v>0.43899452362325198</v>
+      </c>
+      <c r="K2">
+        <v>0.35996122317085599</v>
+      </c>
+      <c r="L2">
+        <v>0.92854612515368096</v>
+      </c>
+      <c r="M2">
+        <v>0.826293525599616</v>
+      </c>
+      <c r="N2">
+        <v>0.695354742861091</v>
+      </c>
+      <c r="O2">
+        <v>0.56917788104410305</v>
+      </c>
+      <c r="P2">
+        <v>0.355864269062453</v>
+      </c>
+      <c r="Q2">
+        <v>0.10040762907117801</v>
+      </c>
+      <c r="R2">
+        <v>0.123857234751759</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0.116140428350629</v>
+      </c>
+      <c r="U2">
+        <v>9.9939280194303301E-2</v>
+      </c>
+      <c r="V2">
+        <v>0.60213659380017204</v>
+      </c>
+      <c r="W2">
+        <v>7.1466798402700593E-2</v>
+      </c>
+      <c r="X2">
+        <v>0.43328185212397402</v>
+      </c>
+      <c r="Y2">
+        <v>0.212697365461606</v>
+      </c>
+      <c r="Z2">
+        <v>0.79845533254624101</v>
+      </c>
+      <c r="AA2">
+        <v>0.60706906729634003</v>
+      </c>
+      <c r="AB2">
+        <v>0.68654487167811096</v>
+      </c>
+      <c r="AC2">
+        <v>0.12558969781971099</v>
+      </c>
+      <c r="AD2">
+        <v>0.68512138841041303</v>
+      </c>
+      <c r="AE2">
+        <v>0.27813708602814502</v>
+      </c>
+      <c r="AF2">
+        <v>0.63778406624884898</v>
+      </c>
+      <c r="AG2">
+        <v>2.68918942379472E-2</v>
+      </c>
+      <c r="AH2">
+        <v>0.71398762283533301</v>
+      </c>
+      <c r="AI2">
+        <v>0.28492447076028599</v>
+      </c>
+      <c r="AJ2">
+        <v>0.35741104952619301</v>
+      </c>
+      <c r="AK2">
+        <v>7.0496283619830902E-2</v>
+      </c>
+      <c r="AL2">
+        <v>6.3156048068769899E-2</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0.69235877004801305</v>
+      </c>
+      <c r="AO2">
+        <v>0.50807028297068102</v>
+      </c>
+      <c r="AP2">
+        <v>0.32977909011373502</v>
+      </c>
+      <c r="AQ2">
+        <v>2.6438101487314E-2</v>
+      </c>
+      <c r="AR2">
+        <v>0.21420744199342501</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0.72785443888142598</v>
+      </c>
+      <c r="AU2">
+        <v>0.12382464281353001</v>
+      </c>
+      <c r="AV2">
+        <v>0.69873102402570397</v>
+      </c>
+      <c r="AW2">
+        <v>0.14697016191628001</v>
+      </c>
+      <c r="AX2">
+        <v>0.55135905721345702</v>
+      </c>
+      <c r="AY2">
+        <v>0.21199391750617699</v>
+      </c>
+    </row>
+    <row r="3" spans="1:51" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3">
+        <v>0.15031758525379299</v>
+      </c>
+      <c r="C3">
+        <v>0.25974263696436001</v>
+      </c>
+      <c r="D3">
+        <v>0.14992915139110599</v>
+      </c>
+      <c r="E3">
+        <v>0.24365173972695101</v>
+      </c>
+      <c r="F3">
+        <v>0.143731988472622</v>
+      </c>
+      <c r="G3">
+        <v>0.39512592406966501</v>
+      </c>
+      <c r="H3">
+        <v>0.13700106058820499</v>
+      </c>
+      <c r="I3">
+        <v>0.21691554014242101</v>
+      </c>
+      <c r="J3">
+        <v>0.30067349229565599</v>
+      </c>
+      <c r="K3">
+        <v>0.28138712201095201</v>
+      </c>
+      <c r="L3">
+        <v>1.1044197628623201E-2</v>
+      </c>
+      <c r="M3">
+        <v>0.123424118027047</v>
+      </c>
+      <c r="N3">
+        <v>0.110888455093544</v>
+      </c>
+      <c r="O3">
+        <v>0.255929656054036</v>
+      </c>
+      <c r="P3">
+        <v>0.46749192240051202</v>
+      </c>
+      <c r="Q3">
+        <v>0.40623849708933701</v>
+      </c>
+      <c r="R3">
+        <v>0.25069686750745601</v>
+      </c>
+      <c r="S3">
+        <v>2.0681858053449201E-2</v>
+      </c>
+      <c r="T3">
+        <v>0.22885846765290299</v>
+      </c>
+      <c r="U3">
+        <v>0.22656767498343999</v>
+      </c>
+      <c r="V3">
+        <v>0.34173150549586201</v>
+      </c>
+      <c r="W3">
+        <v>0.68852661479560295</v>
+      </c>
+      <c r="X3">
+        <v>0.132581607713184</v>
+      </c>
+      <c r="Y3">
+        <v>0.326925672129672</v>
+      </c>
+      <c r="Z3">
+        <v>4.01908697363242E-2</v>
+      </c>
+      <c r="AA3">
+        <v>0.25819067296339998</v>
+      </c>
+      <c r="AB3">
+        <v>8.6555800440793404E-2</v>
+      </c>
+      <c r="AC3">
+        <v>0.44082985737964703</v>
+      </c>
+      <c r="AD3">
+        <v>0.16477623582176801</v>
+      </c>
+      <c r="AE3">
+        <v>0.52593519451395798</v>
+      </c>
+      <c r="AF3">
+        <v>0.28904012083123498</v>
+      </c>
+      <c r="AG3">
+        <v>0.27978680925678301</v>
+      </c>
+      <c r="AH3">
+        <v>0.20964491448342201</v>
+      </c>
+      <c r="AI3">
+        <v>0.52822314565461603</v>
+      </c>
+      <c r="AJ3">
+        <v>0.218027636586549</v>
+      </c>
+      <c r="AK3">
+        <v>0.13473474496181401</v>
+      </c>
+      <c r="AL3">
+        <v>0.15169147100961899</v>
+      </c>
+      <c r="AM3">
+        <v>1.33621823923277E-2</v>
+      </c>
+      <c r="AN3">
+        <v>0.22900704872816399</v>
+      </c>
+      <c r="AO3">
+        <v>0.35110838696496</v>
+      </c>
+      <c r="AP3">
+        <v>0.33970363079615001</v>
+      </c>
+      <c r="AQ3">
+        <v>0.473507217847769</v>
+      </c>
+      <c r="AR3">
+        <v>0.71232550383534199</v>
+      </c>
+      <c r="AS3">
+        <v>0.51803325551479296</v>
+      </c>
+      <c r="AT3">
+        <v>0.20410306508731199</v>
+      </c>
+      <c r="AU3">
+        <v>0.53185981194285004</v>
+      </c>
+      <c r="AV3">
+        <v>0.26164732215382902</v>
+      </c>
+      <c r="AW3">
+        <v>0.28960811566995698</v>
+      </c>
+      <c r="AX3">
+        <v>0.36618513590572099</v>
+      </c>
+      <c r="AY3">
+        <v>0.50058924158905105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:51" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0.15178195530010399</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.30530285003020202</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.37045950383482101</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.41566766379523601</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0.108069164265129</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.118374890364615</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.19615831383310001</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0.26033231763775</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0.25801898023742298</v>
+      </c>
+      <c r="K4" s="3">
+        <v>0.35149154733154098</v>
+      </c>
+      <c r="L4" s="3">
+        <v>6.0388839108962401E-2</v>
+      </c>
+      <c r="M4" s="3">
+        <v>4.9990622851069998E-2</v>
+      </c>
+      <c r="N4" s="3">
+        <v>0.19373952700951799</v>
+      </c>
+      <c r="O4" s="3">
+        <v>0.16620311987147299</v>
+      </c>
+      <c r="P4" s="3">
+        <v>0.17664380853703401</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>0.46040272116262898</v>
+      </c>
+      <c r="R4" s="3">
+        <v>0.62544589774078396</v>
+      </c>
+      <c r="S4" s="3">
+        <v>0.92503070115592201</v>
+      </c>
+      <c r="T4" s="3">
+        <v>0.65381430779421501</v>
+      </c>
+      <c r="U4" s="3">
+        <v>0.38024398321925301</v>
+      </c>
+      <c r="V4" s="3">
+        <v>5.6131900703964399E-2</v>
+      </c>
+      <c r="W4" s="3">
+        <v>0.22852085134411901</v>
+      </c>
+      <c r="X4" s="3">
+        <v>0.42654930950203102</v>
+      </c>
+      <c r="Y4" s="3">
+        <v>0.44551738615405301</v>
+      </c>
+      <c r="Z4" s="3">
+        <v>0.16135379771743399</v>
+      </c>
+      <c r="AA4" s="3">
+        <v>0.13474025974025899</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>0.22689932788109499</v>
+      </c>
+      <c r="AC4" s="3">
+        <v>0.433489371778291</v>
+      </c>
+      <c r="AD4" s="3">
+        <v>0.15010237576781801</v>
+      </c>
+      <c r="AE4" s="3">
+        <v>0.163606227046702</v>
+      </c>
+      <c r="AF4" s="3">
+        <v>7.3175812919914499E-2</v>
+      </c>
+      <c r="AG4" s="3">
+        <v>0.35603548549504299</v>
+      </c>
+      <c r="AH4" s="3">
+        <v>7.6367462681243406E-2</v>
+      </c>
+      <c r="AI4" s="3">
+        <v>0.17344081610814799</v>
+      </c>
+      <c r="AJ4" s="3">
+        <v>0.42456131388725699</v>
+      </c>
+      <c r="AK4" s="3">
+        <v>0.64189931291665603</v>
+      </c>
+      <c r="AL4" s="3">
+        <v>0.78515248092161005</v>
+      </c>
+      <c r="AM4" s="3">
+        <v>0.96657992456360897</v>
+      </c>
+      <c r="AN4" s="3">
+        <v>7.8608642353662203E-2</v>
+      </c>
+      <c r="AO4" s="3">
+        <v>0.140770252324037</v>
+      </c>
+      <c r="AP4" s="3">
+        <v>0.33051727909011303</v>
+      </c>
+      <c r="AQ4" s="3">
+        <v>0.46855861767279</v>
+      </c>
+      <c r="AR4" s="3">
+        <v>7.3467054171232504E-2</v>
+      </c>
+      <c r="AS4" s="3">
+        <v>0.48196674448520599</v>
+      </c>
+      <c r="AT4" s="3">
+        <v>6.8042496031261404E-2</v>
+      </c>
+      <c r="AU4" s="3">
+        <v>0.33659787519843598</v>
+      </c>
+      <c r="AV4" s="3">
+        <v>3.9621653820466E-2</v>
+      </c>
+      <c r="AW4" s="3">
+        <v>0.55623747721077998</v>
+      </c>
+      <c r="AX4" s="3">
+        <v>8.2455806880821103E-2</v>
+      </c>
+      <c r="AY4" s="6">
+        <v>0.27099410758410902</v>
+      </c>
+    </row>
+    <row r="7" spans="1:51" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.15178195530010399</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.30530285003020202</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.37045950383482101</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.41566766379523601</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.108069164265129</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.118374890364615</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.19615831383310001</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0.26033231763775</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0.25801898023742298</v>
+      </c>
+      <c r="K7" s="3">
+        <v>0.35149154733154098</v>
+      </c>
+      <c r="L7" s="3">
+        <v>6.0388839108962401E-2</v>
+      </c>
+      <c r="M7" s="3">
+        <v>4.9990622851069998E-2</v>
+      </c>
+      <c r="N7" s="3">
+        <v>0.19373952700951799</v>
+      </c>
+      <c r="O7" s="3">
+        <v>0.16620311987147299</v>
+      </c>
+      <c r="P7" s="3">
+        <v>0.17664380853703401</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>0.46040272116262898</v>
+      </c>
+      <c r="R7" s="3">
+        <v>0.62544589774078396</v>
+      </c>
+      <c r="S7" s="3">
+        <v>0.92503070115592201</v>
+      </c>
+      <c r="T7" s="3">
+        <v>0.65381430779421501</v>
+      </c>
+      <c r="U7" s="3">
+        <v>0.38024398321925301</v>
+      </c>
+      <c r="V7" s="3">
+        <v>5.6131900703964399E-2</v>
+      </c>
+      <c r="W7" s="3">
+        <v>0.22852085134411901</v>
+      </c>
+      <c r="X7" s="3">
+        <v>0.42654930950203102</v>
+      </c>
+      <c r="Y7" s="3">
+        <v>0.44551738615405301</v>
+      </c>
+      <c r="Z7" s="3">
+        <v>0.16135379771743399</v>
+      </c>
+      <c r="AA7" s="3">
+        <v>0.13474025974025899</v>
+      </c>
+      <c r="AB7" s="3">
+        <v>0.22689932788109499</v>
+      </c>
+      <c r="AC7" s="3">
+        <v>0.433489371778291</v>
+      </c>
+      <c r="AD7" s="3">
+        <v>0.15010237576781801</v>
+      </c>
+      <c r="AE7" s="3">
+        <v>0.163606227046702</v>
+      </c>
+      <c r="AF7" s="3">
+        <v>7.3175812919914499E-2</v>
+      </c>
+      <c r="AG7" s="3">
+        <v>0.35603548549504299</v>
+      </c>
+      <c r="AH7" s="3">
+        <v>7.6367462681243406E-2</v>
+      </c>
+      <c r="AI7" s="3">
+        <v>0.17344081610814799</v>
+      </c>
+      <c r="AJ7" s="3">
+        <v>0.42456131388725699</v>
+      </c>
+      <c r="AK7" s="3">
+        <v>0.64189931291665603</v>
+      </c>
+      <c r="AL7" s="3">
+        <v>0.78515248092161005</v>
+      </c>
+      <c r="AM7" s="3">
+        <v>0.96657992456360897</v>
+      </c>
+      <c r="AN7" s="3">
+        <v>7.8608642353662203E-2</v>
+      </c>
+      <c r="AO7" s="3">
+        <v>0.140770252324037</v>
+      </c>
+      <c r="AP7" s="3">
+        <v>0.33051727909011303</v>
+      </c>
+      <c r="AQ7" s="3">
+        <v>0.46855861767279</v>
+      </c>
+      <c r="AR7" s="3">
+        <v>7.3467054171232504E-2</v>
+      </c>
+      <c r="AS7" s="3">
+        <v>0.48196674448520599</v>
+      </c>
+      <c r="AT7" s="3">
+        <v>6.8042496031261404E-2</v>
+      </c>
+      <c r="AU7" s="3">
+        <v>0.33659787519843598</v>
+      </c>
+      <c r="AV7" s="3">
+        <v>3.9621653820466E-2</v>
+      </c>
+      <c r="AW7" s="3">
+        <v>0.55623747721077998</v>
+      </c>
+      <c r="AX7" s="3">
+        <v>8.2455806880821103E-2</v>
+      </c>
+      <c r="AY7" s="6">
+        <v>0.27099410758410902</v>
+      </c>
+    </row>
+    <row r="8" spans="1:51" x14ac:dyDescent="0.35">
+      <c r="A8" s="4"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+      <c r="Y8" s="2"/>
+      <c r="Z8" s="2"/>
+      <c r="AA8" s="2"/>
+      <c r="AB8" s="2"/>
+      <c r="AC8" s="2"/>
+      <c r="AD8" s="2"/>
+      <c r="AE8" s="2"/>
+      <c r="AF8" s="2"/>
+      <c r="AG8" s="2"/>
+      <c r="AH8" s="2"/>
+      <c r="AI8" s="2"/>
+      <c r="AJ8" s="2"/>
+      <c r="AK8" s="2"/>
+      <c r="AL8" s="2"/>
+      <c r="AM8" s="2"/>
+      <c r="AN8" s="2"/>
+      <c r="AO8" s="2"/>
+      <c r="AP8" s="2"/>
+      <c r="AQ8" s="2"/>
+      <c r="AR8" s="2"/>
+      <c r="AS8" s="2"/>
+      <c r="AT8" s="2"/>
+      <c r="AU8" s="2"/>
+      <c r="AV8" s="2"/>
+      <c r="AW8" s="2"/>
+      <c r="AX8" s="2"/>
+      <c r="AY8" s="5"/>
+    </row>
+    <row r="9" spans="1:51" x14ac:dyDescent="0.35">
+      <c r="A9" s="4"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="2"/>
+      <c r="Z9" s="2"/>
+      <c r="AA9" s="2"/>
+      <c r="AB9" s="2"/>
+      <c r="AC9" s="2"/>
+      <c r="AD9" s="2"/>
+      <c r="AE9" s="2"/>
+      <c r="AF9" s="2"/>
+      <c r="AG9" s="2"/>
+      <c r="AH9" s="2"/>
+      <c r="AI9" s="2"/>
+      <c r="AJ9" s="2"/>
+      <c r="AK9" s="2"/>
+      <c r="AL9" s="2"/>
+      <c r="AM9" s="2"/>
+      <c r="AN9" s="2"/>
+      <c r="AO9" s="2"/>
+      <c r="AP9" s="2"/>
+      <c r="AQ9" s="2"/>
+      <c r="AR9" s="2"/>
+      <c r="AS9" s="2"/>
+      <c r="AT9" s="2"/>
+      <c r="AU9" s="2"/>
+      <c r="AV9" s="2"/>
+      <c r="AW9" s="2"/>
+      <c r="AX9" s="2"/>
+      <c r="AY9" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/data/annotations/TE_discrete_percentages.xlsx
+++ b/data/annotations/TE_discrete_percentages.xlsx
@@ -8,21 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dobregeo\Documents\GitHub\vilearn_ml\data\annotations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{C9FCEF07-616C-433A-A7E2-D45A8732D095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{BF42F981-D633-42A3-9A31-78C18F46FEC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{8450E3AB-A0C1-455F-AE9B-DBE7A60F6C99}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="4" xr2:uid="{8450E3AB-A0C1-455F-AE9B-DBE7A60F6C99}"/>
   </bookViews>
   <sheets>
     <sheet name="TE_discrete_percentages" sheetId="1" r:id="rId1"/>
     <sheet name="TE_discrete_.1" sheetId="2" r:id="rId2"/>
-    <sheet name="TE_discrete_twobins" sheetId="3" r:id="rId3"/>
+    <sheet name="TE_discrete_twobinsV1" sheetId="3" r:id="rId3"/>
+    <sheet name="interraterReliability windV1" sheetId="5" r:id="rId4"/>
+    <sheet name="TE_discrete_twobinsV2" sheetId="6" r:id="rId5"/>
+    <sheet name="interraterReliability windV2" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="99">
   <si>
     <t>task_eng</t>
   </si>
@@ -243,7 +246,82 @@
     <t>Laura</t>
   </si>
   <si>
-    <t>lo</t>
+    <t>dyad_02_interrater_relia</t>
+  </si>
+  <si>
+    <t>dyad_03_interrater_relia</t>
+  </si>
+  <si>
+    <t>dyad_04_interrater_relia</t>
+  </si>
+  <si>
+    <t>dyad_05_interrater_relia</t>
+  </si>
+  <si>
+    <t>dyad_06_interrater_relia</t>
+  </si>
+  <si>
+    <t>dyad_07_interrater_relia</t>
+  </si>
+  <si>
+    <t>dyad_10_interrater_relia</t>
+  </si>
+  <si>
+    <t>dyad_11_interrater_relia</t>
+  </si>
+  <si>
+    <t>triad_01_interrater_relia</t>
+  </si>
+  <si>
+    <t>triad_02_interrater_relia</t>
+  </si>
+  <si>
+    <t>triad_05_interrater_relia</t>
+  </si>
+  <si>
+    <t>triad_06_interrater_relia</t>
+  </si>
+  <si>
+    <t>triad_07_interrater_relia</t>
+  </si>
+  <si>
+    <t>triad_08_interrater_relia</t>
+  </si>
+  <si>
+    <t>triad_09_interrater_relia</t>
+  </si>
+  <si>
+    <t>triad_10_interrater_relia</t>
+  </si>
+  <si>
+    <t>triad_11_interrater_relia</t>
+  </si>
+  <si>
+    <t>triad_12_interrater_relia</t>
+  </si>
+  <si>
+    <t>triad_13_interrater_relia</t>
+  </si>
+  <si>
+    <t>triad_14_interrater_relia</t>
+  </si>
+  <si>
+    <t>continuous</t>
+  </si>
+  <si>
+    <t>discrete</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>AVG all</t>
+  </si>
+  <si>
+    <t>triads</t>
+  </si>
+  <si>
+    <t>dyads</t>
   </si>
 </sst>
 </file>
@@ -386,7 +464,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -566,14 +644,8 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor theme="0" tint="-0.14999847407452621"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -700,19 +772,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color theme="1"/>
@@ -770,14 +829,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -4898,11 +4956,375 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>TE_discrete_twobins!$A$2</c:f>
+              <c:f>TE_discrete_twobinsV1!$A$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>high</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobinsV1!$B$1:$AY$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobinsV1!$D$1,TE_discrete_twobinsV1!$F$1,TE_discrete_twobinsV1!$H$1,TE_discrete_twobinsV1!$J$1,TE_discrete_twobinsV1!$L$1,TE_discrete_twobinsV1!$N$1,TE_discrete_twobinsV1!$T$1,TE_discrete_twobinsV1!$V$1,TE_discrete_twobinsV1!$X$1,TE_discrete_twobinsV1!$Z$1,TE_discrete_twobinsV1!$AF$1,TE_discrete_twobinsV1!$AH$1,TE_discrete_twobinsV1!$AJ$1,TE_discrete_twobinsV1!$AL$1,TE_discrete_twobinsV1!$AN$1,TE_discrete_twobinsV1!$AP$1,TE_discrete_twobinsV1!$AR$1,TE_discrete_twobinsV1!$AT$1,TE_discrete_twobinsV1!$AV$1,TE_discrete_twobinsV1!$AX$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>dyad_02_anno01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>dyad_03_anno01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>dyad_04_anno01</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>dyad_05_anno01</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>dyad_06_anno01</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>dyad_07_anno01</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>dyad_10_anno01</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>dyad_11_anno01</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>triad_01_anno01</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>triad_02_anno01</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>triad_05_anno01</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>triad_06_anno01</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>triad_07_anno01</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>triad_08_anno01</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>triad_09_anno01</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>triad_10_anno01</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>triad_11_anno01</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>triad_12_anno01</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>triad_13_anno01</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>triad_14_anno01</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobinsV1!$B$2:$AY$2</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobinsV1!$D$2,TE_discrete_twobinsV1!$F$2,TE_discrete_twobinsV1!$H$2,TE_discrete_twobinsV1!$J$2,TE_discrete_twobinsV1!$L$2,TE_discrete_twobinsV1!$N$2,TE_discrete_twobinsV1!$T$2,TE_discrete_twobinsV1!$V$2,TE_discrete_twobinsV1!$X$2,TE_discrete_twobinsV1!$Z$2,TE_discrete_twobinsV1!$AF$2,TE_discrete_twobinsV1!$AH$2,TE_discrete_twobinsV1!$AJ$2,TE_discrete_twobinsV1!$AL$2,TE_discrete_twobinsV1!$AN$2,TE_discrete_twobinsV1!$AP$2,TE_discrete_twobinsV1!$AR$2,TE_discrete_twobinsV1!$AT$2,TE_discrete_twobinsV1!$AV$2,TE_discrete_twobinsV1!$AX$2)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.47961134477407102</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.74818318506452797</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.66684062557869395</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.43899452362325198</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.92854612515368096</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.695354742861091</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.116140428350629</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.60213659380017204</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.43328185212397402</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.79845533254624101</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.63778406624884898</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.71398762283533301</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.35741104952619301</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.3156048068769899E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.69235877004801305</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.32977909011373502</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.21420744199342501</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.72785443888142598</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.69873102402570397</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.55135905721345702</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-77AB-4F5E-BAC3-912E0FB8E4E3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>TE_discrete_twobinsV1!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>mid</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobinsV1!$B$1:$AY$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobinsV1!$D$1,TE_discrete_twobinsV1!$F$1,TE_discrete_twobinsV1!$H$1,TE_discrete_twobinsV1!$J$1,TE_discrete_twobinsV1!$L$1,TE_discrete_twobinsV1!$N$1,TE_discrete_twobinsV1!$T$1,TE_discrete_twobinsV1!$V$1,TE_discrete_twobinsV1!$X$1,TE_discrete_twobinsV1!$Z$1,TE_discrete_twobinsV1!$AF$1,TE_discrete_twobinsV1!$AH$1,TE_discrete_twobinsV1!$AJ$1,TE_discrete_twobinsV1!$AL$1,TE_discrete_twobinsV1!$AN$1,TE_discrete_twobinsV1!$AP$1,TE_discrete_twobinsV1!$AR$1,TE_discrete_twobinsV1!$AT$1,TE_discrete_twobinsV1!$AV$1,TE_discrete_twobinsV1!$AX$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>dyad_02_anno01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>dyad_03_anno01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>dyad_04_anno01</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>dyad_05_anno01</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>dyad_06_anno01</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>dyad_07_anno01</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>dyad_10_anno01</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>dyad_11_anno01</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>triad_01_anno01</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>triad_02_anno01</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>triad_05_anno01</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>triad_06_anno01</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>triad_07_anno01</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>triad_08_anno01</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>triad_09_anno01</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>triad_10_anno01</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>triad_11_anno01</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>triad_12_anno01</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>triad_13_anno01</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>triad_14_anno01</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobinsV1!$B$3:$AY$3</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobinsV1!$D$3,TE_discrete_twobinsV1!$F$3,TE_discrete_twobinsV1!$H$3,TE_discrete_twobinsV1!$J$3,TE_discrete_twobinsV1!$L$3,TE_discrete_twobinsV1!$N$3,TE_discrete_twobinsV1!$T$3,TE_discrete_twobinsV1!$V$3,TE_discrete_twobinsV1!$X$3,TE_discrete_twobinsV1!$Z$3,TE_discrete_twobinsV1!$AF$3,TE_discrete_twobinsV1!$AH$3,TE_discrete_twobinsV1!$AJ$3,TE_discrete_twobinsV1!$AL$3,TE_discrete_twobinsV1!$AN$3,TE_discrete_twobinsV1!$AP$3,TE_discrete_twobinsV1!$AR$3,TE_discrete_twobinsV1!$AT$3,TE_discrete_twobinsV1!$AV$3,TE_discrete_twobinsV1!$AX$3)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.14992915139110599</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.143731988472622</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.13700106058820499</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.30067349229565599</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1044197628623201E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.110888455093544</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.22885846765290299</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.34173150549586201</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.132581607713184</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.01908697363242E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.28904012083123498</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.20964491448342201</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.218027636586549</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.15169147100961899</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.22900704872816399</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.33970363079615001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.71232550383534199</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.20410306508731199</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.26164732215382902</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.36618513590572099</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-77AB-4F5E-BAC3-912E0FB8E4E3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>TE_discrete_twobinsV1!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>low</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4922,11 +5344,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>TE_discrete_twobins!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_twobinsV1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(TE_discrete_twobins!$D$1,TE_discrete_twobins!$F$1,TE_discrete_twobins!$H$1,TE_discrete_twobins!$J$1,TE_discrete_twobins!$L$1,TE_discrete_twobins!$N$1,TE_discrete_twobins!$T$1,TE_discrete_twobins!$V$1,TE_discrete_twobins!$X$1,TE_discrete_twobins!$Z$1,TE_discrete_twobins!$AF$1,TE_discrete_twobins!$AH$1,TE_discrete_twobins!$AJ$1,TE_discrete_twobins!$AL$1,TE_discrete_twobins!$AN$1,TE_discrete_twobins!$AP$1,TE_discrete_twobins!$AR$1,TE_discrete_twobins!$AT$1,TE_discrete_twobins!$AV$1,TE_discrete_twobins!$AX$1)</c:f>
+              <c:f>(TE_discrete_twobinsV1!$D$1,TE_discrete_twobinsV1!$F$1,TE_discrete_twobinsV1!$H$1,TE_discrete_twobinsV1!$J$1,TE_discrete_twobinsV1!$L$1,TE_discrete_twobinsV1!$N$1,TE_discrete_twobinsV1!$T$1,TE_discrete_twobinsV1!$V$1,TE_discrete_twobinsV1!$X$1,TE_discrete_twobinsV1!$Z$1,TE_discrete_twobinsV1!$AF$1,TE_discrete_twobinsV1!$AH$1,TE_discrete_twobinsV1!$AJ$1,TE_discrete_twobinsV1!$AL$1,TE_discrete_twobinsV1!$AN$1,TE_discrete_twobinsV1!$AP$1,TE_discrete_twobinsV1!$AR$1,TE_discrete_twobinsV1!$AT$1,TE_discrete_twobinsV1!$AV$1,TE_discrete_twobinsV1!$AX$1)</c:f>
               <c:strCache>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
@@ -4997,373 +5419,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>TE_discrete_twobins!$B$2:$AY$2</c15:sqref>
+                    <c15:sqref>TE_discrete_twobinsV1!$B$4:$AY$4</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(TE_discrete_twobins!$D$2,TE_discrete_twobins!$F$2,TE_discrete_twobins!$H$2,TE_discrete_twobins!$J$2,TE_discrete_twobins!$L$2,TE_discrete_twobins!$N$2,TE_discrete_twobins!$T$2,TE_discrete_twobins!$V$2,TE_discrete_twobins!$X$2,TE_discrete_twobins!$Z$2,TE_discrete_twobins!$AF$2,TE_discrete_twobins!$AH$2,TE_discrete_twobins!$AJ$2,TE_discrete_twobins!$AL$2,TE_discrete_twobins!$AN$2,TE_discrete_twobins!$AP$2,TE_discrete_twobins!$AR$2,TE_discrete_twobins!$AT$2,TE_discrete_twobins!$AV$2,TE_discrete_twobins!$AX$2)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
-                <c:pt idx="0">
-                  <c:v>0.47961134477407102</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.74818318506452797</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.66684062557869395</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.43899452362325198</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.92854612515368096</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.695354742861091</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.116140428350629</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.60213659380017204</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.43328185212397402</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.79845533254624101</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.63778406624884898</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.71398762283533301</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.35741104952619301</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>6.3156048068769899E-2</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.69235877004801305</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.32977909011373502</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.21420744199342501</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.72785443888142598</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.69873102402570397</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.55135905721345702</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-77AB-4F5E-BAC3-912E0FB8E4E3}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>TE_discrete_twobins!$A$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>mid</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>TE_discrete_twobins!$B$1:$AY$1</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(TE_discrete_twobins!$D$1,TE_discrete_twobins!$F$1,TE_discrete_twobins!$H$1,TE_discrete_twobins!$J$1,TE_discrete_twobins!$L$1,TE_discrete_twobins!$N$1,TE_discrete_twobins!$T$1,TE_discrete_twobins!$V$1,TE_discrete_twobins!$X$1,TE_discrete_twobins!$Z$1,TE_discrete_twobins!$AF$1,TE_discrete_twobins!$AH$1,TE_discrete_twobins!$AJ$1,TE_discrete_twobins!$AL$1,TE_discrete_twobins!$AN$1,TE_discrete_twobins!$AP$1,TE_discrete_twobins!$AR$1,TE_discrete_twobins!$AT$1,TE_discrete_twobins!$AV$1,TE_discrete_twobins!$AX$1)</c:f>
-              <c:strCache>
-                <c:ptCount val="20"/>
-                <c:pt idx="0">
-                  <c:v>dyad_02_anno01</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>dyad_03_anno01</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>dyad_04_anno01</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>dyad_05_anno01</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>dyad_06_anno01</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>dyad_07_anno01</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>dyad_10_anno01</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>dyad_11_anno01</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>triad_01_anno01</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>triad_02_anno01</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>triad_05_anno01</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>triad_06_anno01</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>triad_07_anno01</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>triad_08_anno01</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>triad_09_anno01</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>triad_10_anno01</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>triad_11_anno01</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>triad_12_anno01</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>triad_13_anno01</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>triad_14_anno01</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>TE_discrete_twobins!$B$3:$AY$3</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(TE_discrete_twobins!$D$3,TE_discrete_twobins!$F$3,TE_discrete_twobins!$H$3,TE_discrete_twobins!$J$3,TE_discrete_twobins!$L$3,TE_discrete_twobins!$N$3,TE_discrete_twobins!$T$3,TE_discrete_twobins!$V$3,TE_discrete_twobins!$X$3,TE_discrete_twobins!$Z$3,TE_discrete_twobins!$AF$3,TE_discrete_twobins!$AH$3,TE_discrete_twobins!$AJ$3,TE_discrete_twobins!$AL$3,TE_discrete_twobins!$AN$3,TE_discrete_twobins!$AP$3,TE_discrete_twobins!$AR$3,TE_discrete_twobins!$AT$3,TE_discrete_twobins!$AV$3,TE_discrete_twobins!$AX$3)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
-                <c:pt idx="0">
-                  <c:v>0.14992915139110599</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.143731988472622</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.13700106058820499</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.30067349229565599</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.1044197628623201E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.110888455093544</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.22885846765290299</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.34173150549586201</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.132581607713184</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>4.01908697363242E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.28904012083123498</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.20964491448342201</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.218027636586549</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.15169147100961899</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.22900704872816399</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.33970363079615001</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.71232550383534199</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.20410306508731199</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.26164732215382902</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.36618513590572099</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-77AB-4F5E-BAC3-912E0FB8E4E3}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>TE_discrete_twobins!$A$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>low</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>TE_discrete_twobins!$B$1:$AY$1</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(TE_discrete_twobins!$D$1,TE_discrete_twobins!$F$1,TE_discrete_twobins!$H$1,TE_discrete_twobins!$J$1,TE_discrete_twobins!$L$1,TE_discrete_twobins!$N$1,TE_discrete_twobins!$T$1,TE_discrete_twobins!$V$1,TE_discrete_twobins!$X$1,TE_discrete_twobins!$Z$1,TE_discrete_twobins!$AF$1,TE_discrete_twobins!$AH$1,TE_discrete_twobins!$AJ$1,TE_discrete_twobins!$AL$1,TE_discrete_twobins!$AN$1,TE_discrete_twobins!$AP$1,TE_discrete_twobins!$AR$1,TE_discrete_twobins!$AT$1,TE_discrete_twobins!$AV$1,TE_discrete_twobins!$AX$1)</c:f>
-              <c:strCache>
-                <c:ptCount val="20"/>
-                <c:pt idx="0">
-                  <c:v>dyad_02_anno01</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>dyad_03_anno01</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>dyad_04_anno01</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>dyad_05_anno01</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>dyad_06_anno01</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>dyad_07_anno01</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>dyad_10_anno01</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>dyad_11_anno01</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>triad_01_anno01</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>triad_02_anno01</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>triad_05_anno01</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>triad_06_anno01</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>triad_07_anno01</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>triad_08_anno01</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>triad_09_anno01</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>triad_10_anno01</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>triad_11_anno01</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>triad_12_anno01</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>triad_13_anno01</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>triad_14_anno01</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>TE_discrete_twobins!$B$4:$AY$4</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(TE_discrete_twobins!$D$4,TE_discrete_twobins!$F$4,TE_discrete_twobins!$H$4,TE_discrete_twobins!$J$4,TE_discrete_twobins!$L$4,TE_discrete_twobins!$N$4,TE_discrete_twobins!$T$4,TE_discrete_twobins!$V$4,TE_discrete_twobins!$X$4,TE_discrete_twobins!$Z$4,TE_discrete_twobins!$AF$4,TE_discrete_twobins!$AH$4,TE_discrete_twobins!$AJ$4,TE_discrete_twobins!$AL$4,TE_discrete_twobins!$AN$4,TE_discrete_twobins!$AP$4,TE_discrete_twobins!$AR$4,TE_discrete_twobins!$AT$4,TE_discrete_twobins!$AV$4,TE_discrete_twobins!$AX$4)</c:f>
+              <c:f>(TE_discrete_twobinsV1!$D$4,TE_discrete_twobinsV1!$F$4,TE_discrete_twobinsV1!$H$4,TE_discrete_twobinsV1!$J$4,TE_discrete_twobinsV1!$L$4,TE_discrete_twobinsV1!$N$4,TE_discrete_twobinsV1!$T$4,TE_discrete_twobinsV1!$V$4,TE_discrete_twobinsV1!$X$4,TE_discrete_twobinsV1!$Z$4,TE_discrete_twobinsV1!$AF$4,TE_discrete_twobinsV1!$AH$4,TE_discrete_twobinsV1!$AJ$4,TE_discrete_twobinsV1!$AL$4,TE_discrete_twobinsV1!$AN$4,TE_discrete_twobinsV1!$AP$4,TE_discrete_twobinsV1!$AR$4,TE_discrete_twobinsV1!$AT$4,TE_discrete_twobinsV1!$AV$4,TE_discrete_twobinsV1!$AX$4)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -5671,7 +5731,7 @@
             </a:r>
             <a:r>
               <a:rPr lang="en-GB" baseline="0"/>
-              <a:t> Ann</a:t>
+              <a:t> Ann (.25, .5, 1)</a:t>
             </a:r>
             <a:endParaRPr lang="en-GB"/>
           </a:p>
@@ -5718,11 +5778,375 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>TE_discrete_twobins!$A$2</c:f>
+              <c:f>TE_discrete_twobinsV1!$A$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>high</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobinsV1!$B$1:$AY$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobinsV1!$E$1,TE_discrete_twobinsV1!$G$1,TE_discrete_twobinsV1!$I$1,TE_discrete_twobinsV1!$K$1,TE_discrete_twobinsV1!$M$1,TE_discrete_twobinsV1!$O$1,TE_discrete_twobinsV1!$U$1,TE_discrete_twobinsV1!$W$1,TE_discrete_twobinsV1!$Y$1,TE_discrete_twobinsV1!$AA$1,TE_discrete_twobinsV1!$AG$1,TE_discrete_twobinsV1!$AI$1,TE_discrete_twobinsV1!$AK$1,TE_discrete_twobinsV1!$AM$1,TE_discrete_twobinsV1!$AO$1,TE_discrete_twobinsV1!$AQ$1,TE_discrete_twobinsV1!$AS$1,TE_discrete_twobinsV1!$AU$1,TE_discrete_twobinsV1!$AW$1,TE_discrete_twobinsV1!$AY$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>dyad_02_anno02</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>dyad_03_anno02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>dyad_04_anno02</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>dyad_05_anno02</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>dyad_06_anno02</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>dyad_07_anno02</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>dyad_10_anno02</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>dyad_11_anno02</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>triad_01_anno02</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>triad_02_anno02</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>triad_05_anno02</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>triad_06_anno02</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>triad_07_anno02</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>triad_08_anno02</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>triad_09_anno02</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>triad_10_anno02</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>triad_11_anno02</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>triad_12_anno02</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>triad_13_anno02</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>triad_14_anno02</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobinsV1!$B$2:$AY$2</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobinsV1!$E$2,TE_discrete_twobinsV1!$G$2,TE_discrete_twobinsV1!$I$2,TE_discrete_twobinsV1!$K$2,TE_discrete_twobinsV1!$M$2,TE_discrete_twobinsV1!$O$2,TE_discrete_twobinsV1!$U$2,TE_discrete_twobinsV1!$W$2,TE_discrete_twobinsV1!$Y$2,TE_discrete_twobinsV1!$AA$2,TE_discrete_twobinsV1!$AG$2,TE_discrete_twobinsV1!$AI$2,TE_discrete_twobinsV1!$AK$2,TE_discrete_twobinsV1!$AM$2,TE_discrete_twobinsV1!$AO$2,TE_discrete_twobinsV1!$AQ$2,TE_discrete_twobinsV1!$AS$2,TE_discrete_twobinsV1!$AU$2,TE_discrete_twobinsV1!$AW$2,TE_discrete_twobinsV1!$AY$2)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.241717460246058</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.48646786117027901</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.52275214221982702</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.35996122317085599</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.826293525599616</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.56917788104410305</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.9939280194303301E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.1466798402700593E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.212697365461606</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.60706906729634003</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.68918942379472E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.28492447076028599</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7.0496283619830902E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.50807028297068102</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.6438101487314E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.12382464281353001</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.14697016191628001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.21199391750617699</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C46B-4A5C-B8EA-04111DA8B0FC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>TE_discrete_twobinsV1!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>mid</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobinsV1!$B$1:$AY$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobinsV1!$E$1,TE_discrete_twobinsV1!$G$1,TE_discrete_twobinsV1!$I$1,TE_discrete_twobinsV1!$K$1,TE_discrete_twobinsV1!$M$1,TE_discrete_twobinsV1!$O$1,TE_discrete_twobinsV1!$U$1,TE_discrete_twobinsV1!$W$1,TE_discrete_twobinsV1!$Y$1,TE_discrete_twobinsV1!$AA$1,TE_discrete_twobinsV1!$AG$1,TE_discrete_twobinsV1!$AI$1,TE_discrete_twobinsV1!$AK$1,TE_discrete_twobinsV1!$AM$1,TE_discrete_twobinsV1!$AO$1,TE_discrete_twobinsV1!$AQ$1,TE_discrete_twobinsV1!$AS$1,TE_discrete_twobinsV1!$AU$1,TE_discrete_twobinsV1!$AW$1,TE_discrete_twobinsV1!$AY$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>dyad_02_anno02</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>dyad_03_anno02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>dyad_04_anno02</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>dyad_05_anno02</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>dyad_06_anno02</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>dyad_07_anno02</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>dyad_10_anno02</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>dyad_11_anno02</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>triad_01_anno02</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>triad_02_anno02</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>triad_05_anno02</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>triad_06_anno02</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>triad_07_anno02</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>triad_08_anno02</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>triad_09_anno02</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>triad_10_anno02</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>triad_11_anno02</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>triad_12_anno02</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>triad_13_anno02</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>triad_14_anno02</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobinsV1!$B$3:$AY$3</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobinsV1!$E$3,TE_discrete_twobinsV1!$G$3,TE_discrete_twobinsV1!$I$3,TE_discrete_twobinsV1!$K$3,TE_discrete_twobinsV1!$M$3,TE_discrete_twobinsV1!$O$3,TE_discrete_twobinsV1!$U$3,TE_discrete_twobinsV1!$W$3,TE_discrete_twobinsV1!$Y$3,TE_discrete_twobinsV1!$AA$3,TE_discrete_twobinsV1!$AG$3,TE_discrete_twobinsV1!$AI$3,TE_discrete_twobinsV1!$AK$3,TE_discrete_twobinsV1!$AM$3,TE_discrete_twobinsV1!$AO$3,TE_discrete_twobinsV1!$AQ$3,TE_discrete_twobinsV1!$AS$3,TE_discrete_twobinsV1!$AU$3,TE_discrete_twobinsV1!$AW$3,TE_discrete_twobinsV1!$AY$3)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.24365173972695101</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.39512592406966501</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.21691554014242101</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.28138712201095201</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.123424118027047</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.255929656054036</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.22656767498343999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.68852661479560295</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.326925672129672</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.25819067296339998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.27978680925678301</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.52822314565461603</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.13473474496181401</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.33621823923277E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.35110838696496</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.473507217847769</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.51803325551479296</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.53185981194285004</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.28960811566995698</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.50058924158905105</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C46B-4A5C-B8EA-04111DA8B0FC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>TE_discrete_twobinsV1!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>low</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5742,11 +6166,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>TE_discrete_twobins!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_twobinsV1!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(TE_discrete_twobins!$E$1,TE_discrete_twobins!$G$1,TE_discrete_twobins!$I$1,TE_discrete_twobins!$K$1,TE_discrete_twobins!$M$1,TE_discrete_twobins!$O$1,TE_discrete_twobins!$U$1,TE_discrete_twobins!$W$1,TE_discrete_twobins!$Y$1,TE_discrete_twobins!$AA$1,TE_discrete_twobins!$AG$1,TE_discrete_twobins!$AI$1,TE_discrete_twobins!$AK$1,TE_discrete_twobins!$AM$1,TE_discrete_twobins!$AO$1,TE_discrete_twobins!$AQ$1,TE_discrete_twobins!$AS$1,TE_discrete_twobins!$AU$1,TE_discrete_twobins!$AW$1,TE_discrete_twobins!$AY$1)</c:f>
+              <c:f>(TE_discrete_twobinsV1!$E$1,TE_discrete_twobinsV1!$G$1,TE_discrete_twobinsV1!$I$1,TE_discrete_twobinsV1!$K$1,TE_discrete_twobinsV1!$M$1,TE_discrete_twobinsV1!$O$1,TE_discrete_twobinsV1!$U$1,TE_discrete_twobinsV1!$W$1,TE_discrete_twobinsV1!$Y$1,TE_discrete_twobinsV1!$AA$1,TE_discrete_twobinsV1!$AG$1,TE_discrete_twobinsV1!$AI$1,TE_discrete_twobinsV1!$AK$1,TE_discrete_twobinsV1!$AM$1,TE_discrete_twobinsV1!$AO$1,TE_discrete_twobinsV1!$AQ$1,TE_discrete_twobinsV1!$AS$1,TE_discrete_twobinsV1!$AU$1,TE_discrete_twobinsV1!$AW$1,TE_discrete_twobinsV1!$AY$1)</c:f>
               <c:strCache>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
@@ -5817,373 +6241,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>TE_discrete_twobins!$B$2:$AY$2</c15:sqref>
+                    <c15:sqref>TE_discrete_twobinsV1!$B$4:$AY$4</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(TE_discrete_twobins!$E$2,TE_discrete_twobins!$G$2,TE_discrete_twobins!$I$2,TE_discrete_twobins!$K$2,TE_discrete_twobins!$M$2,TE_discrete_twobins!$O$2,TE_discrete_twobins!$U$2,TE_discrete_twobins!$W$2,TE_discrete_twobins!$Y$2,TE_discrete_twobins!$AA$2,TE_discrete_twobins!$AG$2,TE_discrete_twobins!$AI$2,TE_discrete_twobins!$AK$2,TE_discrete_twobins!$AM$2,TE_discrete_twobins!$AO$2,TE_discrete_twobins!$AQ$2,TE_discrete_twobins!$AS$2,TE_discrete_twobins!$AU$2,TE_discrete_twobins!$AW$2,TE_discrete_twobins!$AY$2)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
-                <c:pt idx="0">
-                  <c:v>0.241717460246058</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.48646786117027901</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.52275214221982702</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.35996122317085599</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.826293525599616</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.56917788104410305</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>9.9939280194303301E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>7.1466798402700593E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.212697365461606</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.60706906729634003</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2.68918942379472E-2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.28492447076028599</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>7.0496283619830902E-2</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.50807028297068102</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2.6438101487314E-2</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.12382464281353001</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.14697016191628001</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.21199391750617699</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C46B-4A5C-B8EA-04111DA8B0FC}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>TE_discrete_twobins!$A$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>mid</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>TE_discrete_twobins!$B$1:$AY$1</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(TE_discrete_twobins!$E$1,TE_discrete_twobins!$G$1,TE_discrete_twobins!$I$1,TE_discrete_twobins!$K$1,TE_discrete_twobins!$M$1,TE_discrete_twobins!$O$1,TE_discrete_twobins!$U$1,TE_discrete_twobins!$W$1,TE_discrete_twobins!$Y$1,TE_discrete_twobins!$AA$1,TE_discrete_twobins!$AG$1,TE_discrete_twobins!$AI$1,TE_discrete_twobins!$AK$1,TE_discrete_twobins!$AM$1,TE_discrete_twobins!$AO$1,TE_discrete_twobins!$AQ$1,TE_discrete_twobins!$AS$1,TE_discrete_twobins!$AU$1,TE_discrete_twobins!$AW$1,TE_discrete_twobins!$AY$1)</c:f>
-              <c:strCache>
-                <c:ptCount val="20"/>
-                <c:pt idx="0">
-                  <c:v>dyad_02_anno02</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>dyad_03_anno02</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>dyad_04_anno02</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>dyad_05_anno02</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>dyad_06_anno02</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>dyad_07_anno02</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>dyad_10_anno02</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>dyad_11_anno02</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>triad_01_anno02</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>triad_02_anno02</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>triad_05_anno02</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>triad_06_anno02</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>triad_07_anno02</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>triad_08_anno02</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>triad_09_anno02</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>triad_10_anno02</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>triad_11_anno02</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>triad_12_anno02</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>triad_13_anno02</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>triad_14_anno02</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>TE_discrete_twobins!$B$3:$AY$3</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(TE_discrete_twobins!$E$3,TE_discrete_twobins!$G$3,TE_discrete_twobins!$I$3,TE_discrete_twobins!$K$3,TE_discrete_twobins!$M$3,TE_discrete_twobins!$O$3,TE_discrete_twobins!$U$3,TE_discrete_twobins!$W$3,TE_discrete_twobins!$Y$3,TE_discrete_twobins!$AA$3,TE_discrete_twobins!$AG$3,TE_discrete_twobins!$AI$3,TE_discrete_twobins!$AK$3,TE_discrete_twobins!$AM$3,TE_discrete_twobins!$AO$3,TE_discrete_twobins!$AQ$3,TE_discrete_twobins!$AS$3,TE_discrete_twobins!$AU$3,TE_discrete_twobins!$AW$3,TE_discrete_twobins!$AY$3)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
-                <c:pt idx="0">
-                  <c:v>0.24365173972695101</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.39512592406966501</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.21691554014242101</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.28138712201095201</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.123424118027047</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.255929656054036</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.22656767498343999</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.68852661479560295</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.326925672129672</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.25819067296339998</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.27978680925678301</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.52822314565461603</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.13473474496181401</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1.33621823923277E-2</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.35110838696496</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.473507217847769</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.51803325551479296</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.53185981194285004</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.28960811566995698</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.50058924158905105</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C46B-4A5C-B8EA-04111DA8B0FC}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>TE_discrete_twobins!$A$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>low</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>TE_discrete_twobins!$B$1:$AY$1</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(TE_discrete_twobins!$E$1,TE_discrete_twobins!$G$1,TE_discrete_twobins!$I$1,TE_discrete_twobins!$K$1,TE_discrete_twobins!$M$1,TE_discrete_twobins!$O$1,TE_discrete_twobins!$U$1,TE_discrete_twobins!$W$1,TE_discrete_twobins!$Y$1,TE_discrete_twobins!$AA$1,TE_discrete_twobins!$AG$1,TE_discrete_twobins!$AI$1,TE_discrete_twobins!$AK$1,TE_discrete_twobins!$AM$1,TE_discrete_twobins!$AO$1,TE_discrete_twobins!$AQ$1,TE_discrete_twobins!$AS$1,TE_discrete_twobins!$AU$1,TE_discrete_twobins!$AW$1,TE_discrete_twobins!$AY$1)</c:f>
-              <c:strCache>
-                <c:ptCount val="20"/>
-                <c:pt idx="0">
-                  <c:v>dyad_02_anno02</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>dyad_03_anno02</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>dyad_04_anno02</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>dyad_05_anno02</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>dyad_06_anno02</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>dyad_07_anno02</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>dyad_10_anno02</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>dyad_11_anno02</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>triad_01_anno02</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>triad_02_anno02</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>triad_05_anno02</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>triad_06_anno02</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>triad_07_anno02</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>triad_08_anno02</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>triad_09_anno02</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>triad_10_anno02</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>triad_11_anno02</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>triad_12_anno02</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>triad_13_anno02</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>triad_14_anno02</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>TE_discrete_twobins!$B$4:$AY$4</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(TE_discrete_twobins!$E$4,TE_discrete_twobins!$G$4,TE_discrete_twobins!$I$4,TE_discrete_twobins!$K$4,TE_discrete_twobins!$M$4,TE_discrete_twobins!$O$4,TE_discrete_twobins!$U$4,TE_discrete_twobins!$W$4,TE_discrete_twobins!$Y$4,TE_discrete_twobins!$AA$4,TE_discrete_twobins!$AG$4,TE_discrete_twobins!$AI$4,TE_discrete_twobins!$AK$4,TE_discrete_twobins!$AM$4,TE_discrete_twobins!$AO$4,TE_discrete_twobins!$AQ$4,TE_discrete_twobins!$AS$4,TE_discrete_twobins!$AU$4,TE_discrete_twobins!$AW$4,TE_discrete_twobins!$AY$4)</c:f>
+              <c:f>(TE_discrete_twobinsV1!$E$4,TE_discrete_twobinsV1!$G$4,TE_discrete_twobinsV1!$I$4,TE_discrete_twobinsV1!$K$4,TE_discrete_twobinsV1!$M$4,TE_discrete_twobinsV1!$O$4,TE_discrete_twobinsV1!$U$4,TE_discrete_twobinsV1!$W$4,TE_discrete_twobinsV1!$Y$4,TE_discrete_twobinsV1!$AA$4,TE_discrete_twobinsV1!$AG$4,TE_discrete_twobinsV1!$AI$4,TE_discrete_twobinsV1!$AK$4,TE_discrete_twobinsV1!$AM$4,TE_discrete_twobinsV1!$AO$4,TE_discrete_twobinsV1!$AQ$4,TE_discrete_twobinsV1!$AS$4,TE_discrete_twobinsV1!$AU$4,TE_discrete_twobinsV1!$AW$4,TE_discrete_twobinsV1!$AY$4)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6373,6 +6435,1652 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="1983489136"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Helen</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="percentStacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>TE_discrete_twobinsV2!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>high</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobinsV2!$B$1:$AO$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobinsV2!$B$1,TE_discrete_twobinsV2!$D$1,TE_discrete_twobinsV2!$F$1,TE_discrete_twobinsV2!$H$1,TE_discrete_twobinsV2!$J$1,TE_discrete_twobinsV2!$L$1,TE_discrete_twobinsV2!$N$1,TE_discrete_twobinsV2!$P$1,TE_discrete_twobinsV2!$R$1,TE_discrete_twobinsV2!$T$1,TE_discrete_twobinsV2!$V$1,TE_discrete_twobinsV2!$X$1,TE_discrete_twobinsV2!$Z$1,TE_discrete_twobinsV2!$AB$1,TE_discrete_twobinsV2!$AD$1,TE_discrete_twobinsV2!$AF$1,TE_discrete_twobinsV2!$AH$1,TE_discrete_twobinsV2!$AJ$1,TE_discrete_twobinsV2!$AL$1,TE_discrete_twobinsV2!$AN$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>dyad_02_anno01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>dyad_03_anno01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>dyad_04_anno01</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>dyad_05_anno01</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>dyad_06_anno01</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>dyad_07_anno01</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>dyad_10_anno01</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>dyad_11_anno01</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>triad_01_anno01</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>triad_02_anno01</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>triad_05_anno01</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>triad_06_anno01</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>triad_07_anno01</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>triad_08_anno01</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>triad_09_anno01</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>triad_10_anno01</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>triad_11_anno01</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>triad_12_anno01</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>triad_13_anno01</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>triad_14_anno01</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobinsV2!$B$2:$AO$2</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobinsV2!$B$2,TE_discrete_twobinsV2!$D$2,TE_discrete_twobinsV2!$F$2,TE_discrete_twobinsV2!$H$2,TE_discrete_twobinsV2!$J$2,TE_discrete_twobinsV2!$L$2,TE_discrete_twobinsV2!$N$2,TE_discrete_twobinsV2!$P$2,TE_discrete_twobinsV2!$R$2,TE_discrete_twobinsV2!$T$2,TE_discrete_twobinsV2!$V$2,TE_discrete_twobinsV2!$X$2,TE_discrete_twobinsV2!$Z$2,TE_discrete_twobinsV2!$AB$2,TE_discrete_twobinsV2!$AD$2,TE_discrete_twobinsV2!$AF$2,TE_discrete_twobinsV2!$AH$2,TE_discrete_twobinsV2!$AJ$2,TE_discrete_twobinsV2!$AL$2,TE_discrete_twobinsV2!$AN$2)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.47961134477407102</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.74818318506452797</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.66684062557869395</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.43899452362325198</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.92854612515368096</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.695354742861091</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.116140428350629</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.60213659380017204</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.43328185212397402</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.79845533254624101</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.63778406624884898</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.71398762283533301</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.35741104952619301</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.3156048068769899E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.69235877004801305</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.32977909011373502</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.21420744199342501</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.72785443888142598</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.69873102402570397</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.55135905721345702</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-553D-492A-8E45-EC92A64172B6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>TE_discrete_twobinsV2!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>mid</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobinsV2!$B$1:$AO$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobinsV2!$B$1,TE_discrete_twobinsV2!$D$1,TE_discrete_twobinsV2!$F$1,TE_discrete_twobinsV2!$H$1,TE_discrete_twobinsV2!$J$1,TE_discrete_twobinsV2!$L$1,TE_discrete_twobinsV2!$N$1,TE_discrete_twobinsV2!$P$1,TE_discrete_twobinsV2!$R$1,TE_discrete_twobinsV2!$T$1,TE_discrete_twobinsV2!$V$1,TE_discrete_twobinsV2!$X$1,TE_discrete_twobinsV2!$Z$1,TE_discrete_twobinsV2!$AB$1,TE_discrete_twobinsV2!$AD$1,TE_discrete_twobinsV2!$AF$1,TE_discrete_twobinsV2!$AH$1,TE_discrete_twobinsV2!$AJ$1,TE_discrete_twobinsV2!$AL$1,TE_discrete_twobinsV2!$AN$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>dyad_02_anno01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>dyad_03_anno01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>dyad_04_anno01</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>dyad_05_anno01</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>dyad_06_anno01</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>dyad_07_anno01</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>dyad_10_anno01</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>dyad_11_anno01</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>triad_01_anno01</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>triad_02_anno01</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>triad_05_anno01</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>triad_06_anno01</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>triad_07_anno01</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>triad_08_anno01</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>triad_09_anno01</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>triad_10_anno01</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>triad_11_anno01</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>triad_12_anno01</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>triad_13_anno01</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>triad_14_anno01</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobinsV2!$B$3:$AO$3</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobinsV2!$B$3,TE_discrete_twobinsV2!$D$3,TE_discrete_twobinsV2!$F$3,TE_discrete_twobinsV2!$H$3,TE_discrete_twobinsV2!$J$3,TE_discrete_twobinsV2!$L$3,TE_discrete_twobinsV2!$N$3,TE_discrete_twobinsV2!$P$3,TE_discrete_twobinsV2!$R$3,TE_discrete_twobinsV2!$T$3,TE_discrete_twobinsV2!$V$3,TE_discrete_twobinsV2!$X$3,TE_discrete_twobinsV2!$Z$3,TE_discrete_twobinsV2!$AB$3,TE_discrete_twobinsV2!$AD$3,TE_discrete_twobinsV2!$AF$3,TE_discrete_twobinsV2!$AH$3,TE_discrete_twobinsV2!$AJ$3,TE_discrete_twobinsV2!$AL$3,TE_discrete_twobinsV2!$AN$3)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.14992915139110599</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.143731988472622</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.13700106058820499</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.30067349229565599</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1044197628623201E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.110888455093544</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.22885846765290299</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.34173150549586201</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.132581607713184</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.01908697363242E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.28904012083123498</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.20964491448342201</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.218027636586549</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.15169147100961899</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.22900704872816399</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.33970363079615001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.71232550383534199</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.20410306508731199</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.26164732215382902</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.36618513590572099</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-553D-492A-8E45-EC92A64172B6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>TE_discrete_twobinsV2!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>low</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="C00000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobinsV2!$B$1:$AO$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobinsV2!$B$1,TE_discrete_twobinsV2!$D$1,TE_discrete_twobinsV2!$F$1,TE_discrete_twobinsV2!$H$1,TE_discrete_twobinsV2!$J$1,TE_discrete_twobinsV2!$L$1,TE_discrete_twobinsV2!$N$1,TE_discrete_twobinsV2!$P$1,TE_discrete_twobinsV2!$R$1,TE_discrete_twobinsV2!$T$1,TE_discrete_twobinsV2!$V$1,TE_discrete_twobinsV2!$X$1,TE_discrete_twobinsV2!$Z$1,TE_discrete_twobinsV2!$AB$1,TE_discrete_twobinsV2!$AD$1,TE_discrete_twobinsV2!$AF$1,TE_discrete_twobinsV2!$AH$1,TE_discrete_twobinsV2!$AJ$1,TE_discrete_twobinsV2!$AL$1,TE_discrete_twobinsV2!$AN$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>dyad_02_anno01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>dyad_03_anno01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>dyad_04_anno01</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>dyad_05_anno01</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>dyad_06_anno01</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>dyad_07_anno01</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>dyad_10_anno01</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>dyad_11_anno01</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>triad_01_anno01</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>triad_02_anno01</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>triad_05_anno01</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>triad_06_anno01</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>triad_07_anno01</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>triad_08_anno01</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>triad_09_anno01</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>triad_10_anno01</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>triad_11_anno01</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>triad_12_anno01</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>triad_13_anno01</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>triad_14_anno01</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobinsV2!$B$4:$AO$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobinsV2!$B$4,TE_discrete_twobinsV2!$D$4,TE_discrete_twobinsV2!$F$4,TE_discrete_twobinsV2!$H$4,TE_discrete_twobinsV2!$J$4,TE_discrete_twobinsV2!$L$4,TE_discrete_twobinsV2!$N$4,TE_discrete_twobinsV2!$P$4,TE_discrete_twobinsV2!$R$4,TE_discrete_twobinsV2!$T$4,TE_discrete_twobinsV2!$V$4,TE_discrete_twobinsV2!$X$4,TE_discrete_twobinsV2!$Z$4,TE_discrete_twobinsV2!$AB$4,TE_discrete_twobinsV2!$AD$4,TE_discrete_twobinsV2!$AF$4,TE_discrete_twobinsV2!$AH$4,TE_discrete_twobinsV2!$AJ$4,TE_discrete_twobinsV2!$AL$4,TE_discrete_twobinsV2!$AN$4)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.37045950383482101</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.108069164265129</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.19615831383310001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.25801898023742298</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.0388839108962401E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.19373952700951799</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.65381430779421501</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.6131900703964399E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.42654930950203102</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.16135379771743399</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7.3175812919914499E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7.6367462681243406E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.42456131388725699</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.78515248092161005</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7.8608642353662203E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.33051727909011303</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7.3467054171232504E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>6.8042496031261404E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.9621653820466E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.2455806880821103E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-553D-492A-8E45-EC92A64172B6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="252077904"/>
+        <c:axId val="252079824"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="252077904"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="252079824"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="252079824"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="252077904"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Laura Ann </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>(.2, .45, 1)</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-GB"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="percentStacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>TE_discrete_twobinsV2!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>high</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobinsV2!$B$1:$AO$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobinsV2!$C$1,TE_discrete_twobinsV2!$E$1,TE_discrete_twobinsV2!$G$1,TE_discrete_twobinsV2!$I$1,TE_discrete_twobinsV2!$K$1,TE_discrete_twobinsV2!$M$1,TE_discrete_twobinsV2!$O$1,TE_discrete_twobinsV2!$Q$1,TE_discrete_twobinsV2!$S$1,TE_discrete_twobinsV2!$U$1,TE_discrete_twobinsV2!$W$1,TE_discrete_twobinsV2!$Y$1,TE_discrete_twobinsV2!$AA$1,TE_discrete_twobinsV2!$AC$1,TE_discrete_twobinsV2!$AE$1,TE_discrete_twobinsV2!$AG$1,TE_discrete_twobinsV2!$AI$1,TE_discrete_twobinsV2!$AK$1,TE_discrete_twobinsV2!$AM$1,TE_discrete_twobinsV2!$AO$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>dyad_02_anno02</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>dyad_03_anno02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>dyad_04_anno02</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>dyad_05_anno02</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>dyad_06_anno02</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>dyad_07_anno02</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>dyad_10_anno02</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>dyad_11_anno02</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>triad_01_anno02</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>triad_02_anno02</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>triad_05_anno02</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>triad_06_anno02</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>triad_07_anno02</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>triad_08_anno02</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>triad_09_anno02</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>triad_10_anno02</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>triad_11_anno02</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>triad_12_anno02</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>triad_13_anno02</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>triad_14_anno02</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobinsV2!$B$2:$AO$2</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobinsV2!$C$2,TE_discrete_twobinsV2!$E$2,TE_discrete_twobinsV2!$G$2,TE_discrete_twobinsV2!$I$2,TE_discrete_twobinsV2!$K$2,TE_discrete_twobinsV2!$M$2,TE_discrete_twobinsV2!$O$2,TE_discrete_twobinsV2!$Q$2,TE_discrete_twobinsV2!$S$2,TE_discrete_twobinsV2!$U$2,TE_discrete_twobinsV2!$W$2,TE_discrete_twobinsV2!$Y$2,TE_discrete_twobinsV2!$AA$2,TE_discrete_twobinsV2!$AC$2,TE_discrete_twobinsV2!$AE$2,TE_discrete_twobinsV2!$AG$2,TE_discrete_twobinsV2!$AI$2,TE_discrete_twobinsV2!$AK$2,TE_discrete_twobinsV2!$AM$2,TE_discrete_twobinsV2!$AO$2)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.241717460246058</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.48646786117027901</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.52275214221982702</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.35996122317085599</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.826293525599616</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.56917788104410305</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.9939280194303301E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.1466798402700593E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.212697365461606</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.60706906729634003</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.68918942379472E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.28492447076028599</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7.0496283619830902E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.50807028297068102</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.6438101487314E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.12382464281353001</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.14697016191628001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.21199391750617699</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4B92-45DD-9918-16D1ABE7DAFE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>TE_discrete_twobinsV2!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>mid</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobinsV2!$B$1:$AO$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobinsV2!$C$1,TE_discrete_twobinsV2!$E$1,TE_discrete_twobinsV2!$G$1,TE_discrete_twobinsV2!$I$1,TE_discrete_twobinsV2!$K$1,TE_discrete_twobinsV2!$M$1,TE_discrete_twobinsV2!$O$1,TE_discrete_twobinsV2!$Q$1,TE_discrete_twobinsV2!$S$1,TE_discrete_twobinsV2!$U$1,TE_discrete_twobinsV2!$W$1,TE_discrete_twobinsV2!$Y$1,TE_discrete_twobinsV2!$AA$1,TE_discrete_twobinsV2!$AC$1,TE_discrete_twobinsV2!$AE$1,TE_discrete_twobinsV2!$AG$1,TE_discrete_twobinsV2!$AI$1,TE_discrete_twobinsV2!$AK$1,TE_discrete_twobinsV2!$AM$1,TE_discrete_twobinsV2!$AO$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>dyad_02_anno02</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>dyad_03_anno02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>dyad_04_anno02</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>dyad_05_anno02</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>dyad_06_anno02</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>dyad_07_anno02</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>dyad_10_anno02</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>dyad_11_anno02</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>triad_01_anno02</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>triad_02_anno02</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>triad_05_anno02</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>triad_06_anno02</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>triad_07_anno02</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>triad_08_anno02</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>triad_09_anno02</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>triad_10_anno02</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>triad_11_anno02</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>triad_12_anno02</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>triad_13_anno02</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>triad_14_anno02</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobinsV2!$B$3:$AO$3</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobinsV2!$C$3,TE_discrete_twobinsV2!$E$3,TE_discrete_twobinsV2!$G$3,TE_discrete_twobinsV2!$I$3,TE_discrete_twobinsV2!$K$3,TE_discrete_twobinsV2!$M$3,TE_discrete_twobinsV2!$O$3,TE_discrete_twobinsV2!$Q$3,TE_discrete_twobinsV2!$S$3,TE_discrete_twobinsV2!$U$3,TE_discrete_twobinsV2!$W$3,TE_discrete_twobinsV2!$Y$3,TE_discrete_twobinsV2!$AA$3,TE_discrete_twobinsV2!$AC$3,TE_discrete_twobinsV2!$AE$3,TE_discrete_twobinsV2!$AG$3,TE_discrete_twobinsV2!$AI$3,TE_discrete_twobinsV2!$AK$3,TE_discrete_twobinsV2!$AM$3,TE_discrete_twobinsV2!$AO$3)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.24365173972695101</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.39512592406966501</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.21691554014242101</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.28138712201095201</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.123424118027047</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.255929656054036</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.22656767498343999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.68852661479560295</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.326925672129672</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.25819067296339998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.27978680925678301</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.52822314565461603</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.13473474496181401</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.33621823923277E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.35110838696496</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.473507217847769</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.51803325551479296</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.53185981194285004</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.28960811566995698</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.50058924158905105</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4B92-45DD-9918-16D1ABE7DAFE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>TE_discrete_twobinsV2!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>low</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="C00000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobinsV2!$B$1:$AO$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobinsV2!$C$1,TE_discrete_twobinsV2!$E$1,TE_discrete_twobinsV2!$G$1,TE_discrete_twobinsV2!$I$1,TE_discrete_twobinsV2!$K$1,TE_discrete_twobinsV2!$M$1,TE_discrete_twobinsV2!$O$1,TE_discrete_twobinsV2!$Q$1,TE_discrete_twobinsV2!$S$1,TE_discrete_twobinsV2!$U$1,TE_discrete_twobinsV2!$W$1,TE_discrete_twobinsV2!$Y$1,TE_discrete_twobinsV2!$AA$1,TE_discrete_twobinsV2!$AC$1,TE_discrete_twobinsV2!$AE$1,TE_discrete_twobinsV2!$AG$1,TE_discrete_twobinsV2!$AI$1,TE_discrete_twobinsV2!$AK$1,TE_discrete_twobinsV2!$AM$1,TE_discrete_twobinsV2!$AO$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>dyad_02_anno02</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>dyad_03_anno02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>dyad_04_anno02</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>dyad_05_anno02</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>dyad_06_anno02</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>dyad_07_anno02</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>dyad_10_anno02</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>dyad_11_anno02</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>triad_01_anno02</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>triad_02_anno02</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>triad_05_anno02</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>triad_06_anno02</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>triad_07_anno02</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>triad_08_anno02</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>triad_09_anno02</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>triad_10_anno02</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>triad_11_anno02</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>triad_12_anno02</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>triad_13_anno02</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>triad_14_anno02</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobinsV2!$B$4:$AO$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobinsV2!$C$4,TE_discrete_twobinsV2!$E$4,TE_discrete_twobinsV2!$G$4,TE_discrete_twobinsV2!$I$4,TE_discrete_twobinsV2!$K$4,TE_discrete_twobinsV2!$M$4,TE_discrete_twobinsV2!$O$4,TE_discrete_twobinsV2!$Q$4,TE_discrete_twobinsV2!$S$4,TE_discrete_twobinsV2!$U$4,TE_discrete_twobinsV2!$W$4,TE_discrete_twobinsV2!$Y$4,TE_discrete_twobinsV2!$AA$4,TE_discrete_twobinsV2!$AC$4,TE_discrete_twobinsV2!$AE$4,TE_discrete_twobinsV2!$AG$4,TE_discrete_twobinsV2!$AI$4,TE_discrete_twobinsV2!$AK$4,TE_discrete_twobinsV2!$AM$4,TE_discrete_twobinsV2!$AO$4)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.41566766379523601</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.118374890364615</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.26033231763775</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.35149154733154098</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.9990622851069998E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.16620311987147299</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.38024398321925301</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.22852085134411901</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.44551738615405301</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.13474025974025899</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.35603548549504299</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.17344081610814799</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.64189931291665603</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.96657992456360897</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.140770252324037</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.46855861767279</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.48196674448520599</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.33659787519843598</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.55623747721077998</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.27099410758410902</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-4B92-45DD-9918-16D1ABE7DAFE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="252077904"/>
+        <c:axId val="252079824"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="252077904"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="252079824"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="252079824"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="252077904"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17517,6 +19225,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors14.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors15.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -19756,6 +21544,1016 @@
 </file>
 
 <file path=xl/charts/style13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -24729,15 +27527,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>66674</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:colOff>117474</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>5900</xdr:rowOff>
+      <xdr:colOff>736600</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>94800</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -24765,15 +27563,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>673100</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>145600</xdr:rowOff>
+      <xdr:colOff>723900</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>50350</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -24781,6 +27579,85 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A54DB18-A492-44DF-9E02-F3A178E3E851}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>311150</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>222250</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B13462C-65BC-101C-E27C-78EE8A594B09}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>196850</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57BB5C8E-0FAF-4051-8A01-0273B020C71F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -25082,6 +27959,56 @@
     <tableColumn id="49" xr3:uid="{BBE75FCD-EE61-406C-B693-24BD8C05CE9A}" name="triad_13_anno02"/>
     <tableColumn id="50" xr3:uid="{A72876DC-B454-4519-9E91-F26D1B0BE059}" name="triad_14_anno01"/>
     <tableColumn id="51" xr3:uid="{76C054D2-C636-43FC-B237-541AE5CF3F1D}" name="triad_14_anno02"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{14C2C227-83C2-456E-B0F3-DF58A3760A57}" name="Table6" displayName="Table6" ref="A1:AO4" totalsRowShown="0">
+  <autoFilter ref="A1:AO4" xr:uid="{14C2C227-83C2-456E-B0F3-DF58A3760A57}"/>
+  <tableColumns count="41">
+    <tableColumn id="1" xr3:uid="{0921B5EC-A7F0-474D-9C23-4B7F4CD341DE}" name="task_eng"/>
+    <tableColumn id="2" xr3:uid="{5981E633-E7B5-4E13-BEF9-33BB4738F82C}" name="dyad_02_anno01"/>
+    <tableColumn id="3" xr3:uid="{5FEB605F-2ADE-4349-9157-612B8CCE5B6D}" name="dyad_02_anno02"/>
+    <tableColumn id="4" xr3:uid="{920FCAC9-3DAE-40CC-AE37-0C77C997E7DB}" name="dyad_03_anno01"/>
+    <tableColumn id="5" xr3:uid="{0E9AFEA4-596B-4B97-A989-7437B9BAC7CF}" name="dyad_03_anno02"/>
+    <tableColumn id="6" xr3:uid="{BBB15B86-08AF-4F5E-8F59-64A3E8F6215E}" name="dyad_04_anno01"/>
+    <tableColumn id="7" xr3:uid="{89F8F0B8-AD4A-4FEF-9E16-FBC5CAB912F7}" name="dyad_04_anno02"/>
+    <tableColumn id="8" xr3:uid="{E70D5A0C-8CC8-4A05-BBE8-F98436A59055}" name="dyad_05_anno01"/>
+    <tableColumn id="9" xr3:uid="{89B011F0-A759-4F17-A545-805D3184BD5F}" name="dyad_05_anno02"/>
+    <tableColumn id="10" xr3:uid="{BC226E74-2074-457E-B76A-940E75581BFC}" name="dyad_06_anno01"/>
+    <tableColumn id="11" xr3:uid="{7743632A-0ED2-48FD-8AE6-4C9B3044333F}" name="dyad_06_anno02"/>
+    <tableColumn id="12" xr3:uid="{CCF29A52-D6A5-4864-A469-4789CBAB41C3}" name="dyad_07_anno01"/>
+    <tableColumn id="13" xr3:uid="{2C2F277C-B205-4CCF-A084-A204896B2983}" name="dyad_07_anno02"/>
+    <tableColumn id="14" xr3:uid="{29AA4CBD-C1C0-4040-986E-957AF4E3B20C}" name="dyad_10_anno01"/>
+    <tableColumn id="15" xr3:uid="{992BB7C1-5B3C-4D16-A2F8-5A3E6BE0405B}" name="dyad_10_anno02"/>
+    <tableColumn id="16" xr3:uid="{C4DAAF89-8B2C-4D10-B62F-7B9CA27E2A1D}" name="dyad_11_anno01"/>
+    <tableColumn id="17" xr3:uid="{1C9C0E1B-89F5-4592-ADCF-C656E80B2520}" name="dyad_11_anno02"/>
+    <tableColumn id="18" xr3:uid="{DB8A972E-F6B7-4E7F-B715-D06698F3D413}" name="triad_01_anno01"/>
+    <tableColumn id="19" xr3:uid="{8AB924E4-3055-465E-87EC-C8BCA6DC2FCC}" name="triad_01_anno02"/>
+    <tableColumn id="20" xr3:uid="{BFE07C73-7B52-40AA-9B26-64A48592AA74}" name="triad_02_anno01"/>
+    <tableColumn id="21" xr3:uid="{68CA1866-D65E-4080-A1F5-90A58CCAC5BB}" name="triad_02_anno02"/>
+    <tableColumn id="22" xr3:uid="{F1B8C747-1E95-4281-B2F4-2819ACB61976}" name="triad_05_anno01"/>
+    <tableColumn id="23" xr3:uid="{910CABEE-C7AD-401E-A17E-39577CC2D945}" name="triad_05_anno02"/>
+    <tableColumn id="24" xr3:uid="{E79951D9-6F39-4A22-8655-1D211AFD7C3F}" name="triad_06_anno01"/>
+    <tableColumn id="25" xr3:uid="{BA6F795D-DCC3-4CA3-AA24-28CA336D581D}" name="triad_06_anno02"/>
+    <tableColumn id="26" xr3:uid="{E22911E0-B518-46E7-8D79-A4AECBBDF78F}" name="triad_07_anno01"/>
+    <tableColumn id="27" xr3:uid="{3B517794-54FF-4FC9-8352-BF3A480D7A68}" name="triad_07_anno02"/>
+    <tableColumn id="28" xr3:uid="{9E668EAC-F526-4146-BC3A-6B3F8EE5D3A7}" name="triad_08_anno01"/>
+    <tableColumn id="29" xr3:uid="{9A2C6D39-9723-4E91-8B4F-B881E5652BD1}" name="triad_08_anno02"/>
+    <tableColumn id="30" xr3:uid="{98404BE4-0905-41AC-9B36-D73676C4DE55}" name="triad_09_anno01"/>
+    <tableColumn id="31" xr3:uid="{D66E3A08-2841-4C7B-8E61-8BDE29E2C44E}" name="triad_09_anno02"/>
+    <tableColumn id="32" xr3:uid="{D60F7A15-3072-4905-A07C-CD75F663ECF4}" name="triad_10_anno01"/>
+    <tableColumn id="33" xr3:uid="{AF35407B-CD09-412F-892C-EDF32537B7D3}" name="triad_10_anno02"/>
+    <tableColumn id="34" xr3:uid="{2B8F1CA4-A301-46DE-A8CA-305DF52E86A8}" name="triad_11_anno01"/>
+    <tableColumn id="35" xr3:uid="{B6F05E36-48A7-4109-A324-8200E4E5AF2F}" name="triad_11_anno02"/>
+    <tableColumn id="36" xr3:uid="{6E62DC35-5900-4061-8DC7-52A847316BD5}" name="triad_12_anno01"/>
+    <tableColumn id="37" xr3:uid="{9FFD8BF7-E93D-47A0-8310-E503569670E5}" name="triad_12_anno02"/>
+    <tableColumn id="38" xr3:uid="{4699FF53-6165-4972-9D09-98DB7CD800D6}" name="triad_13_anno01"/>
+    <tableColumn id="39" xr3:uid="{1B61BA44-28AA-4011-AB77-8EC462BBEFCC}" name="triad_13_anno02"/>
+    <tableColumn id="40" xr3:uid="{98A4D2D9-F8DC-47F9-8F60-37376A5D7A94}" name="triad_14_anno01"/>
+    <tableColumn id="41" xr3:uid="{82699084-8F64-4016-9B3D-89C0536F3E0A}" name="triad_14_anno02"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -31026,270 +33953,155 @@
       <c r="AX4" s="3">
         <v>8.2455806880821103E-2</v>
       </c>
-      <c r="AY4" s="6">
+      <c r="AY4" s="4">
         <v>0.27099410758410902</v>
+      </c>
+    </row>
+    <row r="6" spans="1:51" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H6" t="s">
+        <v>79</v>
+      </c>
+      <c r="I6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J6" t="s">
+        <v>81</v>
+      </c>
+      <c r="K6" t="s">
+        <v>82</v>
+      </c>
+      <c r="L6" t="s">
+        <v>83</v>
+      </c>
+      <c r="M6" t="s">
+        <v>84</v>
+      </c>
+      <c r="N6" t="s">
+        <v>85</v>
+      </c>
+      <c r="O6" t="s">
+        <v>86</v>
+      </c>
+      <c r="P6" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>88</v>
+      </c>
+      <c r="R6" t="s">
+        <v>89</v>
+      </c>
+      <c r="S6" t="s">
+        <v>90</v>
+      </c>
+      <c r="T6" t="s">
+        <v>91</v>
+      </c>
+      <c r="U6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:51" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="3">
-        <v>0.15178195530010399</v>
-      </c>
-      <c r="C7" s="3">
-        <v>0.30530285003020202</v>
-      </c>
-      <c r="D7" s="3">
-        <v>0.37045950383482101</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0.41566766379523601</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0.108069164265129</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0.118374890364615</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0.19615831383310001</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0.26033231763775</v>
-      </c>
-      <c r="J7" s="3">
-        <v>0.25801898023742298</v>
-      </c>
-      <c r="K7" s="3">
-        <v>0.35149154733154098</v>
-      </c>
-      <c r="L7" s="3">
-        <v>6.0388839108962401E-2</v>
-      </c>
-      <c r="M7" s="3">
-        <v>4.9990622851069998E-2</v>
-      </c>
-      <c r="N7" s="3">
-        <v>0.19373952700951799</v>
-      </c>
-      <c r="O7" s="3">
-        <v>0.16620311987147299</v>
-      </c>
-      <c r="P7" s="3">
-        <v>0.17664380853703401</v>
-      </c>
-      <c r="Q7" s="3">
-        <v>0.46040272116262898</v>
-      </c>
-      <c r="R7" s="3">
-        <v>0.62544589774078396</v>
-      </c>
-      <c r="S7" s="3">
-        <v>0.92503070115592201</v>
-      </c>
-      <c r="T7" s="3">
-        <v>0.65381430779421501</v>
-      </c>
-      <c r="U7" s="3">
-        <v>0.38024398321925301</v>
-      </c>
-      <c r="V7" s="3">
-        <v>5.6131900703964399E-2</v>
-      </c>
-      <c r="W7" s="3">
-        <v>0.22852085134411901</v>
-      </c>
-      <c r="X7" s="3">
-        <v>0.42654930950203102</v>
-      </c>
-      <c r="Y7" s="3">
-        <v>0.44551738615405301</v>
-      </c>
-      <c r="Z7" s="3">
-        <v>0.16135379771743399</v>
-      </c>
-      <c r="AA7" s="3">
-        <v>0.13474025974025899</v>
-      </c>
-      <c r="AB7" s="3">
-        <v>0.22689932788109499</v>
-      </c>
-      <c r="AC7" s="3">
-        <v>0.433489371778291</v>
-      </c>
-      <c r="AD7" s="3">
-        <v>0.15010237576781801</v>
-      </c>
-      <c r="AE7" s="3">
-        <v>0.163606227046702</v>
-      </c>
-      <c r="AF7" s="3">
-        <v>7.3175812919914499E-2</v>
-      </c>
-      <c r="AG7" s="3">
-        <v>0.35603548549504299</v>
-      </c>
-      <c r="AH7" s="3">
-        <v>7.6367462681243406E-2</v>
-      </c>
-      <c r="AI7" s="3">
-        <v>0.17344081610814799</v>
-      </c>
-      <c r="AJ7" s="3">
-        <v>0.42456131388725699</v>
-      </c>
-      <c r="AK7" s="3">
-        <v>0.64189931291665603</v>
-      </c>
-      <c r="AL7" s="3">
-        <v>0.78515248092161005</v>
-      </c>
-      <c r="AM7" s="3">
-        <v>0.96657992456360897</v>
-      </c>
-      <c r="AN7" s="3">
-        <v>7.8608642353662203E-2</v>
-      </c>
-      <c r="AO7" s="3">
-        <v>0.140770252324037</v>
-      </c>
-      <c r="AP7" s="3">
-        <v>0.33051727909011303</v>
-      </c>
-      <c r="AQ7" s="3">
-        <v>0.46855861767279</v>
-      </c>
-      <c r="AR7" s="3">
-        <v>7.3467054171232504E-2</v>
-      </c>
-      <c r="AS7" s="3">
-        <v>0.48196674448520599</v>
-      </c>
-      <c r="AT7" s="3">
-        <v>6.8042496031261404E-2</v>
-      </c>
-      <c r="AU7" s="3">
-        <v>0.33659787519843598</v>
-      </c>
-      <c r="AV7" s="3">
-        <v>3.9621653820466E-2</v>
-      </c>
-      <c r="AW7" s="3">
-        <v>0.55623747721077998</v>
-      </c>
-      <c r="AX7" s="3">
-        <v>8.2455806880821103E-2</v>
-      </c>
-      <c r="AY7" s="6">
-        <v>0.27099410758410902</v>
+      <c r="B7">
+        <v>0.85629482756780495</v>
+      </c>
+      <c r="C7">
+        <v>0.72480082067718599</v>
+      </c>
+      <c r="D7">
+        <v>0.82777645880776596</v>
+      </c>
+      <c r="E7">
+        <v>0.82659452725981197</v>
+      </c>
+      <c r="F7">
+        <v>0.79078960048874103</v>
+      </c>
+      <c r="G7">
+        <v>0.83794847262402505</v>
+      </c>
+      <c r="H7">
+        <v>0.832584473541637</v>
+      </c>
+      <c r="I7">
+        <v>0.64171827186225805</v>
+      </c>
+      <c r="J7">
+        <v>0.86231599498596401</v>
+      </c>
+      <c r="K7">
+        <v>0.86957035714180098</v>
+      </c>
+      <c r="L7">
+        <v>0.53891218808139896</v>
+      </c>
+      <c r="M7">
+        <v>0.59137022905749004</v>
+      </c>
+      <c r="N7">
+        <v>0.44227699763089001</v>
+      </c>
+      <c r="P7">
+        <v>0.75878204633194901</v>
+      </c>
+      <c r="Q7">
+        <v>0.77646361437990297</v>
+      </c>
+      <c r="R7">
+        <v>0.57801020824920901</v>
+      </c>
+      <c r="S7">
+        <v>0.67676370745270498</v>
+      </c>
+      <c r="T7">
+        <v>0.61168228428765803</v>
+      </c>
+      <c r="U7">
+        <v>0.75541379016388399</v>
       </c>
     </row>
     <row r="8" spans="1:51" x14ac:dyDescent="0.35">
-      <c r="A8" s="4"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
-      <c r="X8" s="2"/>
-      <c r="Y8" s="2"/>
-      <c r="Z8" s="2"/>
-      <c r="AA8" s="2"/>
-      <c r="AB8" s="2"/>
-      <c r="AC8" s="2"/>
-      <c r="AD8" s="2"/>
-      <c r="AE8" s="2"/>
-      <c r="AF8" s="2"/>
-      <c r="AG8" s="2"/>
-      <c r="AH8" s="2"/>
-      <c r="AI8" s="2"/>
-      <c r="AJ8" s="2"/>
-      <c r="AK8" s="2"/>
-      <c r="AL8" s="2"/>
-      <c r="AM8" s="2"/>
-      <c r="AN8" s="2"/>
-      <c r="AO8" s="2"/>
-      <c r="AP8" s="2"/>
-      <c r="AQ8" s="2"/>
-      <c r="AR8" s="2"/>
-      <c r="AS8" s="2"/>
-      <c r="AT8" s="2"/>
-      <c r="AU8" s="2"/>
-      <c r="AV8" s="2"/>
-      <c r="AW8" s="2"/>
-      <c r="AX8" s="2"/>
-      <c r="AY8" s="5"/>
+      <c r="I8" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="U8" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="W8" s="5" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="9" spans="1:51" x14ac:dyDescent="0.35">
-      <c r="A9" s="4"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-      <c r="V9" s="2"/>
-      <c r="W9" s="2"/>
-      <c r="X9" s="2"/>
-      <c r="Y9" s="2"/>
-      <c r="Z9" s="2"/>
-      <c r="AA9" s="2"/>
-      <c r="AB9" s="2"/>
-      <c r="AC9" s="2"/>
-      <c r="AD9" s="2"/>
-      <c r="AE9" s="2"/>
-      <c r="AF9" s="2"/>
-      <c r="AG9" s="2"/>
-      <c r="AH9" s="2"/>
-      <c r="AI9" s="2"/>
-      <c r="AJ9" s="2"/>
-      <c r="AK9" s="2"/>
-      <c r="AL9" s="2"/>
-      <c r="AM9" s="2"/>
-      <c r="AN9" s="2"/>
-      <c r="AO9" s="2"/>
-      <c r="AP9" s="2"/>
-      <c r="AQ9" s="2"/>
-      <c r="AR9" s="2"/>
-      <c r="AS9" s="2"/>
-      <c r="AT9" s="2"/>
-      <c r="AU9" s="2"/>
-      <c r="AV9" s="2"/>
-      <c r="AW9" s="2"/>
-      <c r="AX9" s="2"/>
-      <c r="AY9" s="5"/>
+      <c r="I9" s="5">
+        <f>AVERAGE(B7:I7)</f>
+        <v>0.79231343160365375</v>
+      </c>
+      <c r="U9" s="5">
+        <f>AVERAGE(J7:U7)</f>
+        <v>0.67832376525116833</v>
+      </c>
+      <c r="W9" s="5">
+        <f>AVERAGE(I9,U9)</f>
+        <v>0.7353185984274111</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -31298,4 +34110,1084 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6E884E-4278-4958-AEF6-CE3AB5C8D996}">
+  <dimension ref="A1:U3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L1" t="s">
+        <v>83</v>
+      </c>
+      <c r="M1" t="s">
+        <v>84</v>
+      </c>
+      <c r="N1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O1" t="s">
+        <v>86</v>
+      </c>
+      <c r="P1" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>88</v>
+      </c>
+      <c r="R1" t="s">
+        <v>89</v>
+      </c>
+      <c r="S1" t="s">
+        <v>90</v>
+      </c>
+      <c r="T1" t="s">
+        <v>91</v>
+      </c>
+      <c r="U1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2">
+        <v>0.86276146222643102</v>
+      </c>
+      <c r="C2">
+        <v>0.74074689803015803</v>
+      </c>
+      <c r="D2">
+        <v>0.85054928065416602</v>
+      </c>
+      <c r="E2">
+        <v>0.81814633616452004</v>
+      </c>
+      <c r="F2">
+        <v>0.79085038760443604</v>
+      </c>
+      <c r="G2">
+        <v>0.78505091998955501</v>
+      </c>
+      <c r="H2">
+        <v>-0.33398042471309602</v>
+      </c>
+      <c r="I2">
+        <v>2.2800072977221301E-2</v>
+      </c>
+      <c r="J2">
+        <v>0.81491130084522601</v>
+      </c>
+      <c r="K2">
+        <v>0.86785674397944002</v>
+      </c>
+      <c r="L2">
+        <v>-8.4598923649412197E-2</v>
+      </c>
+      <c r="M2">
+        <v>0.21799042590743101</v>
+      </c>
+      <c r="N2">
+        <v>-8.6805497576840196E-2</v>
+      </c>
+      <c r="O2">
+        <v>-9.8060428060056895E-2</v>
+      </c>
+      <c r="P2">
+        <v>0.29753922699669499</v>
+      </c>
+      <c r="Q2">
+        <v>0.195374044392325</v>
+      </c>
+      <c r="R2">
+        <v>0.35849302300033697</v>
+      </c>
+      <c r="S2">
+        <v>-0.279845157467007</v>
+      </c>
+      <c r="T2">
+        <v>0.12539529152194401</v>
+      </c>
+      <c r="U2">
+        <v>0.64309151947275001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3">
+        <v>0.85629482756780495</v>
+      </c>
+      <c r="C3">
+        <v>0.72480082067718599</v>
+      </c>
+      <c r="D3">
+        <v>0.82777645880776596</v>
+      </c>
+      <c r="E3">
+        <v>0.82659452725981197</v>
+      </c>
+      <c r="F3">
+        <v>0.79078960048874103</v>
+      </c>
+      <c r="G3">
+        <v>0.83794847262402505</v>
+      </c>
+      <c r="H3">
+        <v>0.832584473541637</v>
+      </c>
+      <c r="I3">
+        <v>0.64171827186225805</v>
+      </c>
+      <c r="J3">
+        <v>0.86231599498596401</v>
+      </c>
+      <c r="K3">
+        <v>0.86957035714180098</v>
+      </c>
+      <c r="L3">
+        <v>0.53891218808139896</v>
+      </c>
+      <c r="M3">
+        <v>0.59137022905749004</v>
+      </c>
+      <c r="N3">
+        <v>0.44227699763089001</v>
+      </c>
+      <c r="O3">
+        <v>0.106638622511867</v>
+      </c>
+      <c r="P3">
+        <v>0.75878204633194901</v>
+      </c>
+      <c r="Q3">
+        <v>0.77646361437990297</v>
+      </c>
+      <c r="R3">
+        <v>0.57801020824920901</v>
+      </c>
+      <c r="S3">
+        <v>0.67676370745270498</v>
+      </c>
+      <c r="T3">
+        <v>0.61168228428765803</v>
+      </c>
+      <c r="U3">
+        <v>0.75541379016388399</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02421442-5A43-463D-935D-4B7C818F7F90}">
+  <dimension ref="A1:AO10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="17" width="16.26953125" customWidth="1"/>
+    <col min="18" max="41" width="16.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>22</v>
+      </c>
+      <c r="R1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1" t="s">
+        <v>25</v>
+      </c>
+      <c r="U1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W1" t="s">
+        <v>32</v>
+      </c>
+      <c r="X1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2">
+        <v>0.47961134477407102</v>
+      </c>
+      <c r="C2">
+        <v>0.241717460246058</v>
+      </c>
+      <c r="D2">
+        <v>0.74818318506452797</v>
+      </c>
+      <c r="E2">
+        <v>0.48646786117027901</v>
+      </c>
+      <c r="F2">
+        <v>0.66684062557869395</v>
+      </c>
+      <c r="G2">
+        <v>0.52275214221982702</v>
+      </c>
+      <c r="H2">
+        <v>0.43899452362325198</v>
+      </c>
+      <c r="I2">
+        <v>0.35996122317085599</v>
+      </c>
+      <c r="J2">
+        <v>0.92854612515368096</v>
+      </c>
+      <c r="K2">
+        <v>0.826293525599616</v>
+      </c>
+      <c r="L2">
+        <v>0.695354742861091</v>
+      </c>
+      <c r="M2">
+        <v>0.56917788104410305</v>
+      </c>
+      <c r="N2">
+        <v>0.116140428350629</v>
+      </c>
+      <c r="O2">
+        <v>9.9939280194303301E-2</v>
+      </c>
+      <c r="P2">
+        <v>0.60213659380017204</v>
+      </c>
+      <c r="Q2">
+        <v>7.1466798402700593E-2</v>
+      </c>
+      <c r="R2">
+        <v>0.43328185212397402</v>
+      </c>
+      <c r="S2">
+        <v>0.212697365461606</v>
+      </c>
+      <c r="T2">
+        <v>0.79845533254624101</v>
+      </c>
+      <c r="U2">
+        <v>0.60706906729634003</v>
+      </c>
+      <c r="V2">
+        <v>0.63778406624884898</v>
+      </c>
+      <c r="W2">
+        <v>2.68918942379472E-2</v>
+      </c>
+      <c r="X2">
+        <v>0.71398762283533301</v>
+      </c>
+      <c r="Y2">
+        <v>0.28492447076028599</v>
+      </c>
+      <c r="Z2">
+        <v>0.35741104952619301</v>
+      </c>
+      <c r="AA2">
+        <v>7.0496283619830902E-2</v>
+      </c>
+      <c r="AB2">
+        <v>6.3156048068769899E-2</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0.69235877004801305</v>
+      </c>
+      <c r="AE2">
+        <v>0.50807028297068102</v>
+      </c>
+      <c r="AF2">
+        <v>0.32977909011373502</v>
+      </c>
+      <c r="AG2">
+        <v>2.6438101487314E-2</v>
+      </c>
+      <c r="AH2">
+        <v>0.21420744199342501</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0.72785443888142598</v>
+      </c>
+      <c r="AK2">
+        <v>0.12382464281353001</v>
+      </c>
+      <c r="AL2">
+        <v>0.69873102402570397</v>
+      </c>
+      <c r="AM2">
+        <v>0.14697016191628001</v>
+      </c>
+      <c r="AN2">
+        <v>0.55135905721345702</v>
+      </c>
+      <c r="AO2">
+        <v>0.21199391750617699</v>
+      </c>
+    </row>
+    <row r="3" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3">
+        <v>0.14992915139110599</v>
+      </c>
+      <c r="C3">
+        <v>0.24365173972695101</v>
+      </c>
+      <c r="D3">
+        <v>0.143731988472622</v>
+      </c>
+      <c r="E3">
+        <v>0.39512592406966501</v>
+      </c>
+      <c r="F3">
+        <v>0.13700106058820499</v>
+      </c>
+      <c r="G3">
+        <v>0.21691554014242101</v>
+      </c>
+      <c r="H3">
+        <v>0.30067349229565599</v>
+      </c>
+      <c r="I3">
+        <v>0.28138712201095201</v>
+      </c>
+      <c r="J3">
+        <v>1.1044197628623201E-2</v>
+      </c>
+      <c r="K3">
+        <v>0.123424118027047</v>
+      </c>
+      <c r="L3">
+        <v>0.110888455093544</v>
+      </c>
+      <c r="M3">
+        <v>0.255929656054036</v>
+      </c>
+      <c r="N3">
+        <v>0.22885846765290299</v>
+      </c>
+      <c r="O3">
+        <v>0.22656767498343999</v>
+      </c>
+      <c r="P3">
+        <v>0.34173150549586201</v>
+      </c>
+      <c r="Q3">
+        <v>0.68852661479560295</v>
+      </c>
+      <c r="R3">
+        <v>0.132581607713184</v>
+      </c>
+      <c r="S3">
+        <v>0.326925672129672</v>
+      </c>
+      <c r="T3">
+        <v>4.01908697363242E-2</v>
+      </c>
+      <c r="U3">
+        <v>0.25819067296339998</v>
+      </c>
+      <c r="V3">
+        <v>0.28904012083123498</v>
+      </c>
+      <c r="W3">
+        <v>0.27978680925678301</v>
+      </c>
+      <c r="X3">
+        <v>0.20964491448342201</v>
+      </c>
+      <c r="Y3">
+        <v>0.52822314565461603</v>
+      </c>
+      <c r="Z3">
+        <v>0.218027636586549</v>
+      </c>
+      <c r="AA3">
+        <v>0.13473474496181401</v>
+      </c>
+      <c r="AB3">
+        <v>0.15169147100961899</v>
+      </c>
+      <c r="AC3">
+        <v>1.33621823923277E-2</v>
+      </c>
+      <c r="AD3">
+        <v>0.22900704872816399</v>
+      </c>
+      <c r="AE3">
+        <v>0.35110838696496</v>
+      </c>
+      <c r="AF3">
+        <v>0.33970363079615001</v>
+      </c>
+      <c r="AG3">
+        <v>0.473507217847769</v>
+      </c>
+      <c r="AH3">
+        <v>0.71232550383534199</v>
+      </c>
+      <c r="AI3">
+        <v>0.51803325551479296</v>
+      </c>
+      <c r="AJ3">
+        <v>0.20410306508731199</v>
+      </c>
+      <c r="AK3">
+        <v>0.53185981194285004</v>
+      </c>
+      <c r="AL3">
+        <v>0.26164732215382902</v>
+      </c>
+      <c r="AM3">
+        <v>0.28960811566995698</v>
+      </c>
+      <c r="AN3">
+        <v>0.36618513590572099</v>
+      </c>
+      <c r="AO3">
+        <v>0.50058924158905105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4">
+        <v>0.37045950383482101</v>
+      </c>
+      <c r="C4">
+        <v>0.41566766379523601</v>
+      </c>
+      <c r="D4">
+        <v>0.108069164265129</v>
+      </c>
+      <c r="E4">
+        <v>0.118374890364615</v>
+      </c>
+      <c r="F4">
+        <v>0.19615831383310001</v>
+      </c>
+      <c r="G4">
+        <v>0.26033231763775</v>
+      </c>
+      <c r="H4">
+        <v>0.25801898023742298</v>
+      </c>
+      <c r="I4">
+        <v>0.35149154733154098</v>
+      </c>
+      <c r="J4">
+        <v>6.0388839108962401E-2</v>
+      </c>
+      <c r="K4">
+        <v>4.9990622851069998E-2</v>
+      </c>
+      <c r="L4">
+        <v>0.19373952700951799</v>
+      </c>
+      <c r="M4">
+        <v>0.16620311987147299</v>
+      </c>
+      <c r="N4">
+        <v>0.65381430779421501</v>
+      </c>
+      <c r="O4">
+        <v>0.38024398321925301</v>
+      </c>
+      <c r="P4">
+        <v>5.6131900703964399E-2</v>
+      </c>
+      <c r="Q4">
+        <v>0.22852085134411901</v>
+      </c>
+      <c r="R4">
+        <v>0.42654930950203102</v>
+      </c>
+      <c r="S4">
+        <v>0.44551738615405301</v>
+      </c>
+      <c r="T4">
+        <v>0.16135379771743399</v>
+      </c>
+      <c r="U4">
+        <v>0.13474025974025899</v>
+      </c>
+      <c r="V4">
+        <v>7.3175812919914499E-2</v>
+      </c>
+      <c r="W4">
+        <v>0.35603548549504299</v>
+      </c>
+      <c r="X4">
+        <v>7.6367462681243406E-2</v>
+      </c>
+      <c r="Y4">
+        <v>0.17344081610814799</v>
+      </c>
+      <c r="Z4">
+        <v>0.42456131388725699</v>
+      </c>
+      <c r="AA4">
+        <v>0.64189931291665603</v>
+      </c>
+      <c r="AB4">
+        <v>0.78515248092161005</v>
+      </c>
+      <c r="AC4">
+        <v>0.96657992456360897</v>
+      </c>
+      <c r="AD4">
+        <v>7.8608642353662203E-2</v>
+      </c>
+      <c r="AE4">
+        <v>0.140770252324037</v>
+      </c>
+      <c r="AF4">
+        <v>0.33051727909011303</v>
+      </c>
+      <c r="AG4">
+        <v>0.46855861767279</v>
+      </c>
+      <c r="AH4">
+        <v>7.3467054171232504E-2</v>
+      </c>
+      <c r="AI4">
+        <v>0.48196674448520599</v>
+      </c>
+      <c r="AJ4">
+        <v>6.8042496031261404E-2</v>
+      </c>
+      <c r="AK4">
+        <v>0.33659787519843598</v>
+      </c>
+      <c r="AL4">
+        <v>3.9621653820466E-2</v>
+      </c>
+      <c r="AM4">
+        <v>0.55623747721077998</v>
+      </c>
+      <c r="AN4">
+        <v>8.2455806880821103E-2</v>
+      </c>
+      <c r="AO4">
+        <v>0.27099410758410902</v>
+      </c>
+    </row>
+    <row r="6" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J6" t="s">
+        <v>81</v>
+      </c>
+      <c r="K6" t="s">
+        <v>82</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="M6" t="s">
+        <v>84</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="U6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="B7">
+        <v>0.86337464113650297</v>
+      </c>
+      <c r="C7">
+        <v>0.75723464302009702</v>
+      </c>
+      <c r="D7">
+        <v>0.82919679701550697</v>
+      </c>
+      <c r="E7">
+        <v>0.81807318827423203</v>
+      </c>
+      <c r="F7">
+        <v>0.83794421772255701</v>
+      </c>
+      <c r="G7">
+        <v>0.83649993459370497</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.85515778133937703</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.68241308726725503</v>
+      </c>
+      <c r="J7">
+        <v>0.89546798274557404</v>
+      </c>
+      <c r="K7">
+        <v>0.929829114228505</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0.48798560027497401</v>
+      </c>
+      <c r="M7">
+        <v>0.644813503873365</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0.53651404360751698</v>
+      </c>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2">
+        <v>0.79008838992736796</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0.84159119342196398</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0.61135885828034597</v>
+      </c>
+      <c r="S7" s="2">
+        <v>0.71203412957918499</v>
+      </c>
+      <c r="T7" s="2">
+        <v>0.657101505866444</v>
+      </c>
+      <c r="U7">
+        <v>0.77887246177411396</v>
+      </c>
+    </row>
+    <row r="8" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="L8" s="2"/>
+    </row>
+    <row r="9" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="I9" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="U9" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="W9" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="I10" s="5">
+        <f>AVERAGE(B7:I7)</f>
+        <v>0.80998678629615406</v>
+      </c>
+      <c r="U10" s="5">
+        <f>AVERAGE(J7:U7)</f>
+        <v>0.71687788941630504</v>
+      </c>
+      <c r="W10" s="5">
+        <f>AVERAGE(I10,U10)</f>
+        <v>0.76343233785622955</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20C27C4F-7112-48CC-8600-645EA3A54793}">
+  <dimension ref="A1:U3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="8" max="9" width="8.7265625" style="2"/>
+    <col min="12" max="12" width="8.7265625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="M1" t="s">
+        <v>84</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="U1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2">
+        <v>0.86276146222643102</v>
+      </c>
+      <c r="C2">
+        <v>0.74074689803015803</v>
+      </c>
+      <c r="D2">
+        <v>0.85054928065416602</v>
+      </c>
+      <c r="E2">
+        <v>0.81814633616452004</v>
+      </c>
+      <c r="F2">
+        <v>0.79085038760443604</v>
+      </c>
+      <c r="G2">
+        <v>0.78505091998955501</v>
+      </c>
+      <c r="H2" s="2">
+        <v>-0.33398042471309602</v>
+      </c>
+      <c r="I2" s="2">
+        <v>2.2800072977221301E-2</v>
+      </c>
+      <c r="J2">
+        <v>0.81491130084522601</v>
+      </c>
+      <c r="K2">
+        <v>0.86785674397944002</v>
+      </c>
+      <c r="L2" s="5">
+        <v>-8.4598923649412197E-2</v>
+      </c>
+      <c r="M2">
+        <v>0.21799042590743101</v>
+      </c>
+      <c r="N2" s="5">
+        <v>-8.6805497576840196E-2</v>
+      </c>
+      <c r="O2" s="2">
+        <v>-9.8060428060056895E-2</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0.29753922699669499</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>0.195374044392325</v>
+      </c>
+      <c r="R2" s="2">
+        <v>0.35849302300033697</v>
+      </c>
+      <c r="S2" s="2">
+        <v>-0.279845157467007</v>
+      </c>
+      <c r="T2" s="2">
+        <v>0.12539529152194401</v>
+      </c>
+      <c r="U2">
+        <v>0.64309151947275001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3">
+        <v>0.86337464113650297</v>
+      </c>
+      <c r="C3">
+        <v>0.75723464302009702</v>
+      </c>
+      <c r="D3">
+        <v>0.82919679701550697</v>
+      </c>
+      <c r="E3">
+        <v>0.81807318827423203</v>
+      </c>
+      <c r="F3">
+        <v>0.83794421772255701</v>
+      </c>
+      <c r="G3">
+        <v>0.83649993459370497</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.85515778133937703</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0.68241308726725503</v>
+      </c>
+      <c r="J3">
+        <v>0.89546798274557404</v>
+      </c>
+      <c r="K3">
+        <v>0.929829114228505</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0.48798560027497401</v>
+      </c>
+      <c r="M3">
+        <v>0.644813503873365</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0.53651404360751698</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0.116225612867807</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0.79008838992736796</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>0.84159119342196398</v>
+      </c>
+      <c r="R3" s="2">
+        <v>0.61135885828034597</v>
+      </c>
+      <c r="S3" s="2">
+        <v>0.71203412957918499</v>
+      </c>
+      <c r="T3" s="2">
+        <v>0.657101505866444</v>
+      </c>
+      <c r="U3">
+        <v>0.77887246177411396</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/annotations/TE_discrete_percentages.xlsx
+++ b/data/annotations/TE_discrete_percentages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dobregeo\Documents\GitHub\vilearn_ml\data\annotations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{BF42F981-D633-42A3-9A31-78C18F46FEC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{FA16EFE5-F483-4B50-BE03-C341E916414E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="4" xr2:uid="{8450E3AB-A0C1-455F-AE9B-DBE7A60F6C99}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" activeTab="2" xr2:uid="{8450E3AB-A0C1-455F-AE9B-DBE7A60F6C99}"/>
   </bookViews>
   <sheets>
     <sheet name="TE_discrete_percentages" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="103">
   <si>
     <t>task_eng</t>
   </si>
@@ -322,6 +322,18 @@
   </si>
   <si>
     <t>dyads</t>
+  </si>
+  <si>
+    <t>.8 as top interval and then equal split</t>
+  </si>
+  <si>
+    <t xml:space="preserve">three way might be dificult to get good results; try also </t>
+  </si>
+  <si>
+    <t>Continous</t>
+  </si>
+  <si>
+    <t>Discrete</t>
   </si>
 </sst>
 </file>
@@ -32366,6 +32378,23 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13" spans="1:108" x14ac:dyDescent="0.35">
+      <c r="BO13" t="s">
+        <v>52</v>
+      </c>
+      <c r="BP13" t="s">
+        <v>53</v>
+      </c>
+      <c r="BQ13" t="s">
+        <v>51</v>
+      </c>
+      <c r="BS13" t="s">
+        <v>52</v>
+      </c>
+      <c r="BT13" t="s">
+        <v>51</v>
+      </c>
+    </row>
     <row r="14" spans="1:108" x14ac:dyDescent="0.35">
       <c r="BI14" t="s">
         <v>71</v>
@@ -32378,6 +32407,21 @@
       </c>
       <c r="BL14" t="s">
         <v>70</v>
+      </c>
+      <c r="BO14">
+        <v>0.26600000000000001</v>
+      </c>
+      <c r="BP14">
+        <v>0.52600000000000002</v>
+      </c>
+      <c r="BQ14">
+        <v>0.78659999999999997</v>
+      </c>
+      <c r="BS14">
+        <v>0.4</v>
+      </c>
+      <c r="BT14">
+        <v>0.8</v>
       </c>
     </row>
     <row r="15" spans="1:108" x14ac:dyDescent="0.35">
@@ -32393,9 +32437,16 @@
       <c r="BL15" t="s">
         <v>67</v>
       </c>
+      <c r="BN15" s="2"/>
+      <c r="BO15" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="BS15" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="16" spans="1:108" x14ac:dyDescent="0.35">
-      <c r="BR16" t="s">
+      <c r="BR16" s="5" t="s">
         <v>64</v>
       </c>
     </row>
@@ -33329,7 +33380,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4135E192-98BF-45B4-BA3D-15FECDE552EF}">
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -33957,150 +34008,263 @@
         <v>0.27099410758410902</v>
       </c>
     </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.35">
-      <c r="B6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F6" t="s">
-        <v>77</v>
-      </c>
-      <c r="G6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H6" t="s">
-        <v>79</v>
-      </c>
-      <c r="I6" t="s">
-        <v>80</v>
-      </c>
-      <c r="J6" t="s">
-        <v>81</v>
-      </c>
-      <c r="K6" t="s">
-        <v>82</v>
-      </c>
-      <c r="L6" t="s">
-        <v>83</v>
-      </c>
-      <c r="M6" t="s">
-        <v>84</v>
-      </c>
-      <c r="N6" t="s">
-        <v>85</v>
-      </c>
-      <c r="O6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P6" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>88</v>
-      </c>
-      <c r="R6" t="s">
-        <v>89</v>
-      </c>
-      <c r="S6" t="s">
-        <v>90</v>
-      </c>
-      <c r="T6" t="s">
-        <v>91</v>
-      </c>
-      <c r="U6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.35">
-      <c r="B7">
-        <v>0.85629482756780495</v>
-      </c>
-      <c r="C7">
-        <v>0.72480082067718599</v>
-      </c>
-      <c r="D7">
-        <v>0.82777645880776596</v>
-      </c>
-      <c r="E7">
-        <v>0.82659452725981197</v>
-      </c>
-      <c r="F7">
-        <v>0.79078960048874103</v>
-      </c>
-      <c r="G7">
-        <v>0.83794847262402505</v>
-      </c>
-      <c r="H7">
-        <v>0.832584473541637</v>
-      </c>
-      <c r="I7">
-        <v>0.64171827186225805</v>
-      </c>
-      <c r="J7">
-        <v>0.86231599498596401</v>
-      </c>
-      <c r="K7">
-        <v>0.86957035714180098</v>
-      </c>
-      <c r="L7">
-        <v>0.53891218808139896</v>
-      </c>
-      <c r="M7">
-        <v>0.59137022905749004</v>
-      </c>
-      <c r="N7">
-        <v>0.44227699763089001</v>
-      </c>
-      <c r="P7">
-        <v>0.75878204633194901</v>
-      </c>
-      <c r="Q7">
-        <v>0.77646361437990297</v>
-      </c>
-      <c r="R7">
-        <v>0.57801020824920901</v>
-      </c>
-      <c r="S7">
-        <v>0.67676370745270498</v>
-      </c>
-      <c r="T7">
-        <v>0.61168228428765803</v>
-      </c>
-      <c r="U7">
-        <v>0.75541379016388399</v>
-      </c>
-    </row>
     <row r="8" spans="1:51" x14ac:dyDescent="0.35">
-      <c r="I8" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="U8" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="W8" s="5" t="s">
-        <v>96</v>
-      </c>
+      <c r="I8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="W8" s="5"/>
     </row>
     <row r="9" spans="1:51" x14ac:dyDescent="0.35">
-      <c r="I9" s="5">
-        <f>AVERAGE(B7:I7)</f>
-        <v>0.79231343160365375</v>
-      </c>
-      <c r="U9" s="5">
-        <f>AVERAGE(J7:U7)</f>
-        <v>0.67832376525116833</v>
-      </c>
-      <c r="W9" s="5">
-        <f>AVERAGE(I9,U9)</f>
-        <v>0.7353185984274111</v>
+      <c r="I9" s="5"/>
+      <c r="U9" s="5"/>
+      <c r="W9" s="5"/>
+    </row>
+    <row r="10" spans="1:51" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" t="s">
+        <v>79</v>
+      </c>
+      <c r="I10" t="s">
+        <v>80</v>
+      </c>
+      <c r="J10" t="s">
+        <v>81</v>
+      </c>
+      <c r="K10" t="s">
+        <v>82</v>
+      </c>
+      <c r="L10" t="s">
+        <v>83</v>
+      </c>
+      <c r="M10" t="s">
+        <v>84</v>
+      </c>
+      <c r="N10" t="s">
+        <v>85</v>
+      </c>
+      <c r="O10" t="s">
+        <v>86</v>
+      </c>
+      <c r="P10" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>88</v>
+      </c>
+      <c r="R10" t="s">
+        <v>89</v>
+      </c>
+      <c r="S10" t="s">
+        <v>90</v>
+      </c>
+      <c r="T10" t="s">
+        <v>91</v>
+      </c>
+      <c r="U10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:51" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11">
+        <v>0.86276146222643102</v>
+      </c>
+      <c r="C11">
+        <v>0.74074689803015803</v>
+      </c>
+      <c r="D11">
+        <v>0.85054928065416602</v>
+      </c>
+      <c r="E11">
+        <v>0.81814441680772598</v>
+      </c>
+      <c r="F11">
+        <v>0.79085038760443604</v>
+      </c>
+      <c r="G11">
+        <v>0.78504247080995204</v>
+      </c>
+      <c r="H11">
+        <v>0.86401203098463697</v>
+      </c>
+      <c r="I11">
+        <v>0.71166563560714802</v>
+      </c>
+      <c r="J11">
+        <v>0.81491130084522601</v>
+      </c>
+      <c r="K11">
+        <v>0.86785674397944002</v>
+      </c>
+      <c r="L11">
+        <v>0.33721816546926398</v>
+      </c>
+      <c r="M11">
+        <v>0.69365086432215095</v>
+      </c>
+      <c r="N11">
+        <v>0.68848032279059901</v>
+      </c>
+      <c r="O11">
+        <v>0.449340985843523</v>
+      </c>
+      <c r="P11">
+        <v>0.81228571162530305</v>
+      </c>
+      <c r="Q11">
+        <v>0.83411116863041002</v>
+      </c>
+      <c r="R11">
+        <v>0.64685998237570397</v>
+      </c>
+      <c r="S11">
+        <v>0.73210706007850201</v>
+      </c>
+      <c r="T11">
+        <v>0.705625661637861</v>
+      </c>
+      <c r="U11">
+        <v>0.86637849019393798</v>
+      </c>
+    </row>
+    <row r="12" spans="1:51" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12">
+        <v>0.85352349983328701</v>
+      </c>
+      <c r="C12">
+        <v>0.724798315377438</v>
+      </c>
+      <c r="D12">
+        <v>0.82777645880776596</v>
+      </c>
+      <c r="E12">
+        <v>0.82784987948012601</v>
+      </c>
+      <c r="F12">
+        <v>0.79161955238377801</v>
+      </c>
+      <c r="G12">
+        <v>0.84375318356718498</v>
+      </c>
+      <c r="H12">
+        <v>0.79807061278984004</v>
+      </c>
+      <c r="I12">
+        <v>0.64715346567446697</v>
+      </c>
+      <c r="J12">
+        <v>0.86269506552383102</v>
+      </c>
+      <c r="K12">
+        <v>0.86957035714180098</v>
+      </c>
+      <c r="L12">
+        <v>0.58038210611443397</v>
+      </c>
+      <c r="M12">
+        <v>0.59977673890186201</v>
+      </c>
+      <c r="N12">
+        <v>0.45591494839174301</v>
+      </c>
+      <c r="O12">
+        <v>0.105153463433959</v>
+      </c>
+      <c r="P12">
+        <v>0.75883908005948497</v>
+      </c>
+      <c r="Q12">
+        <v>0.77796162730809604</v>
+      </c>
+      <c r="R12">
+        <v>0.57801020824920901</v>
+      </c>
+      <c r="S12">
+        <v>0.68423457878454397</v>
+      </c>
+      <c r="T12">
+        <v>0.61375646710571996</v>
+      </c>
+      <c r="U12">
+        <v>0.76635249505233505</v>
+      </c>
+    </row>
+    <row r="13" spans="1:51" x14ac:dyDescent="0.35">
+      <c r="I13" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="U13" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="X13" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:51" x14ac:dyDescent="0.35">
+      <c r="H14" t="s">
+        <v>101</v>
+      </c>
+      <c r="I14" s="5">
+        <f>AVERAGE(B11:I11)</f>
+        <v>0.80297157284058174</v>
+      </c>
+      <c r="T14" t="s">
+        <v>101</v>
+      </c>
+      <c r="U14" s="5">
+        <f>AVERAGE(J11:U11)</f>
+        <v>0.70406887148266017</v>
+      </c>
+      <c r="W14" t="s">
+        <v>101</v>
+      </c>
+      <c r="X14" s="5">
+        <f>AVERAGE(I14,U14)</f>
+        <v>0.75352022216162096</v>
+      </c>
+    </row>
+    <row r="15" spans="1:51" x14ac:dyDescent="0.35">
+      <c r="H15" t="s">
+        <v>102</v>
+      </c>
+      <c r="I15" s="5">
+        <f>AVERAGE(B12:I12)</f>
+        <v>0.78931812098923593</v>
+      </c>
+      <c r="T15" t="s">
+        <v>102</v>
+      </c>
+      <c r="U15" s="5">
+        <f>AVERAGE(J12:U12)</f>
+        <v>0.6377205946722514</v>
+      </c>
+      <c r="W15" t="s">
+        <v>102</v>
+      </c>
+      <c r="X15" s="5">
+        <f>AVERAGE(I15,U15)</f>
+        <v>0.71351935783074372</v>
       </c>
     </row>
   </sheetData>
@@ -34114,7 +34278,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6E884E-4278-4958-AEF6-CE3AB5C8D996}">
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
@@ -34136,10 +34300,10 @@
       <c r="G1" t="s">
         <v>78</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="5" t="s">
         <v>80</v>
       </c>
       <c r="J1" t="s">
@@ -34201,10 +34365,10 @@
       <c r="G2">
         <v>0.78505091998955501</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="5">
         <v>-0.33398042471309602</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="5">
         <v>2.2800072977221301E-2</v>
       </c>
       <c r="J2">
@@ -34266,10 +34430,10 @@
       <c r="G3">
         <v>0.83794847262402505</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="5">
         <v>0.832584473541637</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="5">
         <v>0.64171827186225805</v>
       </c>
       <c r="J3">
@@ -34287,7 +34451,7 @@
       <c r="N3">
         <v>0.44227699763089001</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="5">
         <v>0.106638622511867</v>
       </c>
       <c r="P3">
@@ -34307,6 +34471,198 @@
       </c>
       <c r="U3">
         <v>0.75541379016388399</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" t="s">
+        <v>78</v>
+      </c>
+      <c r="H5" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5" t="s">
+        <v>80</v>
+      </c>
+      <c r="J5" t="s">
+        <v>81</v>
+      </c>
+      <c r="K5" t="s">
+        <v>82</v>
+      </c>
+      <c r="L5" t="s">
+        <v>83</v>
+      </c>
+      <c r="M5" t="s">
+        <v>84</v>
+      </c>
+      <c r="N5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O5" t="s">
+        <v>86</v>
+      </c>
+      <c r="P5" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>88</v>
+      </c>
+      <c r="R5" t="s">
+        <v>89</v>
+      </c>
+      <c r="S5" t="s">
+        <v>90</v>
+      </c>
+      <c r="T5" t="s">
+        <v>91</v>
+      </c>
+      <c r="U5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6">
+        <v>0.86276146222643102</v>
+      </c>
+      <c r="C6">
+        <v>0.74074689803015803</v>
+      </c>
+      <c r="D6">
+        <v>0.85054928065416602</v>
+      </c>
+      <c r="E6">
+        <v>0.81814441680772598</v>
+      </c>
+      <c r="F6">
+        <v>0.79085038760443604</v>
+      </c>
+      <c r="G6">
+        <v>0.78504247080995204</v>
+      </c>
+      <c r="H6">
+        <v>0.86401203098463697</v>
+      </c>
+      <c r="I6">
+        <v>0.71166563560714802</v>
+      </c>
+      <c r="J6">
+        <v>0.81491130084522601</v>
+      </c>
+      <c r="K6">
+        <v>0.86785674397944002</v>
+      </c>
+      <c r="L6">
+        <v>0.33721816546926398</v>
+      </c>
+      <c r="M6">
+        <v>0.69365086432215095</v>
+      </c>
+      <c r="N6">
+        <v>0.68848032279059901</v>
+      </c>
+      <c r="O6">
+        <v>0.449340985843523</v>
+      </c>
+      <c r="P6">
+        <v>0.81228571162530305</v>
+      </c>
+      <c r="Q6">
+        <v>0.83411116863041002</v>
+      </c>
+      <c r="R6">
+        <v>0.64685998237570397</v>
+      </c>
+      <c r="S6">
+        <v>0.73210706007850201</v>
+      </c>
+      <c r="T6">
+        <v>0.705625661637861</v>
+      </c>
+      <c r="U6">
+        <v>0.86637849019393798</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7">
+        <v>0.85352349983328701</v>
+      </c>
+      <c r="C7">
+        <v>0.724798315377438</v>
+      </c>
+      <c r="D7">
+        <v>0.82777645880776596</v>
+      </c>
+      <c r="E7">
+        <v>0.82784987948012601</v>
+      </c>
+      <c r="F7">
+        <v>0.79161955238377801</v>
+      </c>
+      <c r="G7">
+        <v>0.84375318356718498</v>
+      </c>
+      <c r="H7">
+        <v>0.79807061278984004</v>
+      </c>
+      <c r="I7">
+        <v>0.64715346567446697</v>
+      </c>
+      <c r="J7">
+        <v>0.86269506552383102</v>
+      </c>
+      <c r="K7">
+        <v>0.86957035714180098</v>
+      </c>
+      <c r="L7">
+        <v>0.58038210611443397</v>
+      </c>
+      <c r="M7">
+        <v>0.59977673890186201</v>
+      </c>
+      <c r="N7">
+        <v>0.45591494839174301</v>
+      </c>
+      <c r="O7">
+        <v>0.105153463433959</v>
+      </c>
+      <c r="P7">
+        <v>0.75883908005948497</v>
+      </c>
+      <c r="Q7">
+        <v>0.77796162730809604</v>
+      </c>
+      <c r="R7">
+        <v>0.57801020824920901</v>
+      </c>
+      <c r="S7">
+        <v>0.68423457878454397</v>
+      </c>
+      <c r="T7">
+        <v>0.61375646710571996</v>
+      </c>
+      <c r="U7">
+        <v>0.76635249505233505</v>
       </c>
     </row>
   </sheetData>

--- a/data/annotations/TE_discrete_percentages.xlsx
+++ b/data/annotations/TE_discrete_percentages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dobregeo\Documents\GitHub\vilearn_ml\data\annotations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{FA16EFE5-F483-4B50-BE03-C341E916414E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{AF11CD2B-0494-416B-A28E-F9A75972BCAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" activeTab="2" xr2:uid="{8450E3AB-A0C1-455F-AE9B-DBE7A60F6C99}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" firstSheet="2" activeTab="2" xr2:uid="{8450E3AB-A0C1-455F-AE9B-DBE7A60F6C99}"/>
   </bookViews>
   <sheets>
     <sheet name="TE_discrete_percentages" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="112">
   <si>
     <t>task_eng</t>
   </si>
@@ -334,6 +334,33 @@
   </si>
   <si>
     <t>Discrete</t>
+  </si>
+  <si>
+    <t>.2666 .5333</t>
+  </si>
+  <si>
+    <t>.2333 .4666</t>
+  </si>
+  <si>
+    <t>avg dyads</t>
+  </si>
+  <si>
+    <t>avg triads</t>
+  </si>
+  <si>
+    <t>avg all</t>
+  </si>
+  <si>
+    <t>.2 .4</t>
+  </si>
+  <si>
+    <t>max val .6</t>
+  </si>
+  <si>
+    <t>max val .7</t>
+  </si>
+  <si>
+    <t>max val .8</t>
   </si>
 </sst>
 </file>
@@ -32450,7 +32477,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="58:83" x14ac:dyDescent="0.35">
+    <row r="17" spans="58:87" x14ac:dyDescent="0.35">
       <c r="BF17" t="s">
         <v>0</v>
       </c>
@@ -32529,8 +32556,17 @@
       <c r="CE17" t="s">
         <v>50</v>
       </c>
+      <c r="CG17" t="s">
+        <v>105</v>
+      </c>
+      <c r="CH17" t="s">
+        <v>106</v>
+      </c>
+      <c r="CI17" t="s">
+        <v>107</v>
+      </c>
     </row>
-    <row r="18" spans="58:83" x14ac:dyDescent="0.35">
+    <row r="18" spans="58:87" x14ac:dyDescent="0.35">
       <c r="BF18" t="s">
         <v>63</v>
       </c>
@@ -32609,8 +32645,20 @@
       <c r="CE18">
         <v>0.11149971488310199</v>
       </c>
+      <c r="CG18">
+        <f>AVERAGE(Table245[[#This Row],[dyad_01_anno02]:[dyad_11_anno02]])</f>
+        <v>0.22317653602407225</v>
+      </c>
+      <c r="CH18">
+        <f>AVERAGE(Table245[[#This Row],[triad_01_anno02]:[triad_14_anno02]])</f>
+        <v>0.23371544919232798</v>
+      </c>
+      <c r="CI18">
+        <f>AVERAGE(Table245[[#This Row],[dyad_01_anno02]:[triad_14_anno02]])</f>
+        <v>0.22907832739829545</v>
+      </c>
     </row>
-    <row r="19" spans="58:83" x14ac:dyDescent="0.35">
+    <row r="19" spans="58:87" x14ac:dyDescent="0.35">
       <c r="BF19" t="s">
         <v>58</v>
       </c>
@@ -32689,8 +32737,20 @@
       <c r="CE19">
         <v>6.8561110055122595E-2</v>
       </c>
+      <c r="CG19">
+        <f>AVERAGE(Table245[[#This Row],[dyad_01_anno02]:[dyad_11_anno02]])</f>
+        <v>6.9687070137527743E-2</v>
+      </c>
+      <c r="CH19">
+        <f>AVERAGE(Table245[[#This Row],[triad_01_anno02]:[triad_14_anno02]])</f>
+        <v>9.4698432668246485E-2</v>
+      </c>
+      <c r="CI19">
+        <f>AVERAGE(Table245[[#This Row],[dyad_01_anno02]:[triad_14_anno02]])</f>
+        <v>8.369343315473024E-2</v>
+      </c>
     </row>
-    <row r="20" spans="58:83" x14ac:dyDescent="0.35">
+    <row r="20" spans="58:87" x14ac:dyDescent="0.35">
       <c r="BF20" t="s">
         <v>56</v>
       </c>
@@ -32769,8 +32829,20 @@
       <c r="CE20">
         <v>0.112621174681619</v>
       </c>
+      <c r="CG20">
+        <f>AVERAGE(Table245[[#This Row],[dyad_01_anno02]:[dyad_11_anno02]])</f>
+        <v>0.10842778079815268</v>
+      </c>
+      <c r="CH20">
+        <f>AVERAGE(Table245[[#This Row],[triad_01_anno02]:[triad_14_anno02]])</f>
+        <v>0.15155441477166101</v>
+      </c>
+      <c r="CI20">
+        <f>AVERAGE(Table245[[#This Row],[dyad_01_anno02]:[triad_14_anno02]])</f>
+        <v>0.13257869582331736</v>
+      </c>
     </row>
-    <row r="21" spans="58:83" x14ac:dyDescent="0.35">
+    <row r="21" spans="58:87" x14ac:dyDescent="0.35">
       <c r="BF21" t="s">
         <v>60</v>
       </c>
@@ -32849,8 +32921,20 @@
       <c r="CE21">
         <v>0.34725337388329203</v>
       </c>
+      <c r="CG21">
+        <f>AVERAGE(Table245[[#This Row],[dyad_01_anno02]:[dyad_11_anno02]])</f>
+        <v>7.6465585566684119E-2</v>
+      </c>
+      <c r="CH21">
+        <f>AVERAGE(Table245[[#This Row],[triad_01_anno02]:[triad_14_anno02]])</f>
+        <v>0.14259582684220984</v>
+      </c>
+      <c r="CI21">
+        <f>AVERAGE(Table245[[#This Row],[dyad_01_anno02]:[triad_14_anno02]])</f>
+        <v>0.11349852068097854</v>
+      </c>
     </row>
-    <row r="22" spans="58:83" x14ac:dyDescent="0.35">
+    <row r="22" spans="58:87" x14ac:dyDescent="0.35">
       <c r="BF22" t="s">
         <v>57</v>
       </c>
@@ -32929,8 +33013,20 @@
       <c r="CE22">
         <v>0.13164797567002401</v>
       </c>
+      <c r="CG22">
+        <f>AVERAGE(Table245[[#This Row],[dyad_01_anno02]:[dyad_11_anno02]])</f>
+        <v>0.13858417753547853</v>
+      </c>
+      <c r="CH22">
+        <f>AVERAGE(Table245[[#This Row],[triad_01_anno02]:[triad_14_anno02]])</f>
+        <v>0.14480217417267682</v>
+      </c>
+      <c r="CI22">
+        <f>AVERAGE(Table245[[#This Row],[dyad_01_anno02]:[triad_14_anno02]])</f>
+        <v>0.14206625565230954</v>
+      </c>
     </row>
-    <row r="23" spans="58:83" x14ac:dyDescent="0.35">
+    <row r="23" spans="58:87" x14ac:dyDescent="0.35">
       <c r="BF23" t="s">
         <v>59</v>
       </c>
@@ -33009,8 +33105,20 @@
       <c r="CE23">
         <v>0.21199391750617699</v>
       </c>
+      <c r="CG23">
+        <f>AVERAGE(Table245[[#This Row],[dyad_01_anno02]:[dyad_11_anno02]])</f>
+        <v>0.21325781237195046</v>
+      </c>
+      <c r="CH23">
+        <f>AVERAGE(Table245[[#This Row],[triad_01_anno02]:[triad_14_anno02]])</f>
+        <v>0.16035287715031482</v>
+      </c>
+      <c r="CI23">
+        <f>AVERAGE(Table245[[#This Row],[dyad_01_anno02]:[triad_14_anno02]])</f>
+        <v>0.18363104864783453</v>
+      </c>
     </row>
-    <row r="24" spans="58:83" x14ac:dyDescent="0.35">
+    <row r="24" spans="58:87" x14ac:dyDescent="0.35">
       <c r="BF24" t="s">
         <v>61</v>
       </c>
@@ -33089,8 +33197,20 @@
       <c r="CE24">
         <v>0</v>
       </c>
+      <c r="CG24">
+        <f>AVERAGE(Table245[[#This Row],[dyad_01_anno02]:[dyad_11_anno02]])</f>
+        <v>6.8800710984991895E-2</v>
+      </c>
+      <c r="CH24">
+        <f>AVERAGE(Table245[[#This Row],[triad_01_anno02]:[triad_14_anno02]])</f>
+        <v>2.6570163231044684E-2</v>
+      </c>
+      <c r="CI24">
+        <f>AVERAGE(Table245[[#This Row],[dyad_01_anno02]:[triad_14_anno02]])</f>
+        <v>4.515160424278146E-2</v>
+      </c>
     </row>
-    <row r="25" spans="58:83" x14ac:dyDescent="0.35">
+    <row r="25" spans="58:87" x14ac:dyDescent="0.35">
       <c r="BF25" t="s">
         <v>62</v>
       </c>
@@ -33169,8 +33289,20 @@
       <c r="CE25">
         <v>0</v>
       </c>
+      <c r="CG25">
+        <f>AVERAGE(Table245[[#This Row],[dyad_01_anno02]:[dyad_11_anno02]])</f>
+        <v>5.1645360089820173E-2</v>
+      </c>
+      <c r="CH25">
+        <f>AVERAGE(Table245[[#This Row],[triad_01_anno02]:[triad_14_anno02]])</f>
+        <v>1.0945230068736001E-5</v>
+      </c>
+      <c r="CI25">
+        <f>AVERAGE(Table245[[#This Row],[dyad_01_anno02]:[triad_14_anno02]])</f>
+        <v>2.2730087768359369E-2</v>
+      </c>
     </row>
-    <row r="26" spans="58:83" x14ac:dyDescent="0.35">
+    <row r="26" spans="58:87" x14ac:dyDescent="0.35">
       <c r="BF26" t="s">
         <v>55</v>
       </c>
@@ -33249,8 +33381,20 @@
       <c r="CE26">
         <v>0</v>
       </c>
+      <c r="CG26">
+        <f>AVERAGE(Table245[[#This Row],[dyad_01_anno02]:[dyad_11_anno02]])</f>
+        <v>3.1286163143248728E-3</v>
+      </c>
+      <c r="CH26">
+        <f>AVERAGE(Table245[[#This Row],[triad_01_anno02]:[triad_14_anno02]])</f>
+        <v>4.3051238270361714E-4</v>
+      </c>
+      <c r="CI26">
+        <f>AVERAGE(Table245[[#This Row],[dyad_01_anno02]:[triad_14_anno02]])</f>
+        <v>1.6176781126169698E-3</v>
+      </c>
     </row>
-    <row r="27" spans="58:83" x14ac:dyDescent="0.35">
+    <row r="27" spans="58:87" x14ac:dyDescent="0.35">
       <c r="BF27" t="s">
         <v>54</v>
       </c>
@@ -33327,6 +33471,18 @@
         <v>0</v>
       </c>
       <c r="CE27">
+        <v>0</v>
+      </c>
+      <c r="CG27">
+        <f>AVERAGE(Table245[[#This Row],[dyad_01_anno02]:[dyad_11_anno02]])</f>
+        <v>0</v>
+      </c>
+      <c r="CH27">
+        <f>AVERAGE(Table245[[#This Row],[triad_01_anno02]:[triad_14_anno02]])</f>
+        <v>0</v>
+      </c>
+      <c r="CI27">
+        <f>AVERAGE(Table245[[#This Row],[dyad_01_anno02]:[triad_14_anno02]])</f>
         <v>0</v>
       </c>
     </row>
@@ -34094,19 +34250,19 @@
         <v>0.85054928065416602</v>
       </c>
       <c r="E11">
-        <v>0.81814441680772598</v>
+        <v>0.81632449232768201</v>
       </c>
       <c r="F11">
         <v>0.79085038760443604</v>
       </c>
       <c r="G11">
-        <v>0.78504247080995204</v>
+        <v>0.77813793483798299</v>
       </c>
       <c r="H11">
-        <v>0.86401203098463697</v>
+        <v>0.83075341522976798</v>
       </c>
       <c r="I11">
-        <v>0.71166563560714802</v>
+        <v>0.70869464818295702</v>
       </c>
       <c r="J11">
         <v>0.81491130084522601</v>
@@ -34115,34 +34271,34 @@
         <v>0.86785674397944002</v>
       </c>
       <c r="L11">
-        <v>0.33721816546926398</v>
+        <v>0.519005742862511</v>
       </c>
       <c r="M11">
-        <v>0.69365086432215095</v>
+        <v>0.69025879886924402</v>
       </c>
       <c r="N11">
-        <v>0.68848032279059901</v>
+        <v>0.65165587962521498</v>
       </c>
       <c r="O11">
-        <v>0.449340985843523</v>
+        <v>0.44824897491003401</v>
       </c>
       <c r="P11">
-        <v>0.81228571162530305</v>
+        <v>0.81223262502022398</v>
       </c>
       <c r="Q11">
-        <v>0.83411116863041002</v>
+        <v>0.83410906420998399</v>
       </c>
       <c r="R11">
         <v>0.64685998237570397</v>
       </c>
       <c r="S11">
-        <v>0.73210706007850201</v>
+        <v>0.73227374615366603</v>
       </c>
       <c r="T11">
-        <v>0.705625661637861</v>
+        <v>0.699216950339417</v>
       </c>
       <c r="U11">
-        <v>0.86637849019393798</v>
+        <v>0.86051623569899005</v>
       </c>
     </row>
     <row r="12" spans="1:51" x14ac:dyDescent="0.35">
@@ -34227,21 +34383,21 @@
       </c>
       <c r="I14" s="5">
         <f>AVERAGE(B11:I11)</f>
-        <v>0.80297157284058174</v>
+        <v>0.79735231488669767</v>
       </c>
       <c r="T14" t="s">
         <v>101</v>
       </c>
       <c r="U14" s="5">
         <f>AVERAGE(J11:U11)</f>
-        <v>0.70406887148266017</v>
+        <v>0.71476217040747125</v>
       </c>
       <c r="W14" t="s">
         <v>101</v>
       </c>
       <c r="X14" s="5">
         <f>AVERAGE(I14,U14)</f>
-        <v>0.75352022216162096</v>
+        <v>0.7560572426470844</v>
       </c>
     </row>
     <row r="15" spans="1:51" x14ac:dyDescent="0.35">
@@ -34278,7 +34434,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6E884E-4278-4958-AEF6-CE3AB5C8D996}">
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
@@ -34662,6 +34818,198 @@
         <v>0.61375646710571996</v>
       </c>
       <c r="U7">
+        <v>0.76635249505233505</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" t="s">
+        <v>76</v>
+      </c>
+      <c r="F9" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" t="s">
+        <v>79</v>
+      </c>
+      <c r="I9" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K9" t="s">
+        <v>82</v>
+      </c>
+      <c r="L9" t="s">
+        <v>83</v>
+      </c>
+      <c r="M9" t="s">
+        <v>84</v>
+      </c>
+      <c r="N9" t="s">
+        <v>85</v>
+      </c>
+      <c r="O9" t="s">
+        <v>86</v>
+      </c>
+      <c r="P9" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>88</v>
+      </c>
+      <c r="R9" t="s">
+        <v>89</v>
+      </c>
+      <c r="S9" t="s">
+        <v>90</v>
+      </c>
+      <c r="T9" t="s">
+        <v>91</v>
+      </c>
+      <c r="U9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10">
+        <v>0.86276146222643102</v>
+      </c>
+      <c r="C10">
+        <v>0.74074689803015803</v>
+      </c>
+      <c r="D10">
+        <v>0.85054928065416602</v>
+      </c>
+      <c r="E10">
+        <v>0.81632449232768201</v>
+      </c>
+      <c r="F10">
+        <v>0.79085038760443604</v>
+      </c>
+      <c r="G10">
+        <v>0.77813793483798299</v>
+      </c>
+      <c r="H10">
+        <v>0.83075341522976798</v>
+      </c>
+      <c r="I10">
+        <v>0.70869464818295702</v>
+      </c>
+      <c r="J10">
+        <v>0.81491130084522601</v>
+      </c>
+      <c r="K10">
+        <v>0.86785674397944002</v>
+      </c>
+      <c r="L10">
+        <v>0.519005742862511</v>
+      </c>
+      <c r="M10">
+        <v>0.69025879886924402</v>
+      </c>
+      <c r="N10">
+        <v>0.65165587962521498</v>
+      </c>
+      <c r="O10">
+        <v>0.44824897491003401</v>
+      </c>
+      <c r="P10">
+        <v>0.81223262502022398</v>
+      </c>
+      <c r="Q10">
+        <v>0.83410906420998399</v>
+      </c>
+      <c r="R10">
+        <v>0.64685998237570397</v>
+      </c>
+      <c r="S10">
+        <v>0.73227374615366603</v>
+      </c>
+      <c r="T10">
+        <v>0.699216950339417</v>
+      </c>
+      <c r="U10">
+        <v>0.86051623569899005</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11">
+        <v>0.85352349983328701</v>
+      </c>
+      <c r="C11">
+        <v>0.724798315377438</v>
+      </c>
+      <c r="D11">
+        <v>0.82777645880776596</v>
+      </c>
+      <c r="E11">
+        <v>0.82784987948012601</v>
+      </c>
+      <c r="F11">
+        <v>0.79161955238377801</v>
+      </c>
+      <c r="G11">
+        <v>0.84375318356718498</v>
+      </c>
+      <c r="H11">
+        <v>0.79807061278984004</v>
+      </c>
+      <c r="I11">
+        <v>0.64715346567446697</v>
+      </c>
+      <c r="J11">
+        <v>0.86269506552383102</v>
+      </c>
+      <c r="K11">
+        <v>0.86957035714180098</v>
+      </c>
+      <c r="L11">
+        <v>0.58038210611443397</v>
+      </c>
+      <c r="M11">
+        <v>0.59977673890186201</v>
+      </c>
+      <c r="N11">
+        <v>0.45591494839174301</v>
+      </c>
+      <c r="O11">
+        <v>0.105153463433959</v>
+      </c>
+      <c r="P11">
+        <v>0.75883908005948497</v>
+      </c>
+      <c r="Q11">
+        <v>0.77796162730809604</v>
+      </c>
+      <c r="R11">
+        <v>0.57801020824920901</v>
+      </c>
+      <c r="S11">
+        <v>0.68423457878454397</v>
+      </c>
+      <c r="T11">
+        <v>0.61375646710571996</v>
+      </c>
+      <c r="U11">
         <v>0.76635249505233505</v>
       </c>
     </row>
@@ -35343,7 +35691,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20C27C4F-7112-48CC-8600-645EA3A54793}">
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -35351,7 +35699,7 @@
     <col min="12" max="12" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>73</v>
       </c>
@@ -35413,7 +35761,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>93</v>
       </c>
@@ -35478,7 +35826,7 @@
         <v>0.64309151947275001</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>94</v>
       </c>
@@ -35541,6 +35889,615 @@
       </c>
       <c r="U3">
         <v>0.77887246177411396</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J6" t="s">
+        <v>81</v>
+      </c>
+      <c r="K6" t="s">
+        <v>82</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M6" t="s">
+        <v>84</v>
+      </c>
+      <c r="N6" t="s">
+        <v>85</v>
+      </c>
+      <c r="O6" t="s">
+        <v>86</v>
+      </c>
+      <c r="P6" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>88</v>
+      </c>
+      <c r="R6" t="s">
+        <v>89</v>
+      </c>
+      <c r="S6" t="s">
+        <v>90</v>
+      </c>
+      <c r="T6" t="s">
+        <v>91</v>
+      </c>
+      <c r="U6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7">
+        <v>0.86276146222643102</v>
+      </c>
+      <c r="C7">
+        <v>0.74074689803015803</v>
+      </c>
+      <c r="D7">
+        <v>0.85054928065416602</v>
+      </c>
+      <c r="E7">
+        <v>0.81632449232768201</v>
+      </c>
+      <c r="F7">
+        <v>0.79085038760443604</v>
+      </c>
+      <c r="G7">
+        <v>0.77813793483798299</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.83075341522976798</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.70869464818295702</v>
+      </c>
+      <c r="J7">
+        <v>0.81491130084522601</v>
+      </c>
+      <c r="K7">
+        <v>0.86785674397944002</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0.519005742862511</v>
+      </c>
+      <c r="M7">
+        <v>0.69025879886924402</v>
+      </c>
+      <c r="N7">
+        <v>0.65165587962521498</v>
+      </c>
+      <c r="O7">
+        <v>0.44824897491003401</v>
+      </c>
+      <c r="P7">
+        <v>0.81223262502022398</v>
+      </c>
+      <c r="Q7">
+        <v>0.83410906420998399</v>
+      </c>
+      <c r="R7">
+        <v>0.64685998237570397</v>
+      </c>
+      <c r="S7">
+        <v>0.73227374615366603</v>
+      </c>
+      <c r="T7">
+        <v>0.699216950339417</v>
+      </c>
+      <c r="U7">
+        <v>0.86051623569899005</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8">
+        <v>0.79314388854752005</v>
+      </c>
+      <c r="C8">
+        <v>0.68072855194797</v>
+      </c>
+      <c r="D8">
+        <v>0.80705331247429002</v>
+      </c>
+      <c r="E8">
+        <v>0.83248747119794897</v>
+      </c>
+      <c r="F8">
+        <v>0.72589040915222303</v>
+      </c>
+      <c r="G8">
+        <v>0.76519008013703005</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.81451810353786502</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.64712438732216104</v>
+      </c>
+      <c r="J8">
+        <v>0.82549835384246695</v>
+      </c>
+      <c r="K8">
+        <v>0.84426950577799498</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0.55553431527228103</v>
+      </c>
+      <c r="M8">
+        <v>0.661630562167414</v>
+      </c>
+      <c r="N8">
+        <v>0.38786666163503603</v>
+      </c>
+      <c r="O8">
+        <v>0.10339809520130799</v>
+      </c>
+      <c r="P8">
+        <v>0.71223983573853999</v>
+      </c>
+      <c r="Q8">
+        <v>0.76989121325268495</v>
+      </c>
+      <c r="R8">
+        <v>0.38238477770825502</v>
+      </c>
+      <c r="S8">
+        <v>0.63020158794381798</v>
+      </c>
+      <c r="T8">
+        <v>0.60734894362150005</v>
+      </c>
+      <c r="U8">
+        <v>0.75178680746486903</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="C10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="D11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" t="s">
+        <v>75</v>
+      </c>
+      <c r="G11" t="s">
+        <v>76</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J11" t="s">
+        <v>79</v>
+      </c>
+      <c r="K11" t="s">
+        <v>80</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M11" t="s">
+        <v>82</v>
+      </c>
+      <c r="N11" t="s">
+        <v>83</v>
+      </c>
+      <c r="O11" t="s">
+        <v>84</v>
+      </c>
+      <c r="P11" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>86</v>
+      </c>
+      <c r="R11" t="s">
+        <v>87</v>
+      </c>
+      <c r="S11" t="s">
+        <v>88</v>
+      </c>
+      <c r="T11" t="s">
+        <v>89</v>
+      </c>
+      <c r="U11" t="s">
+        <v>90</v>
+      </c>
+      <c r="V11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="C12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12">
+        <v>0.86276146222643102</v>
+      </c>
+      <c r="E12">
+        <v>0.74074689803015803</v>
+      </c>
+      <c r="F12">
+        <v>0.85054928065416602</v>
+      </c>
+      <c r="G12">
+        <v>0.81632449232768201</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.79085038760443604</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0.77813793483798299</v>
+      </c>
+      <c r="J12">
+        <v>0.83075341522976798</v>
+      </c>
+      <c r="K12">
+        <v>0.70869464818295702</v>
+      </c>
+      <c r="L12" s="2">
+        <v>0.81491130084522601</v>
+      </c>
+      <c r="M12">
+        <v>0.86785674397944002</v>
+      </c>
+      <c r="N12">
+        <v>0.519005742862511</v>
+      </c>
+      <c r="O12">
+        <v>0.69025879886924402</v>
+      </c>
+      <c r="P12">
+        <v>0.65165587962521498</v>
+      </c>
+      <c r="Q12">
+        <v>0.44824897491003401</v>
+      </c>
+      <c r="R12">
+        <v>0.81223262502022398</v>
+      </c>
+      <c r="S12">
+        <v>0.83410906420998399</v>
+      </c>
+      <c r="T12">
+        <v>0.64685998237570397</v>
+      </c>
+      <c r="U12">
+        <v>0.73227374615366603</v>
+      </c>
+      <c r="V12">
+        <v>0.699216950339417</v>
+      </c>
+      <c r="W12">
+        <v>0.86051623569899005</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="C13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13">
+        <v>0.86162169849713799</v>
+      </c>
+      <c r="E13">
+        <v>0.75992555180224997</v>
+      </c>
+      <c r="F13">
+        <v>0.82971954888468502</v>
+      </c>
+      <c r="G13">
+        <v>0.85654398939697196</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0.82473059663983705</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0.83422441088653598</v>
+      </c>
+      <c r="J13">
+        <v>0.81846720810871798</v>
+      </c>
+      <c r="K13">
+        <v>0.65046311150809499</v>
+      </c>
+      <c r="L13" s="2">
+        <v>0.89051939662495705</v>
+      </c>
+      <c r="M13">
+        <v>0.92563730644572895</v>
+      </c>
+      <c r="N13">
+        <v>0.48520127072790598</v>
+      </c>
+      <c r="O13">
+        <v>0.627092218289234</v>
+      </c>
+      <c r="P13">
+        <v>0.51003115350874895</v>
+      </c>
+      <c r="Q13">
+        <v>0.10701829802528801</v>
+      </c>
+      <c r="R13">
+        <v>0.78469907763097202</v>
+      </c>
+      <c r="S13">
+        <v>0.824431163590569</v>
+      </c>
+      <c r="T13">
+        <v>0.60443420059796604</v>
+      </c>
+      <c r="U13">
+        <v>0.68051973107670205</v>
+      </c>
+      <c r="V13">
+        <v>0.60760210890564204</v>
+      </c>
+      <c r="W13">
+        <v>0.810415670039763</v>
+      </c>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.35">
+      <c r="Q17" s="5"/>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.35">
+      <c r="Q18" s="5"/>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.35">
+      <c r="Q19" s="5"/>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.35">
+      <c r="C21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.35">
+      <c r="D22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" t="s">
+        <v>74</v>
+      </c>
+      <c r="F22" t="s">
+        <v>75</v>
+      </c>
+      <c r="G22" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J22" t="s">
+        <v>79</v>
+      </c>
+      <c r="K22" t="s">
+        <v>80</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M22" t="s">
+        <v>82</v>
+      </c>
+      <c r="N22" t="s">
+        <v>83</v>
+      </c>
+      <c r="O22" t="s">
+        <v>84</v>
+      </c>
+      <c r="P22" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>86</v>
+      </c>
+      <c r="R22" t="s">
+        <v>87</v>
+      </c>
+      <c r="S22" t="s">
+        <v>88</v>
+      </c>
+      <c r="T22" t="s">
+        <v>89</v>
+      </c>
+      <c r="U22" t="s">
+        <v>90</v>
+      </c>
+      <c r="V22" t="s">
+        <v>91</v>
+      </c>
+      <c r="W22" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.35">
+      <c r="C23" t="s">
+        <v>93</v>
+      </c>
+      <c r="D23">
+        <v>0.86276146222643102</v>
+      </c>
+      <c r="E23">
+        <v>0.74074689803015803</v>
+      </c>
+      <c r="F23">
+        <v>0.85054928065416602</v>
+      </c>
+      <c r="G23">
+        <v>0.81632449232768201</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0.79085038760443604</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0.77813793483798299</v>
+      </c>
+      <c r="J23">
+        <v>0.83075341522976798</v>
+      </c>
+      <c r="K23">
+        <v>0.70869464818295702</v>
+      </c>
+      <c r="L23" s="2">
+        <v>0.81491130084522601</v>
+      </c>
+      <c r="M23">
+        <v>0.86785674397944002</v>
+      </c>
+      <c r="N23">
+        <v>0.519005742862511</v>
+      </c>
+      <c r="O23">
+        <v>0.69025879886924402</v>
+      </c>
+      <c r="P23">
+        <v>0.65165587962521498</v>
+      </c>
+      <c r="Q23">
+        <v>0.44824897491003401</v>
+      </c>
+      <c r="R23">
+        <v>0.81223262502022398</v>
+      </c>
+      <c r="S23">
+        <v>0.83410906420998399</v>
+      </c>
+      <c r="T23">
+        <v>0.64685998237570397</v>
+      </c>
+      <c r="U23">
+        <v>0.73227374615366603</v>
+      </c>
+      <c r="V23">
+        <v>0.699216950339417</v>
+      </c>
+      <c r="W23">
+        <v>0.86051623569899005</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.35">
+      <c r="C24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24">
+        <v>0.87329151349427903</v>
+      </c>
+      <c r="E24">
+        <v>0.80176934340182004</v>
+      </c>
+      <c r="F24">
+        <v>0.83605197895137695</v>
+      </c>
+      <c r="G24">
+        <v>0.81975662023687002</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0.86323686557894896</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0.812628478806532</v>
+      </c>
+      <c r="J24">
+        <v>0.82802463353703104</v>
+      </c>
+      <c r="K24">
+        <v>0.70195784309208198</v>
+      </c>
+      <c r="L24" s="2">
+        <v>0.91350308651576595</v>
+      </c>
+      <c r="M24">
+        <v>0.94134455317763999</v>
+      </c>
+      <c r="N24">
+        <v>0.52561884851548002</v>
+      </c>
+      <c r="O24">
+        <v>0.67635327187948402</v>
+      </c>
+      <c r="P24">
+        <v>0.55221033836424405</v>
+      </c>
+      <c r="Q24">
+        <v>0.11462415329616001</v>
+      </c>
+      <c r="R24">
+        <v>0.79259398999524699</v>
+      </c>
+      <c r="S24">
+        <v>0.85806510180867501</v>
+      </c>
+      <c r="T24">
+        <v>0.61135885828034597</v>
+      </c>
+      <c r="U24">
+        <v>0.71711677060452805</v>
+      </c>
+      <c r="V24">
+        <v>0.66093441773720096</v>
+      </c>
+      <c r="W24">
+        <v>0.81024684304642902</v>
       </c>
     </row>
   </sheetData>

--- a/data/annotations/TE_discrete_percentages.xlsx
+++ b/data/annotations/TE_discrete_percentages.xlsx
@@ -8,24 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dobregeo\Documents\GitHub\vilearn_ml\data\annotations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{AF11CD2B-0494-416B-A28E-F9A75972BCAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{906A2D7E-144E-4C96-8037-F1088B3BABA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" firstSheet="2" activeTab="2" xr2:uid="{8450E3AB-A0C1-455F-AE9B-DBE7A60F6C99}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" tabRatio="666" firstSheet="2" activeTab="3" xr2:uid="{8450E3AB-A0C1-455F-AE9B-DBE7A60F6C99}"/>
   </bookViews>
   <sheets>
     <sheet name="TE_discrete_percentages" sheetId="1" r:id="rId1"/>
     <sheet name="TE_discrete_.1" sheetId="2" r:id="rId2"/>
-    <sheet name="TE_discrete_twobinsV1" sheetId="3" r:id="rId3"/>
-    <sheet name="interraterReliability windV1" sheetId="5" r:id="rId4"/>
-    <sheet name="TE_discrete_twobinsV2" sheetId="6" r:id="rId5"/>
-    <sheet name="interraterReliability windV2" sheetId="4" r:id="rId6"/>
+    <sheet name="TE_discrete_twobins_max.75" sheetId="3" r:id="rId3"/>
+    <sheet name="TE_discrete_twobins_max.6" sheetId="7" r:id="rId4"/>
+    <sheet name="interraterReliability windV1" sheetId="5" r:id="rId5"/>
+    <sheet name="TE_discrete_twobinsV2" sheetId="6" r:id="rId6"/>
+    <sheet name="interraterReliability windV2" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="112">
   <si>
     <t>task_eng</t>
   </si>
@@ -684,7 +685,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -811,6 +812,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color theme="1"/>
@@ -821,6 +835,37 @@
       <bottom style="thin">
         <color theme="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -868,13 +913,17 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -4995,7 +5044,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>TE_discrete_twobinsV1!$A$2</c:f>
+              <c:f>TE_discrete_twobins_max.75!$A$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5021,11 +5070,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>TE_discrete_twobinsV1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_twobins_max.75!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(TE_discrete_twobinsV1!$D$1,TE_discrete_twobinsV1!$F$1,TE_discrete_twobinsV1!$H$1,TE_discrete_twobinsV1!$J$1,TE_discrete_twobinsV1!$L$1,TE_discrete_twobinsV1!$N$1,TE_discrete_twobinsV1!$T$1,TE_discrete_twobinsV1!$V$1,TE_discrete_twobinsV1!$X$1,TE_discrete_twobinsV1!$Z$1,TE_discrete_twobinsV1!$AF$1,TE_discrete_twobinsV1!$AH$1,TE_discrete_twobinsV1!$AJ$1,TE_discrete_twobinsV1!$AL$1,TE_discrete_twobinsV1!$AN$1,TE_discrete_twobinsV1!$AP$1,TE_discrete_twobinsV1!$AR$1,TE_discrete_twobinsV1!$AT$1,TE_discrete_twobinsV1!$AV$1,TE_discrete_twobinsV1!$AX$1)</c:f>
+              <c:f>(TE_discrete_twobins_max.75!$D$1,TE_discrete_twobins_max.75!$F$1,TE_discrete_twobins_max.75!$H$1,TE_discrete_twobins_max.75!$J$1,TE_discrete_twobins_max.75!$L$1,TE_discrete_twobins_max.75!$N$1,TE_discrete_twobins_max.75!$T$1,TE_discrete_twobins_max.75!$V$1,TE_discrete_twobins_max.75!$X$1,TE_discrete_twobins_max.75!$Z$1,TE_discrete_twobins_max.75!$AF$1,TE_discrete_twobins_max.75!$AH$1,TE_discrete_twobins_max.75!$AJ$1,TE_discrete_twobins_max.75!$AL$1,TE_discrete_twobins_max.75!$AN$1,TE_discrete_twobins_max.75!$AP$1,TE_discrete_twobins_max.75!$AR$1,TE_discrete_twobins_max.75!$AT$1,TE_discrete_twobins_max.75!$AV$1,TE_discrete_twobins_max.75!$AX$1)</c:f>
               <c:strCache>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
@@ -5096,11 +5145,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>TE_discrete_twobinsV1!$B$2:$AY$2</c15:sqref>
+                    <c15:sqref>TE_discrete_twobins_max.75!$B$2:$AY$2</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(TE_discrete_twobinsV1!$D$2,TE_discrete_twobinsV1!$F$2,TE_discrete_twobinsV1!$H$2,TE_discrete_twobinsV1!$J$2,TE_discrete_twobinsV1!$L$2,TE_discrete_twobinsV1!$N$2,TE_discrete_twobinsV1!$T$2,TE_discrete_twobinsV1!$V$2,TE_discrete_twobinsV1!$X$2,TE_discrete_twobinsV1!$Z$2,TE_discrete_twobinsV1!$AF$2,TE_discrete_twobinsV1!$AH$2,TE_discrete_twobinsV1!$AJ$2,TE_discrete_twobinsV1!$AL$2,TE_discrete_twobinsV1!$AN$2,TE_discrete_twobinsV1!$AP$2,TE_discrete_twobinsV1!$AR$2,TE_discrete_twobinsV1!$AT$2,TE_discrete_twobinsV1!$AV$2,TE_discrete_twobinsV1!$AX$2)</c:f>
+              <c:f>(TE_discrete_twobins_max.75!$D$2,TE_discrete_twobins_max.75!$F$2,TE_discrete_twobins_max.75!$H$2,TE_discrete_twobins_max.75!$J$2,TE_discrete_twobins_max.75!$L$2,TE_discrete_twobins_max.75!$N$2,TE_discrete_twobins_max.75!$T$2,TE_discrete_twobins_max.75!$V$2,TE_discrete_twobins_max.75!$X$2,TE_discrete_twobins_max.75!$Z$2,TE_discrete_twobins_max.75!$AF$2,TE_discrete_twobins_max.75!$AH$2,TE_discrete_twobins_max.75!$AJ$2,TE_discrete_twobins_max.75!$AL$2,TE_discrete_twobins_max.75!$AN$2,TE_discrete_twobins_max.75!$AP$2,TE_discrete_twobins_max.75!$AR$2,TE_discrete_twobins_max.75!$AT$2,TE_discrete_twobins_max.75!$AV$2,TE_discrete_twobins_max.75!$AX$2)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -5178,7 +5227,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>TE_discrete_twobinsV1!$A$3</c:f>
+              <c:f>TE_discrete_twobins_max.75!$A$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5202,11 +5251,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>TE_discrete_twobinsV1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_twobins_max.75!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(TE_discrete_twobinsV1!$D$1,TE_discrete_twobinsV1!$F$1,TE_discrete_twobinsV1!$H$1,TE_discrete_twobinsV1!$J$1,TE_discrete_twobinsV1!$L$1,TE_discrete_twobinsV1!$N$1,TE_discrete_twobinsV1!$T$1,TE_discrete_twobinsV1!$V$1,TE_discrete_twobinsV1!$X$1,TE_discrete_twobinsV1!$Z$1,TE_discrete_twobinsV1!$AF$1,TE_discrete_twobinsV1!$AH$1,TE_discrete_twobinsV1!$AJ$1,TE_discrete_twobinsV1!$AL$1,TE_discrete_twobinsV1!$AN$1,TE_discrete_twobinsV1!$AP$1,TE_discrete_twobinsV1!$AR$1,TE_discrete_twobinsV1!$AT$1,TE_discrete_twobinsV1!$AV$1,TE_discrete_twobinsV1!$AX$1)</c:f>
+              <c:f>(TE_discrete_twobins_max.75!$D$1,TE_discrete_twobins_max.75!$F$1,TE_discrete_twobins_max.75!$H$1,TE_discrete_twobins_max.75!$J$1,TE_discrete_twobins_max.75!$L$1,TE_discrete_twobins_max.75!$N$1,TE_discrete_twobins_max.75!$T$1,TE_discrete_twobins_max.75!$V$1,TE_discrete_twobins_max.75!$X$1,TE_discrete_twobins_max.75!$Z$1,TE_discrete_twobins_max.75!$AF$1,TE_discrete_twobins_max.75!$AH$1,TE_discrete_twobins_max.75!$AJ$1,TE_discrete_twobins_max.75!$AL$1,TE_discrete_twobins_max.75!$AN$1,TE_discrete_twobins_max.75!$AP$1,TE_discrete_twobins_max.75!$AR$1,TE_discrete_twobins_max.75!$AT$1,TE_discrete_twobins_max.75!$AV$1,TE_discrete_twobins_max.75!$AX$1)</c:f>
               <c:strCache>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
@@ -5277,11 +5326,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>TE_discrete_twobinsV1!$B$3:$AY$3</c15:sqref>
+                    <c15:sqref>TE_discrete_twobins_max.75!$B$3:$AY$3</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(TE_discrete_twobinsV1!$D$3,TE_discrete_twobinsV1!$F$3,TE_discrete_twobinsV1!$H$3,TE_discrete_twobinsV1!$J$3,TE_discrete_twobinsV1!$L$3,TE_discrete_twobinsV1!$N$3,TE_discrete_twobinsV1!$T$3,TE_discrete_twobinsV1!$V$3,TE_discrete_twobinsV1!$X$3,TE_discrete_twobinsV1!$Z$3,TE_discrete_twobinsV1!$AF$3,TE_discrete_twobinsV1!$AH$3,TE_discrete_twobinsV1!$AJ$3,TE_discrete_twobinsV1!$AL$3,TE_discrete_twobinsV1!$AN$3,TE_discrete_twobinsV1!$AP$3,TE_discrete_twobinsV1!$AR$3,TE_discrete_twobinsV1!$AT$3,TE_discrete_twobinsV1!$AV$3,TE_discrete_twobinsV1!$AX$3)</c:f>
+              <c:f>(TE_discrete_twobins_max.75!$D$3,TE_discrete_twobins_max.75!$F$3,TE_discrete_twobins_max.75!$H$3,TE_discrete_twobins_max.75!$J$3,TE_discrete_twobins_max.75!$L$3,TE_discrete_twobins_max.75!$N$3,TE_discrete_twobins_max.75!$T$3,TE_discrete_twobins_max.75!$V$3,TE_discrete_twobins_max.75!$X$3,TE_discrete_twobins_max.75!$Z$3,TE_discrete_twobins_max.75!$AF$3,TE_discrete_twobins_max.75!$AH$3,TE_discrete_twobins_max.75!$AJ$3,TE_discrete_twobins_max.75!$AL$3,TE_discrete_twobins_max.75!$AN$3,TE_discrete_twobins_max.75!$AP$3,TE_discrete_twobins_max.75!$AR$3,TE_discrete_twobins_max.75!$AT$3,TE_discrete_twobins_max.75!$AV$3,TE_discrete_twobins_max.75!$AX$3)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -5359,7 +5408,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>TE_discrete_twobinsV1!$A$4</c:f>
+              <c:f>TE_discrete_twobins_max.75!$A$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5383,11 +5432,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>TE_discrete_twobinsV1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_twobins_max.75!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(TE_discrete_twobinsV1!$D$1,TE_discrete_twobinsV1!$F$1,TE_discrete_twobinsV1!$H$1,TE_discrete_twobinsV1!$J$1,TE_discrete_twobinsV1!$L$1,TE_discrete_twobinsV1!$N$1,TE_discrete_twobinsV1!$T$1,TE_discrete_twobinsV1!$V$1,TE_discrete_twobinsV1!$X$1,TE_discrete_twobinsV1!$Z$1,TE_discrete_twobinsV1!$AF$1,TE_discrete_twobinsV1!$AH$1,TE_discrete_twobinsV1!$AJ$1,TE_discrete_twobinsV1!$AL$1,TE_discrete_twobinsV1!$AN$1,TE_discrete_twobinsV1!$AP$1,TE_discrete_twobinsV1!$AR$1,TE_discrete_twobinsV1!$AT$1,TE_discrete_twobinsV1!$AV$1,TE_discrete_twobinsV1!$AX$1)</c:f>
+              <c:f>(TE_discrete_twobins_max.75!$D$1,TE_discrete_twobins_max.75!$F$1,TE_discrete_twobins_max.75!$H$1,TE_discrete_twobins_max.75!$J$1,TE_discrete_twobins_max.75!$L$1,TE_discrete_twobins_max.75!$N$1,TE_discrete_twobins_max.75!$T$1,TE_discrete_twobins_max.75!$V$1,TE_discrete_twobins_max.75!$X$1,TE_discrete_twobins_max.75!$Z$1,TE_discrete_twobins_max.75!$AF$1,TE_discrete_twobins_max.75!$AH$1,TE_discrete_twobins_max.75!$AJ$1,TE_discrete_twobins_max.75!$AL$1,TE_discrete_twobins_max.75!$AN$1,TE_discrete_twobins_max.75!$AP$1,TE_discrete_twobins_max.75!$AR$1,TE_discrete_twobins_max.75!$AT$1,TE_discrete_twobins_max.75!$AV$1,TE_discrete_twobins_max.75!$AX$1)</c:f>
               <c:strCache>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
@@ -5458,11 +5507,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>TE_discrete_twobinsV1!$B$4:$AY$4</c15:sqref>
+                    <c15:sqref>TE_discrete_twobins_max.75!$B$4:$AY$4</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(TE_discrete_twobinsV1!$D$4,TE_discrete_twobinsV1!$F$4,TE_discrete_twobinsV1!$H$4,TE_discrete_twobinsV1!$J$4,TE_discrete_twobinsV1!$L$4,TE_discrete_twobinsV1!$N$4,TE_discrete_twobinsV1!$T$4,TE_discrete_twobinsV1!$V$4,TE_discrete_twobinsV1!$X$4,TE_discrete_twobinsV1!$Z$4,TE_discrete_twobinsV1!$AF$4,TE_discrete_twobinsV1!$AH$4,TE_discrete_twobinsV1!$AJ$4,TE_discrete_twobinsV1!$AL$4,TE_discrete_twobinsV1!$AN$4,TE_discrete_twobinsV1!$AP$4,TE_discrete_twobinsV1!$AR$4,TE_discrete_twobinsV1!$AT$4,TE_discrete_twobinsV1!$AV$4,TE_discrete_twobinsV1!$AX$4)</c:f>
+              <c:f>(TE_discrete_twobins_max.75!$D$4,TE_discrete_twobins_max.75!$F$4,TE_discrete_twobins_max.75!$H$4,TE_discrete_twobins_max.75!$J$4,TE_discrete_twobins_max.75!$L$4,TE_discrete_twobins_max.75!$N$4,TE_discrete_twobins_max.75!$T$4,TE_discrete_twobins_max.75!$V$4,TE_discrete_twobins_max.75!$X$4,TE_discrete_twobins_max.75!$Z$4,TE_discrete_twobins_max.75!$AF$4,TE_discrete_twobins_max.75!$AH$4,TE_discrete_twobins_max.75!$AJ$4,TE_discrete_twobins_max.75!$AL$4,TE_discrete_twobins_max.75!$AN$4,TE_discrete_twobins_max.75!$AP$4,TE_discrete_twobins_max.75!$AR$4,TE_discrete_twobins_max.75!$AT$4,TE_discrete_twobins_max.75!$AV$4,TE_discrete_twobins_max.75!$AX$4)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -5817,7 +5866,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>TE_discrete_twobinsV1!$A$2</c:f>
+              <c:f>TE_discrete_twobins_max.75!$A$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5843,11 +5892,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>TE_discrete_twobinsV1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_twobins_max.75!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(TE_discrete_twobinsV1!$E$1,TE_discrete_twobinsV1!$G$1,TE_discrete_twobinsV1!$I$1,TE_discrete_twobinsV1!$K$1,TE_discrete_twobinsV1!$M$1,TE_discrete_twobinsV1!$O$1,TE_discrete_twobinsV1!$U$1,TE_discrete_twobinsV1!$W$1,TE_discrete_twobinsV1!$Y$1,TE_discrete_twobinsV1!$AA$1,TE_discrete_twobinsV1!$AG$1,TE_discrete_twobinsV1!$AI$1,TE_discrete_twobinsV1!$AK$1,TE_discrete_twobinsV1!$AM$1,TE_discrete_twobinsV1!$AO$1,TE_discrete_twobinsV1!$AQ$1,TE_discrete_twobinsV1!$AS$1,TE_discrete_twobinsV1!$AU$1,TE_discrete_twobinsV1!$AW$1,TE_discrete_twobinsV1!$AY$1)</c:f>
+              <c:f>(TE_discrete_twobins_max.75!$E$1,TE_discrete_twobins_max.75!$G$1,TE_discrete_twobins_max.75!$I$1,TE_discrete_twobins_max.75!$K$1,TE_discrete_twobins_max.75!$M$1,TE_discrete_twobins_max.75!$O$1,TE_discrete_twobins_max.75!$U$1,TE_discrete_twobins_max.75!$W$1,TE_discrete_twobins_max.75!$Y$1,TE_discrete_twobins_max.75!$AA$1,TE_discrete_twobins_max.75!$AG$1,TE_discrete_twobins_max.75!$AI$1,TE_discrete_twobins_max.75!$AK$1,TE_discrete_twobins_max.75!$AM$1,TE_discrete_twobins_max.75!$AO$1,TE_discrete_twobins_max.75!$AQ$1,TE_discrete_twobins_max.75!$AS$1,TE_discrete_twobins_max.75!$AU$1,TE_discrete_twobins_max.75!$AW$1,TE_discrete_twobins_max.75!$AY$1)</c:f>
               <c:strCache>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
@@ -5918,11 +5967,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>TE_discrete_twobinsV1!$B$2:$AY$2</c15:sqref>
+                    <c15:sqref>TE_discrete_twobins_max.75!$B$2:$AY$2</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(TE_discrete_twobinsV1!$E$2,TE_discrete_twobinsV1!$G$2,TE_discrete_twobinsV1!$I$2,TE_discrete_twobinsV1!$K$2,TE_discrete_twobinsV1!$M$2,TE_discrete_twobinsV1!$O$2,TE_discrete_twobinsV1!$U$2,TE_discrete_twobinsV1!$W$2,TE_discrete_twobinsV1!$Y$2,TE_discrete_twobinsV1!$AA$2,TE_discrete_twobinsV1!$AG$2,TE_discrete_twobinsV1!$AI$2,TE_discrete_twobinsV1!$AK$2,TE_discrete_twobinsV1!$AM$2,TE_discrete_twobinsV1!$AO$2,TE_discrete_twobinsV1!$AQ$2,TE_discrete_twobinsV1!$AS$2,TE_discrete_twobinsV1!$AU$2,TE_discrete_twobinsV1!$AW$2,TE_discrete_twobinsV1!$AY$2)</c:f>
+              <c:f>(TE_discrete_twobins_max.75!$E$2,TE_discrete_twobins_max.75!$G$2,TE_discrete_twobins_max.75!$I$2,TE_discrete_twobins_max.75!$K$2,TE_discrete_twobins_max.75!$M$2,TE_discrete_twobins_max.75!$O$2,TE_discrete_twobins_max.75!$U$2,TE_discrete_twobins_max.75!$W$2,TE_discrete_twobins_max.75!$Y$2,TE_discrete_twobins_max.75!$AA$2,TE_discrete_twobins_max.75!$AG$2,TE_discrete_twobins_max.75!$AI$2,TE_discrete_twobins_max.75!$AK$2,TE_discrete_twobins_max.75!$AM$2,TE_discrete_twobins_max.75!$AO$2,TE_discrete_twobins_max.75!$AQ$2,TE_discrete_twobins_max.75!$AS$2,TE_discrete_twobins_max.75!$AU$2,TE_discrete_twobins_max.75!$AW$2,TE_discrete_twobins_max.75!$AY$2)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6000,7 +6049,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>TE_discrete_twobinsV1!$A$3</c:f>
+              <c:f>TE_discrete_twobins_max.75!$A$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6024,11 +6073,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>TE_discrete_twobinsV1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_twobins_max.75!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(TE_discrete_twobinsV1!$E$1,TE_discrete_twobinsV1!$G$1,TE_discrete_twobinsV1!$I$1,TE_discrete_twobinsV1!$K$1,TE_discrete_twobinsV1!$M$1,TE_discrete_twobinsV1!$O$1,TE_discrete_twobinsV1!$U$1,TE_discrete_twobinsV1!$W$1,TE_discrete_twobinsV1!$Y$1,TE_discrete_twobinsV1!$AA$1,TE_discrete_twobinsV1!$AG$1,TE_discrete_twobinsV1!$AI$1,TE_discrete_twobinsV1!$AK$1,TE_discrete_twobinsV1!$AM$1,TE_discrete_twobinsV1!$AO$1,TE_discrete_twobinsV1!$AQ$1,TE_discrete_twobinsV1!$AS$1,TE_discrete_twobinsV1!$AU$1,TE_discrete_twobinsV1!$AW$1,TE_discrete_twobinsV1!$AY$1)</c:f>
+              <c:f>(TE_discrete_twobins_max.75!$E$1,TE_discrete_twobins_max.75!$G$1,TE_discrete_twobins_max.75!$I$1,TE_discrete_twobins_max.75!$K$1,TE_discrete_twobins_max.75!$M$1,TE_discrete_twobins_max.75!$O$1,TE_discrete_twobins_max.75!$U$1,TE_discrete_twobins_max.75!$W$1,TE_discrete_twobins_max.75!$Y$1,TE_discrete_twobins_max.75!$AA$1,TE_discrete_twobins_max.75!$AG$1,TE_discrete_twobins_max.75!$AI$1,TE_discrete_twobins_max.75!$AK$1,TE_discrete_twobins_max.75!$AM$1,TE_discrete_twobins_max.75!$AO$1,TE_discrete_twobins_max.75!$AQ$1,TE_discrete_twobins_max.75!$AS$1,TE_discrete_twobins_max.75!$AU$1,TE_discrete_twobins_max.75!$AW$1,TE_discrete_twobins_max.75!$AY$1)</c:f>
               <c:strCache>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
@@ -6099,11 +6148,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>TE_discrete_twobinsV1!$B$3:$AY$3</c15:sqref>
+                    <c15:sqref>TE_discrete_twobins_max.75!$B$3:$AY$3</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(TE_discrete_twobinsV1!$E$3,TE_discrete_twobinsV1!$G$3,TE_discrete_twobinsV1!$I$3,TE_discrete_twobinsV1!$K$3,TE_discrete_twobinsV1!$M$3,TE_discrete_twobinsV1!$O$3,TE_discrete_twobinsV1!$U$3,TE_discrete_twobinsV1!$W$3,TE_discrete_twobinsV1!$Y$3,TE_discrete_twobinsV1!$AA$3,TE_discrete_twobinsV1!$AG$3,TE_discrete_twobinsV1!$AI$3,TE_discrete_twobinsV1!$AK$3,TE_discrete_twobinsV1!$AM$3,TE_discrete_twobinsV1!$AO$3,TE_discrete_twobinsV1!$AQ$3,TE_discrete_twobinsV1!$AS$3,TE_discrete_twobinsV1!$AU$3,TE_discrete_twobinsV1!$AW$3,TE_discrete_twobinsV1!$AY$3)</c:f>
+              <c:f>(TE_discrete_twobins_max.75!$E$3,TE_discrete_twobins_max.75!$G$3,TE_discrete_twobins_max.75!$I$3,TE_discrete_twobins_max.75!$K$3,TE_discrete_twobins_max.75!$M$3,TE_discrete_twobins_max.75!$O$3,TE_discrete_twobins_max.75!$U$3,TE_discrete_twobins_max.75!$W$3,TE_discrete_twobins_max.75!$Y$3,TE_discrete_twobins_max.75!$AA$3,TE_discrete_twobins_max.75!$AG$3,TE_discrete_twobins_max.75!$AI$3,TE_discrete_twobins_max.75!$AK$3,TE_discrete_twobins_max.75!$AM$3,TE_discrete_twobins_max.75!$AO$3,TE_discrete_twobins_max.75!$AQ$3,TE_discrete_twobins_max.75!$AS$3,TE_discrete_twobins_max.75!$AU$3,TE_discrete_twobins_max.75!$AW$3,TE_discrete_twobins_max.75!$AY$3)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6181,7 +6230,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>TE_discrete_twobinsV1!$A$4</c:f>
+              <c:f>TE_discrete_twobins_max.75!$A$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6205,11 +6254,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>TE_discrete_twobinsV1!$B$1:$AY$1</c15:sqref>
+                    <c15:sqref>TE_discrete_twobins_max.75!$B$1:$AY$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(TE_discrete_twobinsV1!$E$1,TE_discrete_twobinsV1!$G$1,TE_discrete_twobinsV1!$I$1,TE_discrete_twobinsV1!$K$1,TE_discrete_twobinsV1!$M$1,TE_discrete_twobinsV1!$O$1,TE_discrete_twobinsV1!$U$1,TE_discrete_twobinsV1!$W$1,TE_discrete_twobinsV1!$Y$1,TE_discrete_twobinsV1!$AA$1,TE_discrete_twobinsV1!$AG$1,TE_discrete_twobinsV1!$AI$1,TE_discrete_twobinsV1!$AK$1,TE_discrete_twobinsV1!$AM$1,TE_discrete_twobinsV1!$AO$1,TE_discrete_twobinsV1!$AQ$1,TE_discrete_twobinsV1!$AS$1,TE_discrete_twobinsV1!$AU$1,TE_discrete_twobinsV1!$AW$1,TE_discrete_twobinsV1!$AY$1)</c:f>
+              <c:f>(TE_discrete_twobins_max.75!$E$1,TE_discrete_twobins_max.75!$G$1,TE_discrete_twobins_max.75!$I$1,TE_discrete_twobins_max.75!$K$1,TE_discrete_twobins_max.75!$M$1,TE_discrete_twobins_max.75!$O$1,TE_discrete_twobins_max.75!$U$1,TE_discrete_twobins_max.75!$W$1,TE_discrete_twobins_max.75!$Y$1,TE_discrete_twobins_max.75!$AA$1,TE_discrete_twobins_max.75!$AG$1,TE_discrete_twobins_max.75!$AI$1,TE_discrete_twobins_max.75!$AK$1,TE_discrete_twobins_max.75!$AM$1,TE_discrete_twobins_max.75!$AO$1,TE_discrete_twobins_max.75!$AQ$1,TE_discrete_twobins_max.75!$AS$1,TE_discrete_twobins_max.75!$AU$1,TE_discrete_twobins_max.75!$AW$1,TE_discrete_twobins_max.75!$AY$1)</c:f>
               <c:strCache>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
@@ -6280,11 +6329,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>TE_discrete_twobinsV1!$B$4:$AY$4</c15:sqref>
+                    <c15:sqref>TE_discrete_twobins_max.75!$B$4:$AY$4</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(TE_discrete_twobinsV1!$E$4,TE_discrete_twobinsV1!$G$4,TE_discrete_twobinsV1!$I$4,TE_discrete_twobinsV1!$K$4,TE_discrete_twobinsV1!$M$4,TE_discrete_twobinsV1!$O$4,TE_discrete_twobinsV1!$U$4,TE_discrete_twobinsV1!$W$4,TE_discrete_twobinsV1!$Y$4,TE_discrete_twobinsV1!$AA$4,TE_discrete_twobinsV1!$AG$4,TE_discrete_twobinsV1!$AI$4,TE_discrete_twobinsV1!$AK$4,TE_discrete_twobinsV1!$AM$4,TE_discrete_twobinsV1!$AO$4,TE_discrete_twobinsV1!$AQ$4,TE_discrete_twobinsV1!$AS$4,TE_discrete_twobinsV1!$AU$4,TE_discrete_twobinsV1!$AW$4,TE_discrete_twobinsV1!$AY$4)</c:f>
+              <c:f>(TE_discrete_twobins_max.75!$E$4,TE_discrete_twobins_max.75!$G$4,TE_discrete_twobins_max.75!$I$4,TE_discrete_twobins_max.75!$K$4,TE_discrete_twobins_max.75!$M$4,TE_discrete_twobins_max.75!$O$4,TE_discrete_twobins_max.75!$U$4,TE_discrete_twobins_max.75!$W$4,TE_discrete_twobins_max.75!$Y$4,TE_discrete_twobins_max.75!$AA$4,TE_discrete_twobins_max.75!$AG$4,TE_discrete_twobins_max.75!$AI$4,TE_discrete_twobins_max.75!$AK$4,TE_discrete_twobins_max.75!$AM$4,TE_discrete_twobins_max.75!$AO$4,TE_discrete_twobins_max.75!$AQ$4,TE_discrete_twobins_max.75!$AS$4,TE_discrete_twobins_max.75!$AU$4,TE_discrete_twobins_max.75!$AW$4,TE_discrete_twobins_max.75!$AY$4)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6588,6 +6637,1636 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-GB"/>
+              <a:t>Anno Helen</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="percentStacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>TE_discrete_twobins_max.6!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>high</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobins_max.6!$B$1:$AO$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobins_max.6!$B$1,TE_discrete_twobins_max.6!$D$1,TE_discrete_twobins_max.6!$F$1,TE_discrete_twobins_max.6!$H$1,TE_discrete_twobins_max.6!$J$1,TE_discrete_twobins_max.6!$L$1,TE_discrete_twobins_max.6!$N$1,TE_discrete_twobins_max.6!$P$1,TE_discrete_twobins_max.6!$R$1,TE_discrete_twobins_max.6!$T$1,TE_discrete_twobins_max.6!$V$1,TE_discrete_twobins_max.6!$X$1,TE_discrete_twobins_max.6!$Z$1,TE_discrete_twobins_max.6!$AB$1,TE_discrete_twobins_max.6!$AD$1,TE_discrete_twobins_max.6!$AF$1,TE_discrete_twobins_max.6!$AH$1,TE_discrete_twobins_max.6!$AJ$1,TE_discrete_twobins_max.6!$AL$1,TE_discrete_twobins_max.6!$AN$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>dyad_02_anno01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>dyad_03_anno01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>dyad_04_anno01</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>dyad_05_anno01</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>dyad_06_anno01</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>dyad_07_anno01</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>dyad_10_anno01</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>dyad_11_anno01</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>triad_01_anno01</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>triad_02_anno01</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>triad_05_anno01</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>triad_06_anno01</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>triad_07_anno01</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>triad_08_anno01</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>triad_09_anno01</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>triad_10_anno01</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>triad_11_anno01</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>triad_12_anno01</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>triad_13_anno01</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>triad_14_anno01</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobins_max.6!$B$2:$AO$2</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobins_max.6!$B$2,TE_discrete_twobins_max.6!$D$2,TE_discrete_twobins_max.6!$F$2,TE_discrete_twobins_max.6!$H$2,TE_discrete_twobins_max.6!$J$2,TE_discrete_twobins_max.6!$L$2,TE_discrete_twobins_max.6!$N$2,TE_discrete_twobins_max.6!$P$2,TE_discrete_twobins_max.6!$R$2,TE_discrete_twobins_max.6!$T$2,TE_discrete_twobins_max.6!$V$2,TE_discrete_twobins_max.6!$X$2,TE_discrete_twobins_max.6!$Z$2,TE_discrete_twobins_max.6!$AB$2,TE_discrete_twobins_max.6!$AD$2,TE_discrete_twobins_max.6!$AF$2,TE_discrete_twobins_max.6!$AH$2,TE_discrete_twobins_max.6!$AJ$2,TE_discrete_twobins_max.6!$AL$2,TE_discrete_twobins_max.6!$AN$2)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.47961134477407102</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.74818318506452797</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.66684062557869395</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.43899452362325198</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.92854612515368096</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.695354742861091</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.116140428350629</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.60213659380017204</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.43328185212397402</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.79845533254624101</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.63778406624884898</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.71398762283533301</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.35741104952619301</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.3156048068769899E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.69235877004801305</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.32977909011373502</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.21420744199342501</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.72785443888142598</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.69873102402570397</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.55135905721345702</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-985D-4102-B2F8-1BB4EBA5FEE4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>TE_discrete_twobins_max.6!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>mid</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobins_max.6!$B$1:$AO$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobins_max.6!$B$1,TE_discrete_twobins_max.6!$D$1,TE_discrete_twobins_max.6!$F$1,TE_discrete_twobins_max.6!$H$1,TE_discrete_twobins_max.6!$J$1,TE_discrete_twobins_max.6!$L$1,TE_discrete_twobins_max.6!$N$1,TE_discrete_twobins_max.6!$P$1,TE_discrete_twobins_max.6!$R$1,TE_discrete_twobins_max.6!$T$1,TE_discrete_twobins_max.6!$V$1,TE_discrete_twobins_max.6!$X$1,TE_discrete_twobins_max.6!$Z$1,TE_discrete_twobins_max.6!$AB$1,TE_discrete_twobins_max.6!$AD$1,TE_discrete_twobins_max.6!$AF$1,TE_discrete_twobins_max.6!$AH$1,TE_discrete_twobins_max.6!$AJ$1,TE_discrete_twobins_max.6!$AL$1,TE_discrete_twobins_max.6!$AN$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>dyad_02_anno01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>dyad_03_anno01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>dyad_04_anno01</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>dyad_05_anno01</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>dyad_06_anno01</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>dyad_07_anno01</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>dyad_10_anno01</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>dyad_11_anno01</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>triad_01_anno01</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>triad_02_anno01</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>triad_05_anno01</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>triad_06_anno01</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>triad_07_anno01</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>triad_08_anno01</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>triad_09_anno01</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>triad_10_anno01</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>triad_11_anno01</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>triad_12_anno01</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>triad_13_anno01</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>triad_14_anno01</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobins_max.6!$B$3:$AO$3</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobins_max.6!$B$3,TE_discrete_twobins_max.6!$D$3,TE_discrete_twobins_max.6!$F$3,TE_discrete_twobins_max.6!$H$3,TE_discrete_twobins_max.6!$J$3,TE_discrete_twobins_max.6!$L$3,TE_discrete_twobins_max.6!$N$3,TE_discrete_twobins_max.6!$P$3,TE_discrete_twobins_max.6!$R$3,TE_discrete_twobins_max.6!$T$3,TE_discrete_twobins_max.6!$V$3,TE_discrete_twobins_max.6!$X$3,TE_discrete_twobins_max.6!$Z$3,TE_discrete_twobins_max.6!$AB$3,TE_discrete_twobins_max.6!$AD$3,TE_discrete_twobins_max.6!$AF$3,TE_discrete_twobins_max.6!$AH$3,TE_discrete_twobins_max.6!$AJ$3,TE_discrete_twobins_max.6!$AL$3,TE_discrete_twobins_max.6!$AN$3)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.14992915139110599</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.143731988472622</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.13700106058820499</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.30067349229565599</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1044197628623201E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.110888455093544</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.22885846765290299</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.34173150549586201</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.132581607713184</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.01908697363242E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.28904012083123498</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.20964491448342201</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.218027636586549</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.15169147100961899</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.22900704872816399</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.33970363079615001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.71232550383534199</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.20410306508731199</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.26164732215382902</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.36618513590572099</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-985D-4102-B2F8-1BB4EBA5FEE4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>TE_discrete_twobins_max.6!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>low</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="C00000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobins_max.6!$B$1:$AO$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobins_max.6!$B$1,TE_discrete_twobins_max.6!$D$1,TE_discrete_twobins_max.6!$F$1,TE_discrete_twobins_max.6!$H$1,TE_discrete_twobins_max.6!$J$1,TE_discrete_twobins_max.6!$L$1,TE_discrete_twobins_max.6!$N$1,TE_discrete_twobins_max.6!$P$1,TE_discrete_twobins_max.6!$R$1,TE_discrete_twobins_max.6!$T$1,TE_discrete_twobins_max.6!$V$1,TE_discrete_twobins_max.6!$X$1,TE_discrete_twobins_max.6!$Z$1,TE_discrete_twobins_max.6!$AB$1,TE_discrete_twobins_max.6!$AD$1,TE_discrete_twobins_max.6!$AF$1,TE_discrete_twobins_max.6!$AH$1,TE_discrete_twobins_max.6!$AJ$1,TE_discrete_twobins_max.6!$AL$1,TE_discrete_twobins_max.6!$AN$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>dyad_02_anno01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>dyad_03_anno01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>dyad_04_anno01</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>dyad_05_anno01</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>dyad_06_anno01</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>dyad_07_anno01</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>dyad_10_anno01</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>dyad_11_anno01</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>triad_01_anno01</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>triad_02_anno01</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>triad_05_anno01</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>triad_06_anno01</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>triad_07_anno01</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>triad_08_anno01</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>triad_09_anno01</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>triad_10_anno01</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>triad_11_anno01</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>triad_12_anno01</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>triad_13_anno01</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>triad_14_anno01</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobins_max.6!$B$4:$AO$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobins_max.6!$B$4,TE_discrete_twobins_max.6!$D$4,TE_discrete_twobins_max.6!$F$4,TE_discrete_twobins_max.6!$H$4,TE_discrete_twobins_max.6!$J$4,TE_discrete_twobins_max.6!$L$4,TE_discrete_twobins_max.6!$N$4,TE_discrete_twobins_max.6!$P$4,TE_discrete_twobins_max.6!$R$4,TE_discrete_twobins_max.6!$T$4,TE_discrete_twobins_max.6!$V$4,TE_discrete_twobins_max.6!$X$4,TE_discrete_twobins_max.6!$Z$4,TE_discrete_twobins_max.6!$AB$4,TE_discrete_twobins_max.6!$AD$4,TE_discrete_twobins_max.6!$AF$4,TE_discrete_twobins_max.6!$AH$4,TE_discrete_twobins_max.6!$AJ$4,TE_discrete_twobins_max.6!$AL$4,TE_discrete_twobins_max.6!$AN$4)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.37045950383482101</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.108069164265129</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.19615831383310001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.25801898023742298</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.0388839108962401E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.19373952700951799</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.65381430779421501</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.6131900703964399E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.42654930950203102</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.16135379771743399</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7.3175812919914499E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7.6367462681243406E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.42456131388725699</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.78515248092161005</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7.8608642353662203E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.33051727909011303</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7.3467054171232504E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>6.8042496031261404E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.9621653820466E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.2455806880821103E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-985D-4102-B2F8-1BB4EBA5FEE4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="1855509952"/>
+        <c:axId val="1855510912"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1855509952"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1855510912"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1855510912"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1855509952"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Anno Laura</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="percentStacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>TE_discrete_twobins_max.6!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>high</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobins_max.6!$B$1:$AO$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobins_max.6!$C$1,TE_discrete_twobins_max.6!$E$1,TE_discrete_twobins_max.6!$G$1,TE_discrete_twobins_max.6!$I$1,TE_discrete_twobins_max.6!$K$1,TE_discrete_twobins_max.6!$M$1,TE_discrete_twobins_max.6!$O$1,TE_discrete_twobins_max.6!$Q$1,TE_discrete_twobins_max.6!$S$1,TE_discrete_twobins_max.6!$U$1,TE_discrete_twobins_max.6!$W$1,TE_discrete_twobins_max.6!$Y$1,TE_discrete_twobins_max.6!$AA$1,TE_discrete_twobins_max.6!$AC$1,TE_discrete_twobins_max.6!$AE$1,TE_discrete_twobins_max.6!$AG$1,TE_discrete_twobins_max.6!$AI$1,TE_discrete_twobins_max.6!$AK$1,TE_discrete_twobins_max.6!$AM$1,TE_discrete_twobins_max.6!$AO$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>dyad_02_anno02</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>dyad_03_anno02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>dyad_04_anno02</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>dyad_05_anno02</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>dyad_06_anno02</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>dyad_07_anno02</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>dyad_10_anno02</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>dyad_11_anno02</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>triad_01_anno02</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>triad_02_anno02</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>triad_05_anno02</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>triad_06_anno02</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>triad_07_anno02</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>triad_08_anno02</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>triad_09_anno02</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>triad_10_anno02</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>triad_11_anno02</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>triad_12_anno02</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>triad_13_anno02</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>triad_14_anno02</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobins_max.6!$B$2:$AO$2</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobins_max.6!$C$2,TE_discrete_twobins_max.6!$E$2,TE_discrete_twobins_max.6!$G$2,TE_discrete_twobins_max.6!$I$2,TE_discrete_twobins_max.6!$K$2,TE_discrete_twobins_max.6!$M$2,TE_discrete_twobins_max.6!$O$2,TE_discrete_twobins_max.6!$Q$2,TE_discrete_twobins_max.6!$S$2,TE_discrete_twobins_max.6!$U$2,TE_discrete_twobins_max.6!$W$2,TE_discrete_twobins_max.6!$Y$2,TE_discrete_twobins_max.6!$AA$2,TE_discrete_twobins_max.6!$AC$2,TE_discrete_twobins_max.6!$AE$2,TE_discrete_twobins_max.6!$AG$2,TE_discrete_twobins_max.6!$AI$2,TE_discrete_twobins_max.6!$AK$2,TE_discrete_twobins_max.6!$AM$2,TE_discrete_twobins_max.6!$AO$2)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.241717460246058</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.48646786117027901</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.52275214221982702</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.35996122317085599</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.826293525599616</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.56917788104410305</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.9939280194303301E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.1466798402700593E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.212697365461606</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.60706906729634003</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.68918942379472E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.28492447076028599</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7.0496283619830902E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.50807028297068102</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.6438101487314E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.12382464281353001</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.14697016191628001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.21199391750617699</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1047-4E72-A8E9-B5D1A5C11E8C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>TE_discrete_twobins_max.6!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>mid</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobins_max.6!$B$1:$AO$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobins_max.6!$C$1,TE_discrete_twobins_max.6!$E$1,TE_discrete_twobins_max.6!$G$1,TE_discrete_twobins_max.6!$I$1,TE_discrete_twobins_max.6!$K$1,TE_discrete_twobins_max.6!$M$1,TE_discrete_twobins_max.6!$O$1,TE_discrete_twobins_max.6!$Q$1,TE_discrete_twobins_max.6!$S$1,TE_discrete_twobins_max.6!$U$1,TE_discrete_twobins_max.6!$W$1,TE_discrete_twobins_max.6!$Y$1,TE_discrete_twobins_max.6!$AA$1,TE_discrete_twobins_max.6!$AC$1,TE_discrete_twobins_max.6!$AE$1,TE_discrete_twobins_max.6!$AG$1,TE_discrete_twobins_max.6!$AI$1,TE_discrete_twobins_max.6!$AK$1,TE_discrete_twobins_max.6!$AM$1,TE_discrete_twobins_max.6!$AO$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>dyad_02_anno02</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>dyad_03_anno02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>dyad_04_anno02</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>dyad_05_anno02</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>dyad_06_anno02</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>dyad_07_anno02</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>dyad_10_anno02</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>dyad_11_anno02</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>triad_01_anno02</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>triad_02_anno02</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>triad_05_anno02</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>triad_06_anno02</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>triad_07_anno02</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>triad_08_anno02</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>triad_09_anno02</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>triad_10_anno02</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>triad_11_anno02</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>triad_12_anno02</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>triad_13_anno02</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>triad_14_anno02</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobins_max.6!$B$3:$AO$3</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobins_max.6!$C$3,TE_discrete_twobins_max.6!$E$3,TE_discrete_twobins_max.6!$G$3,TE_discrete_twobins_max.6!$I$3,TE_discrete_twobins_max.6!$K$3,TE_discrete_twobins_max.6!$M$3,TE_discrete_twobins_max.6!$O$3,TE_discrete_twobins_max.6!$Q$3,TE_discrete_twobins_max.6!$S$3,TE_discrete_twobins_max.6!$U$3,TE_discrete_twobins_max.6!$W$3,TE_discrete_twobins_max.6!$Y$3,TE_discrete_twobins_max.6!$AA$3,TE_discrete_twobins_max.6!$AC$3,TE_discrete_twobins_max.6!$AE$3,TE_discrete_twobins_max.6!$AG$3,TE_discrete_twobins_max.6!$AI$3,TE_discrete_twobins_max.6!$AK$3,TE_discrete_twobins_max.6!$AM$3,TE_discrete_twobins_max.6!$AO$3)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.24365173972695101</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.39512592406966501</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.21691554014242101</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.28138712201095201</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.123424118027047</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.255929656054036</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.22656767498343999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.68852661479560295</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.326925672129672</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.25819067296339998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.27978680925678301</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.52822314565461603</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.13473474496181401</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.33621823923277E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.35110838696496</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.473507217847769</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.51803325551479296</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.53185981194285004</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.28960811566995698</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.50058924158905105</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1047-4E72-A8E9-B5D1A5C11E8C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>TE_discrete_twobins_max.6!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>low</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="C00000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobins_max.6!$B$1:$AO$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobins_max.6!$C$1,TE_discrete_twobins_max.6!$E$1,TE_discrete_twobins_max.6!$G$1,TE_discrete_twobins_max.6!$I$1,TE_discrete_twobins_max.6!$K$1,TE_discrete_twobins_max.6!$M$1,TE_discrete_twobins_max.6!$O$1,TE_discrete_twobins_max.6!$Q$1,TE_discrete_twobins_max.6!$S$1,TE_discrete_twobins_max.6!$U$1,TE_discrete_twobins_max.6!$W$1,TE_discrete_twobins_max.6!$Y$1,TE_discrete_twobins_max.6!$AA$1,TE_discrete_twobins_max.6!$AC$1,TE_discrete_twobins_max.6!$AE$1,TE_discrete_twobins_max.6!$AG$1,TE_discrete_twobins_max.6!$AI$1,TE_discrete_twobins_max.6!$AK$1,TE_discrete_twobins_max.6!$AM$1,TE_discrete_twobins_max.6!$AO$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>dyad_02_anno02</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>dyad_03_anno02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>dyad_04_anno02</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>dyad_05_anno02</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>dyad_06_anno02</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>dyad_07_anno02</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>dyad_10_anno02</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>dyad_11_anno02</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>triad_01_anno02</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>triad_02_anno02</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>triad_05_anno02</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>triad_06_anno02</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>triad_07_anno02</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>triad_08_anno02</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>triad_09_anno02</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>triad_10_anno02</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>triad_11_anno02</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>triad_12_anno02</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>triad_13_anno02</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>triad_14_anno02</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>TE_discrete_twobins_max.6!$B$4:$AO$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(TE_discrete_twobins_max.6!$C$4,TE_discrete_twobins_max.6!$E$4,TE_discrete_twobins_max.6!$G$4,TE_discrete_twobins_max.6!$I$4,TE_discrete_twobins_max.6!$K$4,TE_discrete_twobins_max.6!$M$4,TE_discrete_twobins_max.6!$O$4,TE_discrete_twobins_max.6!$Q$4,TE_discrete_twobins_max.6!$S$4,TE_discrete_twobins_max.6!$U$4,TE_discrete_twobins_max.6!$W$4,TE_discrete_twobins_max.6!$Y$4,TE_discrete_twobins_max.6!$AA$4,TE_discrete_twobins_max.6!$AC$4,TE_discrete_twobins_max.6!$AE$4,TE_discrete_twobins_max.6!$AG$4,TE_discrete_twobins_max.6!$AI$4,TE_discrete_twobins_max.6!$AK$4,TE_discrete_twobins_max.6!$AM$4,TE_discrete_twobins_max.6!$AO$4)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.41566766379523601</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.118374890364615</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.26033231763775</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.35149154733154098</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.9990622851069998E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.16620311987147299</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.38024398321925301</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.22852085134411901</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.44551738615405301</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.13474025974025899</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.35603548549504299</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.17344081610814799</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.64189931291665603</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.96657992456360897</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.140770252324037</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.46855861767279</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.48196674448520599</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.33659787519843598</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.55623747721077998</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.27099410758410902</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1047-4E72-A8E9-B5D1A5C11E8C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="1855509952"/>
+        <c:axId val="1855510912"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1855509952"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1855510912"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1855510912"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1855509952"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
               <a:t>Helen</a:t>
             </a:r>
           </a:p>
@@ -7370,7 +9049,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -19344,6 +21023,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors16.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors17.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -22593,6 +24352,1016 @@
 </file>
 
 <file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style16.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style17.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -27644,6 +30413,85 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>911860</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>54610</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1035050</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>54610</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E0BAD38-9583-DC64-3811-B74F9C8F599C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>899160</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1026160</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{712A12D7-2452-4884-80DF-56E0858B5574}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>311150</xdr:colOff>
       <xdr:row>11</xdr:row>
@@ -28004,6 +30852,56 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{43D77003-72FC-41C3-87BD-A5FBB1AABC59}" name="Table7" displayName="Table7" ref="A1:AO4" totalsRowShown="0">
+  <autoFilter ref="A1:AO4" xr:uid="{43D77003-72FC-41C3-87BD-A5FBB1AABC59}"/>
+  <tableColumns count="41">
+    <tableColumn id="1" xr3:uid="{FC2DAC51-5BF4-45C9-8CBB-5F2E023FFCCF}" name="task_eng"/>
+    <tableColumn id="2" xr3:uid="{7F24C492-7D02-4601-866A-78BAEB88EB0E}" name="dyad_02_anno01"/>
+    <tableColumn id="3" xr3:uid="{C1891BFD-F445-460C-9E6A-6D77E0E4C621}" name="dyad_02_anno02"/>
+    <tableColumn id="4" xr3:uid="{EDC2C213-DE1A-40C2-B091-BDD51AE57624}" name="dyad_03_anno01"/>
+    <tableColumn id="5" xr3:uid="{F373B450-4B43-449F-A850-52564AD7EB64}" name="dyad_03_anno02"/>
+    <tableColumn id="6" xr3:uid="{92320449-409B-41E0-BE88-3DFE1A3A7F0F}" name="dyad_04_anno01"/>
+    <tableColumn id="7" xr3:uid="{0D6495A1-B397-4940-8D68-188FB75C6AF8}" name="dyad_04_anno02"/>
+    <tableColumn id="8" xr3:uid="{0A02E8D0-B5F5-4E42-8942-CD64D5D77461}" name="dyad_05_anno01"/>
+    <tableColumn id="9" xr3:uid="{9DBF7BE4-D471-4C34-AF7C-BD0A43B75492}" name="dyad_05_anno02"/>
+    <tableColumn id="10" xr3:uid="{3463D826-CF64-4217-BB9E-474C0F41DF2C}" name="dyad_06_anno01"/>
+    <tableColumn id="11" xr3:uid="{AC74516E-9C45-4B4B-9C48-BDE98BF69A0B}" name="dyad_06_anno02"/>
+    <tableColumn id="12" xr3:uid="{B1CF669A-71F9-4878-8832-2975ABA8BA76}" name="dyad_07_anno01"/>
+    <tableColumn id="13" xr3:uid="{618BB242-32B5-43AC-9937-6A903077CD34}" name="dyad_07_anno02"/>
+    <tableColumn id="14" xr3:uid="{E62BFD50-9ED3-4CD1-86DE-65BDFDD2DBED}" name="dyad_10_anno01"/>
+    <tableColumn id="15" xr3:uid="{A4611B9E-2E0B-45A2-98E3-1F158F067633}" name="dyad_10_anno02"/>
+    <tableColumn id="16" xr3:uid="{6A2927A9-E70A-4AA6-BD10-C29A082888AF}" name="dyad_11_anno01"/>
+    <tableColumn id="17" xr3:uid="{353C28AD-ACED-435C-BC6C-A24CC84009E3}" name="dyad_11_anno02"/>
+    <tableColumn id="18" xr3:uid="{B4F86DAA-4D88-49A7-BD94-8D6224A70E3E}" name="triad_01_anno01"/>
+    <tableColumn id="19" xr3:uid="{05B5A658-1CD0-43A7-8107-11477F3A077A}" name="triad_01_anno02"/>
+    <tableColumn id="20" xr3:uid="{D047B543-DCBC-43C6-A17F-4D02A6B6E615}" name="triad_02_anno01"/>
+    <tableColumn id="21" xr3:uid="{3D3513BC-134D-4E60-BC75-65899C48716C}" name="triad_02_anno02"/>
+    <tableColumn id="22" xr3:uid="{276B2177-F32B-4BA6-87B3-EF61C38C6190}" name="triad_05_anno01"/>
+    <tableColumn id="23" xr3:uid="{FB430E1F-00B4-439E-8EE2-B837CA136DE1}" name="triad_05_anno02"/>
+    <tableColumn id="24" xr3:uid="{8F85512B-3E23-4A86-9F51-7743819540B1}" name="triad_06_anno01"/>
+    <tableColumn id="25" xr3:uid="{320A7445-D213-4C91-90B2-16BCC7597505}" name="triad_06_anno02"/>
+    <tableColumn id="26" xr3:uid="{8F834221-57A2-463D-8571-88AB09F5E74D}" name="triad_07_anno01"/>
+    <tableColumn id="27" xr3:uid="{13D95AAE-8749-492A-9FCF-56C6FBBB50C1}" name="triad_07_anno02"/>
+    <tableColumn id="28" xr3:uid="{9ADDFE8F-058B-44D5-AAC7-7AF487B823FC}" name="triad_08_anno01"/>
+    <tableColumn id="29" xr3:uid="{4C28F3A0-3F6D-4F0B-BB67-EE72E81C1D2C}" name="triad_08_anno02"/>
+    <tableColumn id="30" xr3:uid="{417EB2B8-47EB-4A83-8411-E233DCCBB01E}" name="triad_09_anno01"/>
+    <tableColumn id="31" xr3:uid="{3A033465-C487-4DA3-BF89-ADCFDC862AA8}" name="triad_09_anno02"/>
+    <tableColumn id="32" xr3:uid="{9E9EB5C4-71CC-4295-8144-F64F0E2EE899}" name="triad_10_anno01"/>
+    <tableColumn id="33" xr3:uid="{778C1DA6-16AE-4479-8A4F-1237E19FC8B1}" name="triad_10_anno02"/>
+    <tableColumn id="34" xr3:uid="{9B1E0C4F-341B-4C9B-99DC-96EC8328A14E}" name="triad_11_anno01"/>
+    <tableColumn id="35" xr3:uid="{B8272AF2-A1AB-42B6-B4C5-FF42D12E8D41}" name="triad_11_anno02"/>
+    <tableColumn id="36" xr3:uid="{1D38FA2E-A362-4B6A-A98E-00238224768D}" name="triad_12_anno01"/>
+    <tableColumn id="37" xr3:uid="{55144FD5-9909-4DA6-B954-28292E8CBD04}" name="triad_12_anno02"/>
+    <tableColumn id="38" xr3:uid="{7EF44916-A4DB-4D81-9A99-CD3DCD3FA8C9}" name="triad_13_anno01"/>
+    <tableColumn id="39" xr3:uid="{8CA25747-C54D-4C5F-89DA-43E92FDCF4D9}" name="triad_13_anno02"/>
+    <tableColumn id="40" xr3:uid="{1606CA01-AF36-425F-94F0-7B261117F93E}" name="triad_14_anno01"/>
+    <tableColumn id="41" xr3:uid="{730869A0-3E6E-4C09-889B-DF6EDEC6B82C}" name="triad_14_anno02"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{14C2C227-83C2-456E-B0F3-DF58A3760A57}" name="Table6" displayName="Table6" ref="A1:AO4" totalsRowShown="0">
   <autoFilter ref="A1:AO4" xr:uid="{14C2C227-83C2-456E-B0F3-DF58A3760A57}"/>
   <tableColumns count="41">
@@ -32473,7 +35371,7 @@
       </c>
     </row>
     <row r="16" spans="1:108" x14ac:dyDescent="0.35">
-      <c r="BR16" s="5" t="s">
+      <c r="BR16" s="6" t="s">
         <v>64</v>
       </c>
     </row>
@@ -34160,19 +37058,19 @@
       <c r="AX4" s="3">
         <v>8.2455806880821103E-2</v>
       </c>
-      <c r="AY4" s="4">
+      <c r="AY4" s="5">
         <v>0.27099410758410902</v>
       </c>
     </row>
     <row r="8" spans="1:51" x14ac:dyDescent="0.35">
-      <c r="I8" s="5"/>
-      <c r="U8" s="5"/>
-      <c r="W8" s="5"/>
+      <c r="I8" s="6"/>
+      <c r="U8" s="6"/>
+      <c r="W8" s="6"/>
     </row>
     <row r="9" spans="1:51" x14ac:dyDescent="0.35">
-      <c r="I9" s="5"/>
-      <c r="U9" s="5"/>
-      <c r="W9" s="5"/>
+      <c r="I9" s="6"/>
+      <c r="U9" s="6"/>
+      <c r="W9" s="6"/>
     </row>
     <row r="10" spans="1:51" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
@@ -34367,13 +37265,13 @@
       </c>
     </row>
     <row r="13" spans="1:51" x14ac:dyDescent="0.35">
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="U13" s="5" t="s">
+      <c r="U13" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="X13" s="5" t="s">
+      <c r="X13" s="6" t="s">
         <v>96</v>
       </c>
     </row>
@@ -34381,21 +37279,21 @@
       <c r="H14" t="s">
         <v>101</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="6">
         <f>AVERAGE(B11:I11)</f>
         <v>0.79735231488669767</v>
       </c>
       <c r="T14" t="s">
         <v>101</v>
       </c>
-      <c r="U14" s="5">
+      <c r="U14" s="6">
         <f>AVERAGE(J11:U11)</f>
         <v>0.71476217040747125</v>
       </c>
       <c r="W14" t="s">
         <v>101</v>
       </c>
-      <c r="X14" s="5">
+      <c r="X14" s="6">
         <f>AVERAGE(I14,U14)</f>
         <v>0.7560572426470844</v>
       </c>
@@ -34404,21 +37302,21 @@
       <c r="H15" t="s">
         <v>102</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="6">
         <f>AVERAGE(B12:I12)</f>
         <v>0.78931812098923593</v>
       </c>
       <c r="T15" t="s">
         <v>102</v>
       </c>
-      <c r="U15" s="5">
+      <c r="U15" s="6">
         <f>AVERAGE(J12:U12)</f>
         <v>0.6377205946722514</v>
       </c>
       <c r="W15" t="s">
         <v>102</v>
       </c>
-      <c r="X15" s="5">
+      <c r="X15" s="6">
         <f>AVERAGE(I15,U15)</f>
         <v>0.71351935783074372</v>
       </c>
@@ -34433,6 +37331,790 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A44710D-3F52-4CD3-8D0B-15D643BAC720}">
+  <dimension ref="A1:AO15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.7265625" customWidth="1"/>
+    <col min="2" max="17" width="15.90625" customWidth="1"/>
+    <col min="18" max="41" width="15.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>22</v>
+      </c>
+      <c r="R1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1" t="s">
+        <v>25</v>
+      </c>
+      <c r="U1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W1" t="s">
+        <v>32</v>
+      </c>
+      <c r="X1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2">
+        <v>0.47961134477407102</v>
+      </c>
+      <c r="C2">
+        <v>0.241717460246058</v>
+      </c>
+      <c r="D2">
+        <v>0.74818318506452797</v>
+      </c>
+      <c r="E2">
+        <v>0.48646786117027901</v>
+      </c>
+      <c r="F2">
+        <v>0.66684062557869395</v>
+      </c>
+      <c r="G2">
+        <v>0.52275214221982702</v>
+      </c>
+      <c r="H2">
+        <v>0.43899452362325198</v>
+      </c>
+      <c r="I2">
+        <v>0.35996122317085599</v>
+      </c>
+      <c r="J2">
+        <v>0.92854612515368096</v>
+      </c>
+      <c r="K2">
+        <v>0.826293525599616</v>
+      </c>
+      <c r="L2">
+        <v>0.695354742861091</v>
+      </c>
+      <c r="M2">
+        <v>0.56917788104410305</v>
+      </c>
+      <c r="N2">
+        <v>0.116140428350629</v>
+      </c>
+      <c r="O2">
+        <v>9.9939280194303301E-2</v>
+      </c>
+      <c r="P2">
+        <v>0.60213659380017204</v>
+      </c>
+      <c r="Q2">
+        <v>7.1466798402700593E-2</v>
+      </c>
+      <c r="R2">
+        <v>0.43328185212397402</v>
+      </c>
+      <c r="S2">
+        <v>0.212697365461606</v>
+      </c>
+      <c r="T2">
+        <v>0.79845533254624101</v>
+      </c>
+      <c r="U2">
+        <v>0.60706906729634003</v>
+      </c>
+      <c r="V2">
+        <v>0.63778406624884898</v>
+      </c>
+      <c r="W2">
+        <v>2.68918942379472E-2</v>
+      </c>
+      <c r="X2">
+        <v>0.71398762283533301</v>
+      </c>
+      <c r="Y2">
+        <v>0.28492447076028599</v>
+      </c>
+      <c r="Z2">
+        <v>0.35741104952619301</v>
+      </c>
+      <c r="AA2">
+        <v>7.0496283619830902E-2</v>
+      </c>
+      <c r="AB2">
+        <v>6.3156048068769899E-2</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0.69235877004801305</v>
+      </c>
+      <c r="AE2">
+        <v>0.50807028297068102</v>
+      </c>
+      <c r="AF2">
+        <v>0.32977909011373502</v>
+      </c>
+      <c r="AG2">
+        <v>2.6438101487314E-2</v>
+      </c>
+      <c r="AH2">
+        <v>0.21420744199342501</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0.72785443888142598</v>
+      </c>
+      <c r="AK2">
+        <v>0.12382464281353001</v>
+      </c>
+      <c r="AL2">
+        <v>0.69873102402570397</v>
+      </c>
+      <c r="AM2">
+        <v>0.14697016191628001</v>
+      </c>
+      <c r="AN2">
+        <v>0.55135905721345702</v>
+      </c>
+      <c r="AO2">
+        <v>0.21199391750617699</v>
+      </c>
+    </row>
+    <row r="3" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="3">
+        <v>0.14992915139110599</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0.24365173972695101</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0.143731988472622</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.39512592406966501</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.13700106058820499</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0.21691554014242101</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.30067349229565599</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.28138712201095201</v>
+      </c>
+      <c r="J3" s="3">
+        <v>1.1044197628623201E-2</v>
+      </c>
+      <c r="K3" s="3">
+        <v>0.123424118027047</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0.110888455093544</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0.255929656054036</v>
+      </c>
+      <c r="N3" s="3">
+        <v>0.22885846765290299</v>
+      </c>
+      <c r="O3" s="3">
+        <v>0.22656767498343999</v>
+      </c>
+      <c r="P3" s="3">
+        <v>0.34173150549586201</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>0.68852661479560295</v>
+      </c>
+      <c r="R3" s="3">
+        <v>0.132581607713184</v>
+      </c>
+      <c r="S3" s="3">
+        <v>0.326925672129672</v>
+      </c>
+      <c r="T3" s="3">
+        <v>4.01908697363242E-2</v>
+      </c>
+      <c r="U3" s="3">
+        <v>0.25819067296339998</v>
+      </c>
+      <c r="V3" s="3">
+        <v>0.28904012083123498</v>
+      </c>
+      <c r="W3" s="3">
+        <v>0.27978680925678301</v>
+      </c>
+      <c r="X3" s="3">
+        <v>0.20964491448342201</v>
+      </c>
+      <c r="Y3" s="3">
+        <v>0.52822314565461603</v>
+      </c>
+      <c r="Z3" s="3">
+        <v>0.218027636586549</v>
+      </c>
+      <c r="AA3" s="3">
+        <v>0.13473474496181401</v>
+      </c>
+      <c r="AB3" s="3">
+        <v>0.15169147100961899</v>
+      </c>
+      <c r="AC3" s="3">
+        <v>1.33621823923277E-2</v>
+      </c>
+      <c r="AD3" s="3">
+        <v>0.22900704872816399</v>
+      </c>
+      <c r="AE3" s="3">
+        <v>0.35110838696496</v>
+      </c>
+      <c r="AF3" s="3">
+        <v>0.33970363079615001</v>
+      </c>
+      <c r="AG3" s="3">
+        <v>0.473507217847769</v>
+      </c>
+      <c r="AH3" s="3">
+        <v>0.71232550383534199</v>
+      </c>
+      <c r="AI3" s="3">
+        <v>0.51803325551479296</v>
+      </c>
+      <c r="AJ3" s="3">
+        <v>0.20410306508731199</v>
+      </c>
+      <c r="AK3" s="3">
+        <v>0.53185981194285004</v>
+      </c>
+      <c r="AL3" s="3">
+        <v>0.26164732215382902</v>
+      </c>
+      <c r="AM3" s="3">
+        <v>0.28960811566995698</v>
+      </c>
+      <c r="AN3" s="3">
+        <v>0.36618513590572099</v>
+      </c>
+      <c r="AO3" s="5">
+        <v>0.50058924158905105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.37045950383482101</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.41566766379523601</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.108069164265129</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.118374890364615</v>
+      </c>
+      <c r="F4" s="8">
+        <v>0.19615831383310001</v>
+      </c>
+      <c r="G4" s="8">
+        <v>0.26033231763775</v>
+      </c>
+      <c r="H4" s="8">
+        <v>0.25801898023742298</v>
+      </c>
+      <c r="I4" s="8">
+        <v>0.35149154733154098</v>
+      </c>
+      <c r="J4" s="8">
+        <v>6.0388839108962401E-2</v>
+      </c>
+      <c r="K4" s="8">
+        <v>4.9990622851069998E-2</v>
+      </c>
+      <c r="L4" s="8">
+        <v>0.19373952700951799</v>
+      </c>
+      <c r="M4" s="8">
+        <v>0.16620311987147299</v>
+      </c>
+      <c r="N4" s="8">
+        <v>0.65381430779421501</v>
+      </c>
+      <c r="O4" s="8">
+        <v>0.38024398321925301</v>
+      </c>
+      <c r="P4" s="8">
+        <v>5.6131900703964399E-2</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0.22852085134411901</v>
+      </c>
+      <c r="R4" s="8">
+        <v>0.42654930950203102</v>
+      </c>
+      <c r="S4" s="8">
+        <v>0.44551738615405301</v>
+      </c>
+      <c r="T4" s="8">
+        <v>0.16135379771743399</v>
+      </c>
+      <c r="U4" s="8">
+        <v>0.13474025974025899</v>
+      </c>
+      <c r="V4" s="8">
+        <v>7.3175812919914499E-2</v>
+      </c>
+      <c r="W4" s="8">
+        <v>0.35603548549504299</v>
+      </c>
+      <c r="X4" s="8">
+        <v>7.6367462681243406E-2</v>
+      </c>
+      <c r="Y4" s="8">
+        <v>0.17344081610814799</v>
+      </c>
+      <c r="Z4" s="8">
+        <v>0.42456131388725699</v>
+      </c>
+      <c r="AA4" s="8">
+        <v>0.64189931291665603</v>
+      </c>
+      <c r="AB4" s="8">
+        <v>0.78515248092161005</v>
+      </c>
+      <c r="AC4" s="8">
+        <v>0.96657992456360897</v>
+      </c>
+      <c r="AD4" s="8">
+        <v>7.8608642353662203E-2</v>
+      </c>
+      <c r="AE4" s="8">
+        <v>0.140770252324037</v>
+      </c>
+      <c r="AF4" s="8">
+        <v>0.33051727909011303</v>
+      </c>
+      <c r="AG4" s="8">
+        <v>0.46855861767279</v>
+      </c>
+      <c r="AH4" s="8">
+        <v>7.3467054171232504E-2</v>
+      </c>
+      <c r="AI4" s="8">
+        <v>0.48196674448520599</v>
+      </c>
+      <c r="AJ4" s="8">
+        <v>6.8042496031261404E-2</v>
+      </c>
+      <c r="AK4" s="8">
+        <v>0.33659787519843598</v>
+      </c>
+      <c r="AL4" s="8">
+        <v>3.9621653820466E-2</v>
+      </c>
+      <c r="AM4" s="8">
+        <v>0.55623747721077998</v>
+      </c>
+      <c r="AN4" s="8">
+        <v>8.2455806880821103E-2</v>
+      </c>
+      <c r="AO4" s="9">
+        <v>0.27099410758410902</v>
+      </c>
+    </row>
+    <row r="8" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" t="s">
+        <v>79</v>
+      </c>
+      <c r="I10" t="s">
+        <v>80</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K10" t="s">
+        <v>82</v>
+      </c>
+      <c r="L10" t="s">
+        <v>83</v>
+      </c>
+      <c r="M10" t="s">
+        <v>84</v>
+      </c>
+      <c r="N10" t="s">
+        <v>85</v>
+      </c>
+      <c r="O10" t="s">
+        <v>86</v>
+      </c>
+      <c r="P10" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>88</v>
+      </c>
+      <c r="R10" t="s">
+        <v>89</v>
+      </c>
+      <c r="S10" t="s">
+        <v>90</v>
+      </c>
+      <c r="T10" t="s">
+        <v>91</v>
+      </c>
+      <c r="U10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11">
+        <v>0.86276146222643102</v>
+      </c>
+      <c r="C11">
+        <v>0.74074689803015803</v>
+      </c>
+      <c r="D11">
+        <v>0.85054928065416602</v>
+      </c>
+      <c r="E11">
+        <v>0.81632449232768201</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.79085038760443604</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0.77813793483798299</v>
+      </c>
+      <c r="H11">
+        <v>0.83075341522976798</v>
+      </c>
+      <c r="I11">
+        <v>0.70869464818295702</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.81491130084522601</v>
+      </c>
+      <c r="K11">
+        <v>0.86785674397944002</v>
+      </c>
+      <c r="L11">
+        <v>0.519005742862511</v>
+      </c>
+      <c r="M11">
+        <v>0.69025879886924402</v>
+      </c>
+      <c r="N11">
+        <v>0.65165587962521498</v>
+      </c>
+      <c r="O11">
+        <v>0.44824897491003401</v>
+      </c>
+      <c r="P11">
+        <v>0.81223262502022398</v>
+      </c>
+      <c r="Q11">
+        <v>0.83410906420998399</v>
+      </c>
+      <c r="R11">
+        <v>0.64685998237570397</v>
+      </c>
+      <c r="S11">
+        <v>0.73227374615366603</v>
+      </c>
+      <c r="T11">
+        <v>0.699216950339417</v>
+      </c>
+      <c r="U11">
+        <v>0.86051623569899005</v>
+      </c>
+    </row>
+    <row r="12" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12">
+        <v>0.87329151349427903</v>
+      </c>
+      <c r="C12">
+        <v>0.80176934340182004</v>
+      </c>
+      <c r="D12">
+        <v>0.83605197895137695</v>
+      </c>
+      <c r="E12">
+        <v>0.81975662023687002</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.86323686557894896</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0.812628478806532</v>
+      </c>
+      <c r="H12">
+        <v>0.82802463353703104</v>
+      </c>
+      <c r="I12">
+        <v>0.70195784309208198</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0.91350308651576595</v>
+      </c>
+      <c r="K12">
+        <v>0.94134455317763999</v>
+      </c>
+      <c r="L12">
+        <v>0.52561884851548002</v>
+      </c>
+      <c r="M12">
+        <v>0.67635327187948402</v>
+      </c>
+      <c r="N12">
+        <v>0.55221033836424405</v>
+      </c>
+      <c r="O12">
+        <v>0.11462415329616001</v>
+      </c>
+      <c r="P12">
+        <v>0.79259398999524699</v>
+      </c>
+      <c r="Q12">
+        <v>0.85806510180867501</v>
+      </c>
+      <c r="R12">
+        <v>0.61135885828034597</v>
+      </c>
+      <c r="S12">
+        <v>0.71711677060452805</v>
+      </c>
+      <c r="T12">
+        <v>0.66093441773720096</v>
+      </c>
+      <c r="U12">
+        <v>0.81024684304642902</v>
+      </c>
+    </row>
+    <row r="13" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="I13" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="U13" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="X13" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="H14" t="s">
+        <v>101</v>
+      </c>
+      <c r="I14" s="6">
+        <f>AVERAGE(B11:I11)</f>
+        <v>0.79735231488669767</v>
+      </c>
+      <c r="T14" t="s">
+        <v>101</v>
+      </c>
+      <c r="U14" s="6">
+        <f>AVERAGE(J11:U11)</f>
+        <v>0.71476217040747125</v>
+      </c>
+      <c r="W14" t="s">
+        <v>101</v>
+      </c>
+      <c r="X14" s="6">
+        <f>AVERAGE(I14,U14)</f>
+        <v>0.7560572426470844</v>
+      </c>
+    </row>
+    <row r="15" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="H15" t="s">
+        <v>102</v>
+      </c>
+      <c r="I15" s="6">
+        <f>AVERAGE(B12:I12)</f>
+        <v>0.81708965963736746</v>
+      </c>
+      <c r="T15" t="s">
+        <v>102</v>
+      </c>
+      <c r="U15" s="6">
+        <f>AVERAGE(J12:U12)</f>
+        <v>0.68116418610176666</v>
+      </c>
+      <c r="W15" t="s">
+        <v>102</v>
+      </c>
+      <c r="X15" s="6">
+        <f>AVERAGE(I15,U15)</f>
+        <v>0.74912692286956706</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6E884E-4278-4958-AEF6-CE3AB5C8D996}">
   <dimension ref="A1:U11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -34456,10 +38138,10 @@
       <c r="G1" t="s">
         <v>78</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>80</v>
       </c>
       <c r="J1" t="s">
@@ -34521,10 +38203,10 @@
       <c r="G2">
         <v>0.78505091998955501</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="6">
         <v>-0.33398042471309602</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="6">
         <v>2.2800072977221301E-2</v>
       </c>
       <c r="J2">
@@ -34586,10 +38268,10 @@
       <c r="G3">
         <v>0.83794847262402505</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="6">
         <v>0.832584473541637</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="6">
         <v>0.64171827186225805</v>
       </c>
       <c r="J3">
@@ -34607,7 +38289,7 @@
       <c r="N3">
         <v>0.44227699763089001</v>
       </c>
-      <c r="O3" s="5">
+      <c r="O3" s="6">
         <v>0.106638622511867</v>
       </c>
       <c r="P3">
@@ -35018,7 +38700,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02421442-5A43-463D-935D-4B7C818F7F90}">
   <dimension ref="A1:AO10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -35559,13 +39241,13 @@
       <c r="K6" t="s">
         <v>82</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="L6" s="6" t="s">
         <v>83</v>
       </c>
       <c r="M6" t="s">
         <v>84</v>
       </c>
-      <c r="N6" s="5" t="s">
+      <c r="N6" s="6" t="s">
         <v>85</v>
       </c>
       <c r="O6" s="2" t="s">
@@ -35621,13 +39303,13 @@
       <c r="K7">
         <v>0.929829114228505</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="6">
         <v>0.48798560027497401</v>
       </c>
       <c r="M7">
         <v>0.644813503873365</v>
       </c>
-      <c r="N7" s="5">
+      <c r="N7" s="6">
         <v>0.53651404360751698</v>
       </c>
       <c r="O7" s="2"/>
@@ -35656,26 +39338,26 @@
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.35">
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="U9" s="5" t="s">
+      <c r="U9" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="W9" s="5" t="s">
+      <c r="W9" s="6" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.35">
-      <c r="I10" s="5">
+      <c r="I10" s="6">
         <f>AVERAGE(B7:I7)</f>
         <v>0.80998678629615406</v>
       </c>
-      <c r="U10" s="5">
+      <c r="U10" s="6">
         <f>AVERAGE(J7:U7)</f>
         <v>0.71687788941630504</v>
       </c>
-      <c r="W10" s="5">
+      <c r="W10" s="6">
         <f>AVERAGE(I10,U10)</f>
         <v>0.76343233785622955</v>
       </c>
@@ -35689,7 +39371,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20C27C4F-7112-48CC-8600-645EA3A54793}">
   <dimension ref="A1:W24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -35730,13 +39412,13 @@
       <c r="K1" t="s">
         <v>82</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="6" t="s">
         <v>83</v>
       </c>
       <c r="M1" t="s">
         <v>84</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="6" t="s">
         <v>85</v>
       </c>
       <c r="O1" s="2" t="s">
@@ -35795,13 +39477,13 @@
       <c r="K2">
         <v>0.86785674397944002</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="6">
         <v>-8.4598923649412197E-2</v>
       </c>
       <c r="M2">
         <v>0.21799042590743101</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="6">
         <v>-8.6805497576840196E-2</v>
       </c>
       <c r="O2" s="2">
@@ -35860,13 +39542,13 @@
       <c r="K3">
         <v>0.929829114228505</v>
       </c>
-      <c r="L3" s="5">
+      <c r="L3" s="6">
         <v>0.48798560027497401</v>
       </c>
       <c r="M3">
         <v>0.644813503873365</v>
       </c>
-      <c r="N3" s="5">
+      <c r="N3" s="6">
         <v>0.53651404360751698</v>
       </c>
       <c r="O3" s="2">
@@ -36292,13 +39974,13 @@
       </c>
     </row>
     <row r="17" spans="3:23" x14ac:dyDescent="0.35">
-      <c r="Q17" s="5"/>
+      <c r="Q17" s="6"/>
     </row>
     <row r="18" spans="3:23" x14ac:dyDescent="0.35">
-      <c r="Q18" s="5"/>
+      <c r="Q18" s="6"/>
     </row>
     <row r="19" spans="3:23" x14ac:dyDescent="0.35">
-      <c r="Q19" s="5"/>
+      <c r="Q19" s="6"/>
     </row>
     <row r="21" spans="3:23" x14ac:dyDescent="0.35">
       <c r="C21" t="s">

--- a/data/annotations/TE_discrete_percentages.xlsx
+++ b/data/annotations/TE_discrete_percentages.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dobregeo\Documents\GitHub\vilearn_ml\data\annotations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{906A2D7E-144E-4C96-8037-F1088B3BABA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7569F5-656A-4921-AED8-62F2ED16A5B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" tabRatio="666" firstSheet="2" activeTab="3" xr2:uid="{8450E3AB-A0C1-455F-AE9B-DBE7A60F6C99}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="666" activeTab="6" xr2:uid="{8450E3AB-A0C1-455F-AE9B-DBE7A60F6C99}"/>
   </bookViews>
   <sheets>
     <sheet name="TE_discrete_percentages" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,25 @@
     <sheet name="TE_discrete_twobinsV2" sheetId="6" r:id="rId6"/>
     <sheet name="interraterReliability windV2" sheetId="4" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="115">
   <si>
     <t>task_eng</t>
   </si>
@@ -363,6 +376,15 @@
   <si>
     <t>max val .8</t>
   </si>
+  <si>
+    <t>2pass</t>
+  </si>
+  <si>
+    <t>.75 - .6</t>
+  </si>
+  <si>
+    <t>continous</t>
+  </si>
 </sst>
 </file>
 
@@ -504,7 +526,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -682,6 +704,18 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -913,17 +947,26 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -969,7 +1012,359 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="115">
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
@@ -1999,7 +2394,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$B$2,TE_discrete_.1!$D$2,TE_discrete_.1!$F$2,TE_discrete_.1!$H$2,TE_discrete_.1!$J$2,TE_discrete_.1!$L$2,TE_discrete_.1!$N$2,TE_discrete_.1!$P$2,TE_discrete_.1!$R$2,TE_discrete_.1!$T$2,TE_discrete_.1!$V$2)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1.6895169409309699E-2</c:v>
@@ -2128,7 +2523,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$B$3,TE_discrete_.1!$D$3,TE_discrete_.1!$F$3,TE_discrete_.1!$H$3,TE_discrete_.1!$J$3,TE_discrete_.1!$L$3,TE_discrete_.1!$N$3,TE_discrete_.1!$P$3,TE_discrete_.1!$R$3,TE_discrete_.1!$T$3,TE_discrete_.1!$V$3)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>4.42239753985832E-2</c:v>
@@ -2257,7 +2652,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$B$4,TE_discrete_.1!$D$4,TE_discrete_.1!$F$4,TE_discrete_.1!$H$4,TE_discrete_.1!$J$4,TE_discrete_.1!$L$4,TE_discrete_.1!$N$4,TE_discrete_.1!$P$4,TE_discrete_.1!$R$4,TE_discrete_.1!$T$4,TE_discrete_.1!$V$4)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>8.3194523256026803E-2</c:v>
@@ -2386,7 +2781,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$B$5,TE_discrete_.1!$D$5,TE_discrete_.1!$F$5,TE_discrete_.1!$H$5,TE_discrete_.1!$J$5,TE_discrete_.1!$L$5,TE_discrete_.1!$N$5,TE_discrete_.1!$P$5,TE_discrete_.1!$R$5,TE_discrete_.1!$T$5,TE_discrete_.1!$V$5)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>3.4504219216195897E-2</c:v>
@@ -2515,7 +2910,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$B$6,TE_discrete_.1!$D$6,TE_discrete_.1!$F$6,TE_discrete_.1!$H$6,TE_discrete_.1!$J$6,TE_discrete_.1!$L$6,TE_discrete_.1!$N$6,TE_discrete_.1!$P$6,TE_discrete_.1!$R$6,TE_discrete_.1!$T$6,TE_discrete_.1!$V$6)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>7.5323534257106695E-2</c:v>
@@ -2644,7 +3039,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$B$7,TE_discrete_.1!$D$7,TE_discrete_.1!$F$7,TE_discrete_.1!$H$7,TE_discrete_.1!$J$7,TE_discrete_.1!$L$7,TE_discrete_.1!$N$7,TE_discrete_.1!$P$7,TE_discrete_.1!$R$7,TE_discrete_.1!$T$7,TE_discrete_.1!$V$7)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>4.2887737731324697E-2</c:v>
@@ -2773,7 +3168,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$B$8,TE_discrete_.1!$D$8,TE_discrete_.1!$F$8,TE_discrete_.1!$H$8,TE_discrete_.1!$J$8,TE_discrete_.1!$L$8,TE_discrete_.1!$N$8,TE_discrete_.1!$P$8,TE_discrete_.1!$R$8,TE_discrete_.1!$T$8,TE_discrete_.1!$V$8)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1.32525489191118E-2</c:v>
@@ -2902,7 +3297,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$B$9,TE_discrete_.1!$D$9,TE_discrete_.1!$F$9,TE_discrete_.1!$H$9,TE_discrete_.1!$J$9,TE_discrete_.1!$L$9,TE_discrete_.1!$N$9,TE_discrete_.1!$P$9,TE_discrete_.1!$R$9,TE_discrete_.1!$T$9,TE_discrete_.1!$V$9)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>9.7380608079661694E-3</c:v>
@@ -3031,7 +3426,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$B$10,TE_discrete_.1!$D$10,TE_discrete_.1!$F$10,TE_discrete_.1!$H$10,TE_discrete_.1!$J$10,TE_discrete_.1!$L$10,TE_discrete_.1!$N$10,TE_discrete_.1!$P$10,TE_discrete_.1!$R$10,TE_discrete_.1!$T$10,TE_discrete_.1!$V$10)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.20265050978382201</c:v>
@@ -3160,7 +3555,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$B$11,TE_discrete_.1!$D$11,TE_discrete_.1!$F$11,TE_discrete_.1!$H$11,TE_discrete_.1!$J$11,TE_discrete_.1!$L$11,TE_discrete_.1!$N$11,TE_discrete_.1!$P$11,TE_discrete_.1!$R$11,TE_discrete_.1!$T$11,TE_discrete_.1!$V$11)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.47732972122055201</c:v>
@@ -3561,7 +3956,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$C$2,TE_discrete_.1!$E$2,TE_discrete_.1!$G$2,TE_discrete_.1!$I$2,TE_discrete_.1!$K$2,TE_discrete_.1!$M$2,TE_discrete_.1!$O$2,TE_discrete_.1!$Q$2,TE_discrete_.1!$S$2,TE_discrete_.1!$U$2,TE_discrete_.1!$W$2)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.25705185700426397</c:v>
@@ -3690,7 +4085,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$C$3,TE_discrete_.1!$E$3,TE_discrete_.1!$G$3,TE_discrete_.1!$I$3,TE_discrete_.1!$K$3,TE_discrete_.1!$M$3,TE_discrete_.1!$O$3,TE_discrete_.1!$Q$3,TE_discrete_.1!$S$3,TE_discrete_.1!$U$3,TE_discrete_.1!$W$3)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>4.1038970547857399E-2</c:v>
@@ -3819,7 +4214,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$C$4,TE_discrete_.1!$E$4,TE_discrete_.1!$G$4,TE_discrete_.1!$I$4,TE_discrete_.1!$K$4,TE_discrete_.1!$M$4,TE_discrete_.1!$O$4,TE_discrete_.1!$Q$4,TE_discrete_.1!$S$4,TE_discrete_.1!$U$4,TE_discrete_.1!$W$4)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1.5925024253628801E-2</c:v>
@@ -3948,7 +4343,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$C$5,TE_discrete_.1!$E$5,TE_discrete_.1!$G$5,TE_discrete_.1!$I$5,TE_discrete_.1!$K$5,TE_discrete_.1!$M$5,TE_discrete_.1!$O$5,TE_discrete_.1!$Q$5,TE_discrete_.1!$S$5,TE_discrete_.1!$U$5,TE_discrete_.1!$W$5)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>4.4242280024162098E-2</c:v>
@@ -4077,7 +4472,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$C$6,TE_discrete_.1!$E$6,TE_discrete_.1!$G$6,TE_discrete_.1!$I$6,TE_discrete_.1!$K$6,TE_discrete_.1!$M$6,TE_discrete_.1!$O$6,TE_discrete_.1!$Q$6,TE_discrete_.1!$S$6,TE_discrete_.1!$U$6,TE_discrete_.1!$W$6)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.20678735516464999</c:v>
@@ -4206,7 +4601,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$C$7,TE_discrete_.1!$E$7,TE_discrete_.1!$G$7,TE_discrete_.1!$I$7,TE_discrete_.1!$K$7,TE_discrete_.1!$M$7,TE_discrete_.1!$O$7,TE_discrete_.1!$Q$7,TE_discrete_.1!$S$7,TE_discrete_.1!$U$7,TE_discrete_.1!$W$7)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.38410426314729701</c:v>
@@ -4335,7 +4730,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$C$8,TE_discrete_.1!$E$8,TE_discrete_.1!$G$8,TE_discrete_.1!$I$8,TE_discrete_.1!$K$8,TE_discrete_.1!$M$8,TE_discrete_.1!$O$8,TE_discrete_.1!$Q$8,TE_discrete_.1!$S$8,TE_discrete_.1!$U$8,TE_discrete_.1!$W$8)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>4.2869433105745799E-2</c:v>
@@ -4367,7 +4762,7 @@
                 <c:pt idx="9">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="10" formatCode="0.00E+00">
+                <c:pt idx="10">
                   <c:v>4.1167510600633898E-5</c:v>
                 </c:pt>
               </c:numCache>
@@ -4464,7 +4859,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$C$9,TE_discrete_.1!$E$9,TE_discrete_.1!$G$9,TE_discrete_.1!$I$9,TE_discrete_.1!$K$9,TE_discrete_.1!$M$9,TE_discrete_.1!$O$9,TE_discrete_.1!$Q$9,TE_discrete_.1!$S$9,TE_discrete_.1!$U$9,TE_discrete_.1!$W$9)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -4593,7 +4988,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$C$10,TE_discrete_.1!$E$10,TE_discrete_.1!$G$10,TE_discrete_.1!$I$10,TE_discrete_.1!$K$10,TE_discrete_.1!$M$10,TE_discrete_.1!$O$10,TE_discrete_.1!$Q$10,TE_discrete_.1!$S$10,TE_discrete_.1!$U$10,TE_discrete_.1!$W$10)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -4722,7 +5117,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$C$11,TE_discrete_.1!$E$11,TE_discrete_.1!$G$11,TE_discrete_.1!$I$11,TE_discrete_.1!$K$11,TE_discrete_.1!$M$11,TE_discrete_.1!$O$11,TE_discrete_.1!$Q$11,TE_discrete_.1!$S$11,TE_discrete_.1!$U$11,TE_discrete_.1!$W$11)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -4767,7 +5162,6 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -5850,7 +6244,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-GB"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -6788,7 +7182,7 @@
               </c:extLst>
               <c:f>(TE_discrete_twobins_max.6!$B$2,TE_discrete_twobins_max.6!$D$2,TE_discrete_twobins_max.6!$F$2,TE_discrete_twobins_max.6!$H$2,TE_discrete_twobins_max.6!$J$2,TE_discrete_twobins_max.6!$L$2,TE_discrete_twobins_max.6!$N$2,TE_discrete_twobins_max.6!$P$2,TE_discrete_twobins_max.6!$R$2,TE_discrete_twobins_max.6!$T$2,TE_discrete_twobins_max.6!$V$2,TE_discrete_twobins_max.6!$X$2,TE_discrete_twobins_max.6!$Z$2,TE_discrete_twobins_max.6!$AB$2,TE_discrete_twobins_max.6!$AD$2,TE_discrete_twobins_max.6!$AF$2,TE_discrete_twobins_max.6!$AH$2,TE_discrete_twobins_max.6!$AJ$2,TE_discrete_twobins_max.6!$AL$2,TE_discrete_twobins_max.6!$AN$2)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0.47961134477407102</c:v>
@@ -6969,7 +7363,7 @@
               </c:extLst>
               <c:f>(TE_discrete_twobins_max.6!$B$3,TE_discrete_twobins_max.6!$D$3,TE_discrete_twobins_max.6!$F$3,TE_discrete_twobins_max.6!$H$3,TE_discrete_twobins_max.6!$J$3,TE_discrete_twobins_max.6!$L$3,TE_discrete_twobins_max.6!$N$3,TE_discrete_twobins_max.6!$P$3,TE_discrete_twobins_max.6!$R$3,TE_discrete_twobins_max.6!$T$3,TE_discrete_twobins_max.6!$V$3,TE_discrete_twobins_max.6!$X$3,TE_discrete_twobins_max.6!$Z$3,TE_discrete_twobins_max.6!$AB$3,TE_discrete_twobins_max.6!$AD$3,TE_discrete_twobins_max.6!$AF$3,TE_discrete_twobins_max.6!$AH$3,TE_discrete_twobins_max.6!$AJ$3,TE_discrete_twobins_max.6!$AL$3,TE_discrete_twobins_max.6!$AN$3)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0.14992915139110599</c:v>
@@ -7150,7 +7544,7 @@
               </c:extLst>
               <c:f>(TE_discrete_twobins_max.6!$B$4,TE_discrete_twobins_max.6!$D$4,TE_discrete_twobins_max.6!$F$4,TE_discrete_twobins_max.6!$H$4,TE_discrete_twobins_max.6!$J$4,TE_discrete_twobins_max.6!$L$4,TE_discrete_twobins_max.6!$N$4,TE_discrete_twobins_max.6!$P$4,TE_discrete_twobins_max.6!$R$4,TE_discrete_twobins_max.6!$T$4,TE_discrete_twobins_max.6!$V$4,TE_discrete_twobins_max.6!$X$4,TE_discrete_twobins_max.6!$Z$4,TE_discrete_twobins_max.6!$AB$4,TE_discrete_twobins_max.6!$AD$4,TE_discrete_twobins_max.6!$AF$4,TE_discrete_twobins_max.6!$AH$4,TE_discrete_twobins_max.6!$AJ$4,TE_discrete_twobins_max.6!$AL$4,TE_discrete_twobins_max.6!$AN$4)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0.37045950383482101</c:v>
@@ -7603,7 +7997,7 @@
               </c:extLst>
               <c:f>(TE_discrete_twobins_max.6!$C$2,TE_discrete_twobins_max.6!$E$2,TE_discrete_twobins_max.6!$G$2,TE_discrete_twobins_max.6!$I$2,TE_discrete_twobins_max.6!$K$2,TE_discrete_twobins_max.6!$M$2,TE_discrete_twobins_max.6!$O$2,TE_discrete_twobins_max.6!$Q$2,TE_discrete_twobins_max.6!$S$2,TE_discrete_twobins_max.6!$U$2,TE_discrete_twobins_max.6!$W$2,TE_discrete_twobins_max.6!$Y$2,TE_discrete_twobins_max.6!$AA$2,TE_discrete_twobins_max.6!$AC$2,TE_discrete_twobins_max.6!$AE$2,TE_discrete_twobins_max.6!$AG$2,TE_discrete_twobins_max.6!$AI$2,TE_discrete_twobins_max.6!$AK$2,TE_discrete_twobins_max.6!$AM$2,TE_discrete_twobins_max.6!$AO$2)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0.241717460246058</c:v>
@@ -7784,7 +8178,7 @@
               </c:extLst>
               <c:f>(TE_discrete_twobins_max.6!$C$3,TE_discrete_twobins_max.6!$E$3,TE_discrete_twobins_max.6!$G$3,TE_discrete_twobins_max.6!$I$3,TE_discrete_twobins_max.6!$K$3,TE_discrete_twobins_max.6!$M$3,TE_discrete_twobins_max.6!$O$3,TE_discrete_twobins_max.6!$Q$3,TE_discrete_twobins_max.6!$S$3,TE_discrete_twobins_max.6!$U$3,TE_discrete_twobins_max.6!$W$3,TE_discrete_twobins_max.6!$Y$3,TE_discrete_twobins_max.6!$AA$3,TE_discrete_twobins_max.6!$AC$3,TE_discrete_twobins_max.6!$AE$3,TE_discrete_twobins_max.6!$AG$3,TE_discrete_twobins_max.6!$AI$3,TE_discrete_twobins_max.6!$AK$3,TE_discrete_twobins_max.6!$AM$3,TE_discrete_twobins_max.6!$AO$3)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0.24365173972695101</c:v>
@@ -7965,7 +8359,7 @@
               </c:extLst>
               <c:f>(TE_discrete_twobins_max.6!$C$4,TE_discrete_twobins_max.6!$E$4,TE_discrete_twobins_max.6!$G$4,TE_discrete_twobins_max.6!$I$4,TE_discrete_twobins_max.6!$K$4,TE_discrete_twobins_max.6!$M$4,TE_discrete_twobins_max.6!$O$4,TE_discrete_twobins_max.6!$Q$4,TE_discrete_twobins_max.6!$S$4,TE_discrete_twobins_max.6!$U$4,TE_discrete_twobins_max.6!$W$4,TE_discrete_twobins_max.6!$Y$4,TE_discrete_twobins_max.6!$AA$4,TE_discrete_twobins_max.6!$AC$4,TE_discrete_twobins_max.6!$AE$4,TE_discrete_twobins_max.6!$AG$4,TE_discrete_twobins_max.6!$AI$4,TE_discrete_twobins_max.6!$AK$4,TE_discrete_twobins_max.6!$AM$4,TE_discrete_twobins_max.6!$AO$4)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0.41566766379523601</c:v>
@@ -9126,7 +9520,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-GB"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -10909,7 +11303,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-GB"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -11623,7 +12017,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-GB"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -12337,7 +12731,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-GB"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -13822,7 +14216,7 @@
             <c:numRef>
               <c:f>TE_discrete_.1!$B$2:$AY$2</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>1.6895169409309699E-2</c:v>
@@ -14171,7 +14565,7 @@
             <c:numRef>
               <c:f>TE_discrete_.1!$B$3:$AY$3</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>4.42239753985832E-2</c:v>
@@ -14520,7 +14914,7 @@
             <c:numRef>
               <c:f>TE_discrete_.1!$B$4:$AY$4</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>8.3194523256026803E-2</c:v>
@@ -14869,7 +15263,7 @@
             <c:numRef>
               <c:f>TE_discrete_.1!$B$5:$AY$5</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>3.4504219216195897E-2</c:v>
@@ -15218,7 +15612,7 @@
             <c:numRef>
               <c:f>TE_discrete_.1!$B$6:$AY$6</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>7.5323534257106695E-2</c:v>
@@ -15567,7 +15961,7 @@
             <c:numRef>
               <c:f>TE_discrete_.1!$B$7:$AY$7</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>4.2887737731324697E-2</c:v>
@@ -15916,7 +16310,7 @@
             <c:numRef>
               <c:f>TE_discrete_.1!$B$8:$AY$8</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>1.32525489191118E-2</c:v>
@@ -15981,13 +16375,13 @@
                 <c:pt idx="20">
                   <c:v>3.60009880202544E-2</c:v>
                 </c:pt>
-                <c:pt idx="21" formatCode="0.00E+00">
+                <c:pt idx="21">
                   <c:v>4.1167510600633898E-5</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>3.3212877299785497E-2</c:v>
                 </c:pt>
-                <c:pt idx="23" formatCode="0.00E+00">
+                <c:pt idx="23">
                   <c:v>1.49945269976458E-5</c:v>
                 </c:pt>
                 <c:pt idx="24">
@@ -16059,7 +16453,7 @@
                 <c:pt idx="46">
                   <c:v>0.155851188649614</c:v>
                 </c:pt>
-                <c:pt idx="47" formatCode="0.00E+00">
+                <c:pt idx="47">
                   <c:v>3.6101734688351699E-5</c:v>
                 </c:pt>
                 <c:pt idx="48">
@@ -16265,7 +16659,7 @@
             <c:numRef>
               <c:f>TE_discrete_.1!$B$9:$AY$9</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>9.7380608079661694E-3</c:v>
@@ -16614,7 +17008,7 @@
             <c:numRef>
               <c:f>TE_discrete_.1!$B$10:$AY$10</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>0.20265050978382201</c:v>
@@ -16963,7 +17357,7 @@
             <c:numRef>
               <c:f>TE_discrete_.1!$B$11:$AY$11</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>0.47732972122055201</c:v>
@@ -17490,7 +17884,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$X$2,TE_discrete_.1!$Z$2,TE_discrete_.1!$AB$2,TE_discrete_.1!$AD$2,TE_discrete_.1!$AF$2,TE_discrete_.1!$AH$2,TE_discrete_.1!$AJ$2,TE_discrete_.1!$AL$2,TE_discrete_.1!$AN$2,TE_discrete_.1!$AP$2,TE_discrete_.1!$AR$2,TE_discrete_.1!$AT$2,TE_discrete_.1!$AV$2,TE_discrete_.1!$AX$2)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0.42062647133796099</c:v>
@@ -17637,7 +18031,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$X$3,TE_discrete_.1!$Z$3,TE_discrete_.1!$AB$3,TE_discrete_.1!$AD$3,TE_discrete_.1!$AF$3,TE_discrete_.1!$AH$3,TE_discrete_.1!$AJ$3,TE_discrete_.1!$AL$3,TE_discrete_.1!$AN$3,TE_discrete_.1!$AP$3,TE_discrete_.1!$AR$3,TE_discrete_.1!$AT$3,TE_discrete_.1!$AV$3,TE_discrete_.1!$AX$3)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>3.2388178314915E-3</c:v>
@@ -17784,7 +18178,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$X$4,TE_discrete_.1!$Z$4,TE_discrete_.1!$AB$4,TE_discrete_.1!$AD$4,TE_discrete_.1!$AF$4,TE_discrete_.1!$AH$4,TE_discrete_.1!$AJ$4,TE_discrete_.1!$AL$4,TE_discrete_.1!$AN$4,TE_discrete_.1!$AP$4,TE_discrete_.1!$AR$4,TE_discrete_.1!$AT$4,TE_discrete_.1!$AV$4,TE_discrete_.1!$AX$4)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>2.0092666176845398E-3</c:v>
@@ -17931,7 +18325,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$X$5,TE_discrete_.1!$Z$5,TE_discrete_.1!$AB$5,TE_discrete_.1!$AD$5,TE_discrete_.1!$AF$5,TE_discrete_.1!$AH$5,TE_discrete_.1!$AJ$5,TE_discrete_.1!$AL$5,TE_discrete_.1!$AN$5,TE_discrete_.1!$AP$5,TE_discrete_.1!$AR$5,TE_discrete_.1!$AT$5,TE_discrete_.1!$AV$5,TE_discrete_.1!$AX$5)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>2.1442173606633498E-3</c:v>
@@ -18078,7 +18472,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$X$6,TE_discrete_.1!$Z$6,TE_discrete_.1!$AB$6,TE_discrete_.1!$AD$6,TE_discrete_.1!$AF$6,TE_discrete_.1!$AH$6,TE_discrete_.1!$AJ$6,TE_discrete_.1!$AL$6,TE_discrete_.1!$AN$6,TE_discrete_.1!$AP$6,TE_discrete_.1!$AR$6,TE_discrete_.1!$AT$6,TE_discrete_.1!$AV$6,TE_discrete_.1!$AX$6)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0.105396530266452</c:v>
@@ -18225,7 +18619,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$X$7,TE_discrete_.1!$Z$7,TE_discrete_.1!$AB$7,TE_discrete_.1!$AD$7,TE_discrete_.1!$AF$7,TE_discrete_.1!$AH$7,TE_discrete_.1!$AJ$7,TE_discrete_.1!$AL$7,TE_discrete_.1!$AN$7,TE_discrete_.1!$AP$7,TE_discrete_.1!$AR$7,TE_discrete_.1!$AT$7,TE_discrete_.1!$AV$7,TE_discrete_.1!$AX$7)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>1.3105216595942401E-2</c:v>
@@ -18372,7 +18766,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$X$8,TE_discrete_.1!$Z$8,TE_discrete_.1!$AB$8,TE_discrete_.1!$AD$8,TE_discrete_.1!$AF$8,TE_discrete_.1!$AH$8,TE_discrete_.1!$AJ$8,TE_discrete_.1!$AL$8,TE_discrete_.1!$AN$8,TE_discrete_.1!$AP$8,TE_discrete_.1!$AR$8,TE_discrete_.1!$AT$8,TE_discrete_.1!$AV$8,TE_discrete_.1!$AX$8)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>3.3212877299785497E-2</c:v>
@@ -18519,7 +18913,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$X$9,TE_discrete_.1!$Z$9,TE_discrete_.1!$AB$9,TE_discrete_.1!$AD$9,TE_discrete_.1!$AF$9,TE_discrete_.1!$AH$9,TE_discrete_.1!$AJ$9,TE_discrete_.1!$AL$9,TE_discrete_.1!$AN$9,TE_discrete_.1!$AP$9,TE_discrete_.1!$AR$9,TE_discrete_.1!$AT$9,TE_discrete_.1!$AV$9,TE_discrete_.1!$AX$9)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>1.6044143887481001E-3</c:v>
@@ -18666,7 +19060,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$X$10,TE_discrete_.1!$Z$10,TE_discrete_.1!$AB$10,TE_discrete_.1!$AD$10,TE_discrete_.1!$AF$10,TE_discrete_.1!$AH$10,TE_discrete_.1!$AJ$10,TE_discrete_.1!$AL$10,TE_discrete_.1!$AN$10,TE_discrete_.1!$AP$10,TE_discrete_.1!$AR$10,TE_discrete_.1!$AT$10,TE_discrete_.1!$AV$10,TE_discrete_.1!$AX$10)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>1.9972709960864199E-2</c:v>
@@ -18813,7 +19207,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$X$11,TE_discrete_.1!$Z$11,TE_discrete_.1!$AB$11,TE_discrete_.1!$AD$11,TE_discrete_.1!$AF$11,TE_discrete_.1!$AH$11,TE_discrete_.1!$AJ$11,TE_discrete_.1!$AL$11,TE_discrete_.1!$AN$11,TE_discrete_.1!$AP$11,TE_discrete_.1!$AR$11,TE_discrete_.1!$AT$11,TE_discrete_.1!$AV$11,TE_discrete_.1!$AX$11)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0.391102247679596</c:v>
@@ -19239,7 +19633,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$Y$2,TE_discrete_.1!$AA$2,TE_discrete_.1!$AC$2,TE_discrete_.1!$AE$2,TE_discrete_.1!$AG$2,TE_discrete_.1!$AI$2,TE_discrete_.1!$AK$2,TE_discrete_.1!$AM$2,TE_discrete_.1!$AO$2,TE_discrete_.1!$AQ$2,TE_discrete_.1!$AS$2,TE_discrete_.1!$AU$2,TE_discrete_.1!$AW$2,TE_discrete_.1!$AY$2)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0.432052300910167</c:v>
@@ -19386,7 +19780,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$Y$3,TE_discrete_.1!$AA$3,TE_discrete_.1!$AC$3,TE_discrete_.1!$AE$3,TE_discrete_.1!$AG$3,TE_discrete_.1!$AI$3,TE_discrete_.1!$AK$3,TE_discrete_.1!$AM$3,TE_discrete_.1!$AO$3,TE_discrete_.1!$AQ$3,TE_discrete_.1!$AS$3,TE_discrete_.1!$AU$3,TE_discrete_.1!$AW$3,TE_discrete_.1!$AY$3)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>8.8017873476181202E-3</c:v>
@@ -19533,7 +19927,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$Y$4,TE_discrete_.1!$AA$4,TE_discrete_.1!$AC$4,TE_discrete_.1!$AE$4,TE_discrete_.1!$AG$4,TE_discrete_.1!$AI$4,TE_discrete_.1!$AK$4,TE_discrete_.1!$AM$4,TE_discrete_.1!$AO$4,TE_discrete_.1!$AQ$4,TE_discrete_.1!$AS$4,TE_discrete_.1!$AU$4,TE_discrete_.1!$AW$4,TE_discrete_.1!$AY$4)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>1.3570046932869499E-2</c:v>
@@ -19680,7 +20074,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$Y$5,TE_discrete_.1!$AA$5,TE_discrete_.1!$AC$5,TE_discrete_.1!$AE$5,TE_discrete_.1!$AG$5,TE_discrete_.1!$AI$5,TE_discrete_.1!$AK$5,TE_discrete_.1!$AM$5,TE_discrete_.1!$AO$5,TE_discrete_.1!$AQ$5,TE_discrete_.1!$AS$5,TE_discrete_.1!$AU$5,TE_discrete_.1!$AW$5,TE_discrete_.1!$AY$5)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0.120106161251143</c:v>
@@ -19827,7 +20221,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$Y$6,TE_discrete_.1!$AA$6,TE_discrete_.1!$AC$6,TE_discrete_.1!$AE$6,TE_discrete_.1!$AG$6,TE_discrete_.1!$AI$6,TE_discrete_.1!$AK$6,TE_discrete_.1!$AM$6,TE_discrete_.1!$AO$6,TE_discrete_.1!$AQ$6,TE_discrete_.1!$AS$6,TE_discrete_.1!$AU$6,TE_discrete_.1!$AW$6,TE_discrete_.1!$AY$6)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0.19791276184192699</c:v>
@@ -19974,7 +20368,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$Y$7,TE_discrete_.1!$AA$7,TE_discrete_.1!$AC$7,TE_discrete_.1!$AE$7,TE_discrete_.1!$AG$7,TE_discrete_.1!$AI$7,TE_discrete_.1!$AK$7,TE_discrete_.1!$AM$7,TE_discrete_.1!$AO$7,TE_discrete_.1!$AQ$7,TE_discrete_.1!$AS$7,TE_discrete_.1!$AU$7,TE_discrete_.1!$AW$7,TE_discrete_.1!$AY$7)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0.21268237093460801</c:v>
@@ -20121,9 +20515,9 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$Y$8,TE_discrete_.1!$AA$8,TE_discrete_.1!$AC$8,TE_discrete_.1!$AE$8,TE_discrete_.1!$AG$8,TE_discrete_.1!$AI$8,TE_discrete_.1!$AK$8,TE_discrete_.1!$AM$8,TE_discrete_.1!$AO$8,TE_discrete_.1!$AQ$8,TE_discrete_.1!$AS$8,TE_discrete_.1!$AU$8,TE_discrete_.1!$AW$8,TE_discrete_.1!$AY$8)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="14"/>
-                <c:pt idx="0" formatCode="0.00E+00">
+                <c:pt idx="0">
                   <c:v>1.49945269976458E-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
@@ -20159,7 +20553,7 @@
                 <c:pt idx="11">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="12" formatCode="0.00E+00">
+                <c:pt idx="12">
                   <c:v>3.6101734688351699E-5</c:v>
                 </c:pt>
                 <c:pt idx="13">
@@ -20268,7 +20662,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$Y$9,TE_discrete_.1!$AA$9,TE_discrete_.1!$AC$9,TE_discrete_.1!$AE$9,TE_discrete_.1!$AG$9,TE_discrete_.1!$AI$9,TE_discrete_.1!$AK$9,TE_discrete_.1!$AM$9,TE_discrete_.1!$AO$9,TE_discrete_.1!$AQ$9,TE_discrete_.1!$AS$9,TE_discrete_.1!$AU$9,TE_discrete_.1!$AW$9,TE_discrete_.1!$AY$9)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -20415,7 +20809,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$Y$10,TE_discrete_.1!$AA$10,TE_discrete_.1!$AC$10,TE_discrete_.1!$AE$10,TE_discrete_.1!$AG$10,TE_discrete_.1!$AI$10,TE_discrete_.1!$AK$10,TE_discrete_.1!$AM$10,TE_discrete_.1!$AO$10,TE_discrete_.1!$AQ$10,TE_discrete_.1!$AS$10,TE_discrete_.1!$AU$10,TE_discrete_.1!$AW$10,TE_discrete_.1!$AY$10)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -20562,7 +20956,7 @@
               </c:extLst>
               <c:f>(TE_discrete_.1!$Y$11,TE_discrete_.1!$AA$11,TE_discrete_.1!$AC$11,TE_discrete_.1!$AE$11,TE_discrete_.1!$AG$11,TE_discrete_.1!$AI$11,TE_discrete_.1!$AK$11,TE_discrete_.1!$AM$11,TE_discrete_.1!$AO$11,TE_discrete_.1!$AQ$11,TE_discrete_.1!$AS$11,TE_discrete_.1!$AU$11,TE_discrete_.1!$AW$11,TE_discrete_.1!$AY$11)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -30635,56 +31029,56 @@
   </sortState>
   <tableColumns count="51">
     <tableColumn id="1" xr3:uid="{EF2B43FC-B148-4958-955A-24F59D9692B2}" name="task_eng"/>
-    <tableColumn id="2" xr3:uid="{694207B6-7A81-43F2-8007-3C143D280EED}" name="dyad_01_anno01"/>
-    <tableColumn id="3" xr3:uid="{8BDD326B-0907-40B8-A57E-D3A0177791D4}" name="dyad_01_anno02"/>
-    <tableColumn id="4" xr3:uid="{0420D886-2B6A-4C76-8119-C958D597AC1A}" name="dyad_02_anno01"/>
-    <tableColumn id="5" xr3:uid="{92774599-4874-4916-AB0F-CDCE3A4DC526}" name="dyad_02_anno02"/>
-    <tableColumn id="6" xr3:uid="{F9E0B214-E207-4F34-928A-C8D2A89413E0}" name="dyad_03_anno01"/>
-    <tableColumn id="7" xr3:uid="{A646026B-1607-4600-9427-E83AC0D32C9F}" name="dyad_03_anno02"/>
-    <tableColumn id="8" xr3:uid="{02AB03F6-AEEE-444F-8D6D-A60D19545F6B}" name="dyad_04_anno01"/>
-    <tableColumn id="9" xr3:uid="{E1E2364F-956D-4F56-9B22-E8C7F7EF5DB3}" name="dyad_04_anno02"/>
-    <tableColumn id="10" xr3:uid="{50205926-20D3-48DD-BEB5-13DEF9C95B98}" name="dyad_05_anno01"/>
-    <tableColumn id="11" xr3:uid="{0ED7D445-5A27-49F0-A5E6-4004ECA3C0A9}" name="dyad_05_anno02"/>
-    <tableColumn id="12" xr3:uid="{AE486511-3F17-440C-B6CE-A80EC4C20829}" name="dyad_06_anno01"/>
-    <tableColumn id="13" xr3:uid="{C0F39663-FC66-48EB-ACCA-6775F5ADB4D2}" name="dyad_06_anno02"/>
-    <tableColumn id="14" xr3:uid="{5365758D-3C1B-43DC-817D-02E8207FB8A4}" name="dyad_07_anno01"/>
-    <tableColumn id="15" xr3:uid="{3757116E-941A-43B2-B31D-8F93A6E8B56E}" name="dyad_07_anno02"/>
-    <tableColumn id="16" xr3:uid="{4330825D-6B47-4A96-AF10-5FD95E71B38E}" name="dyad_08_anno01"/>
-    <tableColumn id="17" xr3:uid="{4BA99E1A-C006-4CDE-B2C7-F75DCFE641AE}" name="dyad_08_anno02"/>
-    <tableColumn id="18" xr3:uid="{D1D20B6C-9C53-4C26-8208-298E268384F0}" name="dyad_09_anno01"/>
-    <tableColumn id="19" xr3:uid="{5785DD33-91D4-4AEB-A086-5AE6E93C0F75}" name="dyad_09_anno02"/>
-    <tableColumn id="20" xr3:uid="{82A226A6-A269-4C64-975F-1DC21505DC91}" name="dyad_10_anno01"/>
-    <tableColumn id="21" xr3:uid="{4A51699C-53A9-4D3F-9377-C57908025B96}" name="dyad_10_anno02"/>
-    <tableColumn id="22" xr3:uid="{FA148BDD-7272-4506-9446-40376816CA4C}" name="dyad_11_anno01"/>
-    <tableColumn id="23" xr3:uid="{D8F2BE4E-CFCB-4953-9376-2151A6D65E65}" name="dyad_11_anno02"/>
-    <tableColumn id="24" xr3:uid="{21C3C291-E066-4EA4-A7B4-9C6BBF9F9196}" name="triad_01_anno01"/>
-    <tableColumn id="25" xr3:uid="{4CABA6DF-B07E-415A-9E0A-0188F3A1DF1C}" name="triad_01_anno02"/>
-    <tableColumn id="26" xr3:uid="{09C6FD30-D2FB-40F5-8B8E-6AF2538F6FF1}" name="triad_02_anno01"/>
-    <tableColumn id="27" xr3:uid="{7004A2E6-C97D-4298-A547-27464143EDB1}" name="triad_02_anno02"/>
-    <tableColumn id="28" xr3:uid="{12ACF033-3EA8-490E-84C0-A1453B854634}" name="triad_03_anno01"/>
-    <tableColumn id="29" xr3:uid="{B6B681FD-AE39-4A5F-A828-E7051287931A}" name="triad_03_anno02"/>
-    <tableColumn id="30" xr3:uid="{5DFFB97B-A28A-4DA2-A44C-4F125CFF596D}" name="triad_04_anno01"/>
-    <tableColumn id="31" xr3:uid="{529ED5BD-CF70-4C30-B03B-5021BDF78E65}" name="triad_04_anno02"/>
-    <tableColumn id="32" xr3:uid="{B80EFFC8-23BA-4187-B09E-8EE239B57DEC}" name="triad_05_anno01"/>
-    <tableColumn id="33" xr3:uid="{ED9F50A9-72DB-41E8-9DBC-8FBD507445F2}" name="triad_05_anno02"/>
-    <tableColumn id="34" xr3:uid="{F3FE70AC-B0D5-4A23-BCB1-6A38BE2F59EE}" name="triad_06_anno01"/>
-    <tableColumn id="35" xr3:uid="{7D12026F-1104-4BF3-A73D-A45695E8562A}" name="triad_06_anno02"/>
-    <tableColumn id="36" xr3:uid="{AB052A8A-96C1-45CA-B1B1-BCCE7DF4CB2A}" name="triad_07_anno01"/>
-    <tableColumn id="37" xr3:uid="{269FEC62-F0CF-45E0-B403-FC0060E27A2A}" name="triad_07_anno02"/>
-    <tableColumn id="38" xr3:uid="{8876FF70-567B-4D33-A0EF-D83CFFEFA0FC}" name="triad_08_anno01"/>
-    <tableColumn id="39" xr3:uid="{4C10ABA6-198E-47C3-BC25-084ED264397B}" name="triad_08_anno02"/>
-    <tableColumn id="40" xr3:uid="{FBE33867-DBFC-4A34-840F-EF72E3B7356F}" name="triad_09_anno01"/>
-    <tableColumn id="41" xr3:uid="{DCB0D2BB-EF68-4AB7-B735-8812771DAF49}" name="triad_09_anno02"/>
-    <tableColumn id="42" xr3:uid="{2D32EA50-15B7-4E75-B9AC-336D8CF93192}" name="triad_10_anno01"/>
-    <tableColumn id="43" xr3:uid="{0644D05D-FB91-40D9-9EDC-28785758D874}" name="triad_10_anno02"/>
-    <tableColumn id="44" xr3:uid="{E7A39DA1-36E1-4B06-9734-1B6046E1AB67}" name="triad_11_anno01"/>
-    <tableColumn id="45" xr3:uid="{80CC9551-2C39-4075-833D-9B18ECE8E495}" name="triad_11_anno02"/>
-    <tableColumn id="46" xr3:uid="{F9594BF0-9AAA-41C4-A042-1AB3902348D4}" name="triad_12_anno01"/>
-    <tableColumn id="47" xr3:uid="{2EC7D1C7-009C-4733-81E5-01C00BEB2AFC}" name="triad_12_anno02"/>
-    <tableColumn id="48" xr3:uid="{A391761F-1A3C-4C0C-8DF5-E9D719DB9A60}" name="triad_13_anno01"/>
-    <tableColumn id="49" xr3:uid="{BE3FF671-233D-4CD6-85A1-AA9918D92649}" name="triad_13_anno02"/>
-    <tableColumn id="50" xr3:uid="{EEEF7F2A-2128-479C-BF88-A59023F28435}" name="triad_14_anno01"/>
-    <tableColumn id="51" xr3:uid="{94AC0C37-F483-41B9-ADA7-6F0B6DFA0722}" name="triad_14_anno02"/>
+    <tableColumn id="2" xr3:uid="{694207B6-7A81-43F2-8007-3C143D280EED}" name="dyad_01_anno01" dataDxfId="89"/>
+    <tableColumn id="3" xr3:uid="{8BDD326B-0907-40B8-A57E-D3A0177791D4}" name="dyad_01_anno02" dataDxfId="88"/>
+    <tableColumn id="4" xr3:uid="{0420D886-2B6A-4C76-8119-C958D597AC1A}" name="dyad_02_anno01" dataDxfId="87"/>
+    <tableColumn id="5" xr3:uid="{92774599-4874-4916-AB0F-CDCE3A4DC526}" name="dyad_02_anno02" dataDxfId="86"/>
+    <tableColumn id="6" xr3:uid="{F9E0B214-E207-4F34-928A-C8D2A89413E0}" name="dyad_03_anno01" dataDxfId="85"/>
+    <tableColumn id="7" xr3:uid="{A646026B-1607-4600-9427-E83AC0D32C9F}" name="dyad_03_anno02" dataDxfId="84"/>
+    <tableColumn id="8" xr3:uid="{02AB03F6-AEEE-444F-8D6D-A60D19545F6B}" name="dyad_04_anno01" dataDxfId="83"/>
+    <tableColumn id="9" xr3:uid="{E1E2364F-956D-4F56-9B22-E8C7F7EF5DB3}" name="dyad_04_anno02" dataDxfId="82"/>
+    <tableColumn id="10" xr3:uid="{50205926-20D3-48DD-BEB5-13DEF9C95B98}" name="dyad_05_anno01" dataDxfId="81"/>
+    <tableColumn id="11" xr3:uid="{0ED7D445-5A27-49F0-A5E6-4004ECA3C0A9}" name="dyad_05_anno02" dataDxfId="80"/>
+    <tableColumn id="12" xr3:uid="{AE486511-3F17-440C-B6CE-A80EC4C20829}" name="dyad_06_anno01" dataDxfId="79"/>
+    <tableColumn id="13" xr3:uid="{C0F39663-FC66-48EB-ACCA-6775F5ADB4D2}" name="dyad_06_anno02" dataDxfId="78"/>
+    <tableColumn id="14" xr3:uid="{5365758D-3C1B-43DC-817D-02E8207FB8A4}" name="dyad_07_anno01" dataDxfId="77"/>
+    <tableColumn id="15" xr3:uid="{3757116E-941A-43B2-B31D-8F93A6E8B56E}" name="dyad_07_anno02" dataDxfId="76"/>
+    <tableColumn id="16" xr3:uid="{4330825D-6B47-4A96-AF10-5FD95E71B38E}" name="dyad_08_anno01" dataDxfId="75"/>
+    <tableColumn id="17" xr3:uid="{4BA99E1A-C006-4CDE-B2C7-F75DCFE641AE}" name="dyad_08_anno02" dataDxfId="74"/>
+    <tableColumn id="18" xr3:uid="{D1D20B6C-9C53-4C26-8208-298E268384F0}" name="dyad_09_anno01" dataDxfId="73"/>
+    <tableColumn id="19" xr3:uid="{5785DD33-91D4-4AEB-A086-5AE6E93C0F75}" name="dyad_09_anno02" dataDxfId="72"/>
+    <tableColumn id="20" xr3:uid="{82A226A6-A269-4C64-975F-1DC21505DC91}" name="dyad_10_anno01" dataDxfId="71"/>
+    <tableColumn id="21" xr3:uid="{4A51699C-53A9-4D3F-9377-C57908025B96}" name="dyad_10_anno02" dataDxfId="70"/>
+    <tableColumn id="22" xr3:uid="{FA148BDD-7272-4506-9446-40376816CA4C}" name="dyad_11_anno01" dataDxfId="69"/>
+    <tableColumn id="23" xr3:uid="{D8F2BE4E-CFCB-4953-9376-2151A6D65E65}" name="dyad_11_anno02" dataDxfId="68"/>
+    <tableColumn id="24" xr3:uid="{21C3C291-E066-4EA4-A7B4-9C6BBF9F9196}" name="triad_01_anno01" dataDxfId="67"/>
+    <tableColumn id="25" xr3:uid="{4CABA6DF-B07E-415A-9E0A-0188F3A1DF1C}" name="triad_01_anno02" dataDxfId="66"/>
+    <tableColumn id="26" xr3:uid="{09C6FD30-D2FB-40F5-8B8E-6AF2538F6FF1}" name="triad_02_anno01" dataDxfId="65"/>
+    <tableColumn id="27" xr3:uid="{7004A2E6-C97D-4298-A547-27464143EDB1}" name="triad_02_anno02" dataDxfId="64"/>
+    <tableColumn id="28" xr3:uid="{12ACF033-3EA8-490E-84C0-A1453B854634}" name="triad_03_anno01" dataDxfId="63"/>
+    <tableColumn id="29" xr3:uid="{B6B681FD-AE39-4A5F-A828-E7051287931A}" name="triad_03_anno02" dataDxfId="62"/>
+    <tableColumn id="30" xr3:uid="{5DFFB97B-A28A-4DA2-A44C-4F125CFF596D}" name="triad_04_anno01" dataDxfId="61"/>
+    <tableColumn id="31" xr3:uid="{529ED5BD-CF70-4C30-B03B-5021BDF78E65}" name="triad_04_anno02" dataDxfId="60"/>
+    <tableColumn id="32" xr3:uid="{B80EFFC8-23BA-4187-B09E-8EE239B57DEC}" name="triad_05_anno01" dataDxfId="59"/>
+    <tableColumn id="33" xr3:uid="{ED9F50A9-72DB-41E8-9DBC-8FBD507445F2}" name="triad_05_anno02" dataDxfId="58"/>
+    <tableColumn id="34" xr3:uid="{F3FE70AC-B0D5-4A23-BCB1-6A38BE2F59EE}" name="triad_06_anno01" dataDxfId="57"/>
+    <tableColumn id="35" xr3:uid="{7D12026F-1104-4BF3-A73D-A45695E8562A}" name="triad_06_anno02" dataDxfId="56"/>
+    <tableColumn id="36" xr3:uid="{AB052A8A-96C1-45CA-B1B1-BCCE7DF4CB2A}" name="triad_07_anno01" dataDxfId="55"/>
+    <tableColumn id="37" xr3:uid="{269FEC62-F0CF-45E0-B403-FC0060E27A2A}" name="triad_07_anno02" dataDxfId="54"/>
+    <tableColumn id="38" xr3:uid="{8876FF70-567B-4D33-A0EF-D83CFFEFA0FC}" name="triad_08_anno01" dataDxfId="53"/>
+    <tableColumn id="39" xr3:uid="{4C10ABA6-198E-47C3-BC25-084ED264397B}" name="triad_08_anno02" dataDxfId="52"/>
+    <tableColumn id="40" xr3:uid="{FBE33867-DBFC-4A34-840F-EF72E3B7356F}" name="triad_09_anno01" dataDxfId="51"/>
+    <tableColumn id="41" xr3:uid="{DCB0D2BB-EF68-4AB7-B735-8812771DAF49}" name="triad_09_anno02" dataDxfId="50"/>
+    <tableColumn id="42" xr3:uid="{2D32EA50-15B7-4E75-B9AC-336D8CF93192}" name="triad_10_anno01" dataDxfId="49"/>
+    <tableColumn id="43" xr3:uid="{0644D05D-FB91-40D9-9EDC-28785758D874}" name="triad_10_anno02" dataDxfId="48"/>
+    <tableColumn id="44" xr3:uid="{E7A39DA1-36E1-4B06-9734-1B6046E1AB67}" name="triad_11_anno01" dataDxfId="47"/>
+    <tableColumn id="45" xr3:uid="{80CC9551-2C39-4075-833D-9B18ECE8E495}" name="triad_11_anno02" dataDxfId="46"/>
+    <tableColumn id="46" xr3:uid="{F9594BF0-9AAA-41C4-A042-1AB3902348D4}" name="triad_12_anno01" dataDxfId="45"/>
+    <tableColumn id="47" xr3:uid="{2EC7D1C7-009C-4733-81E5-01C00BEB2AFC}" name="triad_12_anno02" dataDxfId="44"/>
+    <tableColumn id="48" xr3:uid="{A391761F-1A3C-4C0C-8DF5-E9D719DB9A60}" name="triad_13_anno01" dataDxfId="43"/>
+    <tableColumn id="49" xr3:uid="{BE3FF671-233D-4CD6-85A1-AA9918D92649}" name="triad_13_anno02" dataDxfId="42"/>
+    <tableColumn id="50" xr3:uid="{EEEF7F2A-2128-479C-BF88-A59023F28435}" name="triad_14_anno01" dataDxfId="41"/>
+    <tableColumn id="51" xr3:uid="{94AC0C37-F483-41B9-ADA7-6F0B6DFA0722}" name="triad_14_anno02" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -30761,31 +31155,31 @@
   </sortState>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{131451C6-4E01-4C99-B010-467E568818F6}" name="task_eng"/>
-    <tableColumn id="3" xr3:uid="{713AB5D4-25E1-4D86-BDD7-92ECEAC0EB63}" name="dyad_01_anno02"/>
-    <tableColumn id="5" xr3:uid="{0D56DF71-0323-4C02-917F-B56A97888C92}" name="dyad_02_anno02"/>
-    <tableColumn id="7" xr3:uid="{4D18F6CC-5566-48F8-8C55-B217CBDB209D}" name="dyad_03_anno02"/>
-    <tableColumn id="9" xr3:uid="{2D6B45A6-ADA1-40E7-B5B9-8DB65D84E1D1}" name="dyad_04_anno02"/>
-    <tableColumn id="11" xr3:uid="{767F93B0-3ACB-4811-9147-8883125A9ED2}" name="dyad_05_anno02"/>
-    <tableColumn id="13" xr3:uid="{93A7525E-5A03-4FCD-B8BC-4DA05C2DA770}" name="dyad_06_anno02"/>
-    <tableColumn id="15" xr3:uid="{3A8AD2AA-2EB5-48E9-8787-20506FBB2859}" name="dyad_07_anno02"/>
-    <tableColumn id="17" xr3:uid="{E77814AA-F4B0-42F8-B644-14E138107107}" name="dyad_08_anno02"/>
-    <tableColumn id="19" xr3:uid="{0957C0DB-A748-4B79-B4FF-6E093648C12E}" name="dyad_09_anno02"/>
-    <tableColumn id="21" xr3:uid="{0C6E5846-52F8-470C-8732-6366292C09D9}" name="dyad_10_anno02"/>
-    <tableColumn id="23" xr3:uid="{724AD850-B6FA-4EBF-BDF5-00D0F1DCB84B}" name="dyad_11_anno02"/>
-    <tableColumn id="25" xr3:uid="{FBD42B91-2391-4E20-8C72-C1BC4FF231E4}" name="triad_01_anno02"/>
-    <tableColumn id="27" xr3:uid="{FB5D4C91-2642-42C0-B945-0623CBC77125}" name="triad_02_anno02"/>
-    <tableColumn id="29" xr3:uid="{48F5244A-15DF-4A9D-B56E-49136687A6A1}" name="triad_03_anno02"/>
-    <tableColumn id="31" xr3:uid="{94301351-5936-4BE8-8D5B-4D6809273F54}" name="triad_04_anno02"/>
-    <tableColumn id="33" xr3:uid="{FBE23FD8-6EDC-4173-8C49-4EEAD3174ECD}" name="triad_05_anno02"/>
-    <tableColumn id="35" xr3:uid="{32F91A85-5B86-42D1-B313-C3E2B74FF2B7}" name="triad_06_anno02"/>
-    <tableColumn id="37" xr3:uid="{F9552E99-5EB2-48AA-A020-77590BAF72B2}" name="triad_07_anno02"/>
-    <tableColumn id="39" xr3:uid="{E106BEBF-4DA3-46F6-8841-EC837A36C8C5}" name="triad_08_anno02"/>
-    <tableColumn id="41" xr3:uid="{B9AD36F7-E9E0-4239-9EA8-FE8D8F72D028}" name="triad_09_anno02"/>
-    <tableColumn id="43" xr3:uid="{BD0861CE-8F6A-4015-88BC-7996C61AF40F}" name="triad_10_anno02"/>
-    <tableColumn id="45" xr3:uid="{6F0FE7C1-3071-4694-A61F-A29A0FC1679E}" name="triad_11_anno02"/>
-    <tableColumn id="47" xr3:uid="{DC688FBD-1D2A-42F3-B6F6-B7A308B97712}" name="triad_12_anno02"/>
-    <tableColumn id="49" xr3:uid="{22C36728-A62B-416E-8AB1-493EA7A816DC}" name="triad_13_anno02"/>
-    <tableColumn id="51" xr3:uid="{B40C0A05-F900-4746-9B23-3C6B0F8C432E}" name="triad_14_anno02"/>
+    <tableColumn id="3" xr3:uid="{713AB5D4-25E1-4D86-BDD7-92ECEAC0EB63}" name="dyad_01_anno02" dataDxfId="114"/>
+    <tableColumn id="5" xr3:uid="{0D56DF71-0323-4C02-917F-B56A97888C92}" name="dyad_02_anno02" dataDxfId="113"/>
+    <tableColumn id="7" xr3:uid="{4D18F6CC-5566-48F8-8C55-B217CBDB209D}" name="dyad_03_anno02" dataDxfId="112"/>
+    <tableColumn id="9" xr3:uid="{2D6B45A6-ADA1-40E7-B5B9-8DB65D84E1D1}" name="dyad_04_anno02" dataDxfId="111"/>
+    <tableColumn id="11" xr3:uid="{767F93B0-3ACB-4811-9147-8883125A9ED2}" name="dyad_05_anno02" dataDxfId="110"/>
+    <tableColumn id="13" xr3:uid="{93A7525E-5A03-4FCD-B8BC-4DA05C2DA770}" name="dyad_06_anno02" dataDxfId="109"/>
+    <tableColumn id="15" xr3:uid="{3A8AD2AA-2EB5-48E9-8787-20506FBB2859}" name="dyad_07_anno02" dataDxfId="108"/>
+    <tableColumn id="17" xr3:uid="{E77814AA-F4B0-42F8-B644-14E138107107}" name="dyad_08_anno02" dataDxfId="107"/>
+    <tableColumn id="19" xr3:uid="{0957C0DB-A748-4B79-B4FF-6E093648C12E}" name="dyad_09_anno02" dataDxfId="106"/>
+    <tableColumn id="21" xr3:uid="{0C6E5846-52F8-470C-8732-6366292C09D9}" name="dyad_10_anno02" dataDxfId="105"/>
+    <tableColumn id="23" xr3:uid="{724AD850-B6FA-4EBF-BDF5-00D0F1DCB84B}" name="dyad_11_anno02" dataDxfId="104"/>
+    <tableColumn id="25" xr3:uid="{FBD42B91-2391-4E20-8C72-C1BC4FF231E4}" name="triad_01_anno02" dataDxfId="103"/>
+    <tableColumn id="27" xr3:uid="{FB5D4C91-2642-42C0-B945-0623CBC77125}" name="triad_02_anno02" dataDxfId="102"/>
+    <tableColumn id="29" xr3:uid="{48F5244A-15DF-4A9D-B56E-49136687A6A1}" name="triad_03_anno02" dataDxfId="101"/>
+    <tableColumn id="31" xr3:uid="{94301351-5936-4BE8-8D5B-4D6809273F54}" name="triad_04_anno02" dataDxfId="100"/>
+    <tableColumn id="33" xr3:uid="{FBE23FD8-6EDC-4173-8C49-4EEAD3174ECD}" name="triad_05_anno02" dataDxfId="99"/>
+    <tableColumn id="35" xr3:uid="{32F91A85-5B86-42D1-B313-C3E2B74FF2B7}" name="triad_06_anno02" dataDxfId="98"/>
+    <tableColumn id="37" xr3:uid="{F9552E99-5EB2-48AA-A020-77590BAF72B2}" name="triad_07_anno02" dataDxfId="97"/>
+    <tableColumn id="39" xr3:uid="{E106BEBF-4DA3-46F6-8841-EC837A36C8C5}" name="triad_08_anno02" dataDxfId="96"/>
+    <tableColumn id="41" xr3:uid="{B9AD36F7-E9E0-4239-9EA8-FE8D8F72D028}" name="triad_09_anno02" dataDxfId="95"/>
+    <tableColumn id="43" xr3:uid="{BD0861CE-8F6A-4015-88BC-7996C61AF40F}" name="triad_10_anno02" dataDxfId="94"/>
+    <tableColumn id="45" xr3:uid="{6F0FE7C1-3071-4694-A61F-A29A0FC1679E}" name="triad_11_anno02" dataDxfId="93"/>
+    <tableColumn id="47" xr3:uid="{DC688FBD-1D2A-42F3-B6F6-B7A308B97712}" name="triad_12_anno02" dataDxfId="92"/>
+    <tableColumn id="49" xr3:uid="{22C36728-A62B-416E-8AB1-493EA7A816DC}" name="triad_13_anno02" dataDxfId="91"/>
+    <tableColumn id="51" xr3:uid="{B40C0A05-F900-4746-9B23-3C6B0F8C432E}" name="triad_14_anno02" dataDxfId="90"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -30856,46 +31250,46 @@
   <autoFilter ref="A1:AO4" xr:uid="{43D77003-72FC-41C3-87BD-A5FBB1AABC59}"/>
   <tableColumns count="41">
     <tableColumn id="1" xr3:uid="{FC2DAC51-5BF4-45C9-8CBB-5F2E023FFCCF}" name="task_eng"/>
-    <tableColumn id="2" xr3:uid="{7F24C492-7D02-4601-866A-78BAEB88EB0E}" name="dyad_02_anno01"/>
-    <tableColumn id="3" xr3:uid="{C1891BFD-F445-460C-9E6A-6D77E0E4C621}" name="dyad_02_anno02"/>
-    <tableColumn id="4" xr3:uid="{EDC2C213-DE1A-40C2-B091-BDD51AE57624}" name="dyad_03_anno01"/>
-    <tableColumn id="5" xr3:uid="{F373B450-4B43-449F-A850-52564AD7EB64}" name="dyad_03_anno02"/>
-    <tableColumn id="6" xr3:uid="{92320449-409B-41E0-BE88-3DFE1A3A7F0F}" name="dyad_04_anno01"/>
-    <tableColumn id="7" xr3:uid="{0D6495A1-B397-4940-8D68-188FB75C6AF8}" name="dyad_04_anno02"/>
-    <tableColumn id="8" xr3:uid="{0A02E8D0-B5F5-4E42-8942-CD64D5D77461}" name="dyad_05_anno01"/>
-    <tableColumn id="9" xr3:uid="{9DBF7BE4-D471-4C34-AF7C-BD0A43B75492}" name="dyad_05_anno02"/>
-    <tableColumn id="10" xr3:uid="{3463D826-CF64-4217-BB9E-474C0F41DF2C}" name="dyad_06_anno01"/>
-    <tableColumn id="11" xr3:uid="{AC74516E-9C45-4B4B-9C48-BDE98BF69A0B}" name="dyad_06_anno02"/>
-    <tableColumn id="12" xr3:uid="{B1CF669A-71F9-4878-8832-2975ABA8BA76}" name="dyad_07_anno01"/>
-    <tableColumn id="13" xr3:uid="{618BB242-32B5-43AC-9937-6A903077CD34}" name="dyad_07_anno02"/>
-    <tableColumn id="14" xr3:uid="{E62BFD50-9ED3-4CD1-86DE-65BDFDD2DBED}" name="dyad_10_anno01"/>
-    <tableColumn id="15" xr3:uid="{A4611B9E-2E0B-45A2-98E3-1F158F067633}" name="dyad_10_anno02"/>
-    <tableColumn id="16" xr3:uid="{6A2927A9-E70A-4AA6-BD10-C29A082888AF}" name="dyad_11_anno01"/>
-    <tableColumn id="17" xr3:uid="{353C28AD-ACED-435C-BC6C-A24CC84009E3}" name="dyad_11_anno02"/>
-    <tableColumn id="18" xr3:uid="{B4F86DAA-4D88-49A7-BD94-8D6224A70E3E}" name="triad_01_anno01"/>
-    <tableColumn id="19" xr3:uid="{05B5A658-1CD0-43A7-8107-11477F3A077A}" name="triad_01_anno02"/>
-    <tableColumn id="20" xr3:uid="{D047B543-DCBC-43C6-A17F-4D02A6B6E615}" name="triad_02_anno01"/>
-    <tableColumn id="21" xr3:uid="{3D3513BC-134D-4E60-BC75-65899C48716C}" name="triad_02_anno02"/>
-    <tableColumn id="22" xr3:uid="{276B2177-F32B-4BA6-87B3-EF61C38C6190}" name="triad_05_anno01"/>
-    <tableColumn id="23" xr3:uid="{FB430E1F-00B4-439E-8EE2-B837CA136DE1}" name="triad_05_anno02"/>
-    <tableColumn id="24" xr3:uid="{8F85512B-3E23-4A86-9F51-7743819540B1}" name="triad_06_anno01"/>
-    <tableColumn id="25" xr3:uid="{320A7445-D213-4C91-90B2-16BCC7597505}" name="triad_06_anno02"/>
-    <tableColumn id="26" xr3:uid="{8F834221-57A2-463D-8571-88AB09F5E74D}" name="triad_07_anno01"/>
-    <tableColumn id="27" xr3:uid="{13D95AAE-8749-492A-9FCF-56C6FBBB50C1}" name="triad_07_anno02"/>
-    <tableColumn id="28" xr3:uid="{9ADDFE8F-058B-44D5-AAC7-7AF487B823FC}" name="triad_08_anno01"/>
-    <tableColumn id="29" xr3:uid="{4C28F3A0-3F6D-4F0B-BB67-EE72E81C1D2C}" name="triad_08_anno02"/>
-    <tableColumn id="30" xr3:uid="{417EB2B8-47EB-4A83-8411-E233DCCBB01E}" name="triad_09_anno01"/>
-    <tableColumn id="31" xr3:uid="{3A033465-C487-4DA3-BF89-ADCFDC862AA8}" name="triad_09_anno02"/>
-    <tableColumn id="32" xr3:uid="{9E9EB5C4-71CC-4295-8144-F64F0E2EE899}" name="triad_10_anno01"/>
-    <tableColumn id="33" xr3:uid="{778C1DA6-16AE-4479-8A4F-1237E19FC8B1}" name="triad_10_anno02"/>
-    <tableColumn id="34" xr3:uid="{9B1E0C4F-341B-4C9B-99DC-96EC8328A14E}" name="triad_11_anno01"/>
-    <tableColumn id="35" xr3:uid="{B8272AF2-A1AB-42B6-B4C5-FF42D12E8D41}" name="triad_11_anno02"/>
-    <tableColumn id="36" xr3:uid="{1D38FA2E-A362-4B6A-A98E-00238224768D}" name="triad_12_anno01"/>
-    <tableColumn id="37" xr3:uid="{55144FD5-9909-4DA6-B954-28292E8CBD04}" name="triad_12_anno02"/>
-    <tableColumn id="38" xr3:uid="{7EF44916-A4DB-4D81-9A99-CD3DCD3FA8C9}" name="triad_13_anno01"/>
-    <tableColumn id="39" xr3:uid="{8CA25747-C54D-4C5F-89DA-43E92FDCF4D9}" name="triad_13_anno02"/>
-    <tableColumn id="40" xr3:uid="{1606CA01-AF36-425F-94F0-7B261117F93E}" name="triad_14_anno01"/>
-    <tableColumn id="41" xr3:uid="{730869A0-3E6E-4C09-889B-DF6EDEC6B82C}" name="triad_14_anno02"/>
+    <tableColumn id="2" xr3:uid="{7F24C492-7D02-4601-866A-78BAEB88EB0E}" name="dyad_02_anno01" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{C1891BFD-F445-460C-9E6A-6D77E0E4C621}" name="dyad_02_anno02" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{EDC2C213-DE1A-40C2-B091-BDD51AE57624}" name="dyad_03_anno01" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{F373B450-4B43-449F-A850-52564AD7EB64}" name="dyad_03_anno02" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{92320449-409B-41E0-BE88-3DFE1A3A7F0F}" name="dyad_04_anno01" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{0D6495A1-B397-4940-8D68-188FB75C6AF8}" name="dyad_04_anno02" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{0A02E8D0-B5F5-4E42-8942-CD64D5D77461}" name="dyad_05_anno01" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{9DBF7BE4-D471-4C34-AF7C-BD0A43B75492}" name="dyad_05_anno02" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{3463D826-CF64-4217-BB9E-474C0F41DF2C}" name="dyad_06_anno01" dataDxfId="31"/>
+    <tableColumn id="11" xr3:uid="{AC74516E-9C45-4B4B-9C48-BDE98BF69A0B}" name="dyad_06_anno02" dataDxfId="30"/>
+    <tableColumn id="12" xr3:uid="{B1CF669A-71F9-4878-8832-2975ABA8BA76}" name="dyad_07_anno01" dataDxfId="29"/>
+    <tableColumn id="13" xr3:uid="{618BB242-32B5-43AC-9937-6A903077CD34}" name="dyad_07_anno02" dataDxfId="28"/>
+    <tableColumn id="14" xr3:uid="{E62BFD50-9ED3-4CD1-86DE-65BDFDD2DBED}" name="dyad_10_anno01" dataDxfId="27"/>
+    <tableColumn id="15" xr3:uid="{A4611B9E-2E0B-45A2-98E3-1F158F067633}" name="dyad_10_anno02" dataDxfId="26"/>
+    <tableColumn id="16" xr3:uid="{6A2927A9-E70A-4AA6-BD10-C29A082888AF}" name="dyad_11_anno01" dataDxfId="25"/>
+    <tableColumn id="17" xr3:uid="{353C28AD-ACED-435C-BC6C-A24CC84009E3}" name="dyad_11_anno02" dataDxfId="24"/>
+    <tableColumn id="18" xr3:uid="{B4F86DAA-4D88-49A7-BD94-8D6224A70E3E}" name="triad_01_anno01" dataDxfId="23"/>
+    <tableColumn id="19" xr3:uid="{05B5A658-1CD0-43A7-8107-11477F3A077A}" name="triad_01_anno02" dataDxfId="22"/>
+    <tableColumn id="20" xr3:uid="{D047B543-DCBC-43C6-A17F-4D02A6B6E615}" name="triad_02_anno01" dataDxfId="21"/>
+    <tableColumn id="21" xr3:uid="{3D3513BC-134D-4E60-BC75-65899C48716C}" name="triad_02_anno02" dataDxfId="20"/>
+    <tableColumn id="22" xr3:uid="{276B2177-F32B-4BA6-87B3-EF61C38C6190}" name="triad_05_anno01" dataDxfId="19"/>
+    <tableColumn id="23" xr3:uid="{FB430E1F-00B4-439E-8EE2-B837CA136DE1}" name="triad_05_anno02" dataDxfId="18"/>
+    <tableColumn id="24" xr3:uid="{8F85512B-3E23-4A86-9F51-7743819540B1}" name="triad_06_anno01" dataDxfId="17"/>
+    <tableColumn id="25" xr3:uid="{320A7445-D213-4C91-90B2-16BCC7597505}" name="triad_06_anno02" dataDxfId="16"/>
+    <tableColumn id="26" xr3:uid="{8F834221-57A2-463D-8571-88AB09F5E74D}" name="triad_07_anno01" dataDxfId="15"/>
+    <tableColumn id="27" xr3:uid="{13D95AAE-8749-492A-9FCF-56C6FBBB50C1}" name="triad_07_anno02" dataDxfId="3"/>
+    <tableColumn id="28" xr3:uid="{9ADDFE8F-058B-44D5-AAC7-7AF487B823FC}" name="triad_08_anno01" dataDxfId="2"/>
+    <tableColumn id="29" xr3:uid="{4C28F3A0-3F6D-4F0B-BB67-EE72E81C1D2C}" name="triad_08_anno02" dataDxfId="0"/>
+    <tableColumn id="30" xr3:uid="{417EB2B8-47EB-4A83-8411-E233DCCBB01E}" name="triad_09_anno01" dataDxfId="1"/>
+    <tableColumn id="31" xr3:uid="{3A033465-C487-4DA3-BF89-ADCFDC862AA8}" name="triad_09_anno02" dataDxfId="14"/>
+    <tableColumn id="32" xr3:uid="{9E9EB5C4-71CC-4295-8144-F64F0E2EE899}" name="triad_10_anno01" dataDxfId="13"/>
+    <tableColumn id="33" xr3:uid="{778C1DA6-16AE-4479-8A4F-1237E19FC8B1}" name="triad_10_anno02" dataDxfId="12"/>
+    <tableColumn id="34" xr3:uid="{9B1E0C4F-341B-4C9B-99DC-96EC8328A14E}" name="triad_11_anno01" dataDxfId="11"/>
+    <tableColumn id="35" xr3:uid="{B8272AF2-A1AB-42B6-B4C5-FF42D12E8D41}" name="triad_11_anno02" dataDxfId="10"/>
+    <tableColumn id="36" xr3:uid="{1D38FA2E-A362-4B6A-A98E-00238224768D}" name="triad_12_anno01" dataDxfId="9"/>
+    <tableColumn id="37" xr3:uid="{55144FD5-9909-4DA6-B954-28292E8CBD04}" name="triad_12_anno02" dataDxfId="8"/>
+    <tableColumn id="38" xr3:uid="{7EF44916-A4DB-4D81-9A99-CD3DCD3FA8C9}" name="triad_13_anno01" dataDxfId="7"/>
+    <tableColumn id="39" xr3:uid="{8CA25747-C54D-4C5F-89DA-43E92FDCF4D9}" name="triad_13_anno02" dataDxfId="6"/>
+    <tableColumn id="40" xr3:uid="{1606CA01-AF36-425F-94F0-7B261117F93E}" name="triad_14_anno01" dataDxfId="5"/>
+    <tableColumn id="41" xr3:uid="{730869A0-3E6E-4C09-889B-DF6EDEC6B82C}" name="triad_14_anno02" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -32227,154 +32621,154 @@
       <c r="A2" t="s">
         <v>63</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="9">
         <v>1.6895169409309699E-2</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="9">
         <v>0.25705185700426397</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="9">
         <v>0.18890713209329499</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="9">
         <v>0.29767661546073998</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="9">
         <v>2.6766695902768999E-2</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="9">
         <v>2.4527001628868499E-2</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="9">
         <v>0.15033416945842601</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="9">
         <v>0.19363310381980101</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="9">
         <v>0.218153678696554</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="9">
         <v>0.194054219531276</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="9">
         <v>5.3137177269790899E-2</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="9">
         <v>4.8240221717476897E-2</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="9">
         <v>0.16889802546340199</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="9">
         <v>0.11942232280131899</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="9">
         <v>0.151395345666725</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="9">
         <v>0.19957464792572699</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="9">
         <v>0.55607103175376604</v>
       </c>
-      <c r="S2">
+      <c r="S2" s="9">
         <v>0.74265608857527099</v>
       </c>
-      <c r="T2">
+      <c r="T2" s="9">
         <v>0.64354714064914997</v>
       </c>
-      <c r="U2">
+      <c r="U2" s="9">
         <v>0.31223780083903702</v>
       </c>
-      <c r="V2">
+      <c r="V2" s="9">
         <v>4.9339261454859798E-2</v>
       </c>
-      <c r="W2">
+      <c r="W2" s="9">
         <v>6.5868016961014297E-2</v>
       </c>
-      <c r="X2">
+      <c r="X2" s="9">
         <v>0.42062647133796099</v>
       </c>
-      <c r="Y2">
+      <c r="Y2" s="9">
         <v>0.432052300910167</v>
       </c>
-      <c r="Z2">
+      <c r="Z2" s="9">
         <v>0.159287682014954</v>
       </c>
-      <c r="AA2">
+      <c r="AA2" s="9">
         <v>0.13144431326249501</v>
       </c>
-      <c r="AB2">
+      <c r="AB2" s="9">
         <v>0.21169013314875801</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="9">
         <v>0.394036538496566</v>
       </c>
-      <c r="AD2">
+      <c r="AD2" s="9">
         <v>0.141294809711072</v>
       </c>
-      <c r="AE2">
+      <c r="AE2" s="9">
         <v>0.123809678572589</v>
       </c>
-      <c r="AF2">
+      <c r="AF2" s="9">
         <v>6.6925921424975193E-2</v>
       </c>
-      <c r="AG2">
+      <c r="AG2" s="9">
         <v>0.20732278953490299</v>
       </c>
-      <c r="AH2">
+      <c r="AH2" s="9">
         <v>5.79265574004387E-2</v>
       </c>
-      <c r="AI2">
+      <c r="AI2" s="9">
         <v>7.6082110181733803E-2</v>
       </c>
-      <c r="AJ2">
+      <c r="AJ2" s="9">
         <v>0.41127940537917201</v>
       </c>
-      <c r="AK2">
+      <c r="AK2" s="9">
         <v>0.27731092436974702</v>
       </c>
-      <c r="AL2">
+      <c r="AL2" s="9">
         <v>0.77541592351100797</v>
       </c>
-      <c r="AM2">
+      <c r="AM2" s="9">
         <v>0.85132013683810404</v>
       </c>
-      <c r="AN2">
+      <c r="AN2" s="9">
         <v>7.3654101542547701E-2</v>
       </c>
-      <c r="AO2">
+      <c r="AO2" s="9">
         <v>7.0282970681376997E-2</v>
       </c>
-      <c r="AP2">
+      <c r="AP2" s="9">
         <v>0.30208333333333298</v>
       </c>
-      <c r="AQ2">
+      <c r="AQ2" s="9">
         <v>0.327564523184601</v>
       </c>
-      <c r="AR2">
+      <c r="AR2" s="9">
         <v>5.4742960598408601E-2</v>
       </c>
-      <c r="AS2">
+      <c r="AS2" s="9">
         <v>6.1413121158702101E-2</v>
       </c>
-      <c r="AT2">
+      <c r="AT2" s="9">
         <v>5.3193308096226598E-2</v>
       </c>
-      <c r="AU2">
+      <c r="AU2" s="9">
         <v>8.7116864085968901E-2</v>
       </c>
-      <c r="AV2">
+      <c r="AV2" s="9">
         <v>3.6859871116807101E-2</v>
       </c>
-      <c r="AW2">
+      <c r="AW2" s="9">
         <v>0.120760302532536</v>
       </c>
-      <c r="AX2">
+      <c r="AX2" s="9">
         <v>3.14769055312678E-2</v>
       </c>
-      <c r="AY2">
+      <c r="AY2" s="9">
         <v>0.11149971488310199</v>
       </c>
       <c r="BF2" t="s">
@@ -32535,154 +32929,154 @@
       <c r="A3" t="s">
         <v>58</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="9">
         <v>4.42239753985832E-2</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="9">
         <v>4.1038970547857399E-2</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="9">
         <v>0.15199838060322499</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="9">
         <v>0.111176086907626</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="9">
         <v>5.3611702794135997E-2</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="9">
         <v>6.7566720962285401E-2</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="9">
         <v>3.68007272604838E-2</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="9">
         <v>4.5201259238059899E-2</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="9">
         <v>1.6871322153814702E-2</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="9">
         <v>6.9917344127351205E-2</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="9">
         <v>3.75085957198524E-3</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="9">
         <v>9.7939111046281405E-4</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="9">
         <v>8.9484685680722795E-3</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="9">
         <v>2.3355848463385499E-2</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="9">
         <v>1.7436708429332901E-2</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="9">
         <v>0.13724420934956499</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="9">
         <v>1.7426560885752701E-2</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="9">
         <v>0.15077678797684199</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="9">
         <v>5.2439832192536897E-3</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="9">
         <v>3.6266283947891297E-2</v>
       </c>
-      <c r="V3">
+      <c r="V3" s="9">
         <v>3.2316495821497599E-3</v>
       </c>
-      <c r="W3">
+      <c r="W3" s="9">
         <v>8.3034868881478693E-2</v>
       </c>
-      <c r="X3">
+      <c r="X3" s="9">
         <v>3.2388178314915E-3</v>
       </c>
-      <c r="Y3">
+      <c r="Y3" s="9">
         <v>8.8017873476181202E-3</v>
       </c>
-      <c r="Z3">
+      <c r="Z3" s="9">
         <v>9.1007477371113702E-4</v>
       </c>
-      <c r="AA3">
+      <c r="AA3" s="9">
         <v>1.5003935458480901E-3</v>
       </c>
-      <c r="AB3">
+      <c r="AB3" s="9">
         <v>4.42614888617693E-3</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="9">
         <v>1.6648148485455601E-2</v>
       </c>
-      <c r="AD3">
+      <c r="AD3" s="9">
         <v>4.3225324189931401E-3</v>
       </c>
-      <c r="AE3">
+      <c r="AE3" s="9">
         <v>2.49114368357762E-2</v>
       </c>
-      <c r="AF3">
+      <c r="AF3" s="9">
         <v>3.09022412805333E-3</v>
       </c>
-      <c r="AG3">
+      <c r="AG3" s="9">
         <v>0.13315741046162299</v>
       </c>
-      <c r="AH3">
+      <c r="AH3" s="9">
         <v>7.0981434253000603E-3</v>
       </c>
-      <c r="AI3">
+      <c r="AI3" s="9">
         <v>3.8183731340621703E-2</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ3" s="9">
         <v>6.8197491762662498E-3</v>
       </c>
-      <c r="AK3">
+      <c r="AK3" s="9">
         <v>0.24563868100431599</v>
       </c>
-      <c r="AL3">
+      <c r="AL3" s="9">
         <v>3.71334171515452E-3</v>
       </c>
-      <c r="AM3">
+      <c r="AM3" s="9">
         <v>0.11327154176778401</v>
       </c>
-      <c r="AN3">
+      <c r="AN3" s="9">
         <v>1.9920318725099601E-3</v>
       </c>
-      <c r="AO3">
+      <c r="AO3" s="9">
         <v>2.7147818980488299E-2</v>
       </c>
-      <c r="AP3">
+      <c r="AP3" s="9">
         <v>1.57206911636045E-2</v>
       </c>
-      <c r="AQ3">
+      <c r="AQ3" s="9">
         <v>8.2513123359579998E-2</v>
       </c>
-      <c r="AR3">
+      <c r="AR3" s="9">
         <v>1.14345609605031E-3</v>
       </c>
-      <c r="AS3">
+      <c r="AS3" s="9">
         <v>0.256801181571299</v>
       </c>
-      <c r="AT3">
+      <c r="AT3" s="9">
         <v>4.6403712296983699E-4</v>
       </c>
-      <c r="AU3">
+      <c r="AU3" s="9">
         <v>0.19789962144339901</v>
       </c>
-      <c r="AV3">
+      <c r="AV3" s="9">
         <v>9.56695969241322E-4</v>
       </c>
-      <c r="AW3">
+      <c r="AW3" s="9">
         <v>0.110742071156519</v>
       </c>
-      <c r="AX3">
+      <c r="AX3" s="9">
         <v>3.02604067667743E-2</v>
       </c>
-      <c r="AY3">
+      <c r="AY3" s="9">
         <v>6.8561110055122595E-2</v>
       </c>
       <c r="BF3" t="s">
@@ -32843,154 +33237,154 @@
       <c r="A4" t="s">
         <v>56</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="9">
         <v>8.3194523256026803E-2</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="9">
         <v>1.5925024253628801E-2</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="9">
         <v>2.3953577292458499E-2</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="9">
         <v>2.4448392973617301E-2</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="9">
         <v>2.4683623606064398E-2</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="9">
         <v>4.67829845883974E-2</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="9">
         <v>7.79448157438427E-3</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="9">
         <v>3.94606151411592E-2</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="9">
         <v>1.6037960474846E-2</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="9">
         <v>0.138593149426851</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="9">
         <v>3.3549355060534698E-3</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="9">
         <v>1.3753151763945899E-3</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="9">
         <v>1.3388152780417001E-2</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="9">
         <v>5.03740045260593E-2</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="9">
         <v>5.8213248626467198E-3</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="9">
         <v>0.30420853158102801</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="9">
         <v>4.88099647180366E-2</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="9">
         <v>4.75039472914758E-2</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="9">
         <v>3.56038860675645E-3</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="9">
         <v>8.1668138661956199E-2</v>
       </c>
-      <c r="V4">
+      <c r="V4" s="9">
         <v>2.6758881890412002E-3</v>
       </c>
-      <c r="W4">
+      <c r="W4" s="9">
         <v>0.442365485159112</v>
       </c>
-      <c r="X4">
+      <c r="X4" s="9">
         <v>2.0092666176845398E-3</v>
       </c>
-      <c r="Y4">
+      <c r="Y4" s="9">
         <v>1.3570046932869499E-2</v>
       </c>
-      <c r="Z4">
+      <c r="Z4" s="9">
         <v>8.1168831168831098E-4</v>
       </c>
-      <c r="AA4">
+      <c r="AA4" s="9">
         <v>1.54466745375836E-2</v>
       </c>
-      <c r="AB4">
+      <c r="AB4" s="9">
         <v>9.2165898617511503E-3</v>
       </c>
-      <c r="AC4">
+      <c r="AC4" s="9">
         <v>5.1638403672064202E-2</v>
       </c>
-      <c r="AD4">
+      <c r="AD4" s="9">
         <v>3.3637752283142098E-3</v>
       </c>
-      <c r="AE4">
+      <c r="AE4" s="9">
         <v>6.00279502096265E-2</v>
       </c>
-      <c r="AF4">
+      <c r="AF4" s="9">
         <v>2.3957917397267399E-3</v>
       </c>
-      <c r="AG4">
+      <c r="AG4" s="9">
         <v>0.11597020885054</v>
       </c>
-      <c r="AH4">
+      <c r="AH4" s="9">
         <v>1.05758770130727E-2</v>
       </c>
-      <c r="AI4">
+      <c r="AI4" s="9">
         <v>0.13903800538602801</v>
       </c>
-      <c r="AJ4">
+      <c r="AJ4" s="9">
         <v>5.03179995402416E-3</v>
       </c>
-      <c r="AK4">
+      <c r="AK4" s="9">
         <v>0.172230594365405</v>
       </c>
-      <c r="AL4">
+      <c r="AL4" s="9">
         <v>4.9121370720154297E-3</v>
       </c>
-      <c r="AM4">
+      <c r="AM4" s="9">
         <v>4.3565977602994001E-3</v>
       </c>
-      <c r="AN4">
+      <c r="AN4" s="9">
         <v>2.1452650934722598E-3</v>
       </c>
-      <c r="AO4">
+      <c r="AO4" s="9">
         <v>0.14031055266115</v>
       </c>
-      <c r="AP4">
+      <c r="AP4" s="9">
         <v>1.0799431321084799E-2</v>
       </c>
-      <c r="AQ4">
+      <c r="AQ4" s="9">
         <v>0.29721675415573001</v>
       </c>
-      <c r="AR4">
+      <c r="AR4" s="9">
         <v>1.7437705464767202E-2</v>
       </c>
-      <c r="AS4">
+      <c r="AS4" s="9">
         <v>0.29734622897708302</v>
       </c>
-      <c r="AT4">
+      <c r="AT4" s="9">
         <v>1.3359384540236901E-2</v>
       </c>
-      <c r="AU4">
+      <c r="AU4" s="9">
         <v>0.24882158993772099</v>
       </c>
-      <c r="AV4">
+      <c r="AV4" s="9">
         <v>1.35381505081319E-3</v>
       </c>
-      <c r="AW4">
+      <c r="AW4" s="9">
         <v>0.45316702467553499</v>
       </c>
-      <c r="AX4">
+      <c r="AX4" s="9">
         <v>1.8190458087816001E-2</v>
       </c>
-      <c r="AY4">
+      <c r="AY4" s="9">
         <v>0.112621174681619</v>
       </c>
       <c r="BF4" t="s">
@@ -33151,154 +33545,154 @@
       <c r="A5" t="s">
         <v>60</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="9">
         <v>3.4504219216195897E-2</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="9">
         <v>4.4242280024162098E-2</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="9">
         <v>5.1055981646836501E-2</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="9">
         <v>2.8541868154112499E-2</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="9">
         <v>1.4675479263250199E-2</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="9">
         <v>0.114788247086831</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="9">
         <v>1.00166663860877E-2</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="9">
         <v>6.2793555664046E-2</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="9">
         <v>1.6020953093642602E-2</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="9">
         <v>8.4900846967583904E-2</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="9">
         <v>2.4588968305236602E-3</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="9">
         <v>4.8261059826210102E-2</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="9">
         <v>8.6893430303867803E-3</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="9">
         <v>5.0892255601430299E-2</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="9">
         <v>1.7014082970920601E-2</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="9">
         <v>0.148027975078731</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="9">
         <v>5.0388881308356497E-2</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="9">
         <v>4.7757353657823399E-3</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="9">
         <v>5.0783837491720002E-3</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="9">
         <v>0.13027158313093301</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="9">
         <v>2.59355316783994E-3</v>
       </c>
-      <c r="W5">
+      <c r="W5" s="9">
         <v>0.12362603433370301</v>
       </c>
-      <c r="X5">
+      <c r="X5" s="9">
         <v>2.1442173606633498E-3</v>
       </c>
-      <c r="Y5">
+      <c r="Y5" s="9">
         <v>0.120106161251143</v>
       </c>
-      <c r="Z5">
+      <c r="Z5" s="9">
         <v>1.0576544667453701E-3</v>
       </c>
-      <c r="AA5">
+      <c r="AA5" s="9">
         <v>5.3153286107831502E-2</v>
       </c>
-      <c r="AB5">
+      <c r="AB5" s="9">
         <v>4.0072129833700603E-3</v>
       </c>
-      <c r="AC5">
+      <c r="AC5" s="9">
         <v>6.1292144041092102E-2</v>
       </c>
-      <c r="AD5">
+      <c r="AD5" s="9">
         <v>3.8675290064675398E-3</v>
       </c>
-      <c r="AE5">
+      <c r="AE5" s="9">
         <v>5.9849198868991503E-2</v>
       </c>
-      <c r="AF5">
+      <c r="AF5" s="9">
         <v>2.4652349785593999E-3</v>
       </c>
-      <c r="AG5">
+      <c r="AG5" s="9">
         <v>5.4721272200135403E-2</v>
       </c>
-      <c r="AH5">
+      <c r="AH5" s="9">
         <v>3.0497048385083199E-3</v>
       </c>
-      <c r="AI5">
+      <c r="AI5" s="9">
         <v>0.28973979418950901</v>
       </c>
-      <c r="AJ5">
+      <c r="AJ5" s="9">
         <v>4.9551735587852102E-3</v>
       </c>
-      <c r="AK5">
+      <c r="AK5" s="9">
         <v>1.8901177492273501E-2</v>
       </c>
-      <c r="AL5">
+      <c r="AL5" s="9">
         <v>3.7718195374404199E-3</v>
       </c>
-      <c r="AM5">
+      <c r="AM5" s="9">
         <v>1.09938305897488E-2</v>
       </c>
-      <c r="AN5">
+      <c r="AN5" s="9">
         <v>2.4006537950761E-3</v>
       </c>
-      <c r="AO5">
+      <c r="AO5" s="9">
         <v>0.136632955358054</v>
       </c>
-      <c r="AP5">
+      <c r="AP5" s="9">
         <v>5.2493438320209904E-3</v>
       </c>
-      <c r="AQ5">
+      <c r="AQ5" s="9">
         <v>0.119340551181102</v>
       </c>
-      <c r="AR5">
+      <c r="AR5" s="9">
         <v>2.477488208109E-3</v>
       </c>
-      <c r="AS5">
+      <c r="AS5" s="9">
         <v>0.38443946829291498</v>
       </c>
-      <c r="AT5">
+      <c r="AT5" s="9">
         <v>3.44364391256563E-3</v>
       </c>
-      <c r="AU5">
+      <c r="AU5" s="9">
         <v>0.21531322505800399</v>
       </c>
-      <c r="AV5">
+      <c r="AV5" s="9">
         <v>1.78703586707341E-3</v>
       </c>
-      <c r="AW5">
+      <c r="AW5" s="9">
         <v>0.124605137276846</v>
       </c>
-      <c r="AX5">
+      <c r="AX5" s="9">
         <v>1.2031933092567899E-2</v>
       </c>
-      <c r="AY5">
+      <c r="AY5" s="9">
         <v>0.34725337388329203</v>
       </c>
       <c r="BF5" t="s">
@@ -33459,154 +33853,154 @@
       <c r="A6" t="s">
         <v>57</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="9">
         <v>7.5323534257106695E-2</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="9">
         <v>0.20678735516464999</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="9">
         <v>4.3768696160680097E-2</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="9">
         <v>0.19747644002608999</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="9">
         <v>7.1028066658313405E-2</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="9">
         <v>0.259835860167898</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="9">
         <v>7.4460025925489406E-2</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="9">
         <v>0.136159323917105</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="9">
         <v>0.18235314126330801</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="9">
         <v>0.14541310928943099</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="9">
         <v>2.5214111567234102E-3</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="9">
         <v>7.4558753047573395E-2</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="9">
         <v>6.0929051427781697E-2</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="9">
         <v>0.17808834453331401</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="9">
         <v>0.15643958500906599</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="9">
         <v>7.7585854316914504E-2</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="9">
         <v>0.134285881366834</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="9">
         <v>0</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="9">
         <v>0.12397880326782899</v>
       </c>
-      <c r="U6">
+      <c r="U6" s="9">
         <v>4.6367851622874802E-2</v>
       </c>
-      <c r="V6">
+      <c r="V6" s="9">
         <v>8.1573422255156194E-2</v>
       </c>
-      <c r="W6">
+      <c r="W6" s="9">
         <v>0.202153060804413</v>
       </c>
-      <c r="X6">
+      <c r="X6" s="9">
         <v>0.105396530266452</v>
       </c>
-      <c r="Y6">
+      <c r="Y6" s="9">
         <v>0.19791276184192699</v>
       </c>
-      <c r="Z6">
+      <c r="Z6" s="9">
         <v>9.83864620228256E-3</v>
       </c>
-      <c r="AA6">
+      <c r="AA6" s="9">
         <v>0.19138626524990099</v>
       </c>
-      <c r="AB6">
+      <c r="AB6" s="9">
         <v>6.8177264530700707E-2</v>
       </c>
-      <c r="AC6">
+      <c r="AC6" s="9">
         <v>0.35070399446276002</v>
       </c>
-      <c r="AD6">
+      <c r="AD6" s="9">
         <v>3.4174006305047203E-2</v>
       </c>
-      <c r="AE6">
+      <c r="AE6" s="9">
         <v>0.42094315707367802</v>
       </c>
-      <c r="AF6">
+      <c r="AF6" s="9">
         <v>7.5293831704310601E-2</v>
       </c>
-      <c r="AG6">
+      <c r="AG6" s="9">
         <v>0.12465061370462301</v>
       </c>
-      <c r="AH6">
+      <c r="AH6" s="9">
         <v>5.4270478500472598E-2</v>
       </c>
-      <c r="AI6">
+      <c r="AI6" s="9">
         <v>0.158620320664871</v>
       </c>
-      <c r="AJ6">
+      <c r="AJ6" s="9">
         <v>8.1300605348522306E-2</v>
       </c>
-      <c r="AK6">
+      <c r="AK6" s="9">
         <v>6.2552680646726699E-2</v>
       </c>
-      <c r="AL6">
+      <c r="AL6" s="9">
         <v>5.5583170082746103E-2</v>
       </c>
-      <c r="AM6">
+      <c r="AM6" s="9">
         <v>0</v>
       </c>
-      <c r="AN6">
+      <c r="AN6" s="9">
         <v>4.8370620083767399E-2</v>
       </c>
-      <c r="AO6">
+      <c r="AO6" s="9">
         <v>0.117504341607927</v>
       </c>
-      <c r="AP6">
+      <c r="AP6" s="9">
         <v>0.15105533683289499</v>
       </c>
-      <c r="AQ6">
+      <c r="AQ6" s="9">
         <v>0.115430883639545</v>
       </c>
-      <c r="AR6">
+      <c r="AR6" s="9">
         <v>1.7485349468769298E-2</v>
       </c>
-      <c r="AS6">
+      <c r="AS6" s="9">
         <v>0</v>
       </c>
-      <c r="AT6">
+      <c r="AT6" s="9">
         <v>0.13779460251556899</v>
       </c>
-      <c r="AU6">
+      <c r="AU6" s="9">
         <v>0.119306386616192</v>
       </c>
-      <c r="AV6">
+      <c r="AV6" s="9">
         <v>5.8990234480766797E-2</v>
       </c>
-      <c r="AW6">
+      <c r="AW6" s="9">
         <v>3.6571057239300299E-2</v>
       </c>
-      <c r="AX6">
+      <c r="AX6" s="9">
         <v>5.3639992396882698E-2</v>
       </c>
-      <c r="AY6">
+      <c r="AY6" s="9">
         <v>0.13164797567002401</v>
       </c>
       <c r="BF6" t="s">
@@ -33767,154 +34161,154 @@
       <c r="A7" t="s">
         <v>59</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="9">
         <v>4.2887737731324697E-2</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="9">
         <v>0.38410426314729701</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="9">
         <v>3.3197633881379099E-2</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="9">
         <v>0.241717460246058</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="9">
         <v>3.8591655181055E-2</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="9">
         <v>0.38414672346823697</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="9">
         <v>3.1851315634416899E-2</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="9">
         <v>0.25501254187639899</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="9">
         <v>9.4033810673832402E-2</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="9">
         <v>0.17112826966903599</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="9">
         <v>2.6464398091229201E-3</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="9">
         <v>0.278855571068369</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="9">
         <v>3.2252491923920698E-2</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="9">
         <v>0.41646656416812</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="9">
         <v>0.27011220024266802</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="9">
         <v>4.3039631361535602E-2</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="9">
         <v>6.4735580203114901E-2</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="9">
         <v>0</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="9">
         <v>9.7703687348200396E-2</v>
       </c>
-      <c r="U7">
+      <c r="U7" s="9">
         <v>9.9939280194303301E-2</v>
       </c>
-      <c r="V7">
+      <c r="V7" s="9">
         <v>0.24161211971512001</v>
       </c>
-      <c r="W7">
+      <c r="W7" s="9">
         <v>7.1425630892099898E-2</v>
       </c>
-      <c r="X7">
+      <c r="X7" s="9">
         <v>1.3105216595942401E-2</v>
       </c>
-      <c r="Y7">
+      <c r="Y7" s="9">
         <v>0.21268237093460801</v>
       </c>
-      <c r="Z7">
+      <c r="Z7" s="9">
         <v>2.87042502951593E-2</v>
       </c>
-      <c r="AA7">
+      <c r="AA7" s="9">
         <v>0.38139512003148301</v>
       </c>
-      <c r="AB7">
+      <c r="AB7" s="9">
         <v>1.29141545691335E-2</v>
       </c>
-      <c r="AC7">
+      <c r="AC7" s="9">
         <v>0.12218356678384699</v>
       </c>
-      <c r="AD7">
+      <c r="AD7" s="9">
         <v>0.101108258311937</v>
       </c>
-      <c r="AE7">
+      <c r="AE7" s="9">
         <v>0.223812928596964</v>
       </c>
-      <c r="AF7">
+      <c r="AF7" s="9">
         <v>0.122185378726063</v>
       </c>
-      <c r="AG7">
+      <c r="AG7" s="9">
         <v>2.68918942379472E-2</v>
       </c>
-      <c r="AH7">
+      <c r="AH7" s="9">
         <v>7.4905031121256904E-2</v>
       </c>
-      <c r="AI7">
+      <c r="AI7" s="9">
         <v>0.23008328726079399</v>
       </c>
-      <c r="AJ7">
+      <c r="AJ7" s="9">
         <v>8.6128068248575995E-2</v>
       </c>
-      <c r="AK7">
+      <c r="AK7" s="9">
         <v>7.0496283619830902E-2</v>
       </c>
-      <c r="AL7">
+      <c r="AL7" s="9">
         <v>3.2250518990672702E-2</v>
       </c>
-      <c r="AM7">
+      <c r="AM7" s="9">
         <v>0</v>
       </c>
-      <c r="AN7">
+      <c r="AN7" s="9">
         <v>0.10302380222698899</v>
       </c>
-      <c r="AO7">
+      <c r="AO7" s="9">
         <v>0.46820410665032097</v>
       </c>
-      <c r="AP7">
+      <c r="AP7" s="9">
         <v>7.8275371828521401E-2</v>
       </c>
-      <c r="AQ7">
+      <c r="AQ7" s="9">
         <v>2.6438101487314E-2</v>
       </c>
-      <c r="AR7">
+      <c r="AR7" s="9">
         <v>0.55962647100862295</v>
       </c>
-      <c r="AS7">
+      <c r="AS7" s="9">
         <v>0</v>
       </c>
-      <c r="AT7">
+      <c r="AT7" s="9">
         <v>5.7882525338869201E-2</v>
       </c>
-      <c r="AU7">
+      <c r="AU7" s="9">
         <v>0.12382464281353001</v>
       </c>
-      <c r="AV7">
+      <c r="AV7" s="9">
         <v>9.7907904474810001E-2</v>
       </c>
-      <c r="AW7">
+      <c r="AW7" s="9">
         <v>0.146934060181591</v>
       </c>
-      <c r="AX7">
+      <c r="AX7" s="9">
         <v>0.17243869986694499</v>
       </c>
-      <c r="AY7">
+      <c r="AY7" s="9">
         <v>0.21199391750617699</v>
       </c>
       <c r="BF7" t="s">
@@ -34075,154 +34469,154 @@
       <c r="A8" t="s">
         <v>61</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="9">
         <v>1.32525489191118E-2</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="9">
         <v>4.2869433105745799E-2</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="9">
         <v>3.11733879130024E-2</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="9">
         <v>0</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="9">
         <v>4.5342062398195701E-2</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="9">
         <v>0.102321137702042</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="9">
         <v>3.0790727428831099E-2</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="9">
         <v>0.173465093180249</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="9">
         <v>2.9235688288717299E-2</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="9">
         <v>5.9151671825572301E-2</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="9">
         <v>4.9803079872470703E-3</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="9">
         <v>0.22203004855279301</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="9">
         <v>1.40791542142449E-2</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="9">
         <v>0.113548810613782</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="9">
         <v>4.8083870703875799E-2</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="9">
         <v>4.3380458344126099E-2</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="9">
         <v>6.4716087405703596E-3</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="9">
         <v>0</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="9">
         <v>3.6128284389489902E-2</v>
       </c>
-      <c r="U8">
+      <c r="U8" s="9">
         <v>0</v>
       </c>
-      <c r="V8">
+      <c r="V8" s="9">
         <v>3.60009880202544E-2</v>
       </c>
-      <c r="W8" s="1">
+      <c r="W8" s="9">
         <v>4.1167510600633898E-5</v>
       </c>
-      <c r="X8">
+      <c r="X8" s="9">
         <v>3.3212877299785497E-2</v>
       </c>
-      <c r="Y8" s="1">
+      <c r="Y8" s="9">
         <v>1.49945269976458E-5</v>
       </c>
-      <c r="Z8">
+      <c r="Z8" s="9">
         <v>1.5249901613537901E-3</v>
       </c>
-      <c r="AA8">
+      <c r="AA8" s="9">
         <v>0.22567394726485601</v>
       </c>
-      <c r="AB8">
+      <c r="AB8" s="9">
         <v>5.0090162292125802E-3</v>
       </c>
-      <c r="AC8">
+      <c r="AC8" s="9">
         <v>3.4061310358645498E-3</v>
       </c>
-      <c r="AD8">
+      <c r="AD8" s="9">
         <v>5.13503851278884E-2</v>
       </c>
-      <c r="AE8">
+      <c r="AE8" s="9">
         <v>5.43241574311807E-2</v>
       </c>
-      <c r="AF8">
+      <c r="AF8" s="9">
         <v>9.1925487404732498E-2</v>
       </c>
-      <c r="AG8">
+      <c r="AG8" s="9">
         <v>0</v>
       </c>
-      <c r="AH8">
+      <c r="AH8" s="9">
         <v>8.2235023452408504E-2</v>
       </c>
-      <c r="AI8">
+      <c r="AI8" s="9">
         <v>5.48411834994917E-2</v>
       </c>
-      <c r="AJ8">
+      <c r="AJ8" s="9">
         <v>4.9577277719598398E-2</v>
       </c>
-      <c r="AK8">
+      <c r="AK8" s="9">
         <v>0</v>
       </c>
-      <c r="AL8">
+      <c r="AL8" s="9">
         <v>7.9997660887108496E-2</v>
       </c>
-      <c r="AM8">
+      <c r="AM8" s="9">
         <v>0</v>
       </c>
-      <c r="AN8">
+      <c r="AN8" s="9">
         <v>8.5172131984880994E-2</v>
       </c>
-      <c r="AO8">
+      <c r="AO8" s="9">
         <v>3.3685769741546599E-2</v>
       </c>
-      <c r="AP8">
+      <c r="AP8" s="9">
         <v>0.15830052493438301</v>
       </c>
-      <c r="AQ8">
+      <c r="AQ8" s="9">
         <v>0</v>
       </c>
-      <c r="AR8">
+      <c r="AR8" s="9">
         <v>0.135404259373957</v>
       </c>
-      <c r="AS8">
+      <c r="AS8" s="9">
         <v>0</v>
       </c>
-      <c r="AT8">
+      <c r="AT8" s="9">
         <v>2.8526071559408901E-2</v>
       </c>
-      <c r="AU8">
+      <c r="AU8" s="9">
         <v>0</v>
       </c>
-      <c r="AV8">
+      <c r="AV8" s="9">
         <v>0.155851188649614</v>
       </c>
-      <c r="AW8" s="1">
+      <c r="AW8" s="9">
         <v>3.6101734688351699E-5</v>
       </c>
-      <c r="AX8">
+      <c r="AX8" s="9">
         <v>0.22661091047329401</v>
       </c>
-      <c r="AY8">
+      <c r="AY8" s="9">
         <v>0</v>
       </c>
       <c r="BF8" t="s">
@@ -34383,154 +34777,154 @@
       <c r="A9" t="s">
         <v>62</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="9">
         <v>9.7380608079661694E-3</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="9">
         <v>0</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="9">
         <v>5.5306898180427701E-2</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="9">
         <v>0</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="9">
         <v>6.8193208871068695E-2</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="9">
         <v>0</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="9">
         <v>3.4780559249844203E-2</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="9">
         <v>9.4274507163179005E-2</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="9">
         <v>4.4797442089867003E-2</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="9">
         <v>0.118813565087247</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="9">
         <v>3.3757736147867201E-3</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="9">
         <v>0.30186084310987898</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="9">
         <v>6.5645136213657602E-3</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="9">
         <v>3.9162506262200497E-2</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="9">
         <v>2.20855884718681E-2</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="9">
         <v>1.39875393655164E-2</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="9">
         <v>1.23584335588E-2</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="9">
         <v>0</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="9">
         <v>1.03499668801059E-2</v>
       </c>
-      <c r="U9">
+      <c r="U9" s="9">
         <v>0</v>
       </c>
-      <c r="V9">
+      <c r="V9" s="9">
         <v>7.6509818451278203E-2</v>
       </c>
-      <c r="W9">
+      <c r="W9" s="9">
         <v>0</v>
       </c>
-      <c r="X9">
+      <c r="X9" s="9">
         <v>1.6044143887481001E-3</v>
       </c>
-      <c r="Y9">
+      <c r="Y9" s="9">
         <v>0</v>
       </c>
-      <c r="Z9">
+      <c r="Z9" s="9">
         <v>4.7274695001967702E-2</v>
       </c>
-      <c r="AA9">
+      <c r="AA9" s="9">
         <v>0</v>
       </c>
-      <c r="AB9">
+      <c r="AB9" s="9">
         <v>0.12732008524434801</v>
       </c>
-      <c r="AC9">
+      <c r="AC9" s="9">
         <v>0</v>
       </c>
-      <c r="AD9">
+      <c r="AD9" s="9">
         <v>0.107153303649777</v>
       </c>
-      <c r="AE9">
+      <c r="AE9" s="9">
         <v>0</v>
       </c>
-      <c r="AF9">
+      <c r="AF9" s="9">
         <v>6.6908560615267093E-2</v>
       </c>
-      <c r="AG9">
+      <c r="AG9" s="9">
         <v>0</v>
       </c>
-      <c r="AH9">
+      <c r="AH9" s="9">
         <v>3.2084321663605003E-2</v>
       </c>
-      <c r="AI9">
+      <c r="AI9" s="9">
         <v>0</v>
       </c>
-      <c r="AJ9">
+      <c r="AJ9" s="9">
         <v>7.6038926208781304E-2</v>
       </c>
-      <c r="AK9">
+      <c r="AK9" s="9">
         <v>0</v>
       </c>
-      <c r="AL9">
+      <c r="AL9" s="9">
         <v>3.3215403058390103E-2</v>
       </c>
-      <c r="AM9">
+      <c r="AM9" s="9">
         <v>0</v>
       </c>
-      <c r="AN9">
+      <c r="AN9" s="9">
         <v>7.5033200531208502E-2</v>
       </c>
-      <c r="AO9">
+      <c r="AO9" s="9">
         <v>1.53233220962304E-4</v>
       </c>
-      <c r="AP9">
+      <c r="AP9" s="9">
         <v>0.14236111111111099</v>
       </c>
-      <c r="AQ9">
+      <c r="AQ9" s="9">
         <v>0</v>
       </c>
-      <c r="AR9">
+      <c r="AR9" s="9">
         <v>0.14964981657058399</v>
       </c>
-      <c r="AS9">
+      <c r="AS9" s="9">
         <v>0</v>
       </c>
-      <c r="AT9">
+      <c r="AT9" s="9">
         <v>9.1000122115032306E-2</v>
       </c>
-      <c r="AU9">
+      <c r="AU9" s="9">
         <v>0</v>
       </c>
-      <c r="AV9">
+      <c r="AV9" s="9">
         <v>0.141356342172241</v>
       </c>
-      <c r="AW9">
+      <c r="AW9" s="9">
         <v>0</v>
       </c>
-      <c r="AX9">
+      <c r="AX9" s="9">
         <v>0.19956282075651</v>
       </c>
-      <c r="AY9">
+      <c r="AY9" s="9">
         <v>0</v>
       </c>
       <c r="BF9" t="s">
@@ -34691,154 +35085,154 @@
       <c r="A10" t="s">
         <v>55</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="9">
         <v>0.20265050978382201</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="9">
         <v>0</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="9">
         <v>0.33561998155687001</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="9">
         <v>0</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="9">
         <v>0.26464415486781101</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="9">
         <v>0</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="9">
         <v>0.26689786367232798</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="9">
         <v>0</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="9">
         <v>5.0477907411816701E-2</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="9">
         <v>1.08677165889996E-2</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="9">
         <v>8.5853007980995592E-3</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="9">
         <v>2.3547062868574001E-2</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="9">
         <v>1.7983312315373E-2</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="9">
         <v>0</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="9">
         <v>3.1028888495044302E-2</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="9">
         <v>0</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="9">
         <v>8.9861796066353396E-3</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="9">
         <v>0</v>
       </c>
-      <c r="T10">
+      <c r="T10" s="9">
         <v>3.6873482004857502E-2</v>
       </c>
-      <c r="U10">
+      <c r="U10" s="9">
         <v>0</v>
       </c>
-      <c r="V10">
+      <c r="V10" s="9">
         <v>5.0944794368284502E-2</v>
       </c>
-      <c r="W10">
+      <c r="W10" s="9">
         <v>0</v>
       </c>
-      <c r="X10">
+      <c r="X10" s="9">
         <v>1.9972709960864199E-2</v>
       </c>
-      <c r="Y10">
+      <c r="Y10" s="9">
         <v>0</v>
       </c>
-      <c r="Z10">
+      <c r="Z10" s="9">
         <v>6.8304801259346695E-2</v>
       </c>
-      <c r="AA10">
+      <c r="AA10" s="9">
         <v>0</v>
       </c>
-      <c r="AB10">
+      <c r="AB10" s="9">
         <v>0.22868435911914101</v>
       </c>
-      <c r="AC10">
+      <c r="AC10" s="9">
         <v>0</v>
       </c>
-      <c r="AD10">
+      <c r="AD10" s="9">
         <v>0.19116643374825301</v>
       </c>
-      <c r="AE10">
+      <c r="AE10" s="9">
         <v>0</v>
       </c>
-      <c r="AF10">
+      <c r="AF10" s="9">
         <v>0.15098696203190901</v>
       </c>
-      <c r="AG10">
+      <c r="AG10" s="9">
         <v>0</v>
       </c>
-      <c r="AH10">
+      <c r="AH10" s="9">
         <v>9.2347202653778201E-2</v>
       </c>
-      <c r="AI10">
+      <c r="AI10" s="9">
         <v>0</v>
       </c>
-      <c r="AJ10">
+      <c r="AJ10" s="9">
         <v>0.132206073918929</v>
       </c>
-      <c r="AK10">
+      <c r="AK10" s="9">
         <v>0</v>
       </c>
-      <c r="AL10">
+      <c r="AL10" s="9">
         <v>1.11400251454635E-2</v>
       </c>
-      <c r="AM10">
+      <c r="AM10" s="9">
         <v>0</v>
       </c>
-      <c r="AN10">
+      <c r="AN10" s="9">
         <v>0.30649198079476903</v>
       </c>
-      <c r="AO10">
+      <c r="AO10" s="9">
         <v>6.02717335785064E-3</v>
       </c>
-      <c r="AP10">
+      <c r="AP10" s="9">
         <v>0.136154855643044</v>
       </c>
-      <c r="AQ10">
+      <c r="AQ10" s="9">
         <v>0</v>
       </c>
-      <c r="AR10">
+      <c r="AR10" s="9">
         <v>6.20324932107294E-2</v>
       </c>
-      <c r="AS10">
+      <c r="AS10" s="9">
         <v>0</v>
       </c>
-      <c r="AT10">
+      <c r="AT10" s="9">
         <v>0.308755647820246</v>
       </c>
-      <c r="AU10">
+      <c r="AU10" s="9">
         <v>0</v>
       </c>
-      <c r="AV10">
+      <c r="AV10" s="9">
         <v>9.3557645444863599E-2</v>
       </c>
-      <c r="AW10">
+      <c r="AW10" s="9">
         <v>0</v>
       </c>
-      <c r="AX10">
+      <c r="AX10" s="9">
         <v>0.25578787302794098</v>
       </c>
-      <c r="AY10">
+      <c r="AY10" s="9">
         <v>0</v>
       </c>
       <c r="BF10" t="s">
@@ -34999,154 +35393,154 @@
       <c r="A11" t="s">
         <v>54</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="9">
         <v>0.47732972122055201</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="9">
         <v>0</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="9">
         <v>8.5018330671824696E-2</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="9">
         <v>0</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="9">
         <v>0.39244768825961601</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="9">
         <v>0</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="9">
         <v>0.356273463409706</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="9">
         <v>0</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="9">
         <v>0.32970509200993198</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="9">
         <v>0</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="9">
         <v>0.91516805934693302</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="9">
         <v>0</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="9">
         <v>0.66825021161918896</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="9">
         <v>0</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="9">
         <v>0.28058240514784999</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="9">
         <v>0</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="9">
         <v>0.10046587785813101</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="9">
         <v>0</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="9">
         <v>3.6349083682932201E-2</v>
       </c>
-      <c r="U11">
+      <c r="U11" s="9">
         <v>0</v>
       </c>
-      <c r="V11">
+      <c r="V11" s="9">
         <v>0.45551850479601402</v>
       </c>
-      <c r="W11">
+      <c r="W11" s="9">
         <v>0</v>
       </c>
-      <c r="X11">
+      <c r="X11" s="9">
         <v>0.391102247679596</v>
       </c>
-      <c r="Y11">
+      <c r="Y11" s="9">
         <v>0</v>
       </c>
-      <c r="Z11">
+      <c r="Z11" s="9">
         <v>0.68228551751278999</v>
       </c>
-      <c r="AA11">
+      <c r="AA11" s="9">
         <v>0</v>
       </c>
-      <c r="AB11">
+      <c r="AB11" s="9">
         <v>0.328555035427405</v>
       </c>
-      <c r="AC11">
+      <c r="AC11" s="9">
         <v>0</v>
       </c>
-      <c r="AD11">
+      <c r="AD11" s="9">
         <v>0.36219896649224798</v>
       </c>
-      <c r="AE11">
+      <c r="AE11" s="9">
         <v>0</v>
       </c>
-      <c r="AF11">
+      <c r="AF11" s="9">
         <v>0.41782260724640102</v>
       </c>
-      <c r="AG11">
+      <c r="AG11" s="9">
         <v>0</v>
       </c>
-      <c r="AH11">
+      <c r="AH11" s="9">
         <v>0.58550765993115805</v>
       </c>
-      <c r="AI11">
+      <c r="AI11" s="9">
         <v>0</v>
       </c>
-      <c r="AJ11">
+      <c r="AJ11" s="9">
         <v>0.146662920487343</v>
       </c>
-      <c r="AK11">
+      <c r="AK11" s="9">
         <v>0</v>
       </c>
-      <c r="AL11">
+      <c r="AL11" s="9">
         <v>0</v>
       </c>
-      <c r="AM11">
+      <c r="AM11" s="9">
         <v>0</v>
       </c>
-      <c r="AN11">
+      <c r="AN11" s="9">
         <v>0.30169067320461701</v>
       </c>
-      <c r="AO11">
+      <c r="AO11" s="9">
         <v>0</v>
       </c>
-      <c r="AP11">
+      <c r="AP11" s="9">
         <v>0</v>
       </c>
-      <c r="AQ11">
+      <c r="AQ11" s="9">
         <v>0</v>
       </c>
-      <c r="AR11">
+      <c r="AR11" s="9">
         <v>0</v>
       </c>
-      <c r="AS11">
+      <c r="AS11" s="9">
         <v>0</v>
       </c>
-      <c r="AT11">
+      <c r="AT11" s="9">
         <v>0.30558065697887399</v>
       </c>
-      <c r="AU11">
+      <c r="AU11" s="9">
         <v>0</v>
       </c>
-      <c r="AV11">
+      <c r="AV11" s="9">
         <v>0.41137926677376802</v>
       </c>
-      <c r="AW11">
+      <c r="AW11" s="9">
         <v>0</v>
       </c>
-      <c r="AX11">
+      <c r="AX11" s="9">
         <v>0</v>
       </c>
-      <c r="AY11">
+      <c r="AY11" s="9">
         <v>0</v>
       </c>
       <c r="BF11" t="s">
@@ -35362,16 +35756,18 @@
       <c r="BL15" t="s">
         <v>67</v>
       </c>
-      <c r="BN15" s="2"/>
-      <c r="BO15" s="2" t="s">
+      <c r="BO15" t="s">
         <v>99</v>
       </c>
       <c r="BS15" t="s">
         <v>100</v>
       </c>
+      <c r="BY15" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="16" spans="1:108" x14ac:dyDescent="0.35">
-      <c r="BR16" s="6" t="s">
+      <c r="BR16" s="5" t="s">
         <v>64</v>
       </c>
     </row>
@@ -35468,79 +35864,79 @@
       <c r="BF18" t="s">
         <v>63</v>
       </c>
-      <c r="BG18">
+      <c r="BG18" s="9">
         <v>0.25705185700426397</v>
       </c>
-      <c r="BH18">
+      <c r="BH18" s="9">
         <v>0.29767661546073998</v>
       </c>
-      <c r="BI18">
+      <c r="BI18" s="9">
         <v>2.4527001628868499E-2</v>
       </c>
-      <c r="BJ18">
+      <c r="BJ18" s="9">
         <v>0.19363310381980101</v>
       </c>
-      <c r="BK18">
+      <c r="BK18" s="9">
         <v>0.194054219531276</v>
       </c>
-      <c r="BL18">
+      <c r="BL18" s="9">
         <v>4.8240221717476897E-2</v>
       </c>
-      <c r="BM18">
+      <c r="BM18" s="9">
         <v>0.11942232280131899</v>
       </c>
-      <c r="BN18">
+      <c r="BN18" s="9">
         <v>0.19957464792572699</v>
       </c>
-      <c r="BO18">
+      <c r="BO18" s="9">
         <v>0.74265608857527099</v>
       </c>
-      <c r="BP18">
+      <c r="BP18" s="9">
         <v>0.31223780083903702</v>
       </c>
-      <c r="BQ18">
+      <c r="BQ18" s="9">
         <v>6.5868016961014297E-2</v>
       </c>
-      <c r="BR18">
+      <c r="BR18" s="9">
         <v>0.432052300910167</v>
       </c>
-      <c r="BS18">
+      <c r="BS18" s="9">
         <v>0.13144431326249501</v>
       </c>
-      <c r="BT18">
+      <c r="BT18" s="9">
         <v>0.394036538496566</v>
       </c>
-      <c r="BU18">
+      <c r="BU18" s="9">
         <v>0.123809678572589</v>
       </c>
-      <c r="BV18">
+      <c r="BV18" s="9">
         <v>0.20732278953490299</v>
       </c>
-      <c r="BW18">
+      <c r="BW18" s="9">
         <v>7.6082110181733803E-2</v>
       </c>
-      <c r="BX18">
+      <c r="BX18" s="9">
         <v>0.27731092436974702</v>
       </c>
-      <c r="BY18">
+      <c r="BY18" s="9">
         <v>0.85132013683810404</v>
       </c>
-      <c r="BZ18">
+      <c r="BZ18" s="9">
         <v>7.0282970681376997E-2</v>
       </c>
-      <c r="CA18">
+      <c r="CA18" s="9">
         <v>0.327564523184601</v>
       </c>
-      <c r="CB18">
+      <c r="CB18" s="9">
         <v>6.1413121158702101E-2</v>
       </c>
-      <c r="CC18">
+      <c r="CC18" s="9">
         <v>8.7116864085968901E-2</v>
       </c>
-      <c r="CD18">
+      <c r="CD18" s="9">
         <v>0.120760302532536</v>
       </c>
-      <c r="CE18">
+      <c r="CE18" s="9">
         <v>0.11149971488310199</v>
       </c>
       <c r="CG18">
@@ -35560,79 +35956,79 @@
       <c r="BF19" t="s">
         <v>58</v>
       </c>
-      <c r="BG19">
+      <c r="BG19" s="9">
         <v>4.1038970547857399E-2</v>
       </c>
-      <c r="BH19">
+      <c r="BH19" s="9">
         <v>0.111176086907626</v>
       </c>
-      <c r="BI19">
+      <c r="BI19" s="9">
         <v>6.7566720962285401E-2</v>
       </c>
-      <c r="BJ19">
+      <c r="BJ19" s="9">
         <v>4.5201259238059899E-2</v>
       </c>
-      <c r="BK19">
+      <c r="BK19" s="9">
         <v>6.9917344127351205E-2</v>
       </c>
-      <c r="BL19">
+      <c r="BL19" s="9">
         <v>9.7939111046281405E-4</v>
       </c>
-      <c r="BM19">
+      <c r="BM19" s="9">
         <v>2.3355848463385499E-2</v>
       </c>
-      <c r="BN19">
+      <c r="BN19" s="9">
         <v>0.13724420934956499</v>
       </c>
-      <c r="BO19">
+      <c r="BO19" s="9">
         <v>0.15077678797684199</v>
       </c>
-      <c r="BP19">
+      <c r="BP19" s="9">
         <v>3.6266283947891297E-2</v>
       </c>
-      <c r="BQ19">
+      <c r="BQ19" s="9">
         <v>8.3034868881478693E-2</v>
       </c>
-      <c r="BR19">
+      <c r="BR19" s="9">
         <v>8.8017873476181202E-3</v>
       </c>
-      <c r="BS19">
+      <c r="BS19" s="9">
         <v>1.5003935458480901E-3</v>
       </c>
-      <c r="BT19">
+      <c r="BT19" s="9">
         <v>1.6648148485455601E-2</v>
       </c>
-      <c r="BU19">
+      <c r="BU19" s="9">
         <v>2.49114368357762E-2</v>
       </c>
-      <c r="BV19">
+      <c r="BV19" s="9">
         <v>0.13315741046162299</v>
       </c>
-      <c r="BW19">
+      <c r="BW19" s="9">
         <v>3.8183731340621703E-2</v>
       </c>
-      <c r="BX19">
+      <c r="BX19" s="9">
         <v>0.24563868100431599</v>
       </c>
-      <c r="BY19">
+      <c r="BY19" s="9">
         <v>0.11327154176778401</v>
       </c>
-      <c r="BZ19">
+      <c r="BZ19" s="9">
         <v>2.7147818980488299E-2</v>
       </c>
-      <c r="CA19">
+      <c r="CA19" s="9">
         <v>8.2513123359579998E-2</v>
       </c>
-      <c r="CB19">
+      <c r="CB19" s="9">
         <v>0.256801181571299</v>
       </c>
-      <c r="CC19">
+      <c r="CC19" s="9">
         <v>0.19789962144339901</v>
       </c>
-      <c r="CD19">
+      <c r="CD19" s="9">
         <v>0.110742071156519</v>
       </c>
-      <c r="CE19">
+      <c r="CE19" s="9">
         <v>6.8561110055122595E-2</v>
       </c>
       <c r="CG19">
@@ -35652,79 +36048,79 @@
       <c r="BF20" t="s">
         <v>56</v>
       </c>
-      <c r="BG20">
+      <c r="BG20" s="9">
         <v>1.5925024253628801E-2</v>
       </c>
-      <c r="BH20">
+      <c r="BH20" s="9">
         <v>2.4448392973617301E-2</v>
       </c>
-      <c r="BI20">
+      <c r="BI20" s="9">
         <v>4.67829845883974E-2</v>
       </c>
-      <c r="BJ20">
+      <c r="BJ20" s="9">
         <v>3.94606151411592E-2</v>
       </c>
-      <c r="BK20">
+      <c r="BK20" s="9">
         <v>0.138593149426851</v>
       </c>
-      <c r="BL20">
+      <c r="BL20" s="9">
         <v>1.3753151763945899E-3</v>
       </c>
-      <c r="BM20">
+      <c r="BM20" s="9">
         <v>5.03740045260593E-2</v>
       </c>
-      <c r="BN20">
+      <c r="BN20" s="9">
         <v>0.30420853158102801</v>
       </c>
-      <c r="BO20">
+      <c r="BO20" s="9">
         <v>4.75039472914758E-2</v>
       </c>
-      <c r="BP20">
+      <c r="BP20" s="9">
         <v>8.1668138661956199E-2</v>
       </c>
-      <c r="BQ20">
+      <c r="BQ20" s="9">
         <v>0.442365485159112</v>
       </c>
-      <c r="BR20">
+      <c r="BR20" s="9">
         <v>1.3570046932869499E-2</v>
       </c>
-      <c r="BS20">
+      <c r="BS20" s="9">
         <v>1.54466745375836E-2</v>
       </c>
-      <c r="BT20">
+      <c r="BT20" s="9">
         <v>5.1638403672064202E-2</v>
       </c>
-      <c r="BU20">
+      <c r="BU20" s="9">
         <v>6.00279502096265E-2</v>
       </c>
-      <c r="BV20">
+      <c r="BV20" s="9">
         <v>0.11597020885054</v>
       </c>
-      <c r="BW20">
+      <c r="BW20" s="9">
         <v>0.13903800538602801</v>
       </c>
-      <c r="BX20">
+      <c r="BX20" s="9">
         <v>0.172230594365405</v>
       </c>
-      <c r="BY20">
+      <c r="BY20" s="9">
         <v>4.3565977602994001E-3</v>
       </c>
-      <c r="BZ20">
+      <c r="BZ20" s="9">
         <v>0.14031055266115</v>
       </c>
-      <c r="CA20">
+      <c r="CA20" s="9">
         <v>0.29721675415573001</v>
       </c>
-      <c r="CB20">
+      <c r="CB20" s="9">
         <v>0.29734622897708302</v>
       </c>
-      <c r="CC20">
+      <c r="CC20" s="9">
         <v>0.24882158993772099</v>
       </c>
-      <c r="CD20">
+      <c r="CD20" s="9">
         <v>0.45316702467553499</v>
       </c>
-      <c r="CE20">
+      <c r="CE20" s="9">
         <v>0.112621174681619</v>
       </c>
       <c r="CG20">
@@ -35744,79 +36140,79 @@
       <c r="BF21" t="s">
         <v>60</v>
       </c>
-      <c r="BG21">
+      <c r="BG21" s="9">
         <v>4.4242280024162098E-2</v>
       </c>
-      <c r="BH21">
+      <c r="BH21" s="9">
         <v>2.8541868154112499E-2</v>
       </c>
-      <c r="BI21">
+      <c r="BI21" s="9">
         <v>0.114788247086831</v>
       </c>
-      <c r="BJ21">
+      <c r="BJ21" s="9">
         <v>6.2793555664046E-2</v>
       </c>
-      <c r="BK21">
+      <c r="BK21" s="9">
         <v>8.4900846967583904E-2</v>
       </c>
-      <c r="BL21">
+      <c r="BL21" s="9">
         <v>4.8261059826210102E-2</v>
       </c>
-      <c r="BM21">
+      <c r="BM21" s="9">
         <v>5.0892255601430299E-2</v>
       </c>
-      <c r="BN21">
+      <c r="BN21" s="9">
         <v>0.148027975078731</v>
       </c>
-      <c r="BO21">
+      <c r="BO21" s="9">
         <v>4.7757353657823399E-3</v>
       </c>
-      <c r="BP21">
+      <c r="BP21" s="9">
         <v>0.13027158313093301</v>
       </c>
-      <c r="BQ21">
+      <c r="BQ21" s="9">
         <v>0.12362603433370301</v>
       </c>
-      <c r="BR21">
+      <c r="BR21" s="9">
         <v>0.120106161251143</v>
       </c>
-      <c r="BS21">
+      <c r="BS21" s="9">
         <v>5.3153286107831502E-2</v>
       </c>
-      <c r="BT21">
+      <c r="BT21" s="9">
         <v>6.1292144041092102E-2</v>
       </c>
-      <c r="BU21">
+      <c r="BU21" s="9">
         <v>5.9849198868991503E-2</v>
       </c>
-      <c r="BV21">
+      <c r="BV21" s="9">
         <v>5.4721272200135403E-2</v>
       </c>
-      <c r="BW21">
+      <c r="BW21" s="9">
         <v>0.28973979418950901</v>
       </c>
-      <c r="BX21">
+      <c r="BX21" s="9">
         <v>1.8901177492273501E-2</v>
       </c>
-      <c r="BY21">
+      <c r="BY21" s="9">
         <v>1.09938305897488E-2</v>
       </c>
-      <c r="BZ21">
+      <c r="BZ21" s="9">
         <v>0.136632955358054</v>
       </c>
-      <c r="CA21">
+      <c r="CA21" s="9">
         <v>0.119340551181102</v>
       </c>
-      <c r="CB21">
+      <c r="CB21" s="9">
         <v>0.38443946829291498</v>
       </c>
-      <c r="CC21">
+      <c r="CC21" s="9">
         <v>0.21531322505800399</v>
       </c>
-      <c r="CD21">
+      <c r="CD21" s="9">
         <v>0.124605137276846</v>
       </c>
-      <c r="CE21">
+      <c r="CE21" s="9">
         <v>0.34725337388329203</v>
       </c>
       <c r="CG21">
@@ -35836,79 +36232,79 @@
       <c r="BF22" t="s">
         <v>57</v>
       </c>
-      <c r="BG22">
+      <c r="BG22" s="9">
         <v>0.20678735516464999</v>
       </c>
-      <c r="BH22">
+      <c r="BH22" s="9">
         <v>0.19747644002608999</v>
       </c>
-      <c r="BI22">
+      <c r="BI22" s="9">
         <v>0.259835860167898</v>
       </c>
-      <c r="BJ22">
+      <c r="BJ22" s="9">
         <v>0.136159323917105</v>
       </c>
-      <c r="BK22">
+      <c r="BK22" s="9">
         <v>0.14541310928943099</v>
       </c>
-      <c r="BL22">
+      <c r="BL22" s="9">
         <v>7.4558753047573395E-2</v>
       </c>
-      <c r="BM22">
+      <c r="BM22" s="9">
         <v>0.17808834453331401</v>
       </c>
-      <c r="BN22">
+      <c r="BN22" s="9">
         <v>7.7585854316914504E-2</v>
       </c>
-      <c r="BO22">
+      <c r="BO22" s="9">
         <v>0</v>
       </c>
-      <c r="BP22">
+      <c r="BP22" s="9">
         <v>4.6367851622874802E-2</v>
       </c>
-      <c r="BQ22">
+      <c r="BQ22" s="9">
         <v>0.202153060804413</v>
       </c>
-      <c r="BR22">
+      <c r="BR22" s="9">
         <v>0.19791276184192699</v>
       </c>
-      <c r="BS22">
+      <c r="BS22" s="9">
         <v>0.19138626524990099</v>
       </c>
-      <c r="BT22">
+      <c r="BT22" s="9">
         <v>0.35070399446276002</v>
       </c>
-      <c r="BU22">
+      <c r="BU22" s="9">
         <v>0.42094315707367802</v>
       </c>
-      <c r="BV22">
+      <c r="BV22" s="9">
         <v>0.12465061370462301</v>
       </c>
-      <c r="BW22">
+      <c r="BW22" s="9">
         <v>0.158620320664871</v>
       </c>
-      <c r="BX22">
+      <c r="BX22" s="9">
         <v>6.2552680646726699E-2</v>
       </c>
-      <c r="BY22">
+      <c r="BY22" s="9">
         <v>0</v>
       </c>
-      <c r="BZ22">
+      <c r="BZ22" s="9">
         <v>0.117504341607927</v>
       </c>
-      <c r="CA22">
+      <c r="CA22" s="9">
         <v>0.115430883639545</v>
       </c>
-      <c r="CB22">
+      <c r="CB22" s="9">
         <v>0</v>
       </c>
-      <c r="CC22">
+      <c r="CC22" s="9">
         <v>0.119306386616192</v>
       </c>
-      <c r="CD22">
+      <c r="CD22" s="9">
         <v>3.6571057239300299E-2</v>
       </c>
-      <c r="CE22">
+      <c r="CE22" s="9">
         <v>0.13164797567002401</v>
       </c>
       <c r="CG22">
@@ -35928,79 +36324,79 @@
       <c r="BF23" t="s">
         <v>59</v>
       </c>
-      <c r="BG23">
+      <c r="BG23" s="9">
         <v>0.38410426314729701</v>
       </c>
-      <c r="BH23">
+      <c r="BH23" s="9">
         <v>0.241717460246058</v>
       </c>
-      <c r="BI23">
+      <c r="BI23" s="9">
         <v>0.38414672346823697</v>
       </c>
-      <c r="BJ23">
+      <c r="BJ23" s="9">
         <v>0.25501254187639899</v>
       </c>
-      <c r="BK23">
+      <c r="BK23" s="9">
         <v>0.17112826966903599</v>
       </c>
-      <c r="BL23">
+      <c r="BL23" s="9">
         <v>0.278855571068369</v>
       </c>
-      <c r="BM23">
+      <c r="BM23" s="9">
         <v>0.41646656416812</v>
       </c>
-      <c r="BN23">
+      <c r="BN23" s="9">
         <v>4.3039631361535602E-2</v>
       </c>
-      <c r="BO23">
+      <c r="BO23" s="9">
         <v>0</v>
       </c>
-      <c r="BP23">
+      <c r="BP23" s="9">
         <v>9.9939280194303301E-2</v>
       </c>
-      <c r="BQ23">
+      <c r="BQ23" s="9">
         <v>7.1425630892099898E-2</v>
       </c>
-      <c r="BR23">
+      <c r="BR23" s="9">
         <v>0.21268237093460801</v>
       </c>
-      <c r="BS23">
+      <c r="BS23" s="9">
         <v>0.38139512003148301</v>
       </c>
-      <c r="BT23">
+      <c r="BT23" s="9">
         <v>0.12218356678384699</v>
       </c>
-      <c r="BU23">
+      <c r="BU23" s="9">
         <v>0.223812928596964</v>
       </c>
-      <c r="BV23">
+      <c r="BV23" s="9">
         <v>2.68918942379472E-2</v>
       </c>
-      <c r="BW23">
+      <c r="BW23" s="9">
         <v>0.23008328726079399</v>
       </c>
-      <c r="BX23">
+      <c r="BX23" s="9">
         <v>7.0496283619830902E-2</v>
       </c>
-      <c r="BY23">
+      <c r="BY23" s="9">
         <v>0</v>
       </c>
-      <c r="BZ23">
+      <c r="BZ23" s="9">
         <v>0.46820410665032097</v>
       </c>
-      <c r="CA23">
+      <c r="CA23" s="9">
         <v>2.6438101487314E-2</v>
       </c>
-      <c r="CB23">
+      <c r="CB23" s="9">
         <v>0</v>
       </c>
-      <c r="CC23">
+      <c r="CC23" s="9">
         <v>0.12382464281353001</v>
       </c>
-      <c r="CD23">
+      <c r="CD23" s="9">
         <v>0.146934060181591</v>
       </c>
-      <c r="CE23">
+      <c r="CE23" s="9">
         <v>0.21199391750617699</v>
       </c>
       <c r="CG23">
@@ -36020,79 +36416,79 @@
       <c r="BF24" t="s">
         <v>61</v>
       </c>
-      <c r="BG24">
+      <c r="BG24" s="9">
         <v>4.2869433105745799E-2</v>
       </c>
-      <c r="BH24">
+      <c r="BH24" s="9">
         <v>0</v>
       </c>
-      <c r="BI24">
+      <c r="BI24" s="9">
         <v>0.102321137702042</v>
       </c>
-      <c r="BJ24">
+      <c r="BJ24" s="9">
         <v>0.173465093180249</v>
       </c>
-      <c r="BK24">
+      <c r="BK24" s="9">
         <v>5.9151671825572301E-2</v>
       </c>
-      <c r="BL24">
+      <c r="BL24" s="9">
         <v>0.22203004855279301</v>
       </c>
-      <c r="BM24">
+      <c r="BM24" s="9">
         <v>0.113548810613782</v>
       </c>
-      <c r="BN24">
+      <c r="BN24" s="9">
         <v>4.3380458344126099E-2</v>
       </c>
-      <c r="BO24">
+      <c r="BO24" s="9">
         <v>0</v>
       </c>
-      <c r="BP24">
+      <c r="BP24" s="9">
         <v>0</v>
       </c>
-      <c r="BQ24" s="1">
+      <c r="BQ24" s="9">
         <v>4.1167510600633898E-5</v>
       </c>
-      <c r="BR24" s="1">
+      <c r="BR24" s="9">
         <v>1.49945269976458E-5</v>
       </c>
-      <c r="BS24">
+      <c r="BS24" s="9">
         <v>0.22567394726485601</v>
       </c>
-      <c r="BT24">
+      <c r="BT24" s="9">
         <v>3.4061310358645498E-3</v>
       </c>
-      <c r="BU24">
+      <c r="BU24" s="9">
         <v>5.43241574311807E-2</v>
       </c>
-      <c r="BV24">
+      <c r="BV24" s="9">
         <v>0</v>
       </c>
-      <c r="BW24">
+      <c r="BW24" s="9">
         <v>5.48411834994917E-2</v>
       </c>
-      <c r="BX24">
+      <c r="BX24" s="9">
         <v>0</v>
       </c>
-      <c r="BY24">
+      <c r="BY24" s="9">
         <v>0</v>
       </c>
-      <c r="BZ24">
+      <c r="BZ24" s="9">
         <v>3.3685769741546599E-2</v>
       </c>
-      <c r="CA24">
+      <c r="CA24" s="9">
         <v>0</v>
       </c>
-      <c r="CB24">
+      <c r="CB24" s="9">
         <v>0</v>
       </c>
-      <c r="CC24">
+      <c r="CC24" s="9">
         <v>0</v>
       </c>
-      <c r="CD24" s="1">
+      <c r="CD24" s="9">
         <v>3.6101734688351699E-5</v>
       </c>
-      <c r="CE24">
+      <c r="CE24" s="9">
         <v>0</v>
       </c>
       <c r="CG24">
@@ -36112,79 +36508,79 @@
       <c r="BF25" t="s">
         <v>62</v>
       </c>
-      <c r="BG25">
+      <c r="BG25" s="9">
         <v>0</v>
       </c>
-      <c r="BH25">
+      <c r="BH25" s="9">
         <v>0</v>
       </c>
-      <c r="BI25">
+      <c r="BI25" s="9">
         <v>0</v>
       </c>
-      <c r="BJ25">
+      <c r="BJ25" s="9">
         <v>9.4274507163179005E-2</v>
       </c>
-      <c r="BK25">
+      <c r="BK25" s="9">
         <v>0.118813565087247</v>
       </c>
-      <c r="BL25">
+      <c r="BL25" s="9">
         <v>0.30186084310987898</v>
       </c>
-      <c r="BM25">
+      <c r="BM25" s="9">
         <v>3.9162506262200497E-2</v>
       </c>
-      <c r="BN25">
+      <c r="BN25" s="9">
         <v>1.39875393655164E-2</v>
       </c>
-      <c r="BO25">
+      <c r="BO25" s="9">
         <v>0</v>
       </c>
-      <c r="BP25">
+      <c r="BP25" s="9">
         <v>0</v>
       </c>
-      <c r="BQ25">
+      <c r="BQ25" s="9">
         <v>0</v>
       </c>
-      <c r="BR25">
+      <c r="BR25" s="9">
         <v>0</v>
       </c>
-      <c r="BS25">
+      <c r="BS25" s="9">
         <v>0</v>
       </c>
-      <c r="BT25">
+      <c r="BT25" s="9">
         <v>0</v>
       </c>
-      <c r="BU25">
+      <c r="BU25" s="9">
         <v>0</v>
       </c>
-      <c r="BV25">
+      <c r="BV25" s="9">
         <v>0</v>
       </c>
-      <c r="BW25">
+      <c r="BW25" s="9">
         <v>0</v>
       </c>
-      <c r="BX25">
+      <c r="BX25" s="9">
         <v>0</v>
       </c>
-      <c r="BY25">
+      <c r="BY25" s="9">
         <v>0</v>
       </c>
-      <c r="BZ25">
+      <c r="BZ25" s="9">
         <v>1.53233220962304E-4</v>
       </c>
-      <c r="CA25">
+      <c r="CA25" s="9">
         <v>0</v>
       </c>
-      <c r="CB25">
+      <c r="CB25" s="9">
         <v>0</v>
       </c>
-      <c r="CC25">
+      <c r="CC25" s="9">
         <v>0</v>
       </c>
-      <c r="CD25">
+      <c r="CD25" s="9">
         <v>0</v>
       </c>
-      <c r="CE25">
+      <c r="CE25" s="9">
         <v>0</v>
       </c>
       <c r="CG25">
@@ -36204,79 +36600,79 @@
       <c r="BF26" t="s">
         <v>55</v>
       </c>
-      <c r="BG26">
+      <c r="BG26" s="9">
         <v>0</v>
       </c>
-      <c r="BH26">
+      <c r="BH26" s="9">
         <v>0</v>
       </c>
-      <c r="BI26">
+      <c r="BI26" s="9">
         <v>0</v>
       </c>
-      <c r="BJ26">
+      <c r="BJ26" s="9">
         <v>0</v>
       </c>
-      <c r="BK26">
+      <c r="BK26" s="9">
         <v>1.08677165889996E-2</v>
       </c>
-      <c r="BL26">
+      <c r="BL26" s="9">
         <v>2.3547062868574001E-2</v>
       </c>
-      <c r="BM26">
+      <c r="BM26" s="9">
         <v>0</v>
       </c>
-      <c r="BN26">
+      <c r="BN26" s="9">
         <v>0</v>
       </c>
-      <c r="BO26">
+      <c r="BO26" s="9">
         <v>0</v>
       </c>
-      <c r="BP26">
+      <c r="BP26" s="9">
         <v>0</v>
       </c>
-      <c r="BQ26">
+      <c r="BQ26" s="9">
         <v>0</v>
       </c>
-      <c r="BR26">
+      <c r="BR26" s="9">
         <v>0</v>
       </c>
-      <c r="BS26">
+      <c r="BS26" s="9">
         <v>0</v>
       </c>
-      <c r="BT26">
+      <c r="BT26" s="9">
         <v>0</v>
       </c>
-      <c r="BU26">
+      <c r="BU26" s="9">
         <v>0</v>
       </c>
-      <c r="BV26">
+      <c r="BV26" s="9">
         <v>0</v>
       </c>
-      <c r="BW26">
+      <c r="BW26" s="9">
         <v>0</v>
       </c>
-      <c r="BX26">
+      <c r="BX26" s="9">
         <v>0</v>
       </c>
-      <c r="BY26">
+      <c r="BY26" s="9">
         <v>0</v>
       </c>
-      <c r="BZ26">
+      <c r="BZ26" s="9">
         <v>6.02717335785064E-3</v>
       </c>
-      <c r="CA26">
+      <c r="CA26" s="9">
         <v>0</v>
       </c>
-      <c r="CB26">
+      <c r="CB26" s="9">
         <v>0</v>
       </c>
-      <c r="CC26">
+      <c r="CC26" s="9">
         <v>0</v>
       </c>
-      <c r="CD26">
+      <c r="CD26" s="9">
         <v>0</v>
       </c>
-      <c r="CE26">
+      <c r="CE26" s="9">
         <v>0</v>
       </c>
       <c r="CG26">
@@ -36296,79 +36692,79 @@
       <c r="BF27" t="s">
         <v>54</v>
       </c>
-      <c r="BG27">
+      <c r="BG27" s="9">
         <v>0</v>
       </c>
-      <c r="BH27">
+      <c r="BH27" s="9">
         <v>0</v>
       </c>
-      <c r="BI27">
+      <c r="BI27" s="9">
         <v>0</v>
       </c>
-      <c r="BJ27">
+      <c r="BJ27" s="9">
         <v>0</v>
       </c>
-      <c r="BK27">
+      <c r="BK27" s="9">
         <v>0</v>
       </c>
-      <c r="BL27">
+      <c r="BL27" s="9">
         <v>0</v>
       </c>
-      <c r="BM27">
+      <c r="BM27" s="9">
         <v>0</v>
       </c>
-      <c r="BN27">
+      <c r="BN27" s="9">
         <v>0</v>
       </c>
-      <c r="BO27">
+      <c r="BO27" s="9">
         <v>0</v>
       </c>
-      <c r="BP27">
+      <c r="BP27" s="9">
         <v>0</v>
       </c>
-      <c r="BQ27">
+      <c r="BQ27" s="9">
         <v>0</v>
       </c>
-      <c r="BR27">
+      <c r="BR27" s="9">
         <v>0</v>
       </c>
-      <c r="BS27">
+      <c r="BS27" s="9">
         <v>0</v>
       </c>
-      <c r="BT27">
+      <c r="BT27" s="9">
         <v>0</v>
       </c>
-      <c r="BU27">
+      <c r="BU27" s="9">
         <v>0</v>
       </c>
-      <c r="BV27">
+      <c r="BV27" s="9">
         <v>0</v>
       </c>
-      <c r="BW27">
+      <c r="BW27" s="9">
         <v>0</v>
       </c>
-      <c r="BX27">
+      <c r="BX27" s="9">
         <v>0</v>
       </c>
-      <c r="BY27">
+      <c r="BY27" s="9">
         <v>0</v>
       </c>
-      <c r="BZ27">
+      <c r="BZ27" s="9">
         <v>0</v>
       </c>
-      <c r="CA27">
+      <c r="CA27" s="9">
         <v>0</v>
       </c>
-      <c r="CB27">
+      <c r="CB27" s="9">
         <v>0</v>
       </c>
-      <c r="CC27">
+      <c r="CC27" s="9">
         <v>0</v>
       </c>
-      <c r="CD27">
+      <c r="CD27" s="9">
         <v>0</v>
       </c>
-      <c r="CE27">
+      <c r="CE27" s="9">
         <v>0</v>
       </c>
       <c r="CG27">
@@ -36397,8 +36793,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BF1:DD11">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="BF17:CE27">
+    <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -36409,8 +36805,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BF17:CE27">
-    <cfRule type="colorScale" priority="34">
+  <conditionalFormatting sqref="BF1:DD11">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -36911,166 +37307,166 @@
       <c r="A4" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>0.15178195530010399</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>0.30530285003020202</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>0.37045950383482101</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>0.41566766379523601</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>0.108069164265129</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>0.118374890364615</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <v>0.19615831383310001</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="2">
         <v>0.26033231763775</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="2">
         <v>0.25801898023742298</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="2">
         <v>0.35149154733154098</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="2">
         <v>6.0388839108962401E-2</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M4" s="2">
         <v>4.9990622851069998E-2</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4" s="2">
         <v>0.19373952700951799</v>
       </c>
-      <c r="O4" s="3">
+      <c r="O4" s="2">
         <v>0.16620311987147299</v>
       </c>
-      <c r="P4" s="3">
+      <c r="P4" s="2">
         <v>0.17664380853703401</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="Q4" s="2">
         <v>0.46040272116262898</v>
       </c>
-      <c r="R4" s="3">
+      <c r="R4" s="2">
         <v>0.62544589774078396</v>
       </c>
-      <c r="S4" s="3">
+      <c r="S4" s="2">
         <v>0.92503070115592201</v>
       </c>
-      <c r="T4" s="3">
+      <c r="T4" s="2">
         <v>0.65381430779421501</v>
       </c>
-      <c r="U4" s="3">
+      <c r="U4" s="2">
         <v>0.38024398321925301</v>
       </c>
-      <c r="V4" s="3">
+      <c r="V4" s="2">
         <v>5.6131900703964399E-2</v>
       </c>
-      <c r="W4" s="3">
+      <c r="W4" s="2">
         <v>0.22852085134411901</v>
       </c>
-      <c r="X4" s="3">
+      <c r="X4" s="2">
         <v>0.42654930950203102</v>
       </c>
-      <c r="Y4" s="3">
+      <c r="Y4" s="2">
         <v>0.44551738615405301</v>
       </c>
-      <c r="Z4" s="3">
+      <c r="Z4" s="2">
         <v>0.16135379771743399</v>
       </c>
-      <c r="AA4" s="3">
+      <c r="AA4" s="2">
         <v>0.13474025974025899</v>
       </c>
-      <c r="AB4" s="3">
+      <c r="AB4" s="2">
         <v>0.22689932788109499</v>
       </c>
-      <c r="AC4" s="3">
+      <c r="AC4" s="2">
         <v>0.433489371778291</v>
       </c>
-      <c r="AD4" s="3">
+      <c r="AD4" s="2">
         <v>0.15010237576781801</v>
       </c>
-      <c r="AE4" s="3">
+      <c r="AE4" s="2">
         <v>0.163606227046702</v>
       </c>
-      <c r="AF4" s="3">
+      <c r="AF4" s="2">
         <v>7.3175812919914499E-2</v>
       </c>
-      <c r="AG4" s="3">
+      <c r="AG4" s="2">
         <v>0.35603548549504299</v>
       </c>
-      <c r="AH4" s="3">
+      <c r="AH4" s="2">
         <v>7.6367462681243406E-2</v>
       </c>
-      <c r="AI4" s="3">
+      <c r="AI4" s="2">
         <v>0.17344081610814799</v>
       </c>
-      <c r="AJ4" s="3">
+      <c r="AJ4" s="2">
         <v>0.42456131388725699</v>
       </c>
-      <c r="AK4" s="3">
+      <c r="AK4" s="2">
         <v>0.64189931291665603</v>
       </c>
-      <c r="AL4" s="3">
+      <c r="AL4" s="2">
         <v>0.78515248092161005</v>
       </c>
-      <c r="AM4" s="3">
+      <c r="AM4" s="2">
         <v>0.96657992456360897</v>
       </c>
-      <c r="AN4" s="3">
+      <c r="AN4" s="2">
         <v>7.8608642353662203E-2</v>
       </c>
-      <c r="AO4" s="3">
+      <c r="AO4" s="2">
         <v>0.140770252324037</v>
       </c>
-      <c r="AP4" s="3">
+      <c r="AP4" s="2">
         <v>0.33051727909011303</v>
       </c>
-      <c r="AQ4" s="3">
+      <c r="AQ4" s="2">
         <v>0.46855861767279</v>
       </c>
-      <c r="AR4" s="3">
+      <c r="AR4" s="2">
         <v>7.3467054171232504E-2</v>
       </c>
-      <c r="AS4" s="3">
+      <c r="AS4" s="2">
         <v>0.48196674448520599</v>
       </c>
-      <c r="AT4" s="3">
+      <c r="AT4" s="2">
         <v>6.8042496031261404E-2</v>
       </c>
-      <c r="AU4" s="3">
+      <c r="AU4" s="2">
         <v>0.33659787519843598</v>
       </c>
-      <c r="AV4" s="3">
+      <c r="AV4" s="2">
         <v>3.9621653820466E-2</v>
       </c>
-      <c r="AW4" s="3">
+      <c r="AW4" s="2">
         <v>0.55623747721077998</v>
       </c>
-      <c r="AX4" s="3">
+      <c r="AX4" s="2">
         <v>8.2455806880821103E-2</v>
       </c>
-      <c r="AY4" s="5">
+      <c r="AY4" s="4">
         <v>0.27099410758410902</v>
       </c>
     </row>
     <row r="8" spans="1:51" x14ac:dyDescent="0.35">
-      <c r="I8" s="6"/>
-      <c r="U8" s="6"/>
-      <c r="W8" s="6"/>
+      <c r="I8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="W8" s="5"/>
     </row>
     <row r="9" spans="1:51" x14ac:dyDescent="0.35">
-      <c r="I9" s="6"/>
-      <c r="U9" s="6"/>
-      <c r="W9" s="6"/>
+      <c r="I9" s="5"/>
+      <c r="U9" s="5"/>
+      <c r="W9" s="5"/>
     </row>
     <row r="10" spans="1:51" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
@@ -37265,13 +37661,13 @@
       </c>
     </row>
     <row r="13" spans="1:51" x14ac:dyDescent="0.35">
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="U13" s="6" t="s">
+      <c r="U13" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="X13" s="6" t="s">
+      <c r="X13" s="5" t="s">
         <v>96</v>
       </c>
     </row>
@@ -37279,21 +37675,21 @@
       <c r="H14" t="s">
         <v>101</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="5">
         <f>AVERAGE(B11:I11)</f>
         <v>0.79735231488669767</v>
       </c>
       <c r="T14" t="s">
         <v>101</v>
       </c>
-      <c r="U14" s="6">
+      <c r="U14" s="5">
         <f>AVERAGE(J11:U11)</f>
         <v>0.71476217040747125</v>
       </c>
       <c r="W14" t="s">
         <v>101</v>
       </c>
-      <c r="X14" s="6">
+      <c r="X14" s="5">
         <f>AVERAGE(I14,U14)</f>
         <v>0.7560572426470844</v>
       </c>
@@ -37302,21 +37698,21 @@
       <c r="H15" t="s">
         <v>102</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="5">
         <f>AVERAGE(B12:I12)</f>
         <v>0.78931812098923593</v>
       </c>
       <c r="T15" t="s">
         <v>102</v>
       </c>
-      <c r="U15" s="6">
+      <c r="U15" s="5">
         <f>AVERAGE(J12:U12)</f>
         <v>0.6377205946722514</v>
       </c>
       <c r="W15" t="s">
         <v>102</v>
       </c>
-      <c r="X15" s="6">
+      <c r="X15" s="5">
         <f>AVERAGE(I15,U15)</f>
         <v>0.71351935783074372</v>
       </c>
@@ -37422,10 +37818,10 @@
       <c r="AA1" t="s">
         <v>36</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="5" t="s">
         <v>38</v>
       </c>
       <c r="AD1" t="s">
@@ -37469,381 +37865,376 @@
       <c r="A2" t="s">
         <v>51</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="9">
         <v>0.47961134477407102</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="9">
         <v>0.241717460246058</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="9">
         <v>0.74818318506452797</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="9">
         <v>0.48646786117027901</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="9">
         <v>0.66684062557869395</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="9">
         <v>0.52275214221982702</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="9">
         <v>0.43899452362325198</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="9">
         <v>0.35996122317085599</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="9">
         <v>0.92854612515368096</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="9">
         <v>0.826293525599616</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="9">
         <v>0.695354742861091</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="9">
         <v>0.56917788104410305</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="9">
         <v>0.116140428350629</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="9">
         <v>9.9939280194303301E-2</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="9">
         <v>0.60213659380017204</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="9">
         <v>7.1466798402700593E-2</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="9">
         <v>0.43328185212397402</v>
       </c>
-      <c r="S2">
+      <c r="S2" s="9">
         <v>0.212697365461606</v>
       </c>
-      <c r="T2">
+      <c r="T2" s="9">
         <v>0.79845533254624101</v>
       </c>
-      <c r="U2">
+      <c r="U2" s="9">
         <v>0.60706906729634003</v>
       </c>
-      <c r="V2">
+      <c r="V2" s="9">
         <v>0.63778406624884898</v>
       </c>
-      <c r="W2">
+      <c r="W2" s="9">
         <v>2.68918942379472E-2</v>
       </c>
-      <c r="X2">
+      <c r="X2" s="9">
         <v>0.71398762283533301</v>
       </c>
-      <c r="Y2">
+      <c r="Y2" s="9">
         <v>0.28492447076028599</v>
       </c>
-      <c r="Z2">
+      <c r="Z2" s="9">
         <v>0.35741104952619301</v>
       </c>
-      <c r="AA2">
+      <c r="AA2" s="9">
         <v>7.0496283619830902E-2</v>
       </c>
-      <c r="AB2">
+      <c r="AB2" s="11">
         <v>6.3156048068769899E-2</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="11">
         <v>0</v>
       </c>
-      <c r="AD2">
+      <c r="AD2" s="9">
         <v>0.69235877004801305</v>
       </c>
-      <c r="AE2">
+      <c r="AE2" s="9">
         <v>0.50807028297068102</v>
       </c>
-      <c r="AF2">
+      <c r="AF2" s="9">
         <v>0.32977909011373502</v>
       </c>
-      <c r="AG2">
+      <c r="AG2" s="9">
         <v>2.6438101487314E-2</v>
       </c>
-      <c r="AH2">
+      <c r="AH2" s="9">
         <v>0.21420744199342501</v>
       </c>
-      <c r="AI2">
+      <c r="AI2" s="9">
         <v>0</v>
       </c>
-      <c r="AJ2">
+      <c r="AJ2" s="9">
         <v>0.72785443888142598</v>
       </c>
-      <c r="AK2">
+      <c r="AK2" s="9">
         <v>0.12382464281353001</v>
       </c>
-      <c r="AL2">
+      <c r="AL2" s="9">
         <v>0.69873102402570397</v>
       </c>
-      <c r="AM2">
+      <c r="AM2" s="9">
         <v>0.14697016191628001</v>
       </c>
-      <c r="AN2">
+      <c r="AN2" s="9">
         <v>0.55135905721345702</v>
       </c>
-      <c r="AO2">
+      <c r="AO2" s="9">
         <v>0.21199391750617699</v>
       </c>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="13">
         <v>0.14992915139110599</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="13">
         <v>0.24365173972695101</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="13">
         <v>0.143731988472622</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="13">
         <v>0.39512592406966501</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="13">
         <v>0.13700106058820499</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="13">
         <v>0.21691554014242101</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="13">
         <v>0.30067349229565599</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="13">
         <v>0.28138712201095201</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="13">
         <v>1.1044197628623201E-2</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="13">
         <v>0.123424118027047</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="13">
         <v>0.110888455093544</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="13">
         <v>0.255929656054036</v>
       </c>
-      <c r="N3" s="3">
+      <c r="N3" s="13">
         <v>0.22885846765290299</v>
       </c>
-      <c r="O3" s="3">
+      <c r="O3" s="13">
         <v>0.22656767498343999</v>
       </c>
-      <c r="P3" s="3">
+      <c r="P3" s="13">
         <v>0.34173150549586201</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="Q3" s="13">
         <v>0.68852661479560295</v>
       </c>
-      <c r="R3" s="3">
+      <c r="R3" s="13">
         <v>0.132581607713184</v>
       </c>
-      <c r="S3" s="3">
+      <c r="S3" s="13">
         <v>0.326925672129672</v>
       </c>
-      <c r="T3" s="3">
+      <c r="T3" s="13">
         <v>4.01908697363242E-2</v>
       </c>
-      <c r="U3" s="3">
+      <c r="U3" s="13">
         <v>0.25819067296339998</v>
       </c>
-      <c r="V3" s="3">
+      <c r="V3" s="13">
         <v>0.28904012083123498</v>
       </c>
-      <c r="W3" s="3">
+      <c r="W3" s="13">
         <v>0.27978680925678301</v>
       </c>
-      <c r="X3" s="3">
+      <c r="X3" s="13">
         <v>0.20964491448342201</v>
       </c>
-      <c r="Y3" s="3">
+      <c r="Y3" s="13">
         <v>0.52822314565461603</v>
       </c>
-      <c r="Z3" s="3">
+      <c r="Z3" s="13">
         <v>0.218027636586549</v>
       </c>
-      <c r="AA3" s="3">
+      <c r="AA3" s="13">
         <v>0.13473474496181401</v>
       </c>
-      <c r="AB3" s="3">
+      <c r="AB3" s="17">
         <v>0.15169147100961899</v>
       </c>
-      <c r="AC3" s="3">
+      <c r="AC3" s="17">
         <v>1.33621823923277E-2</v>
       </c>
-      <c r="AD3" s="3">
+      <c r="AD3" s="13">
         <v>0.22900704872816399</v>
       </c>
-      <c r="AE3" s="3">
+      <c r="AE3" s="13">
         <v>0.35110838696496</v>
       </c>
-      <c r="AF3" s="3">
+      <c r="AF3" s="13">
         <v>0.33970363079615001</v>
       </c>
-      <c r="AG3" s="3">
+      <c r="AG3" s="13">
         <v>0.473507217847769</v>
       </c>
-      <c r="AH3" s="3">
+      <c r="AH3" s="13">
         <v>0.71232550383534199</v>
       </c>
-      <c r="AI3" s="3">
+      <c r="AI3" s="13">
         <v>0.51803325551479296</v>
       </c>
-      <c r="AJ3" s="3">
+      <c r="AJ3" s="13">
         <v>0.20410306508731199</v>
       </c>
-      <c r="AK3" s="3">
+      <c r="AK3" s="13">
         <v>0.53185981194285004</v>
       </c>
-      <c r="AL3" s="3">
+      <c r="AL3" s="13">
         <v>0.26164732215382902</v>
       </c>
-      <c r="AM3" s="3">
+      <c r="AM3" s="13">
         <v>0.28960811566995698</v>
       </c>
-      <c r="AN3" s="3">
+      <c r="AN3" s="13">
         <v>0.36618513590572099</v>
       </c>
-      <c r="AO3" s="5">
+      <c r="AO3" s="14">
         <v>0.50058924158905105</v>
       </c>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="15">
         <v>0.37045950383482101</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="15">
         <v>0.41566766379523601</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="15">
         <v>0.108069164265129</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="15">
         <v>0.118374890364615</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="15">
         <v>0.19615831383310001</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="15">
         <v>0.26033231763775</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="15">
         <v>0.25801898023742298</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="15">
         <v>0.35149154733154098</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4" s="15">
         <v>6.0388839108962401E-2</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4" s="15">
         <v>4.9990622851069998E-2</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L4" s="15">
         <v>0.19373952700951799</v>
       </c>
-      <c r="M4" s="8">
+      <c r="M4" s="15">
         <v>0.16620311987147299</v>
       </c>
-      <c r="N4" s="8">
+      <c r="N4" s="15">
         <v>0.65381430779421501</v>
       </c>
-      <c r="O4" s="8">
+      <c r="O4" s="15">
         <v>0.38024398321925301</v>
       </c>
-      <c r="P4" s="8">
+      <c r="P4" s="15">
         <v>5.6131900703964399E-2</v>
       </c>
-      <c r="Q4" s="8">
+      <c r="Q4" s="15">
         <v>0.22852085134411901</v>
       </c>
-      <c r="R4" s="8">
+      <c r="R4" s="15">
         <v>0.42654930950203102</v>
       </c>
-      <c r="S4" s="8">
+      <c r="S4" s="15">
         <v>0.44551738615405301</v>
       </c>
-      <c r="T4" s="8">
+      <c r="T4" s="15">
         <v>0.16135379771743399</v>
       </c>
-      <c r="U4" s="8">
+      <c r="U4" s="15">
         <v>0.13474025974025899</v>
       </c>
-      <c r="V4" s="8">
+      <c r="V4" s="15">
         <v>7.3175812919914499E-2</v>
       </c>
-      <c r="W4" s="8">
+      <c r="W4" s="15">
         <v>0.35603548549504299</v>
       </c>
-      <c r="X4" s="8">
+      <c r="X4" s="15">
         <v>7.6367462681243406E-2</v>
       </c>
-      <c r="Y4" s="8">
+      <c r="Y4" s="15">
         <v>0.17344081610814799</v>
       </c>
-      <c r="Z4" s="8">
+      <c r="Z4" s="15">
         <v>0.42456131388725699</v>
       </c>
-      <c r="AA4" s="8">
+      <c r="AA4" s="15">
         <v>0.64189931291665603</v>
       </c>
-      <c r="AB4" s="8">
+      <c r="AB4" s="18">
         <v>0.78515248092161005</v>
       </c>
-      <c r="AC4" s="8">
+      <c r="AC4" s="18">
         <v>0.96657992456360897</v>
       </c>
-      <c r="AD4" s="8">
+      <c r="AD4" s="15">
         <v>7.8608642353662203E-2</v>
       </c>
-      <c r="AE4" s="8">
+      <c r="AE4" s="15">
         <v>0.140770252324037</v>
       </c>
-      <c r="AF4" s="8">
+      <c r="AF4" s="15">
         <v>0.33051727909011303</v>
       </c>
-      <c r="AG4" s="8">
+      <c r="AG4" s="15">
         <v>0.46855861767279</v>
       </c>
-      <c r="AH4" s="8">
+      <c r="AH4" s="15">
         <v>7.3467054171232504E-2</v>
       </c>
-      <c r="AI4" s="8">
+      <c r="AI4" s="15">
         <v>0.48196674448520599</v>
       </c>
-      <c r="AJ4" s="8">
+      <c r="AJ4" s="15">
         <v>6.8042496031261404E-2</v>
       </c>
-      <c r="AK4" s="8">
+      <c r="AK4" s="15">
         <v>0.33659787519843598</v>
       </c>
-      <c r="AL4" s="8">
+      <c r="AL4" s="15">
         <v>3.9621653820466E-2</v>
       </c>
-      <c r="AM4" s="8">
+      <c r="AM4" s="15">
         <v>0.55623747721077998</v>
       </c>
-      <c r="AN4" s="8">
+      <c r="AN4" s="15">
         <v>8.2455806880821103E-2</v>
       </c>
-      <c r="AO4" s="9">
+      <c r="AO4" s="16">
         <v>0.27099410758410902</v>
       </c>
-    </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.35">
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
@@ -37852,9 +38243,6 @@
       <c r="B9" t="s">
         <v>109</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
@@ -37869,25 +38257,25 @@
       <c r="E10" t="s">
         <v>76</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" t="s">
         <v>77</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" t="s">
         <v>78</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="7" t="s">
         <v>79</v>
       </c>
       <c r="I10" t="s">
         <v>80</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J10" t="s">
         <v>81</v>
       </c>
       <c r="K10" t="s">
         <v>82</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" s="7" t="s">
         <v>83</v>
       </c>
       <c r="M10" t="s">
@@ -37896,16 +38284,16 @@
       <c r="N10" t="s">
         <v>85</v>
       </c>
-      <c r="O10" t="s">
+      <c r="O10" s="5" t="s">
         <v>86</v>
       </c>
       <c r="P10" t="s">
         <v>87</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="Q10" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="R10" t="s">
+      <c r="R10" s="7" t="s">
         <v>89</v>
       </c>
       <c r="S10" t="s">
@@ -37914,7 +38302,7 @@
       <c r="T10" t="s">
         <v>91</v>
       </c>
-      <c r="U10" t="s">
+      <c r="U10" s="7" t="s">
         <v>92</v>
       </c>
     </row>
@@ -37922,140 +38310,146 @@
       <c r="A11" t="s">
         <v>93</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="9">
         <v>0.86276146222643102</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="9">
         <v>0.74074689803015803</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="9">
         <v>0.85054928065416602</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="9">
         <v>0.81632449232768201</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="9">
         <v>0.79085038760443604</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="9">
         <v>0.77813793483798299</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="10">
         <v>0.83075341522976798</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="9">
         <v>0.70869464818295702</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="9">
         <v>0.81491130084522601</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="9">
         <v>0.86785674397944002</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="10">
         <v>0.519005742862511</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="9">
         <v>0.69025879886924402</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="9">
         <v>0.65165587962521498</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="11">
         <v>0.44824897491003401</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="9">
         <v>0.81223262502022398</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="12">
         <v>0.83410906420998399</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="10">
         <v>0.64685998237570397</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="9">
         <v>0.73227374615366603</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="9">
         <v>0.699216950339417</v>
       </c>
-      <c r="U11">
+      <c r="U11" s="10">
         <v>0.86051623569899005</v>
+      </c>
+      <c r="V11" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>94</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="9">
         <v>0.87329151349427903</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="9">
         <v>0.80176934340182004</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="9">
         <v>0.83605197895137695</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="9">
         <v>0.81975662023687002</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="9">
         <v>0.86323686557894896</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="9">
         <v>0.812628478806532</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="10">
         <v>0.82802463353703104</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="9">
         <v>0.70195784309208198</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="9">
         <v>0.91350308651576595</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="9">
         <v>0.94134455317763999</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="10">
         <v>0.52561884851548002</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="9">
         <v>0.67635327187948402</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="9">
         <v>0.55221033836424405</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="11">
         <v>0.11462415329616001</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="9">
         <v>0.79259398999524699</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="12">
         <v>0.85806510180867501</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="10">
         <v>0.61135885828034597</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="9">
         <v>0.71711677060452805</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="9">
         <v>0.66093441773720096</v>
       </c>
-      <c r="U12">
+      <c r="U12" s="10">
         <v>0.81024684304642902</v>
+      </c>
+      <c r="V12" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.35">
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="U13" s="6" t="s">
+      <c r="U13" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="X13" s="6" t="s">
+      <c r="X13" s="5" t="s">
         <v>96</v>
       </c>
     </row>
@@ -38063,21 +38457,21 @@
       <c r="H14" t="s">
         <v>101</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="5">
         <f>AVERAGE(B11:I11)</f>
         <v>0.79735231488669767</v>
       </c>
       <c r="T14" t="s">
         <v>101</v>
       </c>
-      <c r="U14" s="6">
+      <c r="U14" s="5">
         <f>AVERAGE(J11:U11)</f>
         <v>0.71476217040747125</v>
       </c>
       <c r="W14" t="s">
         <v>101</v>
       </c>
-      <c r="X14" s="6">
+      <c r="X14" s="5">
         <f>AVERAGE(I14,U14)</f>
         <v>0.7560572426470844</v>
       </c>
@@ -38086,21 +38480,21 @@
       <c r="H15" t="s">
         <v>102</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="5">
         <f>AVERAGE(B12:I12)</f>
         <v>0.81708965963736746</v>
       </c>
       <c r="T15" t="s">
         <v>102</v>
       </c>
-      <c r="U15" s="6">
+      <c r="U15" s="5">
         <f>AVERAGE(J12:U12)</f>
         <v>0.68116418610176666</v>
       </c>
       <c r="W15" t="s">
         <v>102</v>
       </c>
-      <c r="X15" s="6">
+      <c r="X15" s="5">
         <f>AVERAGE(I15,U15)</f>
         <v>0.74912692286956706</v>
       </c>
@@ -38138,10 +38532,10 @@
       <c r="G1" t="s">
         <v>78</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>80</v>
       </c>
       <c r="J1" t="s">
@@ -38203,10 +38597,10 @@
       <c r="G2">
         <v>0.78505091998955501</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="5">
         <v>-0.33398042471309602</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="5">
         <v>2.2800072977221301E-2</v>
       </c>
       <c r="J2">
@@ -38268,10 +38662,10 @@
       <c r="G3">
         <v>0.83794847262402505</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <v>0.832584473541637</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="5">
         <v>0.64171827186225805</v>
       </c>
       <c r="J3">
@@ -38289,7 +38683,7 @@
       <c r="N3">
         <v>0.44227699763089001</v>
       </c>
-      <c r="O3" s="6">
+      <c r="O3" s="5">
         <v>0.106638622511867</v>
       </c>
       <c r="P3">
@@ -39229,10 +39623,10 @@
       <c r="G6" t="s">
         <v>78</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" t="s">
         <v>79</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" t="s">
         <v>80</v>
       </c>
       <c r="J6" t="s">
@@ -39241,31 +39635,31 @@
       <c r="K6" t="s">
         <v>82</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L6" s="5" t="s">
         <v>83</v>
       </c>
       <c r="M6" t="s">
         <v>84</v>
       </c>
-      <c r="N6" s="6" t="s">
+      <c r="N6" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="O6" t="s">
         <v>86</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="P6" t="s">
         <v>87</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="Q6" t="s">
         <v>88</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="R6" t="s">
         <v>89</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="S6" t="s">
         <v>90</v>
       </c>
-      <c r="T6" s="2" t="s">
+      <c r="T6" t="s">
         <v>91</v>
       </c>
       <c r="U6" t="s">
@@ -39291,10 +39685,10 @@
       <c r="G7">
         <v>0.83649993459370497</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7">
         <v>0.85515778133937703</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7">
         <v>0.68241308726725503</v>
       </c>
       <c r="J7">
@@ -39303,61 +39697,55 @@
       <c r="K7">
         <v>0.929829114228505</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="5">
         <v>0.48798560027497401</v>
       </c>
       <c r="M7">
         <v>0.644813503873365</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="5">
         <v>0.53651404360751698</v>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2">
+      <c r="P7">
         <v>0.79008838992736796</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7">
         <v>0.84159119342196398</v>
       </c>
-      <c r="R7" s="2">
+      <c r="R7">
         <v>0.61135885828034597</v>
       </c>
-      <c r="S7" s="2">
+      <c r="S7">
         <v>0.71203412957918499</v>
       </c>
-      <c r="T7" s="2">
+      <c r="T7">
         <v>0.657101505866444</v>
       </c>
       <c r="U7">
         <v>0.77887246177411396</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.35">
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="L8" s="2"/>
-    </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.35">
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="U9" s="6" t="s">
+      <c r="U9" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="W9" s="6" t="s">
+      <c r="W9" s="5" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.35">
-      <c r="I10" s="6">
+      <c r="I10" s="5">
         <f>AVERAGE(B7:I7)</f>
         <v>0.80998678629615406</v>
       </c>
-      <c r="U10" s="6">
+      <c r="U10" s="5">
         <f>AVERAGE(J7:U7)</f>
         <v>0.71687788941630504</v>
       </c>
-      <c r="W10" s="6">
+      <c r="W10" s="5">
         <f>AVERAGE(I10,U10)</f>
         <v>0.76343233785622955</v>
       </c>
@@ -39373,12 +39761,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20C27C4F-7112-48CC-8600-645EA3A54793}">
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="8" max="9" width="8.7265625" style="2"/>
-    <col min="12" max="12" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.35">
@@ -39400,10 +39786,10 @@
       <c r="G1" t="s">
         <v>78</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>79</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>80</v>
       </c>
       <c r="J1" t="s">
@@ -39412,31 +39798,31 @@
       <c r="K1" t="s">
         <v>82</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>83</v>
       </c>
       <c r="M1" t="s">
         <v>84</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" t="s">
         <v>86</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" t="s">
         <v>87</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" t="s">
         <v>88</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" t="s">
         <v>89</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" t="s">
         <v>90</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" t="s">
         <v>91</v>
       </c>
       <c r="U1" t="s">
@@ -39465,10 +39851,10 @@
       <c r="G2">
         <v>0.78505091998955501</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2">
         <v>-0.33398042471309602</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2">
         <v>2.2800072977221301E-2</v>
       </c>
       <c r="J2">
@@ -39477,31 +39863,31 @@
       <c r="K2">
         <v>0.86785674397944002</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="5">
         <v>-8.4598923649412197E-2</v>
       </c>
       <c r="M2">
         <v>0.21799042590743101</v>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="5">
         <v>-8.6805497576840196E-2</v>
       </c>
-      <c r="O2" s="2">
+      <c r="O2">
         <v>-9.8060428060056895E-2</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2">
         <v>0.29753922699669499</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2">
         <v>0.195374044392325</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2">
         <v>0.35849302300033697</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2">
         <v>-0.279845157467007</v>
       </c>
-      <c r="T2" s="2">
+      <c r="T2">
         <v>0.12539529152194401</v>
       </c>
       <c r="U2">
@@ -39530,10 +39916,10 @@
       <c r="G3">
         <v>0.83649993459370497</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3">
         <v>0.85515778133937703</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3">
         <v>0.68241308726725503</v>
       </c>
       <c r="J3">
@@ -39542,31 +39928,31 @@
       <c r="K3">
         <v>0.929829114228505</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="5">
         <v>0.48798560027497401</v>
       </c>
       <c r="M3">
         <v>0.644813503873365</v>
       </c>
-      <c r="N3" s="6">
+      <c r="N3" s="5">
         <v>0.53651404360751698</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3">
         <v>0.116225612867807</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3">
         <v>0.79008838992736796</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3">
         <v>0.84159119342196398</v>
       </c>
-      <c r="R3" s="2">
+      <c r="R3">
         <v>0.61135885828034597</v>
       </c>
-      <c r="S3" s="2">
+      <c r="S3">
         <v>0.71203412957918499</v>
       </c>
-      <c r="T3" s="2">
+      <c r="T3">
         <v>0.657101505866444</v>
       </c>
       <c r="U3">
@@ -39600,10 +39986,10 @@
       <c r="G6" t="s">
         <v>78</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" t="s">
         <v>79</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" t="s">
         <v>80</v>
       </c>
       <c r="J6" t="s">
@@ -39612,7 +39998,7 @@
       <c r="K6" t="s">
         <v>82</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="L6" t="s">
         <v>83</v>
       </c>
       <c r="M6" t="s">
@@ -39665,10 +40051,10 @@
       <c r="G7">
         <v>0.77813793483798299</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7">
         <v>0.83075341522976798</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7">
         <v>0.70869464818295702</v>
       </c>
       <c r="J7">
@@ -39677,7 +40063,7 @@
       <c r="K7">
         <v>0.86785674397944002</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7">
         <v>0.519005742862511</v>
       </c>
       <c r="M7">
@@ -39730,10 +40116,10 @@
       <c r="G8">
         <v>0.76519008013703005</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8">
         <v>0.81451810353786502</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8">
         <v>0.64712438732216104</v>
       </c>
       <c r="J8">
@@ -39742,7 +40128,7 @@
       <c r="K8">
         <v>0.84426950577799498</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8">
         <v>0.55553431527228103</v>
       </c>
       <c r="M8">
@@ -39794,10 +40180,10 @@
       <c r="G11" t="s">
         <v>76</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" t="s">
         <v>77</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" t="s">
         <v>78</v>
       </c>
       <c r="J11" t="s">
@@ -39806,7 +40192,7 @@
       <c r="K11" t="s">
         <v>80</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="L11" t="s">
         <v>81</v>
       </c>
       <c r="M11" t="s">
@@ -39859,10 +40245,10 @@
       <c r="G12">
         <v>0.81632449232768201</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12">
         <v>0.79085038760443604</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12">
         <v>0.77813793483798299</v>
       </c>
       <c r="J12">
@@ -39871,7 +40257,7 @@
       <c r="K12">
         <v>0.70869464818295702</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12">
         <v>0.81491130084522601</v>
       </c>
       <c r="M12">
@@ -39924,10 +40310,10 @@
       <c r="G13">
         <v>0.85654398939697196</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13">
         <v>0.82473059663983705</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13">
         <v>0.83422441088653598</v>
       </c>
       <c r="J13">
@@ -39936,7 +40322,7 @@
       <c r="K13">
         <v>0.65046311150809499</v>
       </c>
-      <c r="L13" s="2">
+      <c r="L13">
         <v>0.89051939662495705</v>
       </c>
       <c r="M13">
@@ -39974,13 +40360,13 @@
       </c>
     </row>
     <row r="17" spans="3:23" x14ac:dyDescent="0.35">
-      <c r="Q17" s="6"/>
+      <c r="Q17" s="5"/>
     </row>
     <row r="18" spans="3:23" x14ac:dyDescent="0.35">
-      <c r="Q18" s="6"/>
+      <c r="Q18" s="5"/>
     </row>
     <row r="19" spans="3:23" x14ac:dyDescent="0.35">
-      <c r="Q19" s="6"/>
+      <c r="Q19" s="5"/>
     </row>
     <row r="21" spans="3:23" x14ac:dyDescent="0.35">
       <c r="C21" t="s">
@@ -40003,25 +40389,25 @@
       <c r="G22" t="s">
         <v>76</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="H22" t="s">
         <v>77</v>
       </c>
-      <c r="I22" s="2" t="s">
+      <c r="I22" t="s">
         <v>78</v>
       </c>
-      <c r="J22" t="s">
+      <c r="J22" s="5" t="s">
         <v>79</v>
       </c>
       <c r="K22" t="s">
         <v>80</v>
       </c>
-      <c r="L22" s="2" t="s">
+      <c r="L22" t="s">
         <v>81</v>
       </c>
       <c r="M22" t="s">
         <v>82</v>
       </c>
-      <c r="N22" t="s">
+      <c r="N22" s="5" t="s">
         <v>83</v>
       </c>
       <c r="O22" t="s">
@@ -40039,7 +40425,7 @@
       <c r="S22" t="s">
         <v>88</v>
       </c>
-      <c r="T22" t="s">
+      <c r="T22" s="5" t="s">
         <v>89</v>
       </c>
       <c r="U22" t="s">
@@ -40048,7 +40434,7 @@
       <c r="V22" t="s">
         <v>91</v>
       </c>
-      <c r="W22" t="s">
+      <c r="W22" s="5" t="s">
         <v>92</v>
       </c>
     </row>
@@ -40056,64 +40442,64 @@
       <c r="C23" t="s">
         <v>93</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="9">
         <v>0.86276146222643102</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="9">
         <v>0.74074689803015803</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="9">
         <v>0.85054928065416602</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="9">
         <v>0.81632449232768201</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="9">
         <v>0.79085038760443604</v>
       </c>
-      <c r="I23" s="2">
+      <c r="I23" s="9">
         <v>0.77813793483798299</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="11">
         <v>0.83075341522976798</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="9">
         <v>0.70869464818295702</v>
       </c>
-      <c r="L23" s="2">
+      <c r="L23" s="9">
         <v>0.81491130084522601</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="9">
         <v>0.86785674397944002</v>
       </c>
-      <c r="N23">
+      <c r="N23" s="11">
         <v>0.519005742862511</v>
       </c>
-      <c r="O23">
+      <c r="O23" s="9">
         <v>0.69025879886924402</v>
       </c>
-      <c r="P23">
+      <c r="P23" s="9">
         <v>0.65165587962521498</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" s="9">
         <v>0.44824897491003401</v>
       </c>
-      <c r="R23">
+      <c r="R23" s="9">
         <v>0.81223262502022398</v>
       </c>
-      <c r="S23">
+      <c r="S23" s="9">
         <v>0.83410906420998399</v>
       </c>
-      <c r="T23">
+      <c r="T23" s="11">
         <v>0.64685998237570397</v>
       </c>
-      <c r="U23">
+      <c r="U23" s="9">
         <v>0.73227374615366603</v>
       </c>
-      <c r="V23">
+      <c r="V23" s="9">
         <v>0.699216950339417</v>
       </c>
-      <c r="W23">
+      <c r="W23" s="11">
         <v>0.86051623569899005</v>
       </c>
     </row>
@@ -40121,68 +40507,272 @@
       <c r="C24" t="s">
         <v>94</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="9">
         <v>0.87329151349427903</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="9">
         <v>0.80176934340182004</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="9">
         <v>0.83605197895137695</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="9">
         <v>0.81975662023687002</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="9">
         <v>0.86323686557894896</v>
       </c>
-      <c r="I24" s="2">
+      <c r="I24" s="9">
         <v>0.812628478806532</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="11">
         <v>0.82802463353703104</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="9">
         <v>0.70195784309208198</v>
       </c>
-      <c r="L24" s="2">
+      <c r="L24" s="9">
         <v>0.91350308651576595</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="9">
         <v>0.94134455317763999</v>
       </c>
-      <c r="N24">
+      <c r="N24" s="11">
         <v>0.52561884851548002</v>
       </c>
-      <c r="O24">
+      <c r="O24" s="9">
         <v>0.67635327187948402</v>
       </c>
-      <c r="P24">
+      <c r="P24" s="9">
         <v>0.55221033836424405</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" s="9">
         <v>0.11462415329616001</v>
       </c>
-      <c r="R24">
+      <c r="R24" s="9">
         <v>0.79259398999524699</v>
       </c>
-      <c r="S24">
+      <c r="S24" s="9">
         <v>0.85806510180867501</v>
       </c>
-      <c r="T24">
+      <c r="T24" s="11">
         <v>0.61135885828034597</v>
       </c>
-      <c r="U24">
+      <c r="U24" s="9">
         <v>0.71711677060452805</v>
       </c>
-      <c r="V24">
+      <c r="V24" s="9">
         <v>0.66093441773720096</v>
       </c>
-      <c r="W24">
+      <c r="W24" s="11">
         <v>0.81024684304642902</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.35">
+      <c r="C28" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.35">
+      <c r="D29" t="s">
+        <v>73</v>
+      </c>
+      <c r="E29" t="s">
+        <v>74</v>
+      </c>
+      <c r="F29" t="s">
+        <v>75</v>
+      </c>
+      <c r="G29" t="s">
+        <v>76</v>
+      </c>
+      <c r="H29" t="s">
+        <v>77</v>
+      </c>
+      <c r="I29" t="s">
+        <v>78</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="K29" t="s">
+        <v>80</v>
+      </c>
+      <c r="L29" t="s">
+        <v>81</v>
+      </c>
+      <c r="M29" t="s">
+        <v>82</v>
+      </c>
+      <c r="N29" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="O29" t="s">
+        <v>84</v>
+      </c>
+      <c r="P29" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>86</v>
+      </c>
+      <c r="R29" t="s">
+        <v>87</v>
+      </c>
+      <c r="S29" t="s">
+        <v>88</v>
+      </c>
+      <c r="T29" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="U29" t="s">
+        <v>90</v>
+      </c>
+      <c r="V29" t="s">
+        <v>91</v>
+      </c>
+      <c r="W29" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.35">
+      <c r="C30" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" s="9">
+        <v>0.86276146222643102</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0.74074689803015803</v>
+      </c>
+      <c r="F30" s="9">
+        <v>0.85054928065416602</v>
+      </c>
+      <c r="G30" s="9">
+        <v>0.81632449232768201</v>
+      </c>
+      <c r="H30" s="9">
+        <v>0.79085038760443604</v>
+      </c>
+      <c r="I30" s="9">
+        <v>0.77813793483798299</v>
+      </c>
+      <c r="J30" s="11">
+        <v>0.72627785476929396</v>
+      </c>
+      <c r="K30" s="9">
+        <v>0.70869464818295702</v>
+      </c>
+      <c r="L30" s="9">
+        <v>0.81491130084522601</v>
+      </c>
+      <c r="M30" s="9">
+        <v>0.86785674397944002</v>
+      </c>
+      <c r="N30" s="11">
+        <v>0.26870556935134698</v>
+      </c>
+      <c r="O30" s="9">
+        <v>0.69025879886924402</v>
+      </c>
+      <c r="P30" s="9">
+        <v>0.65165587962521498</v>
+      </c>
+      <c r="Q30" s="9">
+        <v>0.44824897491003401</v>
+      </c>
+      <c r="R30" s="9">
+        <v>0.81223262502022398</v>
+      </c>
+      <c r="S30" s="9">
+        <v>0.83410906420998399</v>
+      </c>
+      <c r="T30" s="11">
+        <v>8.6677445842567605E-2</v>
+      </c>
+      <c r="U30" s="9">
+        <v>0.73227374615366603</v>
+      </c>
+      <c r="V30" s="9">
+        <v>0.699216950339417</v>
+      </c>
+      <c r="W30" s="11">
+        <v>0.72677847634386294</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.35">
+      <c r="C31" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" s="9">
+        <v>0.85352349983328701</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0.724798315377438</v>
+      </c>
+      <c r="F31" s="9">
+        <v>0.82777645880776596</v>
+      </c>
+      <c r="G31" s="9">
+        <v>0.82784987948012601</v>
+      </c>
+      <c r="H31" s="9">
+        <v>0.79161955238377801</v>
+      </c>
+      <c r="I31" s="9">
+        <v>0.84375318356718498</v>
+      </c>
+      <c r="J31" s="11">
+        <v>0.34286085387001902</v>
+      </c>
+      <c r="K31" s="9">
+        <v>0.64715346567446697</v>
+      </c>
+      <c r="L31" s="9">
+        <v>0.86269506552383102</v>
+      </c>
+      <c r="M31" s="9">
+        <v>0.86957035714180098</v>
+      </c>
+      <c r="N31" s="11">
+        <v>0.35622951229699601</v>
+      </c>
+      <c r="O31" s="9">
+        <v>0.59977673890186201</v>
+      </c>
+      <c r="P31" s="9">
+        <v>0.45591494839174301</v>
+      </c>
+      <c r="Q31" s="9">
+        <v>0.105153463433959</v>
+      </c>
+      <c r="R31" s="9">
+        <v>0.75883908005948497</v>
+      </c>
+      <c r="S31" s="9">
+        <v>0.77796162730809604</v>
+      </c>
+      <c r="T31" s="11">
+        <v>-0.38565545638960202</v>
+      </c>
+      <c r="U31" s="9">
+        <v>0.68423457878454397</v>
+      </c>
+      <c r="V31" s="9">
+        <v>0.61375646710571996</v>
+      </c>
+      <c r="W31" s="11">
+        <v>0.59277790034791999</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/annotations/TE_discrete_percentages.xlsx
+++ b/data/annotations/TE_discrete_percentages.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dobregeo\Documents\GitHub\vilearn_ml\data\annotations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7569F5-656A-4921-AED8-62F2ED16A5B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE28567C-60ED-418F-AD89-6FFA4C831842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="666" activeTab="6" xr2:uid="{8450E3AB-A0C1-455F-AE9B-DBE7A60F6C99}"/>
   </bookViews>
@@ -20,6 +20,7 @@
     <sheet name="interraterReliability windV1" sheetId="5" r:id="rId5"/>
     <sheet name="TE_discrete_twobinsV2" sheetId="6" r:id="rId6"/>
     <sheet name="interraterReliability windV2" sheetId="4" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="141">
   <si>
     <t>task_eng</t>
   </si>
@@ -384,6 +385,84 @@
   </si>
   <si>
     <t>continous</t>
+  </si>
+  <si>
+    <t>2nd pass</t>
+  </si>
+  <si>
+    <t>recording time</t>
+  </si>
+  <si>
+    <t>dyad_02_interrater_LinsCCC</t>
+  </si>
+  <si>
+    <t>dyad_03_interrater_LinsCCC</t>
+  </si>
+  <si>
+    <t>dyad_04_interrater_LinsCCC</t>
+  </si>
+  <si>
+    <t>dyad_05_interrater_LinsCCC</t>
+  </si>
+  <si>
+    <t>dyad_06_interrater_LinsCCC</t>
+  </si>
+  <si>
+    <t>dyad_07_interrater_LinsCCC</t>
+  </si>
+  <si>
+    <t>dyad_10_interrater_LinsCCC</t>
+  </si>
+  <si>
+    <t>dyad_11_interrater_LinsCCC</t>
+  </si>
+  <si>
+    <t>triad_01_interrater_LinsCCC</t>
+  </si>
+  <si>
+    <t>triad_02_interrater_LinsCCC</t>
+  </si>
+  <si>
+    <t>triad_05_interrater_LinsCCC</t>
+  </si>
+  <si>
+    <t>triad_06_interrater_LinsCCC</t>
+  </si>
+  <si>
+    <t>triad_07_interrater_LinsCCC</t>
+  </si>
+  <si>
+    <t>triad_08_interrater_LinsCCC</t>
+  </si>
+  <si>
+    <t>triad_09_interrater_LinsCCC</t>
+  </si>
+  <si>
+    <t>triad_10_interrater_LinsCCC</t>
+  </si>
+  <si>
+    <t>triad_11_interrater_LinsCCC</t>
+  </si>
+  <si>
+    <t>triad_12_interrater_LinsCCC</t>
+  </si>
+  <si>
+    <t>triad_13_interrater_LinsCCC</t>
+  </si>
+  <si>
+    <t>triad_14_interrater_LinsCCC</t>
+  </si>
+  <si>
+    <t>interaction time</t>
+  </si>
+  <si>
+    <t>1pass</t>
+  </si>
+  <si>
+    <t>nova</t>
+  </si>
+  <si>
+    <t>max val .1, equal sizes</t>
   </si>
 </sst>
 </file>
@@ -947,7 +1026,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -967,6 +1046,8 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="8"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="6"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -39761,7 +39842,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20C27C4F-7112-48CC-8600-645EA3A54793}">
-  <dimension ref="A1:W31"/>
+  <dimension ref="A1:AB82"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -40771,8 +40852,1448 @@
         <v>0.59277790034791999</v>
       </c>
     </row>
+    <row r="41" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="D41" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="E41" t="s">
+        <v>109</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="42" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="D42" t="s">
+        <v>117</v>
+      </c>
+      <c r="E42" t="s">
+        <v>118</v>
+      </c>
+      <c r="F42" t="s">
+        <v>119</v>
+      </c>
+      <c r="G42" t="s">
+        <v>120</v>
+      </c>
+      <c r="H42" t="s">
+        <v>121</v>
+      </c>
+      <c r="I42" t="s">
+        <v>122</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="K42" t="s">
+        <v>124</v>
+      </c>
+      <c r="L42" t="s">
+        <v>125</v>
+      </c>
+      <c r="M42" t="s">
+        <v>126</v>
+      </c>
+      <c r="N42" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="O42" t="s">
+        <v>128</v>
+      </c>
+      <c r="P42" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>130</v>
+      </c>
+      <c r="R42" t="s">
+        <v>131</v>
+      </c>
+      <c r="S42" t="s">
+        <v>132</v>
+      </c>
+      <c r="T42" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="U42" t="s">
+        <v>134</v>
+      </c>
+      <c r="V42" t="s">
+        <v>135</v>
+      </c>
+      <c r="W42" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="43" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="C43" t="s">
+        <v>93</v>
+      </c>
+      <c r="D43" s="9">
+        <v>0.56695299087627804</v>
+      </c>
+      <c r="E43" s="9">
+        <v>0.29786362151490098</v>
+      </c>
+      <c r="F43" s="9">
+        <v>0.54485610409552698</v>
+      </c>
+      <c r="G43" s="9">
+        <v>0.58000858400930699</v>
+      </c>
+      <c r="H43" s="9">
+        <v>0.30292688681248198</v>
+      </c>
+      <c r="I43" s="9">
+        <v>0.42134019300679998</v>
+      </c>
+      <c r="J43" s="9">
+        <v>0.66568539532105298</v>
+      </c>
+      <c r="K43" s="9">
+        <v>0.16491538563025299</v>
+      </c>
+      <c r="L43" s="9">
+        <v>0.56408883544882205</v>
+      </c>
+      <c r="M43" s="9">
+        <v>0.48967294123562799</v>
+      </c>
+      <c r="N43" s="9">
+        <v>8.18916630910482E-2</v>
+      </c>
+      <c r="O43" s="9">
+        <v>0.183040347275708</v>
+      </c>
+      <c r="P43" s="9">
+        <v>0.28752386374973898</v>
+      </c>
+      <c r="Q43" s="9">
+        <v>0.245814331884945</v>
+      </c>
+      <c r="R43" s="9">
+        <v>0.332122520790402</v>
+      </c>
+      <c r="S43" s="9">
+        <v>0.48384258471076902</v>
+      </c>
+      <c r="T43" s="9">
+        <v>0.116744968004624</v>
+      </c>
+      <c r="U43" s="9">
+        <v>0.16268956198352</v>
+      </c>
+      <c r="V43" s="9">
+        <v>0.115483992643605</v>
+      </c>
+      <c r="W43" s="9">
+        <v>0.29621162834199899</v>
+      </c>
+    </row>
+    <row r="44" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="C44" t="s">
+        <v>94</v>
+      </c>
+      <c r="D44" s="9">
+        <v>0.77390100041473098</v>
+      </c>
+      <c r="E44" s="9">
+        <v>0.66897224519254095</v>
+      </c>
+      <c r="F44" s="9">
+        <v>0.71694249552464295</v>
+      </c>
+      <c r="G44" s="9">
+        <v>0.69287765357339803</v>
+      </c>
+      <c r="H44" s="9">
+        <v>0.75891478580969396</v>
+      </c>
+      <c r="I44" s="9">
+        <v>0.67905632713620001</v>
+      </c>
+      <c r="J44" s="9">
+        <v>0.70425628128408102</v>
+      </c>
+      <c r="K44" s="9">
+        <v>0.43613100621275802</v>
+      </c>
+      <c r="L44" s="9">
+        <v>0.83979820344496803</v>
+      </c>
+      <c r="M44" s="9">
+        <v>0.88850087146123802</v>
+      </c>
+      <c r="N44" s="9">
+        <v>0.20566570063543399</v>
+      </c>
+      <c r="O44" s="9">
+        <v>0.45592105526330101</v>
+      </c>
+      <c r="P44" s="9">
+        <v>0.306885540779189</v>
+      </c>
+      <c r="Q44" s="9">
+        <v>5.03817374526472E-2</v>
+      </c>
+      <c r="R44" s="9">
+        <v>0.65074341613959197</v>
+      </c>
+      <c r="S44" s="9">
+        <v>0.69685022599482904</v>
+      </c>
+      <c r="T44" s="9">
+        <v>0.30691285884403902</v>
+      </c>
+      <c r="U44" s="9">
+        <v>0.35494765659611599</v>
+      </c>
+      <c r="V44" s="9">
+        <v>0.28838447185198302</v>
+      </c>
+      <c r="W44" s="9">
+        <v>0.61031416354652201</v>
+      </c>
+      <c r="Z44" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB44" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="45" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="Z45" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="46" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="J46" t="s">
+        <v>93</v>
+      </c>
+      <c r="K46" s="9">
+        <f>AVERAGE(D43:K43)</f>
+        <v>0.44306864515832511</v>
+      </c>
+      <c r="V46" t="s">
+        <v>93</v>
+      </c>
+      <c r="W46" s="9">
+        <f>AVERAGE(L43:W43)</f>
+        <v>0.2799272699300675</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA46" s="9">
+        <f xml:space="preserve"> AVERAGE(K46,W46)</f>
+        <v>0.36149795754419634</v>
+      </c>
+    </row>
+    <row r="47" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="J47" t="s">
+        <v>94</v>
+      </c>
+      <c r="K47" s="9">
+        <f>AVERAGE(D44:K44)</f>
+        <v>0.67888147439350588</v>
+      </c>
+      <c r="V47" t="s">
+        <v>94</v>
+      </c>
+      <c r="W47" s="9">
+        <f>AVERAGE(L44:W44)</f>
+        <v>0.47127549183415485</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA47" s="9">
+        <f xml:space="preserve"> AVERAGE(K47,W47)</f>
+        <v>0.57507848311383036</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="D50" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="E50" t="s">
+        <v>109</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="D51" t="s">
+        <v>117</v>
+      </c>
+      <c r="E51" t="s">
+        <v>118</v>
+      </c>
+      <c r="F51" t="s">
+        <v>119</v>
+      </c>
+      <c r="G51" t="s">
+        <v>120</v>
+      </c>
+      <c r="H51" t="s">
+        <v>121</v>
+      </c>
+      <c r="I51" t="s">
+        <v>122</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="K51" t="s">
+        <v>124</v>
+      </c>
+      <c r="L51" t="s">
+        <v>125</v>
+      </c>
+      <c r="M51" t="s">
+        <v>126</v>
+      </c>
+      <c r="N51" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="O51" t="s">
+        <v>128</v>
+      </c>
+      <c r="P51" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>130</v>
+      </c>
+      <c r="R51" t="s">
+        <v>131</v>
+      </c>
+      <c r="S51" t="s">
+        <v>132</v>
+      </c>
+      <c r="T51" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="U51" t="s">
+        <v>134</v>
+      </c>
+      <c r="V51" t="s">
+        <v>135</v>
+      </c>
+      <c r="W51" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="C52" t="s">
+        <v>93</v>
+      </c>
+      <c r="D52" s="9">
+        <v>0.56695299087627804</v>
+      </c>
+      <c r="E52" s="9">
+        <v>0.29786362151490098</v>
+      </c>
+      <c r="F52" s="9">
+        <v>0.54485610409552698</v>
+      </c>
+      <c r="G52" s="9">
+        <v>0.58000858400930699</v>
+      </c>
+      <c r="H52" s="9">
+        <v>0.30292688681248198</v>
+      </c>
+      <c r="I52" s="9">
+        <v>0.42134019300679998</v>
+      </c>
+      <c r="J52" s="9">
+        <v>0.543207223798435</v>
+      </c>
+      <c r="K52" s="9">
+        <v>0.16491538563025299</v>
+      </c>
+      <c r="L52" s="9">
+        <v>0.56408883544882205</v>
+      </c>
+      <c r="M52" s="9">
+        <v>0.48967294123562799</v>
+      </c>
+      <c r="N52" s="9">
+        <v>0.109880619361216</v>
+      </c>
+      <c r="O52" s="9">
+        <v>0.183040347275708</v>
+      </c>
+      <c r="P52" s="9">
+        <v>0.28752386374973898</v>
+      </c>
+      <c r="Q52" s="9">
+        <v>0.245814331884945</v>
+      </c>
+      <c r="R52" s="9">
+        <v>0.332122520790402</v>
+      </c>
+      <c r="S52" s="9">
+        <v>0.48384258471076902</v>
+      </c>
+      <c r="T52" s="9">
+        <v>1.62192036523598E-2</v>
+      </c>
+      <c r="U52" s="9">
+        <v>0.16268956198352</v>
+      </c>
+      <c r="V52" s="9">
+        <v>0.115483992643605</v>
+      </c>
+      <c r="W52" s="9">
+        <v>0.55620123815463995</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="C53" t="s">
+        <v>94</v>
+      </c>
+      <c r="D53" s="9">
+        <v>0.77390100041473098</v>
+      </c>
+      <c r="E53" s="9">
+        <v>0.66897224519254095</v>
+      </c>
+      <c r="F53" s="9">
+        <v>0.71694249552464295</v>
+      </c>
+      <c r="G53" s="9">
+        <v>0.69287765357339803</v>
+      </c>
+      <c r="H53" s="9">
+        <v>0.75891478580969396</v>
+      </c>
+      <c r="I53" s="9">
+        <v>0.67905632713620001</v>
+      </c>
+      <c r="J53" s="9">
+        <v>0.13716333267177</v>
+      </c>
+      <c r="K53" s="9">
+        <v>0.43613100621275802</v>
+      </c>
+      <c r="L53" s="9">
+        <v>0.83979820344496803</v>
+      </c>
+      <c r="M53" s="9">
+        <v>0.88850087146123802</v>
+      </c>
+      <c r="N53" s="9">
+        <v>0.20738131494357201</v>
+      </c>
+      <c r="O53" s="9">
+        <v>0.45592105526330101</v>
+      </c>
+      <c r="P53" s="9">
+        <v>0.306885540779189</v>
+      </c>
+      <c r="Q53" s="9">
+        <v>5.03817374526472E-2</v>
+      </c>
+      <c r="R53" s="9">
+        <v>0.65074341613959197</v>
+      </c>
+      <c r="S53" s="9">
+        <v>0.69685022599482904</v>
+      </c>
+      <c r="T53" s="9">
+        <v>-2.9072222080026602E-2</v>
+      </c>
+      <c r="U53" s="9">
+        <v>0.35494765659611599</v>
+      </c>
+      <c r="V53" s="9">
+        <v>0.28838447185198302</v>
+      </c>
+      <c r="W53" s="9">
+        <v>0.303794889260384</v>
+      </c>
+      <c r="Z53" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB53" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="Z54" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="J55" t="s">
+        <v>93</v>
+      </c>
+      <c r="K55" s="9">
+        <f>AVERAGE(D52:K52)</f>
+        <v>0.42775887371799792</v>
+      </c>
+      <c r="V55" t="s">
+        <v>93</v>
+      </c>
+      <c r="W55" s="9">
+        <f>AVERAGE(L52:W52)</f>
+        <v>0.29554833674094616</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA55" s="9">
+        <f xml:space="preserve"> AVERAGE(K55,W55)</f>
+        <v>0.36165360522947204</v>
+      </c>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="J56" t="s">
+        <v>94</v>
+      </c>
+      <c r="K56" s="9">
+        <f>AVERAGE(D53:K53)</f>
+        <v>0.60799485581696699</v>
+      </c>
+      <c r="V56" t="s">
+        <v>94</v>
+      </c>
+      <c r="W56" s="9">
+        <f>AVERAGE(L53:W53)</f>
+        <v>0.41787643009231612</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA56" s="9">
+        <f xml:space="preserve"> AVERAGE(K56,W56)</f>
+        <v>0.51293564295464156</v>
+      </c>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="K57" s="9"/>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="D59" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="E59" t="s">
+        <v>109</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="D60" t="s">
+        <v>117</v>
+      </c>
+      <c r="E60" t="s">
+        <v>118</v>
+      </c>
+      <c r="F60" t="s">
+        <v>119</v>
+      </c>
+      <c r="G60" t="s">
+        <v>120</v>
+      </c>
+      <c r="H60" t="s">
+        <v>121</v>
+      </c>
+      <c r="I60" t="s">
+        <v>122</v>
+      </c>
+      <c r="J60" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="K60" t="s">
+        <v>124</v>
+      </c>
+      <c r="L60" t="s">
+        <v>125</v>
+      </c>
+      <c r="M60" t="s">
+        <v>126</v>
+      </c>
+      <c r="N60" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="O60" t="s">
+        <v>128</v>
+      </c>
+      <c r="P60" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>130</v>
+      </c>
+      <c r="R60" t="s">
+        <v>131</v>
+      </c>
+      <c r="S60" t="s">
+        <v>132</v>
+      </c>
+      <c r="T60" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="U60" t="s">
+        <v>134</v>
+      </c>
+      <c r="V60" t="s">
+        <v>135</v>
+      </c>
+      <c r="W60" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="C61" t="s">
+        <v>93</v>
+      </c>
+      <c r="D61" s="9">
+        <v>0.62900527901329695</v>
+      </c>
+      <c r="E61" s="9">
+        <v>0.30888142554504899</v>
+      </c>
+      <c r="F61" s="9">
+        <v>0.61786225082377999</v>
+      </c>
+      <c r="G61" s="9">
+        <v>0.603445672836594</v>
+      </c>
+      <c r="H61" s="9">
+        <v>0.65988685245150303</v>
+      </c>
+      <c r="I61" s="9">
+        <v>0.47780984191333398</v>
+      </c>
+      <c r="J61" s="9">
+        <v>0.73981263227810101</v>
+      </c>
+      <c r="K61" s="9">
+        <v>0.26407178197488201</v>
+      </c>
+      <c r="L61" s="9">
+        <v>0.57308153521365102</v>
+      </c>
+      <c r="M61" s="9">
+        <v>0.47805368471019999</v>
+      </c>
+      <c r="N61" s="9">
+        <v>0.16601301331808399</v>
+      </c>
+      <c r="O61" s="9">
+        <v>0.40618088037582101</v>
+      </c>
+      <c r="P61" s="9">
+        <v>0.43161067379881601</v>
+      </c>
+      <c r="Q61" s="9">
+        <v>0.257048219973393</v>
+      </c>
+      <c r="R61" s="9">
+        <v>0.62840582562066205</v>
+      </c>
+      <c r="S61" s="9">
+        <v>0.52165372621942996</v>
+      </c>
+      <c r="T61" s="9">
+        <v>9.8306605260632299E-2</v>
+      </c>
+      <c r="U61" s="9">
+        <v>0.307999405627222</v>
+      </c>
+      <c r="V61" s="9">
+        <v>0.196320632255579</v>
+      </c>
+      <c r="W61" s="9">
+        <v>0.37569047584833898</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="C62" t="s">
+        <v>94</v>
+      </c>
+      <c r="D62" s="9">
+        <v>0.80711792988199504</v>
+      </c>
+      <c r="E62" s="9">
+        <v>0.67626239322022197</v>
+      </c>
+      <c r="F62" s="9">
+        <v>0.77190861421301404</v>
+      </c>
+      <c r="G62" s="9">
+        <v>0.71265252093283604</v>
+      </c>
+      <c r="H62" s="9">
+        <v>0.91844360595528796</v>
+      </c>
+      <c r="I62" s="9">
+        <v>0.73184432264408505</v>
+      </c>
+      <c r="J62" s="9">
+        <v>0.77177908934774397</v>
+      </c>
+      <c r="K62" s="9">
+        <v>0.56824165287888795</v>
+      </c>
+      <c r="L62" s="9">
+        <v>0.84426599053088502</v>
+      </c>
+      <c r="M62" s="9">
+        <v>0.85954124433123602</v>
+      </c>
+      <c r="N62" s="9">
+        <v>0.26980283483985001</v>
+      </c>
+      <c r="O62" s="9">
+        <v>0.69509225118126505</v>
+      </c>
+      <c r="P62" s="9">
+        <v>0.44406689682755401</v>
+      </c>
+      <c r="Q62" s="9">
+        <v>5.5447925938649001E-2</v>
+      </c>
+      <c r="R62" s="9">
+        <v>0.85662946315966304</v>
+      </c>
+      <c r="S62" s="9">
+        <v>0.71999295837365196</v>
+      </c>
+      <c r="T62" s="9">
+        <v>0.19595881912879501</v>
+      </c>
+      <c r="U62" s="9">
+        <v>0.51041432723851399</v>
+      </c>
+      <c r="V62" s="9">
+        <v>0.40525177290240399</v>
+      </c>
+      <c r="W62" s="9">
+        <v>0.64920786975383205</v>
+      </c>
+      <c r="Z62" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA62" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB62" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="Z63" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="Z64" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA64" s="9">
+        <f xml:space="preserve"> AVERAGE(D61:W61)</f>
+        <v>0.43705702075291847</v>
+      </c>
+    </row>
+    <row r="65" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="Z65" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA65" s="9">
+        <f xml:space="preserve"> AVERAGE(D62:W62)</f>
+        <v>0.62319612416401848</v>
+      </c>
+    </row>
+    <row r="67" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="D67" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="E67" t="s">
+        <v>109</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="68" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="D68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F68" t="s">
+        <v>119</v>
+      </c>
+      <c r="G68" t="s">
+        <v>120</v>
+      </c>
+      <c r="H68" t="s">
+        <v>121</v>
+      </c>
+      <c r="I68" t="s">
+        <v>122</v>
+      </c>
+      <c r="J68" t="s">
+        <v>123</v>
+      </c>
+      <c r="K68" t="s">
+        <v>124</v>
+      </c>
+      <c r="L68" t="s">
+        <v>125</v>
+      </c>
+      <c r="M68" t="s">
+        <v>126</v>
+      </c>
+      <c r="N68" t="s">
+        <v>127</v>
+      </c>
+      <c r="O68" t="s">
+        <v>128</v>
+      </c>
+      <c r="P68" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>130</v>
+      </c>
+      <c r="R68" t="s">
+        <v>131</v>
+      </c>
+      <c r="S68" t="s">
+        <v>132</v>
+      </c>
+      <c r="T68" t="s">
+        <v>133</v>
+      </c>
+      <c r="U68" t="s">
+        <v>134</v>
+      </c>
+      <c r="V68" t="s">
+        <v>135</v>
+      </c>
+      <c r="W68" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="69" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="C69" t="s">
+        <v>93</v>
+      </c>
+      <c r="D69" s="9">
+        <v>0.62900527901329695</v>
+      </c>
+      <c r="E69" s="9">
+        <v>0.30888142554504899</v>
+      </c>
+      <c r="F69" s="9">
+        <v>0.61786225082377999</v>
+      </c>
+      <c r="G69" s="9">
+        <v>0.603445672836594</v>
+      </c>
+      <c r="H69" s="9">
+        <v>0.65988685245150303</v>
+      </c>
+      <c r="I69" s="9">
+        <v>0.47780984191333398</v>
+      </c>
+      <c r="J69" s="9">
+        <v>0.60107527981205999</v>
+      </c>
+      <c r="K69" s="9">
+        <v>0.26407178197488201</v>
+      </c>
+      <c r="L69" s="9">
+        <v>0.57308153521365102</v>
+      </c>
+      <c r="M69" s="9">
+        <v>0.47805368471019999</v>
+      </c>
+      <c r="N69" s="9">
+        <v>0.25393365984337501</v>
+      </c>
+      <c r="O69" s="9">
+        <v>0.40618088037582101</v>
+      </c>
+      <c r="P69" s="9">
+        <v>0.43161067379881601</v>
+      </c>
+      <c r="Q69" s="9">
+        <v>0.257048219973393</v>
+      </c>
+      <c r="R69" s="9">
+        <v>0.62840582562066205</v>
+      </c>
+      <c r="S69" s="9">
+        <v>0.52165372621942996</v>
+      </c>
+      <c r="T69" s="9">
+        <v>2.6280436585339399E-2</v>
+      </c>
+      <c r="U69" s="9">
+        <v>0.307999405627222</v>
+      </c>
+      <c r="V69" s="9">
+        <v>0.196320632255579</v>
+      </c>
+      <c r="W69" s="9">
+        <v>0.68482443749672695</v>
+      </c>
+    </row>
+    <row r="70" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="C70" t="s">
+        <v>94</v>
+      </c>
+      <c r="D70" s="9">
+        <v>0.80711792988199504</v>
+      </c>
+      <c r="E70" s="9">
+        <v>0.67626239322022197</v>
+      </c>
+      <c r="F70" s="9">
+        <v>0.77190861421301404</v>
+      </c>
+      <c r="G70" s="9">
+        <v>0.71265252093283604</v>
+      </c>
+      <c r="H70" s="9">
+        <v>0.91844360595528796</v>
+      </c>
+      <c r="I70" s="9">
+        <v>0.73184432264408505</v>
+      </c>
+      <c r="J70" s="9">
+        <v>0.18963729390917899</v>
+      </c>
+      <c r="K70" s="9">
+        <v>0.56824165287888795</v>
+      </c>
+      <c r="L70" s="9">
+        <v>0.84426599053088502</v>
+      </c>
+      <c r="M70" s="9">
+        <v>0.85954124433123602</v>
+      </c>
+      <c r="N70" s="9">
+        <v>0.23289743517784001</v>
+      </c>
+      <c r="O70" s="9">
+        <v>0.69509225118126505</v>
+      </c>
+      <c r="P70" s="9">
+        <v>0.44406689682755401</v>
+      </c>
+      <c r="Q70" s="9">
+        <v>5.5447925938649001E-2</v>
+      </c>
+      <c r="R70" s="9">
+        <v>0.85662946315966304</v>
+      </c>
+      <c r="S70" s="9">
+        <v>0.71999295837365196</v>
+      </c>
+      <c r="T70" s="9">
+        <v>3.7900727635926799E-2</v>
+      </c>
+      <c r="U70" s="9">
+        <v>0.51041432723851399</v>
+      </c>
+      <c r="V70" s="9">
+        <v>0.40525177290240399</v>
+      </c>
+      <c r="W70" s="9">
+        <v>0.38652694199728299</v>
+      </c>
+    </row>
+    <row r="71" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="C71" t="s">
+        <v>139</v>
+      </c>
+      <c r="J71">
+        <v>0.76</v>
+      </c>
+      <c r="L71">
+        <v>0.64</v>
+      </c>
+      <c r="N71">
+        <v>0.11</v>
+      </c>
+      <c r="O71">
+        <v>0.5</v>
+      </c>
+      <c r="T71">
+        <v>0.48</v>
+      </c>
+      <c r="W71">
+        <v>0.23</v>
+      </c>
+      <c r="Z71" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA71" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB71" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="72" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="Z72" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="73" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="Z73" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA73" s="9">
+        <f xml:space="preserve"> AVERAGE(D70:W70)</f>
+        <v>0.57120681344651902</v>
+      </c>
+    </row>
+    <row r="74" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="Z74" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA74" s="9">
+        <f xml:space="preserve"> AVERAGE(D71:W71)</f>
+        <v>0.45333333333333331</v>
+      </c>
+    </row>
+    <row r="79" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="D79" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="E79" t="s">
+        <v>140</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="80" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="D80" t="s">
+        <v>117</v>
+      </c>
+      <c r="E80" t="s">
+        <v>118</v>
+      </c>
+      <c r="F80" t="s">
+        <v>119</v>
+      </c>
+      <c r="G80" t="s">
+        <v>120</v>
+      </c>
+      <c r="H80" t="s">
+        <v>121</v>
+      </c>
+      <c r="I80" t="s">
+        <v>122</v>
+      </c>
+      <c r="J80" t="s">
+        <v>123</v>
+      </c>
+      <c r="K80" t="s">
+        <v>124</v>
+      </c>
+      <c r="L80" t="s">
+        <v>125</v>
+      </c>
+      <c r="M80" t="s">
+        <v>126</v>
+      </c>
+      <c r="N80" t="s">
+        <v>127</v>
+      </c>
+      <c r="O80" t="s">
+        <v>128</v>
+      </c>
+      <c r="P80" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>130</v>
+      </c>
+      <c r="R80" t="s">
+        <v>131</v>
+      </c>
+      <c r="S80" t="s">
+        <v>132</v>
+      </c>
+      <c r="T80" t="s">
+        <v>133</v>
+      </c>
+      <c r="U80" t="s">
+        <v>134</v>
+      </c>
+      <c r="V80" t="s">
+        <v>135</v>
+      </c>
+      <c r="W80" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.35">
+      <c r="C81" t="s">
+        <v>93</v>
+      </c>
+      <c r="D81">
+        <v>0.56695299087627804</v>
+      </c>
+      <c r="E81">
+        <v>0.29786362151490098</v>
+      </c>
+      <c r="F81">
+        <v>0.54485610409552698</v>
+      </c>
+      <c r="G81">
+        <v>0.58000858400930699</v>
+      </c>
+      <c r="H81">
+        <v>0.30292688681248198</v>
+      </c>
+      <c r="I81">
+        <v>0.42134019300679998</v>
+      </c>
+      <c r="J81">
+        <v>0.66568539532105298</v>
+      </c>
+      <c r="K81">
+        <v>0.16491538563025299</v>
+      </c>
+      <c r="L81">
+        <v>0.56408883544882205</v>
+      </c>
+      <c r="M81">
+        <v>0.48967294123562799</v>
+      </c>
+      <c r="N81">
+        <v>8.18916630910482E-2</v>
+      </c>
+      <c r="O81">
+        <v>0.183040347275708</v>
+      </c>
+      <c r="P81">
+        <v>0.28752386374973898</v>
+      </c>
+      <c r="Q81">
+        <v>0.245814331884945</v>
+      </c>
+      <c r="R81">
+        <v>0.332122520790402</v>
+      </c>
+      <c r="S81">
+        <v>0.48384258471076902</v>
+      </c>
+      <c r="T81">
+        <v>0.116744968004624</v>
+      </c>
+      <c r="U81">
+        <v>0.16268956198352</v>
+      </c>
+      <c r="V81">
+        <v>0.115483992643605</v>
+      </c>
+      <c r="W81">
+        <v>0.29621162834199899</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.35">
+      <c r="C82" t="s">
+        <v>94</v>
+      </c>
+      <c r="D82">
+        <v>0.50202106496160004</v>
+      </c>
+      <c r="E82">
+        <v>0.25103485476759901</v>
+      </c>
+      <c r="F82">
+        <v>0.44678811890460801</v>
+      </c>
+      <c r="G82">
+        <v>0.58543792387631799</v>
+      </c>
+      <c r="H82">
+        <v>0.31813326284791799</v>
+      </c>
+      <c r="I82">
+        <v>0.37669637533626998</v>
+      </c>
+      <c r="J82">
+        <v>0.32499434272904998</v>
+      </c>
+      <c r="K82">
+        <v>0.114558396241001</v>
+      </c>
+      <c r="L82">
+        <v>0.50595291038024504</v>
+      </c>
+      <c r="M82">
+        <v>0.35430067451708502</v>
+      </c>
+      <c r="N82">
+        <v>5.9979607854705297E-2</v>
+      </c>
+      <c r="O82">
+        <v>0.183870046843114</v>
+      </c>
+      <c r="P82">
+        <v>8.9975552164238595E-2</v>
+      </c>
+      <c r="Q82">
+        <v>3.1198372952606999E-2</v>
+      </c>
+      <c r="R82">
+        <v>0.25736771559273403</v>
+      </c>
+      <c r="S82">
+        <v>0.275305969572469</v>
+      </c>
+      <c r="T82">
+        <v>-1.9828883537705799E-2</v>
+      </c>
+      <c r="U82">
+        <v>9.1069604534750104E-2</v>
+      </c>
+      <c r="V82">
+        <v>6.3801412827765205E-2</v>
+      </c>
+      <c r="W82">
+        <v>0.22815204344407</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF647019-D9D4-4DFE-844F-0A523C731963}">
+  <dimension ref="A1:U11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="10" max="10" width="12.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" t="s">
+        <v>76</v>
+      </c>
+      <c r="F9" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" t="s">
+        <v>79</v>
+      </c>
+      <c r="I9" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K9" t="s">
+        <v>82</v>
+      </c>
+      <c r="L9" t="s">
+        <v>83</v>
+      </c>
+      <c r="M9" t="s">
+        <v>84</v>
+      </c>
+      <c r="N9" t="s">
+        <v>85</v>
+      </c>
+      <c r="O9" t="s">
+        <v>86</v>
+      </c>
+      <c r="P9" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>88</v>
+      </c>
+      <c r="R9" t="s">
+        <v>89</v>
+      </c>
+      <c r="S9" t="s">
+        <v>90</v>
+      </c>
+      <c r="T9" t="s">
+        <v>91</v>
+      </c>
+      <c r="U9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10">
+        <v>0.87679832543452596</v>
+      </c>
+      <c r="C10">
+        <v>0.74424022775423404</v>
+      </c>
+      <c r="D10">
+        <v>0.87597463417352595</v>
+      </c>
+      <c r="E10">
+        <v>0.82833629475958603</v>
+      </c>
+      <c r="F10">
+        <v>0.91720469407852401</v>
+      </c>
+      <c r="G10">
+        <v>0.80825763238031001</v>
+      </c>
+      <c r="H10">
+        <v>0.75158993302107602</v>
+      </c>
+      <c r="I10">
+        <v>0.77266859787776099</v>
+      </c>
+      <c r="J10">
+        <v>0.81717182427240698</v>
+      </c>
+      <c r="K10">
+        <v>0.85712755435300403</v>
+      </c>
+      <c r="L10">
+        <v>0.43852932031233299</v>
+      </c>
+      <c r="M10">
+        <v>0.80920216285187097</v>
+      </c>
+      <c r="N10">
+        <v>0.70766956904197398</v>
+      </c>
+      <c r="O10">
+        <v>0.454974577076318</v>
+      </c>
+      <c r="P10">
+        <v>0.89698964088228295</v>
+      </c>
+      <c r="Q10">
+        <v>0.825538361689096</v>
+      </c>
+      <c r="R10">
+        <v>0.14670277351968999</v>
+      </c>
+      <c r="S10">
+        <v>0.783034824591754</v>
+      </c>
+      <c r="T10">
+        <v>0.74171046174998201</v>
+      </c>
+      <c r="U10">
+        <v>0.82417078891634499</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11">
+        <v>0.89447358124555898</v>
+      </c>
+      <c r="C11">
+        <v>0.80703612246095102</v>
+      </c>
+      <c r="D11">
+        <v>0.87195882220170196</v>
+      </c>
+      <c r="E11">
+        <v>0.83329169112988399</v>
+      </c>
+      <c r="F11">
+        <v>0.95806365625644296</v>
+      </c>
+      <c r="G11">
+        <v>0.84820340055889698</v>
+      </c>
+      <c r="H11">
+        <v>0.37780916779162199</v>
+      </c>
+      <c r="I11">
+        <v>0.79345113851506199</v>
+      </c>
+      <c r="J11">
+        <v>0.91610643778803502</v>
+      </c>
+      <c r="K11">
+        <v>0.92487997403585998</v>
+      </c>
+      <c r="L11">
+        <v>0.396526477869034</v>
+      </c>
+      <c r="M11">
+        <v>0.84578998283020901</v>
+      </c>
+      <c r="N11">
+        <v>0.66243418353207095</v>
+      </c>
+      <c r="O11">
+        <v>0.117994272287108</v>
+      </c>
+      <c r="P11">
+        <v>0.92411657208375597</v>
+      </c>
+      <c r="Q11">
+        <v>0.86336986893276402</v>
+      </c>
+      <c r="R11">
+        <v>8.7706314257473605E-2</v>
+      </c>
+      <c r="S11">
+        <v>0.80336372219964802</v>
+      </c>
+      <c r="T11">
+        <v>0.74757396492422601</v>
+      </c>
+      <c r="U11">
+        <v>0.65924843795771004</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>